--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="Reference" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="multiple_screens" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="home" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="networth" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="performance" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="plan" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="cashflow" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="menu" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="inputs" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Specification" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="multiple_screens" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="home" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="networth" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="performance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="plan" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="cashflow" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="menu" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="inputs" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +37,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
     </font>
     <font>
       <b val="1"/>
@@ -66,15 +71,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -502,364 +508,442 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TAB — Reference</t>
+          <t>TAB — Specification</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>This tab. What the file is, what each tab holds, what each column means, and what it must comply with.</t>
+          <t>Everything a row must carry before its calculation can be written in code. The index tabs say what exists and where it is shown; this tab says what is still needed to say what each number IS.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TAB — multiple_screens</t>
+          <t>TAB — Reference</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Figures shown on more than one parent screen. A figure lives here ONCE, with every screen and every label it wears listed, so the same figure can never have two definitions.</t>
+          <t>This tab. What the file is, what each tab holds, what each column means, and what it must comply with.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TAB — home</t>
+          <t>TAB — multiple_screens</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Figures shown only on Home and the screens reached from it.</t>
+          <t>Figures shown on more than one parent screen. A figure lives here ONCE, with every screen and every label it wears listed, so the same figure can never have two definitions.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TAB — networth</t>
+          <t>TAB — home</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Figures shown only on Net worth and the screens reached from it.</t>
+          <t>Figures shown only on Home and the screens reached from it.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TAB — performance</t>
+          <t>TAB — networth</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Figures shown only on Performance and the screens reached from it.</t>
+          <t>Figures shown only on Net worth and the screens reached from it.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TAB — plan</t>
+          <t>TAB — performance</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Figures shown only on Plan and the screens reached from it.</t>
+          <t>Figures shown only on Performance and the screens reached from it.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TAB — cashflow</t>
+          <t>TAB — plan</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Figures shown only on Cash flow and the screens reached from it.</t>
+          <t>Figures shown only on Plan and the screens reached from it.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TAB — menu</t>
+          <t>TAB — cashflow</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Screens reachable only from the menu, and the figures on them.</t>
+          <t>Figures shown only on Cash flow and the screens reached from it.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>TAB — menu</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Screens reachable only from the menu, and the figures on them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>TAB — inputs</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>The raw values the engines need before any calculation happens.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="3" t="inlineStr"/>
-    </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN — Metric ID</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>The identifier of the figure, per moneykeel_naming_spec_unique-identifier_v01.md. Given once, never changed, never reused.</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Parent Screen Name</t>
+          <t>COLUMN — Metric ID</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>One of: Home, Networth, Performance, Cashflow, Plan, Menu. Menu means reachable only from the menu.</t>
+          <t>The identifier of the figure, per moneykeel_naming_spec_unique-identifier_v01.md. Given once, never changed, never reused.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Secondary Screen Name</t>
+          <t>COLUMN — Parent Screen Name</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>The screen reached from the parent, or NA when the figure is on the parent screen itself.</t>
+          <t>One of: Home, Networth, Performance, Cashflow, Plan, Menu. Menu means reachable only from the menu.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name on Screen</t>
+          <t>COLUMN — Secondary Screen Name</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>The label copied exactly as it is worded on screen, including capitals. Where a figure wears different labels on different screens, all are listed.</t>
+          <t>The screen reached from the parent, or NA when the figure is on the parent screen itself.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name of Underlying Metric</t>
+          <t>COLUMN — Name on Screen</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>The metric's name in the code.</t>
+          <t>The label copied exactly as it is worded on screen, including capitals. Where a figure wears different labels on different screens, all are listed.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name of Underlying Engine</t>
+          <t>COLUMN — Name of Underlying Metric</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>The engine that produces the figure. NOT IN OLD MASTER means the engine exists in the code but has no row in the old master file.</t>
+          <t>The metric's name in the code.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Engine ID</t>
+          <t>COLUMN — Name of Underlying Engine</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
+          <t>The engine that produces the figure. NOT IN OLD MASTER means the engine exists in the code but has no row in the old master file.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Your name for it (72-metric file)</t>
+          <t>COLUMN — Engine ID</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
+          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Core screen?</t>
+          <t>COLUMN — Your name for it (72-metric file)</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Whether the screen is part of the 55-70 core, the agreed first scope.</t>
+          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>COLUMN — Core screen?</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Whether the screen is part of the 55-70 core, the agreed first scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>COLUMN — Row status</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>VERIFIED with its date means a person read the screen and confirmed the chain. NOT STARTED means the screen has not been read yet. Nothing in between is claimed.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr"/>
-    </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN — Input ID</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>The identifier of a raw input, per the same standard.</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Variable name</t>
+          <t>COLUMN — Input ID</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>What the raw value is called.</t>
+          <t>The identifier of a raw input, per the same standard.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Source</t>
+          <t>COLUMN — Variable name</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
+          <t>What the raw value is called.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Which metric uses it</t>
+          <t>COLUMN — Source</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Every metric identifier that depends on this input.</t>
+          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>COLUMN — Which metric uses it</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Every metric identifier that depends on this input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>COLUMN — Which engine uses it</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Every engine identifier that reads this input.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="3" t="inlineStr"/>
-    </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Complies with — naming</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Complies with — identifiers</t>
+          <t>Complies with — naming</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>Complies with — identifiers</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
           <t>Complies with — objectives</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>MoneyKeel/documents/standards/moneykeel_calc_spec_objectives-and-verification_v01.md</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
-      <c r="B36" s="3" t="inlineStr"/>
-    </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>COVERAGE — screens read so far</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>1 of 49 (Home)</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>COVERAGE — screens read so far</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>1 of 49 (Home)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>COVERAGE — what that means</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Every screen in the app is listed on its tab. Only Home carries figures so far; the rest are marked NOT STARTED. A rising count is not completeness while screens remain unread.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Input ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Variable name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Which metric uses it</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Which engine uses it</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Row status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NOT STARTED — filled as each screen is read</t>
         </is>
       </c>
     </row>
@@ -869,6 +953,244 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>What is needed</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Why it is needed, and whether the file carries it today</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SECTION — WHAT THE NUMBER IS</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>The formula</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>The actual rules in plain English, followable by hand. Nothing in the index tabs carries it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>The inputs, one by one</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Every input named separately, with its unit, and where it comes from: the person typed it, an institution download, a connected provider, or another engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>The decisions and assumptions applied</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Rounding, timing conventions, inflation, which balance is used, which date wins. Each labelled with whose decision it was — the founder's, the person's, or built in. This is the fourth link of objective 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>What comes out</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Dollars, a percentage, a date, a count or a range; its unit and its rounding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>What it says when it cannot be computed</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>The exact refusal. This is where wrong numbers get invented, so the refusal is part of the specification, not an afterthought.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>The grain</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Whether the figure is per holding, per account, per person or per household. Without it a total and a single line look identical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>The period</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>As of when, and over what window — this month, twelve months, since the person owned it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SECTION — WHAT PROVES IT</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Worked examples</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>These inputs give this answer. Rung 2 re-runs them through the real engine on every build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>An example for every case</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>One per case the grid names: input missing, input degraded, a different shape per institution, time-bounded, related events, account type. This is rung 3, the floor for every calculation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Verification level</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Whether this engine is marked for rung 4 (the written formula made executable and checked against the code on generated inputs) and rung 5 (laws that must hold for every input). Marked by the founder, recommended by me.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SECTION — WHAT CONNECTS IT</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Which engines feed this engine</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>The engines it depends on. Without this, build order and the one-door design cannot be worked out — a metric points at an engine today, but engines do not point at each other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Where it is implemented</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>The file and function that carry it, so file and code can be checked against each other on every build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SECTION — GOVERNANCE</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>The founder's verdict</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>His approval of the row. A row counts as documented only when he has approved it, so without this column the coverage count is meaningless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Lifecycle</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Live, cut, or superseded by another identifier. Identifiers are never reused, so a retired one must say what replaced it.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1032,508 +1354,6 @@
         </is>
       </c>
       <c r="J3" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="33" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Metric ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Parent Screen Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Secondary Screen Name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Name on Screen</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Name of Underlying Metric</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Name of Underlying Engine</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Engine ID</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Your name for it (72-metric file)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Core screen?</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Row status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MK-HM-M-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>YOUR INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>investTotal</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TOTAL_INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MK-XS-E-003</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MK-HM-M-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>▲ up / ▼ down $X (Y%) this month</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>youReturn</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VALUE_WEIGHTED_RETURN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MK-XS-E-004</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MK-HM-M-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>prices updated &lt;when&gt;</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>freshness</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PRICE_FRESHNESS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MK-XS-E-005</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MK-HM-M-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Your net worth just crossed X</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>NOT IN OLD MASTER — milestoneCrossed, src/domain/milestones.ts</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MK-HM-E-001</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MK-HM-M-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Needs your attention (1,2,3)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>topInsights</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>NOT IN OLD MASTER — useInsights, src/domain/insights</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MK-HM-E-002</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>MK-HM-M-006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Income</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>thisMonthNet</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>NOT IN OLD MASTER — incomeMonthlyGrid, src/domain/income</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MK-CF-E-001</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>MK-HM-M-007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Spent so far</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>bva.spent_total</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>NOT IN OLD MASTER — budgetVsActual, src/domain/budget</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MK-CF-E-002</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MK-HM-M-008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Left / Over</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>derived on screen: Income − Spent so far</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MK-HM-M-009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>&lt;n&gt;% spent · day n of m</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>pctSpent</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>derived on screen: Spent so far ÷ Income</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -1618,10 +1438,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MK-HM-M-001</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Networth</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1629,207 +1453,411 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>YOUR INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>investTotal</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TOTAL_INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MK-XS-E-003</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MK-HM-M-002</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Networth</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>/account-detail</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>▲ up / ▼ down $X (Y%) this month</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>youReturn</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VALUE_WEIGHTED_RETURN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-004</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MK-HM-M-003</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Networth</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>/add-account</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>prices updated &lt;when&gt;</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>freshness</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PRICE_FRESHNESS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MK-XS-E-005</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MK-HM-M-004</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Networth</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/bonds</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Your net worth just crossed X</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — milestoneCrossed, src/domain/milestones.ts</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MK-HM-E-001</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MK-HM-M-005</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Networth</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/connect</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Needs your attention (1,2,3)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>topInsights</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — useInsights, src/domain/insights</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MK-HM-E-002</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MK-HM-M-006</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Networth</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/holding-detail</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>thisMonthNet</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — incomeMonthlyGrid, src/domain/income</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MK-CF-E-001</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MK-HM-M-007</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Networth</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/import-holdings</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Spent so far</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>bva.spent_total</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — budgetVsActual, src/domain/budget</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MK-CF-E-002</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MK-HM-M-008</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Networth</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/itemize</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Left / Over</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>derived on screen: Income − Spent so far</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MK-HM-M-009</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Networth</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/look-back</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>&lt;n&gt;% spent · day n of m</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>pctSpent</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>derived on screen: Spent so far ÷ Income</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1943,7 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Networth</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1939,7 +1967,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Networth</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1963,7 +1991,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Networth</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1987,7 +2015,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Networth</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2011,7 +2039,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Networth</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2035,7 +2063,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Networth</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2059,7 +2087,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Networth</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2083,12 +2111,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Networth</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/look-back</t>
+          <t>/itemize</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -2107,12 +2135,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Networth</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/what-if</t>
+          <t>/look-back</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -2133,6 +2161,300 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Parent Screen Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary Screen Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Name on Screen</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Name of Underlying Metric</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Name of Underlying Engine</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Engine ID</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Your name for it (72-metric file)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Core screen?</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Row status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>/account-detail</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>/add-account</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>/bonds</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>/connect</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>/holding-detail</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>/import-holdings</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>/look-back</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>/what-if</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2690,7 +3012,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3176,7 +3498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3732,70 +4054,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Input ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Variable name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Which metric uses it</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Which engine uses it</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Row status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>NOT STARTED — filled as each screen is read</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -865,7 +865,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>1 of 49 (Home)</t>
+          <t>5 of 49 — Home, Net worth, Performance, Cash flow, Plan (the five parent screens). The 44 secondary and menu screens are listed and marked NOT STARTED.</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Net worth</t>
+          <t>Net worth · YOUR NET WORTH</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>netWorth</t>
+          <t>nw.net_worth</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Home · Plan</t>
+          <t>Home · Plan · Cashflow</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Will your money last (odds)</t>
+          <t>Will my money last / Is my money lasting (odds)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1354,6 +1354,242 @@
         </is>
       </c>
       <c r="J3" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MK-XS-M-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Home · Performance · Networth</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>YOUR INVESTMENTS · 📈 INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>investTotal</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TOTAL_INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MK-XS-E-003</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MK-XS-M-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Home · Performance</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>▲ up/▼ down $X (Y%) this month · Return · YOUR RETURN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>youReturn / shownReturn</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VALUE_WEIGHTED_RETURN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MK-XS-E-004</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MK-XS-M-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Home · Cashflow</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Spent so far · Spent $X of $Y left to spend this month</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>bva.spent_total</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — budgetVsActual, src/domain/budget</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MK-XS-E-005</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MK-XS-M-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Home · Cashflow</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Income · In (received) · In (take-home)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>thisMonthNet</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — incomeMonthlyGrid, src/domain/income</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MK-XS-E-006</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MK-XS-M-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Home · Cashflow</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Left / Over · left to spend this month</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>worked out on the screen: money in − spent so far</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -1365,1096 +1601,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="33" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Metric ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Parent Screen Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Secondary Screen Name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Name on Screen</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Name of Underlying Metric</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Name of Underlying Engine</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Engine ID</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Your name for it (72-metric file)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Core screen?</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Row status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MK-HM-M-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>YOUR INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>investTotal</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TOTAL_INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MK-XS-E-003</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MK-HM-M-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>▲ up / ▼ down $X (Y%) this month</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>youReturn</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>VALUE_WEIGHTED_RETURN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MK-XS-E-004</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MK-HM-M-003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>prices updated &lt;when&gt;</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>freshness</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PRICE_FRESHNESS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MK-XS-E-005</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MK-HM-M-004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Your net worth just crossed X</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>milestone</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>NOT IN OLD MASTER — milestoneCrossed, src/domain/milestones.ts</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MK-HM-E-001</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MK-HM-M-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Needs your attention (1,2,3)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>topInsights</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>NOT IN OLD MASTER — useInsights, src/domain/insights</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MK-HM-E-002</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>MK-HM-M-006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Income</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>thisMonthNet</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>NOT IN OLD MASTER — incomeMonthlyGrid, src/domain/income</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MK-CF-E-001</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>MK-HM-M-007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Spent so far</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>bva.spent_total</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>NOT IN OLD MASTER — budgetVsActual, src/domain/budget</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MK-CF-E-002</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MK-HM-M-008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Left / Over</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>derived on screen: Income − Spent so far</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MK-HM-M-009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>&lt;n&gt;% spent · day n of m</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>pctSpent</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>derived on screen: Spent so far ÷ Income</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-08-22</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="33" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Metric ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Parent Screen Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Secondary Screen Name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Name on Screen</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Name of Underlying Metric</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Name of Underlying Engine</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Engine ID</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Your name for it (72-metric file)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Core screen?</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Row status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Networth</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Networth</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>/account-detail</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Networth</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>/add-account</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Networth</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>/bonds</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Networth</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>/connect</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Networth</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>/holding-detail</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Networth</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>/import-holdings</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Networth</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>/itemize</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Networth</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>/look-back</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="33" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Metric ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Parent Screen Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Secondary Screen Name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Name on Screen</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Name of Underlying Metric</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Name of Underlying Engine</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Engine ID</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Your name for it (72-metric file)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Core screen?</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Row status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>/account-detail</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>/add-account</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>/bonds</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>/connect</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>/holding-detail</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>/import-holdings</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>/look-back</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>/what-if</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2528,10 +1674,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MK-HM-M-001</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2539,87 +1689,175 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>prices updated &lt;when&gt;</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>freshness</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PRICE_FRESHNESS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MK-HM-E-001</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MK-HM-M-002</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>/account-detail</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Your net worth just crossed X</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>milestone</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — milestoneCrossed, src/domain/milestones.ts</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MK-HM-E-002</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MK-HM-M-003</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>/add-account</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Needs your attention (1, 2, 3)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>topInsights</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — useInsights, src/domain/insights</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MK-HM-E-003</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MK-HM-M-004</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/bonds</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>&lt;n&gt;% spent · day n of m</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>pctSpent</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>worked out on the screen: spent so far ÷ money in</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -2627,12 +1865,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/connect</t>
+          <t>/account-detail</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -2651,12 +1889,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/education</t>
+          <t>/add-account</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -2675,12 +1913,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/holding-detail</t>
+          <t>/bill-calendar</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -2699,12 +1937,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/import-holdings</t>
+          <t>/bonds</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -2723,12 +1961,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/look-back</t>
+          <t>/connect</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -2747,12 +1985,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/monthly-income</t>
+          <t>/holding-detail</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -2771,12 +2009,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/multi-goal</t>
+          <t>/import-holdings</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -2795,12 +2033,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/paycheck-months</t>
+          <t>/income-manager</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -2819,12 +2057,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/performance</t>
+          <t>/look-back</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -2843,12 +2081,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/required-withdrawals</t>
+          <t>/month-detail</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2867,12 +2105,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/retirement</t>
+          <t>/monthly-income</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2891,12 +2129,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/roth</t>
+          <t>/onboarding</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2915,12 +2153,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/sharpen</t>
+          <t>/paycheck-months</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2939,12 +2177,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>/ss-timing</t>
+          <t>/performance</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2963,12 +2201,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>/what-if</t>
+          <t>/retirement</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -2987,12 +2225,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Plan</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>/will-it-last</t>
+          <t>/what-if</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -3012,7 +2250,1089 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Parent Screen Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary Screen Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Name on Screen</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Name of Underlying Metric</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Name of Underlying Engine</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Engine ID</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Your name for it (72-metric file)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Core screen?</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Row status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MK-NW-M-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Change in net worth +$X</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>changeThisYear</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TREND_SERIES</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MK-NW-E-001</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Return on cash + investments ±X%</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>invPct</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_PCT</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-002</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MK-NW-M-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>the trend line</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TREND_SERIES</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MK-NW-E-001</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MK-NW-M-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>WHAT YOU OWN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>totalAssets</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ACCOUNT_SHARE_OF_TOTAL</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MK-NW-E-003</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MK-NW-M-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>💵 CASH</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>cashOnHand</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TOTAL_CASH</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MK-NW-E-004</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MK-NW-M-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>🏠 PERSONAL PROPERTY</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sectionTotals</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ACCOUNT_SHARE_OF_TOTAL</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MK-NW-E-003</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MK-NW-M-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>class rows — by class, institution or type</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>classRows</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ALLOCATION_BY_CLASS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MK-NW-E-005</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MK-NW-M-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>each account and its balance</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>a.balance</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ACCOUNT_SPLIT</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MK-NW-E-006</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MK-NW-M-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>WHAT YOU OWE · 💳 DEBTS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>dState.total_debt_balance</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>DEBT_PICTURE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MK-NW-E-007</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MK-NW-M-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>each debt and what is left on it</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>d.remaining_balance</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DEBT_PICTURE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MK-NW-E-007</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MK-NW-M-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>minimum monthly payment on a debt</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>d.minimum_monthly_payment</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>DEBT_REQUIRED_PAYMENT</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MK-NW-E-008</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MK-NW-M-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Monthly debt payments $X/mo</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>dState.total_monthly_debt_service</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DEBT_PICTURE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MK-NW-E-007</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MK-NW-M-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EMERGENCY CUSHION — X.X months</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>runwayMonths</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>worked out on the screen: cash ÷ a typical month of essentials</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MK-NW-M-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>of essentials covered by your cash — $X cash ÷ $Y/mo essentials</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>cashOnHand / monthlySpend</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>TOTAL_CASH · PLANNED_SPENDING</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MK-NW-E-009</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MK-NW-M-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>YOUR RETIREMENT PLAN — on track for $X by age Y</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>pathAhead</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>POT_AT_RETIREMENT</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MK-NW-E-010</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MK-NW-M-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Net worth so far (setup)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>nw.net_worth</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NET_WORTH</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MK-XS-E-001</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MK-NW-M-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Assets $X − Debts $Y = Net worth $Z</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>totalAssets / dState.total_debt_balance</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NET_WORTH · DEBT_PICTURE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MK-NW-E-011</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>/account-detail</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>/add-account</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>/bonds</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>/connect</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>/holding-detail</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>/import-holdings</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>/itemize</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>/look-back</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3086,10 +3406,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MK-PF-M-001</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3097,159 +3421,1020 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ending value</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>walk.ending</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_WALK</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MK-PF-E-001</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MK-PF-M-002</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Wealth generated</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>walk.wealthGenerated</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_WALK</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MK-PF-E-001</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MK-PF-M-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HOW $X BECAME $Y · ALL ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>walk.beginning / walk.ending</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_WALK</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MK-PF-E-001</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MK-PF-M-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ending market value (per account)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>w.ending</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_WALK</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MK-PF-E-001</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MK-PF-M-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>each account and its ending value</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>a.ending</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PERFORMANCE_TABLE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MK-PF-E-002</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MK-PF-M-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>WHAT EACH CATEGORY EARNED — RETURN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>b.earned / b.ret</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PERFORMANCE_TABLE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MK-PF-E-002</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MK-PF-M-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>All categories</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PERFORMANCE_TABLE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MK-PF-E-002</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MK-PF-M-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HONEST COMPARISON</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>benchPort</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BENCHMARK_RETURN_BLENDED</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MK-PF-E-003</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MK-PF-M-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Return (money-weighted, when the record covers it)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>mw.rate</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MODIFIED_DIETZ (Calculation Module code/engines/window-return.ts)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MK-PF-E-004</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>/account-detail</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>/add-account</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>/bonds</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>/connect</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>/holding-detail</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>/import-holdings</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>/look-back</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>/what-if</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Parent Screen Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary Screen Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Name on Screen</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Name of Underlying Metric</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Name of Underlying Engine</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Engine ID</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Your name for it (72-metric file)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Core screen?</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Row status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MK-PL-M-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>✓ What you have — already in: N accounts, $X counted</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>door.credit.total</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>WHAT_THE_PLAN_STILL_NEEDS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MK-PL-E-001</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Your odds — can't work them out yet. Add &lt;what&gt; below.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>door.missing</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>WHAT_THE_PLAN_STILL_NEEDS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-001</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MK-PL-M-003</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>/add-account</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>YOUR RETIREMENT PAYCHECK — each guaranteed source</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>g.amount</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — retirementPaycheckYear, src/domain/paycheck</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MK-PL-E-002</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MK-PL-M-004</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/bill-calendar</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D5">
+        <f> Guaranteed</f>
+        <v/>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>payMonth.guaranteedTotal</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — retirementPaycheckYear, src/domain/paycheck</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MK-PL-E-002</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MK-PL-M-005</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/bonds</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+ Draw from savings</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>payMonth.safeDraw</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — retirementPaycheckYear, src/domain/paycheck</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MK-PL-E-002</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MK-PL-M-006</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/connect</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Your paycheck $X/mo</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>paycheckTotal</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>worked out on the screen: guaranteed + draw from savings</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MK-PL-M-007</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/holding-detail</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SAVED SCENARIOS (n)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>scenarios.length</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — saved scenarios, src/domain/scenarios</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MK-PL-E-003</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -3257,12 +4442,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/import-holdings</t>
+          <t>/account-detail</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -3281,12 +4466,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/income-manager</t>
+          <t>/add-account</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -3305,12 +4490,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/look-back</t>
+          <t>/bonds</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -3329,12 +4514,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/month-detail</t>
+          <t>/connect</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -3353,12 +4538,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/monthly-income</t>
+          <t>/education</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -3377,12 +4562,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/onboarding</t>
+          <t>/holding-detail</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -3401,12 +4586,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/paycheck-months</t>
+          <t>/import-holdings</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -3425,12 +4610,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/performance</t>
+          <t>/look-back</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -3449,12 +4634,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/retirement</t>
+          <t>/monthly-income</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -3473,12 +4658,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cashflow</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/what-if</t>
+          <t>/multi-goal</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -3488,6 +4673,1774 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>/paycheck-months</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>/performance</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>/required-withdrawals</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>/retirement</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>/roth</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>/sharpen</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>/ss-timing</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>/what-if</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>/will-it-last</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Parent Screen Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary Screen Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Name on Screen</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Name of Underlying Metric</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Name of Underlying Engine</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Engine ID</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Your name for it (72-metric file)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Core screen?</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Row status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MK-CF-M-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Expected in</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>cell.inflow</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — the by-month grid, src/domain/cashflow</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MK-CF-E-001</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Planned out · incl. &lt;big bill&gt;</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>cell.outflow</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — the by-month grid, src/domain/cashflow</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MK-CF-E-001</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MK-CF-M-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D4">
+        <f> Planned surplus</f>
+        <v/>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>cell.net</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>worked out on the screen: expected in − planned out</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MK-CF-M-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Out (spent + debt)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — budgetVsActual, src/domain/budget</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MK-XS-E-005</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MK-CF-M-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D6">
+        <f> Surplus</f>
+        <v/>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>inn - out</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>worked out on the screen: in − out</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MK-CF-M-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>YOUR SOURCES — Base salary</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>op.baseSalary</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>TOTAL_INCOME</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MK-CF-E-002</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MK-CF-M-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>YOUR SOURCES — Self-employment</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>op.seAmount</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>TOTAL_INCOME</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MK-CF-E-002</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MK-CF-M-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>YOUR SOURCES — Bonus</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>op.bonusAnnual</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>TOTAL_INCOME</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MK-CF-E-002</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MK-CF-M-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>YOUR SOURCES — Stock vesting (equity)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>rsuTotal</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — the equity schedule, src/domain/income</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MK-CF-E-003</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MK-CF-M-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>YOUR SOURCES — Rental property</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>rentalTotal</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>RENTAL_INCOME_A_YEAR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MK-CF-E-004</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MK-CF-M-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>YOUR SOURCES — Social Security · pension</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>guaranteed</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME_NOW</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MK-CF-E-005</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MK-CF-M-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>RECEIVED · &lt;month&gt; — each payment</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>i.amount</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — the received list, src/domain/income</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MK-CF-E-006</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MK-CF-M-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>&lt;MONTH&gt; · $X SPENT</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>spent</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SPENDING_BY_KIND</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MK-CF-E-007</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MK-CF-M-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>each expense and its amount</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>e.amount</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SPENDING_BY_KIND</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MK-CF-E-007</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MK-CF-M-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BY CATEGORY VS PLAN — $X of $Y</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>b.spent / b.planned</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PLANNED_SPENDING</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MK-CF-E-008</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MK-CF-M-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BIG-TICKET RADAR — &lt;bill&gt; · due &lt;month&gt;</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>b.amount</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — the big-bill radar, src/domain/cashflow</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MK-CF-E-009</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MK-CF-M-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>well above your usual &lt;category&gt;</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>e.amount</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — the unusual-spend check, src/domain/budget</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MK-CF-E-010</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MK-CF-M-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>THIS MONTH — In (take-home)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>inflow</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — incomeMonthlyGrid, src/domain/income</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MK-XS-E-006</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MK-CF-M-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>THIS MONTH — Out (bills + debt)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>outflow</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SPENDING_BY_KIND · DEBT_REQUIRED_PAYMENT</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MK-CF-E-011</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MK-CF-M-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>THIS MONTH — free to use</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>worked out on the screen: in − out − what the Plan committed</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MK-CF-M-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>&lt;goal&gt; · from your Plan</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>c.monthlyAmount</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — plan commitments, src/domain/planning</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MK-CF-E-012</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MK-CF-M-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>YOUR FUTURE PAYCHECK — At &lt;age&gt;: ~$X / mo</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>projection.monthly</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>POT_AT_RETIREMENT</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MK-NW-E-010</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MK-CF-M-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>YOUR FUTURE PAYCHECK — Social Security · pension</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>projection.guaranteed</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MK-CF-E-013</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>/account-detail</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>/add-account</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>/bill-calendar</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>/bonds</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>/connect</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>/holding-detail</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>/import-holdings</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>/income-manager</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>/look-back</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>/month-detail</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>/monthly-income</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>/onboarding</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>/paycheck-months</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>/performance</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>/retirement</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>NOT STARTED — screen not yet read</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>/what-if</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
         <is>
           <t>NOT STARTED — screen not yet read</t>
         </is>

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -865,7 +865,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>5 of 49 — Home, Net worth, Performance, Cash flow, Plan (the five parent screens). The 44 secondary and menu screens are listed and marked NOT STARTED.</t>
+          <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -936,14 +936,994 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MK-XS-I-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>account balance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>the institution download, a connection, or typed by hand</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>net worth · what you own · cushion · required withdrawal</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NET_WORTH · TOTAL_CASH · TOTAL_INVESTMENTS · REQUIRED_WITHDRAWAL</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NOT STARTED — filled as each screen is read</t>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>account type (taxable, pre-tax, Roth)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>typed at setup, or guessed from the account name</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>how this account is taxed · required withdrawal · Roth move</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TAX_TREATMENT · REQUIRED_WITHDRAWAL</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MK-XS-I-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>institution name</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>the download or the connection</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>net worth by institution · account rows</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ACCOUNT_SPLIT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MK-XS-I-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>holding quantity (shares)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>the download, a connection, or typed</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>current value · cost basis · gains</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HOLDING_SHARES · HOLDING_MARKET_VALUE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MK-XS-I-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>holding price</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>the price feed</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>current value · today's market value · freshness</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HOLDING_MARKET_VALUE · PRICE_FRESHNESS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MK-XS-I-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>price fetched at</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>the app, when it last asked for prices</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>prices updated &lt;when&gt;</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PRICE_FRESHNESS</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MK-XS-I-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>purchase price and date (per lot)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>the download or typed</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>price paid · total paid · long or short-term gain</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HOLDING_COST_BASIS · HOLDING_CAP_GAINS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MK-XS-I-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>transaction amount</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>the institution download</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>contributions · withdrawals · income · the change walk</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LEDGER · NW_CHANGE_WALK</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MK-XS-I-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>transaction date</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>the institution download</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>the period a figure covers · the change walk</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LEDGER · NW_CHANGE_WALK</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MK-XS-I-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>transaction words (the institution's own wording)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>the institution download</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>what each line means: money in, money out, income, cost</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>LEDGER · the institution-words table</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MK-XS-I-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>bond face value</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>typed, or the download</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>face value · what comes back at maturity</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BOND_FACTS</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MK-XS-I-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>bond coupon rate</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>typed, or the download</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>interest payments a year · yield</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BOND_COUPON · BOND_CURRENT_YIELD</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MK-XS-I-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>bond maturity date</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>typed, or the download</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>years away · yield if held to maturity</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BOND_YEARS_LEFT · BOND_YIELD_TO_MATURITY</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MK-XS-I-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>debt balance</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>typed, or a connection</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>what you owe · net worth · payoff</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DEBT_PICTURE</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MK-XS-I-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>debt interest rate</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>typed</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>payoff date · what extra payments save</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>DEBT_PAYOFF</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MK-XS-I-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>debt minimum payment</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>typed</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>monthly debt payments · money out</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>DEBT_REQUIRED_PAYMENT</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MK-XS-I-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>birth year</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>typed at setup</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>current age · retirement age · Social Security · required withdrawal</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SS_BENEFIT_AT_AGE · RMD_START_AGE</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MK-XS-I-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>retirement age</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>typed, or the dial on Plan</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>the odds · projected pot · the paycheck</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_RESULT · POT_AT_RETIREMENT</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MK-XS-I-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>monthly spending in retirement</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>typed</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>the odds · the draw from savings</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MK-XS-I-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Social Security monthly amount</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>typed from the statement, or a worked example</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>guaranteed income · the paycheck · claim timing</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SS_BENEFIT_AT_AGE · RETIREMENT_INCOME_NOW</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MK-XS-I-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Social Security claim age</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>typed</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>how much the check is · lifetime total</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SS_CLAIM_FACTOR</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MK-XS-I-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>pension monthly amount</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>typed</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>guaranteed income · the paycheck</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME_NOW</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MK-XS-I-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>salary and other income</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>typed at setup</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>money in · take-home · savings capacity</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TOTAL_INCOME</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MK-XS-I-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>logged spending</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>typed, or read from a download</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>spent so far · by category · essentials</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SPENDING_BY_KIND · PLANNED_SPENDING</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MK-XS-I-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>typical monthly essentials</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>typed</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>the cushion · job-safety runway · stress test</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PLANNED_SPENDING · JOB_SAFETY_RUNWAY</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MK-XS-I-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>big costs (amount and year)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>typed</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>the odds · the plan · the radar</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>BIG_COSTS</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MK-XS-I-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>goals (target, saved, date)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>typed</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>goal progress · what you can afford together</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>GOAL_PROGRESS</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MK-XS-I-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>assumed return</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>built in, and adjustable on the cockpit</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>projected pot · the odds</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>POT_AT_RETIREMENT · WILL_IT_LAST_RESULT</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MK-XS-I-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>inflation rate</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>a published feed, with a built-in fallback</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>tomorrow's dollars · the odds</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MK-XS-I-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>tax filing status and age</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>typed at setup</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>tax bands · the deduction · tax on a Roth move</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>TAXABLE_INCOME · TAX_ON_CONVERSION</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MK-XS-I-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>daily and monthly snapshots</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>the app itself, once a day</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>the trend line · change in net worth · beginning values</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>TREND_SERIES · NW_CHANGE_WALK</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -1606,7 +2586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1870,18 +2850,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/account-detail</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>/add-account</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
       </c>
     </row>
@@ -1894,18 +2890,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/add-account</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>/connect</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
       </c>
     </row>
@@ -1918,18 +2930,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/bill-calendar</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>/import-holdings</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
       </c>
     </row>
@@ -1942,18 +2970,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/bonds</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>/onboarding</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
       </c>
     </row>
@@ -1966,282 +3010,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/connect</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>/performance</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>/holding-detail</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>/import-holdings</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>/income-manager</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>/look-back</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>/month-detail</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>/monthly-income</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>/onboarding</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>/paycheck-months</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>/performance</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>/retirement</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>/what-if</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
         </is>
       </c>
     </row>
@@ -2256,7 +3052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3136,7 +3932,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MK-NW-M-018</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Networth</t>
@@ -3147,20 +3947,44 @@
           <t>/account-detail</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Market value</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>account.balance</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>HAND_VALUE_AGE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MK-NW-E-012</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MK-NW-M-019</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Networth</t>
@@ -3168,162 +3992,1402 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>/account-detail</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>acctIncome</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>the ledger sum of interest and dividends for the account</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MK-NW-E-013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MK-NW-M-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>/account-detail</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>each asset class inside the account</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>breakdown[k]</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ACCOUNT_SPLIT</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>MK-NW-E-006</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MK-NW-M-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>/account-detail</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Income: &lt;amount&gt; on a holding row</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>incomeOf(rw)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>the ledger sum for that holding</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MK-NW-E-014</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MK-NW-M-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>/account-detail</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ACTIVITY — n records</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>txns.length</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>HISTORY_DEPTH</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MK-NW-E-015</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MK-NW-M-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>/account-detail</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Face value</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>b.face</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>BOND_FACTS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MK-NW-E-016</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MK-NW-M-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>/account-detail</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Interest payments — X%/yr · $Y/yr</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>annualCoupon(b)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BOND_COUPON</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MK-NW-E-017</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MK-NW-M-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>/account-detail</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Matures — &lt;date&gt; (n years away)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>BOND_YEARS_LEFT</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MK-NW-E-018</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MK-NW-M-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>/account-detail</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Yield if held to maturity</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ytm</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>BOND_YIELD_TO_MATURITY</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MK-NW-E-019</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MK-NW-M-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>/account-detail</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Yield on today's value</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>BOND_CURRENT_YIELD</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MK-NW-E-020</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MK-NW-M-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>/account-detail</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Rates rise 1% → value roughly $X–$Y</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>sens.ratesUp</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>BOND_RATE_SENSITIVITY</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>MK-NW-E-021</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MK-NW-M-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>/holding-detail</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CURRENT PRICE · LIVE</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>the price feed, with its freshness</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>MK-NW-E-022</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MK-NW-M-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>/holding-detail</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Current value</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>HOLDING_MARKET_VALUE</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>MK-NW-E-023</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MK-NW-M-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>/holding-detail</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Quantity — n shares</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>HOLDING_SHARES</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>MK-NW-E-024</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MK-NW-M-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>/holding-detail</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Price paid (average)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>rawAvg</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>HOLDING_COST_BASIS</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>MK-NW-E-025</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MK-NW-M-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>/holding-detail</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Total paid</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>HOLDING_COST_BASIS</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>MK-NW-E-025</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MK-NW-M-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>/holding-detail</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Dividends received (12 mo)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>dividends.trailing12</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>the ledger sum of dividends over twelve months</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>MK-NW-E-026</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MK-NW-M-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>/holding-detail</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Realized gain from your buys and sells</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>realized</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>REALISED_GAIN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>MK-NW-E-027</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MK-NW-M-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>/holding-detail</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Gain — long-term (held over 1 yr)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>cg.longGain</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>HOLDING_CAP_GAINS</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>MK-NW-E-028</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MK-NW-M-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>/holding-detail</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Gain — short-term (under 1 yr)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>cg.shortGain</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>HOLDING_CAP_GAINS</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>MK-NW-E-028</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MK-NW-M-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>/itemize</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>We keep the total at $X</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>lump.balance</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>the account balance being itemised</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>MK-NW-E-029</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MK-NW-M-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>/itemize</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>$X of $Y itemized · remainder</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>allocated / remainder</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>worked out on the screen: total − what has been itemised</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MK-NW-M-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>/itemize</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>each holding and its value</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>h.value</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>HOLDING_MARKET_VALUE</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>MK-NW-E-023</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MK-NW-M-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>/bonds</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>total value of your bonds</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>summary.totalValue</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>BOND_FACTS</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>MK-NW-E-016</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MK-NW-M-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>/bonds</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>n bonds · face $X</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>summary.totalFace</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>BOND_FACTS</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>MK-NW-E-016</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MK-NW-M-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>/bonds</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>COUPON / YR</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>summary.coupon</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>BOND_COUPON</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>MK-NW-E-017</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MK-NW-M-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>/bonds</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AVG YIELD</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>summary.yield</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>BOND_CURRENT_YIELD</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>MK-NW-E-020</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MK-NW-M-045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>/bonds</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>each bond — face, coupon, yield</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>bi</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>BOND_FACTS · BOND_COUPON</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>MK-NW-E-030</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Networth</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>/add-account</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
         <is>
           <t>Networth</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>/bonds</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>/connect</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
         <is>
           <t>Networth</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>/connect</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Networth</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>/holding-detail</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Networth</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>/import-holdings</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Networth</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>/itemize</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Networth</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>/look-back</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
       </c>
     </row>
@@ -3338,7 +5402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3838,7 +5902,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MK-PF-M-010</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Performance</t>
@@ -3846,23 +5914,47 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/account-detail</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>/look-back</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Left in &lt;fund&gt; it became $X (up/down $Y, Z%)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>result.stayed</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>LOOK_BACK</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MK-PF-E-005</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MK-PF-M-011</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Performance</t>
@@ -3870,23 +5962,47 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/add-account</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+          <t>/look-back</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Moved to &lt;fund&gt; it would be $X</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>result.moved</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>LOOK_BACK</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MK-PF-E-005</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MK-PF-M-012</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Performance</t>
@@ -3894,18 +6010,38 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/bonds</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>/look-back</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Difference: $X more/less if you had moved</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>result.difference</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>LOOK_BACK</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MK-PF-E-005</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -3918,18 +6054,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/connect</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+          <t>/add-account</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
       </c>
     </row>
@@ -3942,18 +6094,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/holding-detail</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>/connect</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
       </c>
     </row>
@@ -3969,63 +6137,31 @@
           <t>/import-holdings</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>/look-back</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>/what-if</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
       </c>
     </row>
@@ -4040,7 +6176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4439,7 +6575,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MK-PL-M-008</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Plan</t>
@@ -4447,23 +6587,47 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/account-detail</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t>/will-it-last</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>What you have (nest egg)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>inp.start_balance</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MK-PL-E-004</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MK-PL-M-009</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Plan</t>
@@ -4471,23 +6635,47 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/add-account</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>/will-it-last</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Monthly spending in retirement</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>inp.retire_monthly_spend_today</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>RETIREMENT_SPENDING</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MK-PL-E-005</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MK-PL-M-010</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Plan</t>
@@ -4495,23 +6683,47 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/bonds</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>/will-it-last</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Guaranteed income — $X/mo from age Y</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>inp.guaranteed_monthly_income</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>GUARANTEED_STREAMS (engines: B1 rebuild)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MK-PL-E-006</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MK-PL-M-011</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Plan</t>
@@ -4519,23 +6731,47 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/connect</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+          <t>/will-it-last</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Monthly saving until then</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>inp.annual_contrib</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MK-PL-E-004</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MK-PL-M-012</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Plan</t>
@@ -4543,23 +6779,47 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/education</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>/required-withdrawals</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Yours starts in &lt;year&gt; (age N)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>rmdStartAgeFor(age)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>RMD_START_AGE (Calculation Module code/engines/rmd.ts)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MK-PL-E-007</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MK-PL-M-013</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Plan</t>
@@ -4567,23 +6827,47 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/holding-detail</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+          <t>/required-withdrawals</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Required $X</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>REQUIRED_WITHDRAWAL</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MK-PL-E-008</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MK-PL-M-014</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Plan</t>
@@ -4591,23 +6875,43 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/import-holdings</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>/required-withdrawals</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Taken so far $X · still to take</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>taken / still</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>worked out on the screen: required − taken so far</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MK-PL-M-015</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Plan</t>
@@ -4615,23 +6919,47 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/look-back</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+          <t>/required-withdrawals</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>YEAR BY YEAR (ESTIMATES) — each year and amount</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>r.amount</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>REQUIRED_WITHDRAWAL</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MK-PL-E-008</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MK-PL-M-016</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Plan</t>
@@ -4639,23 +6967,47 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/monthly-income</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+          <t>/required-withdrawals</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BASED ON THESE ACCOUNTS — each balance</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>a.balance</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>HAND_VALUE_AGE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MK-NW-E-012</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MK-PL-M-017</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Plan</t>
@@ -4663,234 +7015,1194 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>/ss-timing</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Monthly check (today's dollars)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>A.guaranteedMonthly</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SS_BENEFIT_AT_AGE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MK-PL-E-009</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MK-PL-M-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>/ss-timing</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>You receive $X/mo ✓</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>op.ri_ss</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME_NOW</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MK-PL-E-010</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MK-PL-M-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>/ss-timing</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Claiming at N pays $X a month</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>r.monthly</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SS_CLAIM_FACTOR · SS_BENEFIT_AT_AGE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MK-PL-E-011</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MK-PL-M-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>/ss-timing</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>about $X in total by age N</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>r.lifetime</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SS_LIFETIME_TOTAL</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>MK-PL-E-012</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MK-PL-M-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>/ss-timing</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Showing example numbers (a $X/mo statement)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>exampleStmt</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>the worked example used until a real statement goes in</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MK-PL-E-013</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MK-PL-M-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>/roth</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Convert to Roth this year (&lt;year&gt;)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>A.rothConversionThisYear</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>the amount the person chose</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MK-PL-E-014</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MK-PL-M-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>/roth</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Extra tax next April (estimate) — about $X</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>taxCost</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>TAX_ON_CONVERSION</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MK-PL-E-015</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MK-PL-M-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>/roth</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>from your pre-tax $X</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>preTax</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PRE_TAX_BALANCE</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MK-PL-E-016</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MK-PL-M-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>/what-if</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>+$X/mo (the saving dial)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>addMonthly</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>the amount the person chose</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MK-PL-E-014</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MK-PL-M-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>/what-if</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>$X → $Y (nest egg before and after)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>result.before.egg / result.after.egg</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>POT_AT_RETIREMENT</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MK-NW-E-010</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MK-PL-M-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>/what-if</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>the difference the change makes</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>result.after.egg - result.before.egg</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>worked out on the screen: after − before</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MK-PL-M-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>/multi-goal</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>each goal and its monthly amount</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>d.monthlyAmount</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>the amounts the person chose</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>MK-PL-E-017</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MK-PL-M-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>/paycheck-months</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>/multi-goal</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Retirement saving — $X/mo now → $Y/mo</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>A.contribMonthly / retirementMo</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>MK-PL-E-004</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MK-PL-M-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>/multi-goal</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Extra on debt $X/mo</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>extraDebt</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DEBT_PICTURE</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>MK-NW-E-007</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MK-PL-M-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>/multi-goal</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>paid off &lt;month&gt; · saves $X</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>weighed.debtPayoff</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>DEBT_PAYOFF</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>MK-PL-E-018</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MK-PL-M-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>/retirement</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>incl. Social Security $X/mo from age N</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ssIncome</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME_NOW</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>MK-PL-E-010</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MK-PL-M-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>/retirement</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>your $X grows to $Y by age N at Z%/yr</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>nestEgg / scProjected</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>POT_AT_RETIREMENT</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>MK-NW-E-010</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MK-PL-M-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>/retirement</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>At Z% return, your money lasts past age N</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>scDeplete</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_RESULT</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>MK-XS-E-002</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MK-PL-M-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>/retirement</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Retire at age (the dial)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>rAge</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>the age the person chose</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>MK-PL-E-019</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MK-PL-M-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>/education</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>the future total cost of school</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>plan.futureTotalCost</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>EDUCATION_COST</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>MK-PL-E-020</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MK-PL-M-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>/education</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>$X/mo set aside closes the $Y gap</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>plan.monthlyNeeded / plan.gap</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>EDUCATION_COST</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>MK-PL-E-020</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>/add-account</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>/connect</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>/import-holdings</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>/performance</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>/required-withdrawals</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Plan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>/retirement</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Plan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>/roth</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Plan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>/sharpen</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Plan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>/ss-timing</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Plan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>/what-if</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Plan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>/will-it-last</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
       </c>
     </row>
@@ -4905,7 +8217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5475,7 +8787,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MK-CF-E-005</t>
+          <t>MK-PL-E-010</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -5523,7 +8835,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MK-CF-E-006</t>
+          <t>MK-CF-E-005</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -5571,7 +8883,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MK-CF-E-007</t>
+          <t>MK-CF-E-006</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -5619,7 +8931,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MK-CF-E-007</t>
+          <t>MK-CF-E-006</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -5667,7 +8979,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MK-CF-E-008</t>
+          <t>MK-CF-E-007</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -5715,7 +9027,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MK-CF-E-009</t>
+          <t>MK-CF-E-008</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -5763,7 +9075,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MK-CF-E-010</t>
+          <t>MK-CF-E-009</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -5859,7 +9171,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MK-CF-E-011</t>
+          <t>MK-CF-E-010</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -5951,7 +9263,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MK-CF-E-012</t>
+          <t>MK-CF-E-011</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -6047,7 +9359,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MK-CF-E-013</t>
+          <t>MK-CF-E-012</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -6063,7 +9375,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MK-CF-M-024</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Cashflow</t>
@@ -6071,23 +9387,47 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>/account-detail</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+          <t>/monthly-income</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>each source of guaranteed income</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>g.amount</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME_NOW</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MK-PL-E-010</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MK-CF-M-025</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Cashflow</t>
@@ -6095,23 +9435,47 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>/add-account</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+          <t>/month-detail</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>what came in and went out that month</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>the by-month grid</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MK-CF-E-013</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MK-CF-M-026</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Cashflow</t>
@@ -6119,66 +9483,134 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>/paycheck-months</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>the months a paycheck lands</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>payYear</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>RETIREMENT_PAYCHECK</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MK-CF-E-014</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MK-CF-M-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>/income-manager</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>each income source and its amount</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>TOTAL_INCOME</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MK-CF-E-002</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MK-CF-M-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cashflow</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>/bill-calendar</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Cashflow</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>/bonds</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Cashflow</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>/connect</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>each bill and the day it falls</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>bills</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>THE_BILL_CALENDAR</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>MK-CF-E-015</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -6191,18 +9623,34 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>/holding-detail</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+          <t>/add-account</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
       </c>
     </row>
@@ -6215,18 +9663,34 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>/import-holdings</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+          <t>/connect</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
       </c>
     </row>
@@ -6239,18 +9703,34 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>/income-manager</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+          <t>/import-holdings</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
       </c>
     </row>
@@ -6263,18 +9743,34 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>/look-back</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+          <t>/onboarding</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
       </c>
     </row>
@@ -6287,162 +9783,34 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>/month-detail</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+          <t>/performance</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Cashflow</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>/monthly-income</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Cashflow</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>/onboarding</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Cashflow</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>/paycheck-months</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Cashflow</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>/performance</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Cashflow</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>/retirement</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Cashflow</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>/what-if</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
         </is>
       </c>
     </row>
@@ -6457,7 +9825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6525,7 +9893,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MK-MN-M-001</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>Menu</t>
@@ -6533,23 +9905,47 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>/auth</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>/big-costs</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>each big cost and its year</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>c.amount</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>BIG_COSTS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MK-MN-E-001</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MK-MN-M-002</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Menu</t>
@@ -6560,20 +9956,44 @@
           <t>/big-costs</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>the total of your big costs</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>BIG_COSTS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MK-MN-E-001</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MK-MN-M-003</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Menu</t>
@@ -6584,20 +10004,44 @@
           <t>/contribution-room</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>$X left / up to $Y</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>room / limit</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CONTRIBUTION_ROOM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MK-MN-E-002</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MK-MN-M-004</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Menu</t>
@@ -6605,23 +10049,47 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/credit</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>/contribution-room</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>about $X of the $Y limit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>used / limit</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CONTRIBUTION_ROOM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MK-MN-E-002</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MK-MN-M-005</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Menu</t>
@@ -6629,23 +10097,43 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/estate</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>/contribution-room</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>about $X/mo for the rest of the year</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>perMonth</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>worked out on the screen: room left ÷ months left</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>NOT STARTED — screen not yet read</t>
+          <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MK-MN-M-006</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Menu</t>
@@ -6653,354 +10141,1470 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>/credit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>$X of $Y used — the line marks 30%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>bal / lim</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CREDIT_USE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MK-MN-E-003</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MK-MN-M-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>/expense</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>$X of $Y this month · over by $Z</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>catSpend / catBudget</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PLANNED_SPENDING</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MK-CF-E-007</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MK-MN-M-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Menu</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>/goals</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>typical free cash to save $X/mo</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>capacity.avg</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>GOAL_CAPACITY</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MK-MN-E-004</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MK-MN-M-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>/goals</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>each goal — $X of $Y · $Z to go</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>g.saved / g.target</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>GOAL_PROGRESS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MK-MN-E-005</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MK-MN-M-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>/goals</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>your non-monthly budget</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sinkBasis</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SINKING_FUNDS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MK-MN-E-006</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MK-MN-M-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>/income-detail</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>net a year</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>state.total_net_annual</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>TOTAL_INCOME</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MK-CF-E-002</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MK-MN-M-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>/income-detail</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Gross / year</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>state.total_gross_annual</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>TOTAL_INCOME</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MK-CF-E-002</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MK-MN-M-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>/income-detail</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Net / month</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>state.net_monthly_income</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>TOTAL_INCOME</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MK-CF-E-002</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MK-MN-M-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>/income-detail</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Employer 401(k) match</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>state.employer_match_annual</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>EMPLOYER_MATCH</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MK-MN-E-007</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MK-MN-M-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>/insights</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>each insight and the dollars behind it</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>shareOf(v)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — useInsights, src/domain/insights</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MK-HM-E-003</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MK-MN-M-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>/insights</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Total invested · Cash total · Investable total</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>investable / cash</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>TOTAL_INVESTABLE · TOTAL_CASH</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MK-MN-E-008</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MK-MN-M-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>/insurance</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>the life-cover gap</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>need.gap</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>INSURANCE_NEED</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MK-MN-E-009</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MK-MN-M-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>/insurance</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Income replacement (N yrs)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>need.incomeReplacement</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>INSURANCE_NEED</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MK-MN-E-009</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MK-MN-M-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>/insurance</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>+ Debts, goals &amp; final expenses · Total need</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>need.total</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>INSURANCE_NEED</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MK-MN-E-009</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MK-MN-M-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>/jobsafety</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>N months of essentials is $X ($Y/mo)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>target / ess</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>JOB_SAFETY_RUNWAY</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>MK-MN-E-010</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MK-MN-M-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>/jobsafety</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Using $X/mo from your logged spending</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>monthSpend</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SPENDING_BY_KIND</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MK-CF-E-006</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MK-MN-M-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>/other-investments</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>the total value of these investments</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>summary.totalValue</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ALTERNATIVES_TOTAL</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MK-MN-E-011</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MK-MN-M-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>/other-investments</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EST. GROWTH / YR</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>summary.growth</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ALTERNATIVES_GROWTH</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MK-MN-E-012</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MK-MN-M-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>/stress-test</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>You could cover a $X hit</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STRESS_TEST</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MK-MN-E-013</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MK-MN-M-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>/stress-test</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>You'd have $X left — about N months of essentials</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>r.cashAfter / r.runwayAfter</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STRESS_TEST</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MK-MN-E-013</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MK-MN-M-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>/stress-test</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>your $X/mo of must-pay bills</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ess</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PLANNED_SPENDING</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MK-CF-E-007</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MK-MN-M-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>/tax-organizer</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>each taxable line and its amount</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>l.amount</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>TAXABLE_INCOME</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MK-MN-E-014</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MK-MN-M-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>/tax-organizer</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Taxable income · Non-taxable</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>org.taxableTotal</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>TAXABLE_INCOME</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>MK-MN-E-014</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MK-MN-M-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>/tax-organizer</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>each contribution and its amount</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>c.amount</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CONTRIBUTION_ROOM</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>MK-MN-E-002</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MK-MN-M-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>/worth-a-look</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>$X left &lt;account&gt; on &lt;date&gt;</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>f.amount</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — the outflow watch, src/domain/insights</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>MK-MN-E-015</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>/auth</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>/estate</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>/first-run</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
         <is>
           <t>Menu</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>/goals</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>/income</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
         <is>
           <t>Menu</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>/income</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>/rewards</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
         <is>
           <t>Menu</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>/income-detail</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>/settings</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
         <is>
           <t>Menu</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>/insights</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Menu</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>/insurance</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Menu</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>/jobsafety</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Menu</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>/other-investments</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Menu</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>/rewards</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Menu</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>/settings</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Menu</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>/stress-test</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Menu</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>/tax-organizer</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Menu</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>/tips</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Menu</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>/worth-a-look</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>NOT STARTED — screen not yet read</t>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
       </c>
     </row>

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -704,178 +704,202 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Engine ID</t>
+          <t>COLUMN — Formula (mathematical)</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
+          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Your name for it (72-metric file)</t>
+          <t>COLUMN — Formula (in words)</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
+          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Core screen?</t>
+          <t>COLUMN — Engine ID</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Whether the screen is part of the 55-70 core, the agreed first scope.</t>
+          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Row status</t>
+          <t>COLUMN — Your name for it (72-metric file)</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>VERIFIED with its date means a person read the screen and confirmed the chain. NOT STARTED means the screen has not been read yet. Nothing in between is claimed.</t>
+          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
-      <c r="B27" s="3" t="inlineStr"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>COLUMN — Core screen?</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Whether the screen is part of the 55-70 core, the agreed first scope.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Input ID</t>
+          <t>COLUMN — Row status</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>The identifier of a raw input, per the same standard.</t>
+          <t>VERIFIED with its date means a person read the screen and confirmed the chain. NOT STARTED means the screen has not been read yet. Nothing in between is claimed.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN — Variable name</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>What the raw value is called.</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Source</t>
+          <t>COLUMN — Input ID</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
+          <t>The identifier of a raw input, per the same standard.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Which metric uses it</t>
+          <t>COLUMN — Variable name</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Every metric identifier that depends on this input.</t>
+          <t>What the raw value is called.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Which engine uses it</t>
+          <t>COLUMN — Source</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Every engine identifier that reads this input.</t>
+          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="3" t="inlineStr"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>COLUMN — Which metric uses it</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Every metric identifier that depends on this input.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Complies with — naming</t>
+          <t>COLUMN — Which engine uses it</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
+          <t>Every engine identifier that reads this input.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Complies with — identifiers</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Complies with — objectives</t>
+          <t>Complies with — naming</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/standards/moneykeel_calc_spec_objectives-and-verification_v01.md</t>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
-      <c r="B37" s="3" t="inlineStr"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Complies with — identifiers</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>Complies with — objectives</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/standards/moneykeel_calc_spec_objectives-and-verification_v01.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t>COVERAGE — screens read so far</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>COVERAGE — what that means</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Every screen in the app is listed on its tab. Only Home carries figures so far; the rest are marked NOT STARTED. A rising count is not completeness while screens remain unread.</t>
         </is>
@@ -1948,9 +1972,11 @@
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="41" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2176,7 +2202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2186,9 +2212,11 @@
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="41" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2229,15 +2257,25 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Formula (mathematical)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Formula (in words)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -2279,13 +2317,24 @@
           <t>MK-XS-E-001</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>net worth = Σ(all asset balances) − Σ(all debt balances)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+          <t>total assets − total debts, computed here and never stored as a third number that could disagree with its own two halves.
+Owing more than you own gives a REAL negative — it is never floored at zero, because someone early in a mortgage genuinely has a negative net worth and hiding it would be a lie about their position.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -2327,13 +2376,24 @@
           <t>MK-XS-E-002</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>run 1,000 futures; in each year: balance ← balance × (1 + random return) − (spending − guaranteed income);  odds = futures that never run out ÷ 1,000</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+          <t>If age, spending and a pot are all known, run the simulation and report the chance. Otherwise report that it could not be answered — NOT a confident zero.
+The best-to-worst range re-runs the same plan at a lower and a higher return, so it reads as a range rather than a promise. It always contains the headline figure, and it is repeatable.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -2375,13 +2435,23 @@
           <t>MK-XS-E-003</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>investments = Σ(balance of each account whose class ∈ {brokerage, retirement, other investments})</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+          <t>Add up the balances of every account whose class is Stocks / Funds, Bonds &amp; CDs, Alternatives or Unclassified. Excludes cash, the house and the car.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -2423,13 +2493,27 @@
           <t>MK-XS-E-004</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>return = (ending − beginning − net money in) ÷ (beginning + net money in weighted by when it arrived)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+          <t>Weight each holding's return by how much money is in it, and add: Σ(return × value) ÷ Σ(value).
+Money-weighted, not an equal average: $90,000 up 10% and $10,000 flat is +9%, where averaging the two would say +5% and be badly wrong.
+A holding with no return is dropped from BOTH the top and the bottom of the sum, so it neither drags the answer down nor distorts the weights.
+Nothing usable → nothing, never 0%.
+This is a PRICE-based return. It does not know when you added money, which is what PERSONAL_RETURN answers — the two will differ, and both are right about different questions.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -2471,13 +2555,23 @@
           <t>MK-XS-E-005</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>spent(bucket) = Σ(expenses dated in this month in that bucket, debt payments excluded);  remaining = planned − spent</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+          <t>Adds up this month’s logged expenses by bucket and sets each against what was planned. Debt payments are deliberately left out, because debt is tracked on its own.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -2519,13 +2613,23 @@
           <t>MK-XS-E-006</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>money in month m = salary(m) + tips(m) + rental ÷ 12 + bonus(m) + equity vesting(m) − withholding(m) − pre-tax contributions(m)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+          <t>Builds twelve months of money in, one month at a time. Salary comes from the per-month table, equity lands in the months it vests, the bonus lands in its own month, and each month has its own withholding rate.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -2563,13 +2667,23 @@
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>left to spend = money in this month − spent so far</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+          <t>Worked out on the screen itself, with no engine behind it — a place a second definition can appear.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -2586,7 +2700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2596,9 +2710,11 @@
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="41" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2639,15 +2755,25 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Formula (mathematical)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Formula (in words)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -2689,13 +2815,24 @@
           <t>MK-HM-E-001</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>age = now − the moment prices were last fetched;  stale when age &gt; the freshness limit</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+          <t>Time since the last successful fetch, in words. Four days or more → stale. Four, because a long weekend or a holiday can put three days between two perfectly normal updates, and a false alarm teaches people to ignore the real one.
+Never fetched, unreadable, or dated in the future → STALE. Silence is not good news.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -2737,13 +2874,23 @@
           <t>MK-HM-E-002</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>crossed when net worth ≥ the next round mark above the highest mark already seen</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+          <t>Notices when net worth passes a round number for the first time, and remembers the highest one already shown so the same milestone is never announced twice.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -2785,13 +2932,23 @@
           <t>MK-HM-E-003</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>each insight scores its own dollars at stake; the list = the highest few, ranked</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+          <t>Works out what is worth saying today, puts a dollar amount against each, and shows the few that matter most.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -2829,13 +2986,23 @@
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>share spent = spent so far ÷ money in this month</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+          <t>Worked out on the screen itself, with no engine behind it — a place a second definition can appear.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -2870,12 +3037,14 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -2910,12 +3079,14 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -2950,12 +3121,14 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -2990,12 +3163,14 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -3030,12 +3205,14 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
         </is>
@@ -3052,7 +3229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3062,9 +3239,11 @@
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="41" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3105,15 +3284,25 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Formula (mathematical)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Formula (in words)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -3155,13 +3344,26 @@
           <t>MK-NW-E-001</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>the line is the recorded net worth at each point;  change over the year = net worth today − net worth at the first point of the year</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+          <t>Monthly snapshots and daily points merged into one series and sorted by their date text. A month ("2026-07") sorts before its own days ("2026-07-04"), which is what makes plain text sorting safe.
+A daily value that is not a real date or not a real number is ignored rather than drawn as zero.
+No history → an empty series, NOT a flat line at zero.
+THE LIMIT THAT MATTERS, and it is the mechanism behind the founder's F15: a daily point is ONE NUMBER — total net worth. There is no per-account daily history anywhere in the app, so "what was my Vanguard account worth in April" has no answer to read, and a beginning value gets BACK-SOLVED from today minus whatever the ledger claims happened. It also only ever starts the day the app was first opened: an account connected today has no yesterday, whatever the market did before that.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3203,13 +3405,26 @@
           <t>MK-NW-E-002</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>return = (investable now − investable then) ÷ investable then — money paid in or taken out is NOT removed, so a deposit shows up as a gain</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+          <t>(today's investable − the baseline value) ÷ the baseline value.
+The baseline is the EARLIEST stored daily point on or after the baseline date. The house is left out because it only moves when someone retypes it, which would otherwise read as a market gain.
+No history → NO percentage. It is never back-guessed, which is right.
+THE DEFECT IS WHAT THE BASELINE IS. It is whatever day the app happened to be opened, not a date a person chose. If the only stored point was written after a fall, the fall is invisible and the small recovery since reads as a gain — which is exactly how a −4.2% year showed as +2.0%.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3251,13 +3466,26 @@
           <t>MK-NW-E-001</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>the line is the recorded net worth at each point;  change over the year = net worth today − net worth at the first point of the year</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+          <t>Monthly snapshots and daily points merged into one series and sorted by their date text. A month ("2026-07") sorts before its own days ("2026-07-04"), which is what makes plain text sorting safe.
+A daily value that is not a real date or not a real number is ignored rather than drawn as zero.
+No history → an empty series, NOT a flat line at zero.
+THE LIMIT THAT MATTERS, and it is the mechanism behind the founder's F15: a daily point is ONE NUMBER — total net worth. There is no per-account daily history anywhere in the app, so "what was my Vanguard account worth in April" has no answer to read, and a beginning value gets BACK-SOLVED from today minus whatever the ledger claims happened. It also only ever starts the day the app was first opened: an account connected today has no yesterday, whatever the market did before that.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3299,13 +3527,24 @@
           <t>MK-NW-E-003</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>assets = Σ(balance of every account);  share of an account = balance ÷ assets</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+          <t>Each account's share = its balance ÷ the total, so the shares add to 100. The blended return is weighted by money, not an average of the rates.
+No money at all → every share is 0 and a stated default return is used, rather than dividing by nothing.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3347,13 +3586,23 @@
           <t>MK-NW-E-004</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>cash = Σ(balance of each account whose class = Cash)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+          <t>Add up the balances of every account whose class is Cash. Under the founder's 2026-08-04 rule that means checking, savings, high-yield savings and the uninvested sweep at a broker — and NOT money-market funds, which pay dividends and are measured with the investments.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3395,13 +3644,24 @@
           <t>MK-NW-E-003</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>assets = Σ(balance of every account);  share of an account = balance ÷ assets</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+          <t>Each account's share = its balance ÷ the total, so the shares add to 100. The blended return is weighted by money, not an average of the rates.
+No money at all → every share is 0 and a stated default return is used, rather than dividing by nothing.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3443,13 +3703,24 @@
           <t>MK-NW-E-005</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>value in class k = Σ(balance of accounts in class k);  share(k) = value(k) ÷ Σ value</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+          <t>For every account: if it has its own breakdown (an account holding several classes at once), add each piece to its own class. Otherwise put the WHOLE balance in the one class the account resolves to. Round each total to the cent at the end, never during.
+The totals must add to total assets — this is what the donut draws, so any leak shows as a wrong slice.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3491,13 +3762,27 @@
           <t>MK-NW-E-006</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>for one account: value in class k = balance × weight(k), where Σ weight(k) = 1</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+          <t>WHY IT EXISTS. Your Vanguard account is not one thing. It might hold a CD, a money-market fund, some shares, and a little uninvested cash. Showing it as one lump under a single heading would be wrong four ways at once.
+HOW IT SPLITS. Start with the uninvested cash. Then place each holding by reading its NAME first — a money-market fund goes with the shares, a CD goes with the bonds — and only fall back to the broker's own label when the name tells us nothing.
+THE LEFTOVER. Add the pieces up and they rarely match the broker's total to the penny. What to do with the difference matters more than it sounds.
+A WORKED EXAMPLE, AND IT IS YOUR OWN FINDING. Say the account totals $10,100 and holds one CD worth $10,000. There is $100 unaccounted for. The app used to add it to the biggest holding — so your $100 of spare cash was reported as MORE CD. You asked "why is cash added to CD and not cash?", and you were right: it is money sitting there, not another certificate you own. A small positive leftover is now cash.
+(If the pieces come to MORE than the broker's total, that is a pricing quirk rather than money, and it goes to the largest holding — putting it in cash would show you a negative cash balance, which reads worse than a rounding nudge.)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3539,13 +3824,25 @@
           <t>MK-NW-E-007</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>owed = Σ(remaining balance);  monthly debt payments = Σ(required payment of each debt)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+          <t>Total the balances. Find the highest-rate debt. Add up separately the balances above the rate we treat as dangerous.
+TWO MONTHLY FIGURES ARE KEPT DELIBERATELY: the minimum that must be paid to stay current, and what is actually going out. Confusing them misstates affordability in one direction or the other.
+No debts gives zero and nothing to point at.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3587,13 +3884,25 @@
           <t>MK-NW-E-007</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>owed = Σ(remaining balance);  monthly debt payments = Σ(required payment of each debt)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+          <t>Total the balances. Find the highest-rate debt. Add up separately the balances above the rate we treat as dangerous.
+TWO MONTHLY FIGURES ARE KEPT DELIBERATELY: the minimum that must be paid to stay current, and what is actually going out. Confusing them misstates affordability in one direction or the other.
+No debts gives zero and nothing to point at.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3635,13 +3944,23 @@
           <t>MK-NW-E-008</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>required payment = the stated minimum, or interest + 1% of balance when none is stated</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+          <t>Due in full → 0. It is a dated bill, and calling it a monthly payment overstates what a person is committed to. Otherwise the LARGER of the minimum and whatever payment they have chosen, so overpaying on purpose shows up.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3683,13 +4002,25 @@
           <t>MK-NW-E-007</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>owed = Σ(remaining balance);  monthly debt payments = Σ(required payment of each debt)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+          <t>Total the balances. Find the highest-rate debt. Add up separately the balances above the rate we treat as dangerous.
+TWO MONTHLY FIGURES ARE KEPT DELIBERATELY: the minimum that must be paid to stay current, and what is actually going out. Confusing them misstates affordability in one direction or the other.
+No debts gives zero and nothing to point at.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3727,13 +4058,23 @@
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>cushion in months = cash ÷ essentials a month</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+          <t>Worked out on the screen itself, with no engine behind it — a place a second definition can appear.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3775,13 +4116,24 @@
           <t>MK-NW-E-009</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>months of cushion = cash ÷ essentials a month</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+          <t>Add up the balances of every account whose class is Cash. Under the founder's 2026-08-04 rule that means checking, savings, high-yield savings and the uninvested sweep at a broker — and NOT money-market funds, which pay dividends and are measured with the investments. · The LARGER of two answers: the categories added up, or the single monthly figure they typed.
+The larger wins deliberately. Someone may answer both and the two rarely agree, and understating spending is the direction that FLATTERS a plan — it makes the odds look better than they are. Taking the larger errs toward the cautious side.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3823,13 +4175,29 @@
           <t>MK-NW-E-010</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>pot = balance × (1 + r)^n + Σ(contribution × (1 + r)^(n − year)),  n = years to retirement</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+          <t>TWO FIGURES, no random runs anywhere in this one — it is the straight-line check beside the 1,000-run odds.
+WHAT YOU WILL HAVE. Today's pot grown at your expected return for the years until you retire, plus every year's saving grown for however many years it has left. Worked at 6%: $600,000 today over 7 years becomes $902,000; $24,000 saved each of those years adds about $201,000; $1,103,000 in all.
+WHAT YOU WILL NEED — the target pot. Walk every retirement year one at a time, from the year you retire to the age you plan to. In each year: take that year's spending, take off the guaranteed income you receive that year, and that difference is what the pot must hand you. Bring each of those amounts back to a retirement-year value by dividing by your expected return once for every year you have to wait for it. Add them all up. That total is the pot that pays for the whole plan.
+Two rules ride along: spending rises with inflation every year, and so does Social Security, but a pension stays flat.
+WHY THE NUMBER IS SMALLER THAN THE SUM OF THE SPENDING. Money you do not need until year fifteen keeps earning until then, so you need less than fifteen years' spending set aside today.
+MONEY IS NEEDED AT THE START OF ITS YEAR. The first retirement year's spending is not discounted at all — January's groceries cannot be paid out of December's growth. Some published calculators charge each year at its END, which gives every year one more year of growth and reports a target about (1 + return) / (1 + inflation) smaller — roughly 3% lower at a 6% return and 2.5% inflation. Neither is wrong; ours is the cautious side, and the difference is a timing convention, not a disagreement about the arithmetic.
+HOW IT DIFFERS FROM THE 25 x YARDSTICK reported by the odds engine: this one knows how long you plan for and what your money earns; the yardstick knows neither.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3871,13 +4239,24 @@
           <t>MK-XS-E-001</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>net worth = Σ(all asset balances) − Σ(all debt balances)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+          <t>total assets − total debts, computed here and never stored as a third number that could disagree with its own two halves.
+Owing more than you own gives a REAL negative — it is never floored at zero, because someone early in a mortgage genuinely has a negative net worth and hiding it would be a lie about their position.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3919,13 +4298,26 @@
           <t>MK-NW-E-011</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>net worth = Σ(assets) − Σ(debts);  debts = Σ(remaining balance of each debt)</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+          <t>total assets − total debts, computed here and never stored as a third number that could disagree with its own two halves.
+Owing more than you own gives a REAL negative — it is never floored at zero, because someone early in a mortgage genuinely has a negative net worth and hiding it would be a lie about their position. · Total the balances. Find the highest-rate debt. Add up separately the balances above the rate we treat as dangerous.
+TWO MONTHLY FIGURES ARE KEPT DELIBERATELY: the minimum that must be paid to stay current, and what is actually going out. Confusing them misstates affordability in one direction or the other.
+No debts gives zero and nothing to point at.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3967,13 +4359,24 @@
           <t>MK-NW-E-012</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>value = the balance last recorded;  age = today − date it was recorded</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+          <t>Months between the date the value was set and today. Six months or more → stale.
+A LIVE-PRICED account returns nothing: its value comes from today's prices, so staleness is not a question that applies to it. A value with no date recorded also returns nothing rather than being assumed fresh.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4015,13 +4418,23 @@
           <t>MK-NW-E-013</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>income = Σ(interest + dividends recorded on this account in the period)</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+          <t>Adds the income lines the ledger holds for this account over the period shown.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4063,13 +4476,27 @@
           <t>MK-NW-E-006</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>for one account: value in class k = balance × weight(k), where Σ weight(k) = 1</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+          <t>WHY IT EXISTS. Your Vanguard account is not one thing. It might hold a CD, a money-market fund, some shares, and a little uninvested cash. Showing it as one lump under a single heading would be wrong four ways at once.
+HOW IT SPLITS. Start with the uninvested cash. Then place each holding by reading its NAME first — a money-market fund goes with the shares, a CD goes with the bonds — and only fall back to the broker's own label when the name tells us nothing.
+THE LEFTOVER. Add the pieces up and they rarely match the broker's total to the penny. What to do with the difference matters more than it sounds.
+A WORKED EXAMPLE, AND IT IS YOUR OWN FINDING. Say the account totals $10,100 and holds one CD worth $10,000. There is $100 unaccounted for. The app used to add it to the biggest holding — so your $100 of spare cash was reported as MORE CD. You asked "why is cash added to CD and not cash?", and you were right: it is money sitting there, not another certificate you own. A small positive leftover is now cash.
+(If the pieces come to MORE than the broker's total, that is a pricing quirk rather than money, and it goes to the largest holding — putting it in cash would show you a negative cash balance, which reads worse than a rounding nudge.)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4111,13 +4538,23 @@
           <t>MK-NW-E-014</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>income = Σ(income lines recorded against this holding)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+          <t>Adds the income the ledger holds for that one holding.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4159,13 +4596,24 @@
           <t>MK-NW-E-015</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>records = count(transactions held for this account)</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+          <t>Take the earliest valid date in this sync and keep whichever is earlier — it or what we already had. Depth only ever grows; a shallower sync never shortens it. Unreadable dates are ignored, and a sync with no activity leaves the answer untouched.
+It exists because brokers back-fill DIFFERENT depths — one sends a year, the next ninety days. Without knowing the depth, a "past year" income figure silently understates, so year-scale figures label themselves with this date.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4207,13 +4655,23 @@
           <t>MK-NW-E-016</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>face, coupon rate and maturity as recorded;  bonds total = Σ(value of each bond),  face total = Σ(face)</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+          <t>Reads the stored bond fields off the holding and computes its yields. A holding with none of them is not a bond and returns nothing.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4255,13 +4713,23 @@
           <t>MK-NW-E-017</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>annual coupon = face × coupon rate</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+          <t>face value × coupon rate. NOT what the bond is worth today × the rate — a $10,000 bond paying 4% pays $400 whether it is trading at $9,800 or $11,000.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4303,13 +4771,23 @@
           <t>MK-NW-E-018</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>years to maturity = (maturity date − today) ÷ 365</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+          <t>maturity date − today, in years. Anything already past → 0. No maturity date → 0, treated as due now rather than as never.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4351,13 +4829,25 @@
           <t>MK-NW-E-019</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>y solves: value = Σ(coupon ÷ (1+y)ᵗ) + face ÷ (1+y)ⁿ,  t = 1…n years to maturity</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+          <t>Adds the pull back to face value to the running income:
+(annual coupon + (face − value) ÷ years left) ÷ ((face + value) ÷ 2).
+A bond bought below face gains as it matures, so this comes out above the current yield. Already matured, or no value → no answer, never zero.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4399,13 +4889,23 @@
           <t>MK-NW-E-020</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>current yield = annual coupon ÷ current value</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+          <t>annual coupon ÷ current value. A bond bought at a discount yields MORE than its stated coupon; one bought at a premium yields less. No value → no answer, never a division by zero.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4447,13 +4947,23 @@
           <t>MK-NW-E-021</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>change in value ≈ − duration × change in rate × value</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+          <t>Shows roughly what a one percent move in interest rates would do to the bond's value. Longer to maturity means a bigger swing. An illustration, not a forecast.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4495,13 +5005,23 @@
           <t>MK-NW-E-022</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>price = the latest close from the feed, with the time it was fetched</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+          <t>The most recent price the feed gave, carrying the moment it was fetched so staleness can be shown.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4543,13 +5063,24 @@
           <t>MK-NW-E-023</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>value = quantity × latest price</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+          <t>shares × latest price.
+NO PRICE MEANS ZERO, NOT A GUESS. An unpriced holding contributes nothing and the screen says the price is missing — it is never valued at what it cost, which would silently report a gain of exactly zero.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4591,13 +5122,23 @@
           <t>MK-NW-E-024</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>quantity = Σ(shares bought) − Σ(shares sold)</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+          <t>Add the shares across every purchase lot. A position is the SUM OF ITS LOTS, never one stored figure — that is what makes gain-since-purchase possible.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4639,13 +5180,23 @@
           <t>MK-NW-E-025</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>total paid = Σ(shares in each lot × price paid in that lot);  average = total paid ÷ quantity</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+          <t>Add shares × cost per share across every lot. A lot with no cost recorded contributes nothing, but its shares still count as owned.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4687,13 +5238,23 @@
           <t>MK-NW-E-025</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>total paid = Σ(shares in each lot × price paid in that lot);  average = total paid ÷ quantity</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+          <t>Add shares × cost per share across every lot. A lot with no cost recorded contributes nothing, but its shares still count as owned.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4735,13 +5296,23 @@
           <t>MK-NW-E-026</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>dividends = Σ(dividend lines in the last 12 months)</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+          <t>Adds the dividends recorded for this holding over the last twelve months.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4783,13 +5354,25 @@
           <t>MK-NW-E-027</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>realised gain = Σ over sales of (proceeds − cost of the shares sold, oldest first)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+          <t>Walk buys and sells in date order. Each sale consumes the OLDEST buy lots first, and the gain is proceeds minus the cost of the shares it consumed.
+Lots are kept separately per account AND per ticker, so a Schwab holding never covers a Robinhood sale of the same share.
+A SALE WITH NO RECORDED BUY CONTRIBUTES NOTHING and is counted separately, so the screen can say how much it could not see. A cost is never invented — inventing one would report the entire sale as profit.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4831,13 +5414,25 @@
           <t>MK-NW-E-028</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>per lot: gain = shares × (price − cost per share);  long-term if the lot was held ≥ 365 whole days, otherwise short-term;  a lot with no cost recorded is skipped</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+          <t>Each LOT is judged on its OWN purchase date, not the position's: held twelve whole months or more → long-term, otherwise short-term. Gain per lot = shares × (price − cost per share).
+A lot with no cost recorded is SKIPPED, not treated as free shares — treating it as free would report the entire value as gain and tax it.
+An unreadable purchase date is treated as SHORT-term: the cautious side, since understating a tax bill is the worse mistake.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4879,13 +5474,25 @@
           <t>MK-NW-E-028</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>per lot: gain = shares × (price − cost per share);  long-term if the lot was held ≥ 365 whole days, otherwise short-term;  a lot with no cost recorded is skipped</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+          <t>Each LOT is judged on its OWN purchase date, not the position's: held twelve whole months or more → long-term, otherwise short-term. Gain per lot = shares × (price − cost per share).
+A lot with no cost recorded is SKIPPED, not treated as free shares — treating it as free would report the entire value as gain and tax it.
+An unreadable purchase date is treated as SHORT-term: the cautious side, since understating a tax bill is the worse mistake.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4927,13 +5534,23 @@
           <t>MK-NW-E-029</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>the balance of the account being broken into holdings</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+          <t>The single account total that the holdings entered must add up to.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4971,13 +5588,23 @@
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>left to itemise = the account total − Σ(holdings entered)</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+          <t>Worked out on the screen itself, with no engine behind it — a place a second definition can appear.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5019,13 +5646,24 @@
           <t>MK-NW-E-023</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>value = quantity × latest price</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+          <t>shares × latest price.
+NO PRICE MEANS ZERO, NOT A GUESS. An unpriced holding contributes nothing and the screen says the price is missing — it is never valued at what it cost, which would silently report a gain of exactly zero.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5067,13 +5705,23 @@
           <t>MK-NW-E-016</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>face, coupon rate and maturity as recorded;  bonds total = Σ(value of each bond),  face total = Σ(face)</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+          <t>Reads the stored bond fields off the holding and computes its yields. A holding with none of them is not a bond and returns nothing.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5115,13 +5763,23 @@
           <t>MK-NW-E-016</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>face, coupon rate and maturity as recorded;  bonds total = Σ(value of each bond),  face total = Σ(face)</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+          <t>Reads the stored bond fields off the holding and computes its yields. A holding with none of them is not a bond and returns nothing.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5163,13 +5821,23 @@
           <t>MK-NW-E-017</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>annual coupon = face × coupon rate</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+          <t>face value × coupon rate. NOT what the bond is worth today × the rate — a $10,000 bond paying 4% pays $400 whether it is trading at $9,800 or $11,000.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5211,13 +5879,23 @@
           <t>MK-NW-E-020</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>current yield = annual coupon ÷ current value</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+          <t>annual coupon ÷ current value. A bond bought at a discount yields MORE than its stated coupon; one bought at a premium yields less. No value → no answer, never a division by zero.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5259,13 +5937,23 @@
           <t>MK-NW-E-030</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>annual coupon = face × coupon rate</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+          <t>Reads the stored bond fields off the holding and computes its yields. A holding with none of them is not a bond and returns nothing. · face value × coupon rate. NOT what the bond is worth today × the rate — a $10,000 bond paying 4% pays $400 whether it is trading at $9,800 or $11,000.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5300,12 +5988,14 @@
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -5340,12 +6030,14 @@
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -5380,12 +6072,14 @@
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -5402,7 +6096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5412,9 +6106,11 @@
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="41" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5455,15 +6151,25 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Formula (mathematical)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Formula (in words)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -5505,13 +6211,27 @@
           <t>MK-PF-E-001</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ending = beginning + money in − money out + income − costs + market change  (the identity that must close)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+          <t>WHAT IT IS TRYING TO DO. If you were worth $500,000 last month and $520,000 today, you gained $20,000 — but you want to know why. Did you save it? Did the market give it to you? Did you pay down a loan? Those feel completely different, and only one of them is luck.
+HOW IT WORKS OUT EACH LINE. Everything except the last one is a real record: your deposits, your withdrawals, dividends paid, interest received, loan payments made.
+THE PROBLEM IS THE LAST LINE. "How your investments moved" is not measured against a single share price. It is simply what is left over after everything else is accounted for. Whatever the app cannot explain lands there — wearing the label of a market movement.
+A WORKED EXAMPLE OF THE FAULT. You were worth $939,089. You are still worth $939,089. Nothing moved. But the app thinks you deposited $500. Now the sums must balance: you put in $500 and ended level, so the investments must have LOST $500. The screen tells you the market took $500 from you. It did not. The deposit was wrong.
+And a real $500 loss produces exactly the same line. You cannot tell them apart, which is why a wrong deposit anywhere becomes a market movement that never happened.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5553,13 +6273,27 @@
           <t>MK-PF-E-001</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ending = beginning + money in − money out + income − costs + market change  (the identity that must close)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+          <t>WHAT IT IS TRYING TO DO. If you were worth $500,000 last month and $520,000 today, you gained $20,000 — but you want to know why. Did you save it? Did the market give it to you? Did you pay down a loan? Those feel completely different, and only one of them is luck.
+HOW IT WORKS OUT EACH LINE. Everything except the last one is a real record: your deposits, your withdrawals, dividends paid, interest received, loan payments made.
+THE PROBLEM IS THE LAST LINE. "How your investments moved" is not measured against a single share price. It is simply what is left over after everything else is accounted for. Whatever the app cannot explain lands there — wearing the label of a market movement.
+A WORKED EXAMPLE OF THE FAULT. You were worth $939,089. You are still worth $939,089. Nothing moved. But the app thinks you deposited $500. Now the sums must balance: you put in $500 and ended level, so the investments must have LOST $500. The screen tells you the market took $500 from you. It did not. The deposit was wrong.
+And a real $500 loss produces exactly the same line. You cannot tell them apart, which is why a wrong deposit anywhere becomes a market movement that never happened.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5601,13 +6335,27 @@
           <t>MK-PF-E-001</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ending = beginning + money in − money out + income − costs + market change  (the identity that must close)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+          <t>WHAT IT IS TRYING TO DO. If you were worth $500,000 last month and $520,000 today, you gained $20,000 — but you want to know why. Did you save it? Did the market give it to you? Did you pay down a loan? Those feel completely different, and only one of them is luck.
+HOW IT WORKS OUT EACH LINE. Everything except the last one is a real record: your deposits, your withdrawals, dividends paid, interest received, loan payments made.
+THE PROBLEM IS THE LAST LINE. "How your investments moved" is not measured against a single share price. It is simply what is left over after everything else is accounted for. Whatever the app cannot explain lands there — wearing the label of a market movement.
+A WORKED EXAMPLE OF THE FAULT. You were worth $939,089. You are still worth $939,089. Nothing moved. But the app thinks you deposited $500. Now the sums must balance: you put in $500 and ended level, so the investments must have LOST $500. The screen tells you the market took $500 from you. It did not. The deposit was wrong.
+And a real $500 loss produces exactly the same line. You cannot tell them apart, which is why a wrong deposit anywhere becomes a market movement that never happened.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5649,13 +6397,27 @@
           <t>MK-PF-E-001</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ending = beginning + money in − money out + income − costs + market change  (the identity that must close)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+          <t>WHAT IT IS TRYING TO DO. If you were worth $500,000 last month and $520,000 today, you gained $20,000 — but you want to know why. Did you save it? Did the market give it to you? Did you pay down a loan? Those feel completely different, and only one of them is luck.
+HOW IT WORKS OUT EACH LINE. Everything except the last one is a real record: your deposits, your withdrawals, dividends paid, interest received, loan payments made.
+THE PROBLEM IS THE LAST LINE. "How your investments moved" is not measured against a single share price. It is simply what is left over after everything else is accounted for. Whatever the app cannot explain lands there — wearing the label of a market movement.
+A WORKED EXAMPLE OF THE FAULT. You were worth $939,089. You are still worth $939,089. Nothing moved. But the app thinks you deposited $500. Now the sums must balance: you put in $500 and ended level, so the investments must have LOST $500. The screen tells you the market took $500 from you. It did not. The deposit was wrong.
+And a real $500 loss produces exactly the same line. You cannot tell them apart, which is why a wrong deposit anywhere becomes a market movement that never happened.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5697,13 +6459,26 @@
           <t>MK-PF-E-002</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>per account: ending;  per category: earned = Σ(ending − beginning − net money in);  return = earned ÷ average value held</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+          <t>For each holding: fetch its price series; work out value, cost and gain from its lots; then choose HOW to measure its period return —
+• bought BEFORE the period started → the ordinary period return from the price series
+• bought DURING the period → return since purchase instead, and the row is marked as shortened, because measuring a full year on something owned for a month would be nonsense
+The benchmark is measured over THE SAME window, shortened the same way, so the comparison is like for like. Beat-by is simply one minus the other, and is left blank when either side is missing.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5745,13 +6520,26 @@
           <t>MK-PF-E-002</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>per account: ending;  per category: earned = Σ(ending − beginning − net money in);  return = earned ÷ average value held</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+          <t>For each holding: fetch its price series; work out value, cost and gain from its lots; then choose HOW to measure its period return —
+• bought BEFORE the period started → the ordinary period return from the price series
+• bought DURING the period → return since purchase instead, and the row is marked as shortened, because measuring a full year on something owned for a month would be nonsense
+The benchmark is measured over THE SAME window, shortened the same way, so the comparison is like for like. Beat-by is simply one minus the other, and is left blank when either side is missing.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5793,13 +6581,26 @@
           <t>MK-PF-E-002</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>per account: ending;  per category: earned = Σ(ending − beginning − net money in);  return = earned ÷ average value held</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+          <t>For each holding: fetch its price series; work out value, cost and gain from its lots; then choose HOW to measure its period return —
+• bought BEFORE the period started → the ordinary period return from the price series
+• bought DURING the period → return since purchase instead, and the row is marked as shortened, because measuring a full year on something owned for a month would be nonsense
+The benchmark is measured over THE SAME window, shortened the same way, so the comparison is like for like. Beat-by is simply one minus the other, and is left blank when either side is missing.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5841,13 +6642,23 @@
           <t>MK-PF-E-003</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>benchmark return = Σ(weight of each class × that class’s index return over the same window)</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+          <t>The same money-weighted blend, over each holding's own benchmark rather than the holding itself. Blending the benchmarks the same way is what makes "you beat it by" a fair statement rather than a comparison against a single index nobody holds.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5889,13 +6700,23 @@
           <t>MK-PF-E-004</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>r = (EMV − BMV − F) ÷ (BMV + Σ(Fᵢ × wᵢ)),  wᵢ = (days in window − days before flow i) ÷ days in window</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+          <t>A return that accounts for WHEN money moved in or out: each flow is weighted by how much of the window it was invested for. Refused, with the dollar walk shown instead, when the timing matters too much for one percentage to be honest.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5937,13 +6758,26 @@
           <t>MK-PF-E-005</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>stayed = value × (1 + return of what is held);  moved = value × (1 + return of the alternative);  difference = moved − stayed</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+          <t>Grow the amount by each holding's real price movement over the window, and subtract one from the other. Every figure comes from ACTUAL PAST PRICES.
+A move that would have lost money returns a real negative — it never quietly reports zero.
+Nothing to compare, or a history too short on either side → nothing at all.
+It is explicitly BACKWARD-looking: a fact about what did happen, never a suggestion about what to do next.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5985,13 +6819,26 @@
           <t>MK-PF-E-005</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>stayed = value × (1 + return of what is held);  moved = value × (1 + return of the alternative);  difference = moved − stayed</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+          <t>Grow the amount by each holding's real price movement over the window, and subtract one from the other. Every figure comes from ACTUAL PAST PRICES.
+A move that would have lost money returns a real negative — it never quietly reports zero.
+Nothing to compare, or a history too short on either side → nothing at all.
+It is explicitly BACKWARD-looking: a fact about what did happen, never a suggestion about what to do next.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6033,13 +6880,26 @@
           <t>MK-PF-E-005</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>stayed = value × (1 + return of what is held);  moved = value × (1 + return of the alternative);  difference = moved − stayed</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+          <t>Grow the amount by each holding's real price movement over the window, and subtract one from the other. Every figure comes from ACTUAL PAST PRICES.
+A move that would have lost money returns a real negative — it never quietly reports zero.
+Nothing to compare, or a history too short on either side → nothing at all.
+It is explicitly BACKWARD-looking: a fact about what did happen, never a suggestion about what to do next.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6074,12 +6934,14 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -6114,12 +6976,14 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -6154,12 +7018,14 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -6176,7 +7042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6186,9 +7052,11 @@
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="41" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6229,15 +7097,25 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Formula (mathematical)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Formula (in words)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -6279,13 +7157,24 @@
           <t>MK-PL-E-001</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>missing = the inputs with no answer;  counted = Σ(balances already in)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+          <t>Three things are needed: their age, what they expect to spend, and money that actually counts toward retirement.
+THAT LAST ONE IS A FOUNDER FINDING (2026-08-11). It used to accept ANY account with a balance, so someone whose only asset was the home they live in looked complete here — and then produced no odds at all, because the odds run on the money counted toward retirement, and a primary home is not. The question this asks now means the same thing the odds mean.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6327,13 +7216,24 @@
           <t>MK-PL-E-001</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>missing = the inputs with no answer;  counted = Σ(balances already in)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+          <t>Three things are needed: their age, what they expect to spend, and money that actually counts toward retirement.
+THAT LAST ONE IS A FOUNDER FINDING (2026-08-11). It used to accept ANY account with a balance, so someone whose only asset was the home they live in looked complete here — and then produced no odds at all, because the odds run on the money counted toward retirement, and a primary home is not. The question this asks now means the same thing the odds mean.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6375,13 +7275,23 @@
           <t>MK-PL-E-002</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>for each month: guaranteed total = Σ(streams live that month);  paycheck = guaranteed total + safe draw</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+          <t>Builds the retirement paycheck month by month: what is guaranteed that month, plus what can safely be drawn from savings.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6422,13 +7332,23 @@
           <t>MK-PL-E-002</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>for each month: guaranteed total = Σ(streams live that month);  paycheck = guaranteed total + safe draw</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+          <t>Builds the retirement paycheck month by month: what is guaranteed that month, plus what can safely be drawn from savings.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6470,13 +7390,23 @@
           <t>MK-PL-E-002</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>for each month: guaranteed total = Σ(streams live that month);  paycheck = guaranteed total + safe draw</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+          <t>Builds the retirement paycheck month by month: what is guaranteed that month, plus what can safely be drawn from savings.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6514,13 +7444,23 @@
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>paycheck = guaranteed income + draw from savings</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+          <t>Worked out on the screen itself, with no engine behind it — a place a second definition can appear.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6562,13 +7502,23 @@
           <t>MK-PL-E-003</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>count of scenarios saved</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+          <t>How many what-if scenarios have been saved.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6610,13 +7560,27 @@
           <t>MK-PL-E-004</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>the inputs one plan is built from: what is held, what will be spent, what is guaranteed, and what is still being saved</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+          <t>Gather everything the odds need. The person's own choices override every default, one by one.
+NO AGE MEANS NO ANSWER — the odds are never computed from a guessed age.
+SOCIAL SECURITY USES THE CHEQUE THE CHOSEN CLAIM AGE ACTUALLY PAYS. The figure on a statement is the age-67 amount; claiming at 62 pays about 70% of it. Using the statement figure regardless would overstate guaranteed income for everyone claiming early.
+Not eligible means ZERO guaranteed income, not a default.
+A LEGACY TARGET — money someone means to leave behind — is taken off the pot, but ONLY once they are retired. See the defect note.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6658,13 +7622,23 @@
           <t>MK-PL-E-005</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>spending in retirement a month = what is spent today × the share expected to continue</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+          <t>What the person said they expect to spend, adjusted for where they plan to live. Stated in TODAY'S dollars — the simulation inflates it to each future year, so inflating it here as well would count inflation twice.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6706,13 +7680,23 @@
           <t>MK-PL-E-006</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>each stream grows on its own rule: Social Security rises with inflation, a fixed pension does not</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+          <t>Each guaranteed stream grows on its own rule: Social Security rises with inflation, a fixed pension stays flat. They are never grown together.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6754,13 +7738,27 @@
           <t>MK-PL-E-004</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>the inputs one plan is built from: what is held, what will be spent, what is guaranteed, and what is still being saved</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+          <t>Gather everything the odds need. The person's own choices override every default, one by one.
+NO AGE MEANS NO ANSWER — the odds are never computed from a guessed age.
+SOCIAL SECURITY USES THE CHEQUE THE CHOSEN CLAIM AGE ACTUALLY PAYS. The figure on a statement is the age-67 amount; claiming at 62 pays about 70% of it. Using the statement figure regardless would overstate guaranteed income for everyone claiming early.
+Not eligible means ZERO guaranteed income, not a default.
+A LEGACY TARGET — money someone means to leave behind — is taken off the pot, but ONLY once they are retired. See the defect note.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6802,13 +7800,23 @@
           <t>MK-PL-E-007</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>start age = 73 for those born 1951–1959, 75 for those born 1960 or later;  Roth 401(k) is exempt</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+          <t>The age required withdrawals begin, from one dated table: 73 for those born 1951 to 1959, 75 for those born in 1960 or later. A Roth 401(k) is exempt.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6850,13 +7858,23 @@
           <t>MK-PL-E-008</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>required = balance on 31 December last year ÷ the life-expectancy factor for this age</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+          <t>The amount the law requires to be taken out this year: last 31 December's balance divided by the life-expectancy factor for the person's age.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6894,13 +7912,23 @@
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>still to take = required this year − taken so far</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+          <t>Worked out on the screen itself, with no engine behind it — a place a second definition can appear.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6942,13 +7970,23 @@
           <t>MK-PL-E-008</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>required = balance on 31 December last year ÷ the life-expectancy factor for this age</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+          <t>The amount the law requires to be taken out this year: last 31 December's balance divided by the life-expectancy factor for the person's age.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6990,13 +8028,24 @@
           <t>MK-NW-E-012</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>value = the balance last recorded;  age = today − date it was recorded</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+          <t>Months between the date the value was set and today. Six months or more → stale.
+A LIVE-PRICED account returns nothing: its value comes from today's prices, so staleness is not a question that applies to it. A value with no date recorded also returns nothing rather than being assumed fresh.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7038,13 +8087,23 @@
           <t>MK-PL-E-009</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>benefit at claim age = the statement amount at full retirement age × the claim factor for that age</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+          <t>Statement monthly amount × the claim factor for (claim age, birth year), rounded to whole dollars.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7086,13 +8145,24 @@
           <t>MK-PL-E-010</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>guaranteed income now = Σ(streams already being received)</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+          <t>Zero unless the person said retirement income is one of their current sources; otherwise the same total as above.
+The distinction stops a future pension being counted as money arriving now — which would overstate today's income and flatter every current figure built on it.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7134,13 +8204,23 @@
           <t>MK-PL-E-011</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>factor = 1 − 5/9% per month for the first 36 months early, − 5/12% per month beyond that; + 2/3% per month for each month claimed late up to 70</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+          <t>Months between the claim age and the full retirement age. Early: minus 5/9 of 1% per month for the first 36 months, minus 5/12 of 1% per month beyond. Late: plus 2/3 of 1% per month (8% a year) to 70. At the full retirement age exactly: 100%. · Statement monthly amount × the claim factor for (claim age, birth year), rounded to whole dollars.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7182,13 +8262,23 @@
           <t>MK-PL-E-012</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>lifetime total = monthly benefit × 12 × (life expectancy − claim age)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+          <t>The monthly Social Security check multiplied out to a life expectancy, so claiming early and claiming late can be compared in total dollars.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7230,13 +8320,23 @@
           <t>MK-PL-E-013</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>a stated example amount, shown labelled as an example</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+          <t>A worked example shown in place of a real Social Security statement, always labelled as such.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7278,13 +8378,23 @@
           <t>MK-PL-E-014</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>the value typed by the person</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+          <t>A number the person entered; no calculation.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7326,13 +8436,23 @@
           <t>MK-PL-E-015</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>extra tax ≈ Σ over bands of (amount converted falling in that band × its rate)</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+          <t>The extra tax a Roth conversion would cause: the converted amount is stacked on top of this year's income and taxed band by band.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7374,13 +8494,23 @@
           <t>MK-PL-E-016</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>pre-tax balance = Σ(balance of accounts whose tax type = pre-tax)</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+          <t>Adds the balances of accounts whose money has not been taxed yet — the pot a Roth move would come from.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7422,13 +8552,23 @@
           <t>MK-PL-E-014</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>the value typed by the person</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+          <t>A number the person entered; no calculation.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7470,13 +8610,29 @@
           <t>MK-NW-E-010</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>pot = balance × (1 + r)^n + Σ(contribution × (1 + r)^(n − year)),  n = years to retirement</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+          <t>TWO FIGURES, no random runs anywhere in this one — it is the straight-line check beside the 1,000-run odds.
+WHAT YOU WILL HAVE. Today's pot grown at your expected return for the years until you retire, plus every year's saving grown for however many years it has left. Worked at 6%: $600,000 today over 7 years becomes $902,000; $24,000 saved each of those years adds about $201,000; $1,103,000 in all.
+WHAT YOU WILL NEED — the target pot. Walk every retirement year one at a time, from the year you retire to the age you plan to. In each year: take that year's spending, take off the guaranteed income you receive that year, and that difference is what the pot must hand you. Bring each of those amounts back to a retirement-year value by dividing by your expected return once for every year you have to wait for it. Add them all up. That total is the pot that pays for the whole plan.
+Two rules ride along: spending rises with inflation every year, and so does Social Security, but a pension stays flat.
+WHY THE NUMBER IS SMALLER THAN THE SUM OF THE SPENDING. Money you do not need until year fifteen keeps earning until then, so you need less than fifteen years' spending set aside today.
+MONEY IS NEEDED AT THE START OF ITS YEAR. The first retirement year's spending is not discounted at all — January's groceries cannot be paid out of December's growth. Some published calculators charge each year at its END, which gives every year one more year of growth and reports a target about (1 + return) / (1 + inflation) smaller — roughly 3% lower at a 6% return and 2.5% inflation. Neither is wrong; ours is the cautious side, and the difference is a timing convention, not a disagreement about the arithmetic.
+HOW IT DIFFERS FROM THE 25 x YARDSTICK reported by the odds engine: this one knows how long you plan for and what your money earns; the yardstick knows neither.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7514,13 +8670,23 @@
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>difference = pot after the change − pot before it</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+          <t>Worked out on the screen itself, with no engine behind it — a place a second definition can appear.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7562,13 +8728,23 @@
           <t>MK-PL-E-017</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>the values typed by the person</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+          <t>Amounts the person entered; no calculation.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7610,13 +8786,27 @@
           <t>MK-PL-E-004</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>the inputs one plan is built from: what is held, what will be spent, what is guaranteed, and what is still being saved</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+          <t>Gather everything the odds need. The person's own choices override every default, one by one.
+NO AGE MEANS NO ANSWER — the odds are never computed from a guessed age.
+SOCIAL SECURITY USES THE CHEQUE THE CHOSEN CLAIM AGE ACTUALLY PAYS. The figure on a statement is the age-67 amount; claiming at 62 pays about 70% of it. Using the statement figure regardless would overstate guaranteed income for everyone claiming early.
+Not eligible means ZERO guaranteed income, not a default.
+A LEGACY TARGET — money someone means to leave behind — is taken off the pot, but ONLY once they are retired. See the defect note.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7658,13 +8848,25 @@
           <t>MK-NW-E-007</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>owed = Σ(remaining balance);  monthly debt payments = Σ(required payment of each debt)</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+          <t>Total the balances. Find the highest-rate debt. Add up separately the balances above the rate we treat as dangerous.
+TWO MONTHLY FIGURES ARE KEPT DELIBERATELY: the minimum that must be paid to stay current, and what is actually going out. Confusing them misstates affordability in one direction or the other.
+No debts gives zero and nothing to point at.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7706,13 +8908,23 @@
           <t>MK-PL-E-018</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>each month: balance ← balance × (1 + rate ÷ 12) − payment, until balance ≤ 0;  payoff month = the first month it does</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+          <t>Runs the debt forward month by month: interest is added, the payment is taken off, and the month the balance reaches zero is the payoff date.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7754,13 +8966,24 @@
           <t>MK-PL-E-010</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>guaranteed income now = Σ(streams already being received)</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+          <t>Zero unless the person said retirement income is one of their current sources; otherwise the same total as above.
+The distinction stops a future pension being counted as money arriving now — which would overstate today's income and flatter every current figure built on it.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7802,13 +9025,29 @@
           <t>MK-NW-E-010</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>pot = balance × (1 + r)^n + Σ(contribution × (1 + r)^(n − year)),  n = years to retirement</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+          <t>TWO FIGURES, no random runs anywhere in this one — it is the straight-line check beside the 1,000-run odds.
+WHAT YOU WILL HAVE. Today's pot grown at your expected return for the years until you retire, plus every year's saving grown for however many years it has left. Worked at 6%: $600,000 today over 7 years becomes $902,000; $24,000 saved each of those years adds about $201,000; $1,103,000 in all.
+WHAT YOU WILL NEED — the target pot. Walk every retirement year one at a time, from the year you retire to the age you plan to. In each year: take that year's spending, take off the guaranteed income you receive that year, and that difference is what the pot must hand you. Bring each of those amounts back to a retirement-year value by dividing by your expected return once for every year you have to wait for it. Add them all up. That total is the pot that pays for the whole plan.
+Two rules ride along: spending rises with inflation every year, and so does Social Security, but a pension stays flat.
+WHY THE NUMBER IS SMALLER THAN THE SUM OF THE SPENDING. Money you do not need until year fifteen keeps earning until then, so you need less than fifteen years' spending set aside today.
+MONEY IS NEEDED AT THE START OF ITS YEAR. The first retirement year's spending is not discounted at all — January's groceries cannot be paid out of December's growth. Some published calculators charge each year at its END, which gives every year one more year of growth and reports a target about (1 + return) / (1 + inflation) smaller — roughly 3% lower at a 6% return and 2.5% inflation. Neither is wrong; ours is the cautious side, and the difference is a timing convention, not a disagreement about the arithmetic.
+HOW IT DIFFERS FROM THE 25 x YARDSTICK reported by the odds engine: this one knows how long you plan for and what your money earns; the yardstick knows neither.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7850,13 +9089,24 @@
           <t>MK-XS-E-002</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>run 1,000 futures; in each year: balance ← balance × (1 + random return) − (spending − guaranteed income);  odds = futures that never run out ÷ 1,000</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+          <t>If age, spending and a pot are all known, run the simulation and report the chance. Otherwise report that it could not be answered — NOT a confident zero.
+The best-to-worst range re-runs the same plan at a lower and a higher return, so it reads as a range rather than a promise. It always contains the headline figure, and it is repeatable.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7898,13 +9148,23 @@
           <t>MK-PL-E-019</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>the age set by the person</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+          <t>An age the person set on a dial; no calculation.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7946,13 +9206,23 @@
           <t>MK-PL-E-020</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>future cost = today’s cost × (1 + education inflation)^years;  monthly needed = gap ÷ months until school starts</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+          <t>Grows today's cost of school by education inflation to the year it starts, then divides what is still missing by the months until then.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7994,13 +9264,23 @@
           <t>MK-PL-E-020</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>future cost = today’s cost × (1 + education inflation)^years;  monthly needed = gap ÷ months until school starts</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+          <t>Grows today's cost of school by education inflation to the year it starts, then divides what is still missing by the months until then.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8035,12 +9315,14 @@
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -8075,12 +9357,14 @@
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -8115,12 +9399,14 @@
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -8155,12 +9441,14 @@
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
         </is>
@@ -8195,12 +9483,14 @@
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -8217,7 +9507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -8227,9 +9517,11 @@
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="41" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8270,15 +9562,25 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Formula (mathematical)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Formula (in words)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -8320,13 +9622,23 @@
           <t>MK-CF-E-001</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>for month m: expected in = Σ(income landing in m);  planned out = Σ(bills and planned spending dated in m);  planned surplus = expected in − planned out</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+          <t>Lays the year out month by month so a month with a big bill in it can be seen before it arrives.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8368,13 +9680,23 @@
           <t>MK-CF-E-001</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>for month m: expected in = Σ(income landing in m);  planned out = Σ(bills and planned spending dated in m);  planned surplus = expected in − planned out</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+          <t>Lays the year out month by month so a month with a big bill in it can be seen before it arrives.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8411,13 +9733,23 @@
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>planned surplus = expected in − planned out</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+          <t>Worked out on the screen itself, with no engine behind it — a place a second definition can appear.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8459,13 +9791,23 @@
           <t>MK-XS-E-005</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>spent(bucket) = Σ(expenses dated in this month in that bucket, debt payments excluded);  remaining = planned − spent</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+          <t>Adds up this month’s logged expenses by bucket and sets each against what was planned. Debt payments are deliberately left out, because debt is tracked on its own.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8502,13 +9844,23 @@
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>surplus = money in − money out</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+          <t>Worked out on the screen itself, with no engine behind it — a place a second definition can appear.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8550,13 +9902,24 @@
           <t>MK-CF-E-002</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gross a year = salary + self-employment + bonus + equity vesting + rental + other;  net a month = (gross − tax withheld − pre-tax contributions) ÷ 12</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+          <t>Salary + tips + bonus + a signing amount + vesting equity + net rental income + other income (recurring and one-off, taxable and not) + retirement income currently being received.
+This is the figure every tax calculation and every savings-capacity figure is built on, which is why each part above has its own row.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8598,13 +9961,24 @@
           <t>MK-CF-E-002</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gross a year = salary + self-employment + bonus + equity vesting + rental + other;  net a month = (gross − tax withheld − pre-tax contributions) ÷ 12</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+          <t>Salary + tips + bonus + a signing amount + vesting equity + net rental income + other income (recurring and one-off, taxable and not) + retirement income currently being received.
+This is the figure every tax calculation and every savings-capacity figure is built on, which is why each part above has its own row.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8646,13 +10020,24 @@
           <t>MK-CF-E-002</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gross a year = salary + self-employment + bonus + equity vesting + rental + other;  net a month = (gross − tax withheld − pre-tax contributions) ÷ 12</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+          <t>Salary + tips + bonus + a signing amount + vesting equity + net rental income + other income (recurring and one-off, taxable and not) + retirement income currently being received.
+This is the figure every tax calculation and every savings-capacity figure is built on, which is why each part above has its own row.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8694,13 +10079,23 @@
           <t>MK-CF-E-003</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>equity a year ÷ the vest months it lands in, by the stated weights</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+          <t>Spreads stock that vests across the months it actually vests in, rather than smoothing it over the year.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8742,13 +10137,24 @@
           <t>MK-CF-E-004</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>rental net a year = rent received − running costs</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+          <t>(income − costs) each month, added across properties, × 12.
+A property that costs more than it earns REDUCES income rather than being floored at zero — a loss-making rental is a real fact about a plan.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8790,13 +10196,24 @@
           <t>MK-PL-E-010</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>guaranteed income now = Σ(streams already being received)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+          <t>Zero unless the person said retirement income is one of their current sources; otherwise the same total as above.
+The distinction stops a future pension being counted as money arriving now — which would overstate today's income and flatter every current figure built on it.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8838,13 +10255,23 @@
           <t>MK-CF-E-005</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>each payment recorded this month, with its date and source</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+          <t>Lists what has actually been received this month, rather than what was expected.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8886,13 +10313,23 @@
           <t>MK-CF-E-006</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>spent in a bucket = Σ(expenses this month in that bucket);  debt payments are excluded</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+          <t>If the person answered category by category, total each category into its bucket. If they gave three summary figures instead, use those. Nothing answered is zero — never a guessed household average, which would put a number in their plan that nobody chose.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8934,13 +10371,23 @@
           <t>MK-CF-E-006</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>spent in a bucket = Σ(expenses this month in that bucket);  debt payments are excluded</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+          <t>If the person answered category by category, total each category into its bucket. If they gave three summary figures instead, use those. Nothing answered is zero — never a guessed household average, which would put a number in their plan that nobody chose.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8982,13 +10429,24 @@
           <t>MK-CF-E-007</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>planned a month = Σ(each category’s planned amount);  remaining = planned − spent</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+          <t>The LARGER of two answers: the categories added up, or the single monthly figure they typed.
+The larger wins deliberately. Someone may answer both and the two rarely agree, and understating spending is the direction that FLATTERS a plan — it makes the odds look better than they are. Taking the larger errs toward the cautious side.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9030,13 +10488,23 @@
           <t>MK-CF-E-008</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>a bill is flagged when its amount is large relative to a typical month and it falls within the horizon shown</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+          <t>Points out the big one-off bills coming up, so they are not a surprise.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9078,13 +10546,23 @@
           <t>MK-CF-E-009</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>flagged when an expense is well above the usual amount for its category</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+          <t>Marks a single expense that sits well above what that category normally costs.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9126,13 +10604,23 @@
           <t>MK-XS-E-006</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>money in month m = salary(m) + tips(m) + rental ÷ 12 + bonus(m) + equity vesting(m) − withholding(m) − pre-tax contributions(m)</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+          <t>Builds twelve months of money in, one month at a time. Salary comes from the per-month table, equity lands in the months it vests, the bonus lands in its own month, and each month has its own withholding rate.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9174,13 +10662,23 @@
           <t>MK-CF-E-010</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>money out = Σ(expenses this month) + Σ(required debt payments)</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+          <t>If the person answered category by category, total each category into its bucket. If they gave three summary figures instead, use those. Nothing answered is zero — never a guessed household average, which would put a number in their plan that nobody chose. · Due in full → 0. It is a dated bill, and calling it a monthly payment overstates what a person is committed to. Otherwise the LARGER of the minimum and whatever payment they have chosen, so overpaying on purpose shows up.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9218,13 +10716,23 @@
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>free to use = money in − money out − Σ(monthly amounts the Plan committed)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+          <t>Worked out on the screen itself, with no engine behind it — a place a second definition can appear.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9266,13 +10774,23 @@
           <t>MK-CF-E-011</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Σ(monthly amount of each goal the Plan has committed to)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+          <t>The monthly amounts the Plan has already promised to goals, so cash flow can show what is genuinely free.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9314,13 +10832,29 @@
           <t>MK-NW-E-010</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>pot = balance × (1 + r)^n + Σ(contribution × (1 + r)^(n − year)),  n = years to retirement</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+          <t>TWO FIGURES, no random runs anywhere in this one — it is the straight-line check beside the 1,000-run odds.
+WHAT YOU WILL HAVE. Today's pot grown at your expected return for the years until you retire, plus every year's saving grown for however many years it has left. Worked at 6%: $600,000 today over 7 years becomes $902,000; $24,000 saved each of those years adds about $201,000; $1,103,000 in all.
+WHAT YOU WILL NEED — the target pot. Walk every retirement year one at a time, from the year you retire to the age you plan to. In each year: take that year's spending, take off the guaranteed income you receive that year, and that difference is what the pot must hand you. Bring each of those amounts back to a retirement-year value by dividing by your expected return once for every year you have to wait for it. Add them all up. That total is the pot that pays for the whole plan.
+Two rules ride along: spending rises with inflation every year, and so does Social Security, but a pension stays flat.
+WHY THE NUMBER IS SMALLER THAN THE SUM OF THE SPENDING. Money you do not need until year fifteen keeps earning until then, so you need less than fifteen years' spending set aside today.
+MONEY IS NEEDED AT THE START OF ITS YEAR. The first retirement year's spending is not discounted at all — January's groceries cannot be paid out of December's growth. Some published calculators charge each year at its END, which gives every year one more year of growth and reports a target about (1 + return) / (1 + inflation) smaller — roughly 3% lower at a 6% return and 2.5% inflation. Neither is wrong; ours is the cautious side, and the difference is a timing convention, not a disagreement about the arithmetic.
+HOW IT DIFFERS FROM THE 25 x YARDSTICK reported by the odds engine: this one knows how long you plan for and what your money earns; the yardstick knows neither.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9362,13 +10896,23 @@
           <t>MK-CF-E-012</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>guaranteed income a month = Social Security + pension + annuity + any other stated stream</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+          <t>Add Social Security, pension, withdrawals, required minimum distributions, annuities and other — each converted to a monthly figure from however it was entered (yearly, quarterly, monthly).</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9410,13 +10954,24 @@
           <t>MK-PL-E-010</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>guaranteed income now = Σ(streams already being received)</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+          <t>Zero unless the person said retirement income is one of their current sources; otherwise the same total as above.
+The distinction stops a future pension being counted as money arriving now — which would overstate today's income and flatter every current figure built on it.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9458,13 +11013,23 @@
           <t>MK-CF-E-013</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>see the by-month grid</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+          <t>The month-by-month view of money in and money out.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9506,13 +11071,23 @@
           <t>MK-CF-E-014</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>paycheck a month = guaranteed income + the draw from savings</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+          <t>Builds the monthly paycheck in retirement: what is guaranteed that month, plus what can be drawn from savings without breaking the plan.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9554,13 +11129,24 @@
           <t>MK-CF-E-002</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>gross a year = salary + self-employment + bonus + equity vesting + rental + other;  net a month = (gross − tax withheld − pre-tax contributions) ÷ 12</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+          <t>Salary + tips + bonus + a signing amount + vesting equity + net rental income + other income (recurring and one-off, taxable and not) + retirement income currently being received.
+This is the figure every tax calculation and every savings-capacity figure is built on, which is why each part above has its own row.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9602,13 +11188,23 @@
           <t>MK-CF-E-015</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>each bill falls on its stated day;  the month’s bills = Σ(amounts due in that month)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+          <t>Places each recurring bill on the day of the month it falls, so the shape of the month can be seen.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9643,12 +11239,14 @@
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -9683,12 +11281,14 @@
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -9723,12 +11323,14 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -9763,12 +11365,14 @@
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -9803,12 +11407,14 @@
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
         </is>
@@ -9825,7 +11431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -9835,9 +11441,11 @@
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="41" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9878,15 +11486,25 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Formula (mathematical)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Formula (in words)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -9928,13 +11546,23 @@
           <t>MK-MN-E-001</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>total = Σ(each big cost);  each one lands in the year it is dated</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+          <t>Adds up the one-off costs the person has told us about, each sitting in the year it is expected.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9976,13 +11604,23 @@
           <t>MK-MN-E-001</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>total = Σ(each big cost);  each one lands in the year it is dated</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+          <t>Adds up the one-off costs the person has told us about, each sitting in the year it is expected.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10024,13 +11662,23 @@
           <t>MK-MN-E-002</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>room left = the year’s limit − what has already gone in;  per month = room left ÷ months left in the year</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+          <t>Takes the year's legal limit for the account, subtracts what has already gone in, and divides what is left by the months remaining.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10072,13 +11720,23 @@
           <t>MK-MN-E-002</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>room left = the year’s limit − what has already gone in;  per month = room left ÷ months left in the year</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+          <t>Takes the year's legal limit for the account, subtracts what has already gone in, and divides what is left by the months remaining.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10116,13 +11774,23 @@
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>per month = room left ÷ months left in the year</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+          <t>Worked out on the screen itself, with no engine behind it — a place a second definition can appear.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10164,13 +11832,23 @@
           <t>MK-MN-E-003</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>use = balance ÷ credit limit</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+          <t>The balance on the card against its limit — the share of the line being used.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10212,13 +11890,24 @@
           <t>MK-CF-E-007</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>planned a month = Σ(each category’s planned amount);  remaining = planned − spent</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+          <t>The LARGER of two answers: the categories added up, or the single monthly figure they typed.
+The larger wins deliberately. Someone may answer both and the two rarely agree, and understating spending is the direction that FLATTERS a plan — it makes the odds look better than they are. Taking the larger errs toward the cautious side.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10260,13 +11949,23 @@
           <t>MK-MN-E-004</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>typical free cash a month = median over recent months of (money in − money out)</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+          <t>Looks at recent months and takes the typical amount left after money in and money out — what could realistically be saved, not the best month.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10308,13 +12007,23 @@
           <t>MK-MN-E-005</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>to go = target − saved;  progress = saved ÷ target</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+          <t>What has been put aside against the target, and what is still to go.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10356,13 +12065,23 @@
           <t>MK-MN-E-006</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>set aside a month = Σ(each non-monthly cost ÷ months until it falls due)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+          <t>Takes the costs that do not arrive monthly and spreads each one across the months until it falls due.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10404,13 +12123,24 @@
           <t>MK-CF-E-002</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>gross a year = salary + self-employment + bonus + equity vesting + rental + other;  net a month = (gross − tax withheld − pre-tax contributions) ÷ 12</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+          <t>Salary + tips + bonus + a signing amount + vesting equity + net rental income + other income (recurring and one-off, taxable and not) + retirement income currently being received.
+This is the figure every tax calculation and every savings-capacity figure is built on, which is why each part above has its own row.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10452,13 +12182,24 @@
           <t>MK-CF-E-002</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>gross a year = salary + self-employment + bonus + equity vesting + rental + other;  net a month = (gross − tax withheld − pre-tax contributions) ÷ 12</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+          <t>Salary + tips + bonus + a signing amount + vesting equity + net rental income + other income (recurring and one-off, taxable and not) + retirement income currently being received.
+This is the figure every tax calculation and every savings-capacity figure is built on, which is why each part above has its own row.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10500,13 +12241,24 @@
           <t>MK-CF-E-002</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>gross a year = salary + self-employment + bonus + equity vesting + rental + other;  net a month = (gross − tax withheld − pre-tax contributions) ÷ 12</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+          <t>Salary + tips + bonus + a signing amount + vesting equity + net rental income + other income (recurring and one-off, taxable and not) + retirement income currently being received.
+This is the figure every tax calculation and every savings-capacity figure is built on, which is why each part above has its own row.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10548,13 +12300,23 @@
           <t>MK-MN-E-007</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>match a year = the employer’s stated rate × pay, capped at the stated limit</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+          <t>Either a percentage of what the person contributes to their 401(k), or a flat monthly amount — whichever way they described it.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10596,13 +12358,23 @@
           <t>MK-HM-E-003</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>each insight scores its own dollars at stake; the list = the highest few, ranked</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+          <t>Works out what is worth saying today, puts a dollar amount against each, and shows the few that matter most.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10644,13 +12416,23 @@
           <t>MK-MN-E-008</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>investable = cash + investments  (excludes home and belongings)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+          <t>Cash + investments — everything except the house and the car. Selling the roof you live under is not a plan, so physical assets are excluded by CLASS, not by tax type. · Add up the balances of every account whose class is Cash. Under the founder's 2026-08-04 rule that means checking, savings, high-yield savings and the uninvested sweep at a broker — and NOT money-market funds, which pay dividends and are measured with the investments.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10692,13 +12474,23 @@
           <t>MK-MN-E-009</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>need = income to replace × years + debts + goals + final expenses;  gap = need − cover already held</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+          <t>Adds the income that would need replacing for the chosen number of years to debts, goals and final expenses, then subtracts cover already held.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10740,13 +12532,23 @@
           <t>MK-MN-E-009</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>need = income to replace × years + debts + goals + final expenses;  gap = need − cover already held</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+          <t>Adds the income that would need replacing for the chosen number of years to debts, goals and final expenses, then subtracts cover already held.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10788,13 +12590,23 @@
           <t>MK-MN-E-009</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>need = income to replace × years + debts + goals + final expenses;  gap = need − cover already held</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+          <t>Adds the income that would need replacing for the chosen number of years to debts, goals and final expenses, then subtracts cover already held.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10836,13 +12648,23 @@
           <t>MK-MN-E-010</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>runway in months = cash ÷ essentials a month;  target = months wanted × essentials a month</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+          <t>How many months of essential bills the cash on hand would cover with no pay coming in.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10884,13 +12706,23 @@
           <t>MK-CF-E-006</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>spent in a bucket = Σ(expenses this month in that bucket);  debt payments are excluded</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+          <t>If the person answered category by category, total each category into its bucket. If they gave three summary figures instead, use those. Nothing answered is zero — never a guessed household average, which would put a number in their plan that nobody chose.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10932,13 +12764,23 @@
           <t>MK-MN-E-011</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>total = Σ(recorded value of each alternative holding)</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+          <t>Adds up the recorded value of every alternative holding — the things with no market price of their own.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10980,13 +12822,23 @@
           <t>MK-MN-E-012</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>estimated growth a year = Σ(value × its stated growth rate)</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+          <t>Applies each alternative holding's own stated growth rate to its value and adds the results. An estimate, and labelled as one.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11028,13 +12880,23 @@
           <t>MK-MN-E-013</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>cash after = cash − the shock;  runway after = cash after ÷ essentials a month</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+          <t>Takes a one-off hit out of the cash on hand and shows what would be left and how many months of essentials it would cover.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11076,13 +12938,23 @@
           <t>MK-MN-E-013</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>cash after = cash − the shock;  runway after = cash after ÷ essentials a month</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+          <t>Takes a one-off hit out of the cash on hand and shows what would be left and how many months of essentials it would cover.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11124,13 +12996,24 @@
           <t>MK-CF-E-007</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>planned a month = Σ(each category’s planned amount);  remaining = planned − spent</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+          <t>The LARGER of two answers: the categories added up, or the single monthly figure they typed.
+The larger wins deliberately. Someone may answer both and the two rarely agree, and understating spending is the direction that FLATTERS a plan — it makes the odds look better than they are. Taking the larger errs toward the cautious side.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11172,13 +13055,23 @@
           <t>MK-MN-E-014</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>taxable income = gross income − pre-tax contributions − the deduction for the filing status and age</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+          <t>gross − the deduction for that filing status: $16,100 single · $32,200 married · $24,150 head of household.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11220,13 +13113,23 @@
           <t>MK-MN-E-014</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>taxable income = gross income − pre-tax contributions − the deduction for the filing status and age</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+          <t>gross − the deduction for that filing status: $16,100 single · $32,200 married · $24,150 head of household.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11268,13 +13171,23 @@
           <t>MK-MN-E-002</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>room left = the year’s limit − what has already gone in;  per month = room left ÷ months left in the year</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+          <t>Takes the year's legal limit for the account, subtracts what has already gone in, and divides what is left by the months remaining.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11316,13 +13229,23 @@
           <t>MK-MN-E-015</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>flagged when money left an account and has not arrived anywhere else</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+          <t>Notices money leaving an account so it can be asked about rather than quietly lost.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11357,12 +13280,14 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -11397,12 +13322,14 @@
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -11437,12 +13364,14 @@
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -11477,12 +13406,14 @@
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -11517,12 +13448,14 @@
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -11557,12 +13490,14 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -11597,12 +13532,14 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -17,6 +17,7 @@
     <sheet name="cashflow" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="menu" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="inputs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="database" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -616,290 +617,302 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>TAB — database</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>What the app saves in the cloud: where each thing is stored, what it holds, which figures depend on it, how often it is written and at what grain. Also names what is deliberately NOT saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>TAB — inputs</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>The raw values the engines need before any calculation happens.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN — Metric ID</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>The identifier of the figure, per moneykeel_naming_spec_unique-identifier_v01.md. Given once, never changed, never reused.</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Parent Screen Name</t>
+          <t>COLUMN — Metric ID</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>One of: Home, Networth, Performance, Cashflow, Plan, Menu. Menu means reachable only from the menu.</t>
+          <t>The identifier of the figure, per moneykeel_naming_spec_unique-identifier_v01.md. Given once, never changed, never reused.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Secondary Screen Name</t>
+          <t>COLUMN — Parent Screen Name</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>The screen reached from the parent, or NA when the figure is on the parent screen itself.</t>
+          <t>One of: Home, Networth, Performance, Cashflow, Plan, Menu. Menu means reachable only from the menu.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name on Screen</t>
+          <t>COLUMN — Secondary Screen Name</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>The label copied exactly as it is worded on screen, including capitals. Where a figure wears different labels on different screens, all are listed.</t>
+          <t>The screen reached from the parent, or NA when the figure is on the parent screen itself.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name of Underlying Metric</t>
+          <t>COLUMN — Name on Screen</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>The metric's name in the code.</t>
+          <t>The label copied exactly as it is worded on screen, including capitals. Where a figure wears different labels on different screens, all are listed.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name of Underlying Engine</t>
+          <t>COLUMN — Name of Underlying Metric</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>The engine that produces the figure. NOT IN OLD MASTER means the engine exists in the code but has no row in the old master file.</t>
+          <t>The metric's name in the code.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (mathematical)</t>
+          <t>COLUMN — Name of Underlying Engine</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
+          <t>The engine that produces the figure. NOT IN OLD MASTER means the engine exists in the code but has no row in the old master file.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (in words)</t>
+          <t>COLUMN — Formula (mathematical)</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
+          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Engine ID</t>
+          <t>COLUMN — Formula (in words)</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
+          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Your name for it (72-metric file)</t>
+          <t>COLUMN — Engine ID</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
+          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Core screen?</t>
+          <t>COLUMN — Your name for it (72-metric file)</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Whether the screen is part of the 55-70 core, the agreed first scope.</t>
+          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>COLUMN — Core screen?</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Whether the screen is part of the 55-70 core, the agreed first scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>COLUMN — Row status</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>VERIFIED with its date means a person read the screen and confirmed the chain. NOT STARTED means the screen has not been read yet. Nothing in between is claimed.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
-      <c r="B29" s="3" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN — Input ID</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>The identifier of a raw input, per the same standard.</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Variable name</t>
+          <t>COLUMN — Input ID</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>What the raw value is called.</t>
+          <t>The identifier of a raw input, per the same standard.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Source</t>
+          <t>COLUMN — Variable name</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
+          <t>What the raw value is called.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Which metric uses it</t>
+          <t>COLUMN — Source</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Every metric identifier that depends on this input.</t>
+          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>COLUMN — Which metric uses it</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Every metric identifier that depends on this input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>COLUMN — Which engine uses it</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Every engine identifier that reads this input.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-      <c r="B35" s="3" t="inlineStr"/>
-    </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Complies with — naming</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Complies with — identifiers</t>
+          <t>Complies with — naming</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>Complies with — identifiers</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>Complies with — objectives</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>MoneyKeel/documents/standards/moneykeel_calc_spec_objectives-and-verification_v01.md</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="3" t="inlineStr"/>
-    </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>COVERAGE — screens read so far</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>COVERAGE — screens read so far</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
           <t>COVERAGE — what that means</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Every screen in the app is listed on its tab. Only Home carries figures so far; the rest are marked NOT STARTED. A rising count is not completeness while screens remain unread.</t>
         </is>
@@ -1948,6 +1961,1102 @@
       <c r="F32" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Where it is stored</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Field name in the database</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>What it holds</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Metric or input it serves</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>How often it is written</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Grain — one row per what</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Encrypted?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>users/{uid}</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>appStateEnc</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>THE WHOLE app state, encrypted on the device before it leaves it. Everything below lives inside this one field.</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>every metric in this file, through the inputs tab</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2 seconds after any change in the app, the whole payload rewritten</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>ONE document per person — or per household when two people share</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Yes — the server cannot read it</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>users/{uid}</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>keyEnvelope</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>The encryption key, wrapped by the password and by the recovery code.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>when the password or recovery code is set or changed</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>one per person</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>the key itself is wrapped, never stored bare</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>users/{uid}</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>appState</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>The old plaintext copy from before encryption. Deleted on the first save by an updated app.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>never written now; removed on first save</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>one per person</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>No — which is why it is being removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>users/{uid}</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>householdId</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Whose document this person reads and writes — their own, or the partner who invited them.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>when an invite is redeemed</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>one per person</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>households/{owner}/members/{member}</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>code, householdId</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>The record that a partner joined a household, bound to a real invite.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>once, when the invite is redeemed</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>one per member</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>invites/{code}</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>householdId</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>An invite code and the household it points at.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>when an invite is created</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>one per invite</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>feedback/{doc}</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>the message</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Feedback sent from inside the app.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>when feedback is sent</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>one per message</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>snaptrade_users/{uid}</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>the connection record</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>The link to the brokerage connection service.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>when an account is connected</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>one per person</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>inside appStateEnc</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>assetAccounts</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Every account: its name, institution, balance, class and where the figure came from.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>account balance · account type · institution</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>with every save</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>one entry per account</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>inside the encrypted blob</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>inside appStateEnc</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>liabilities</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Every debt: balance, rate, minimum payment, due day.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>debt balance · debt interest rate · debt minimum payment</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>with every save</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>one entry per debt</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>inside the encrypted blob</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>inside appStateEnc</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>investments</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Holdings: ticker, quantity, price paid, lots.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>holding quantity · purchase price and date</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>with every save</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>one entry per holding</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>inside the encrypted blob</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>inside appStateEnc</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>expenses</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Logged spending: date, amount, category, store.</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>logged spending</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>with every save</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>one entry per expense</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>inside the encrypted blob</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>inside appStateEnc</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>incomes · recurringIncomes</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Money received and the sources that repeat.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>salary and other income</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>with every save</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>one entry per payment or source</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>inside the encrypted blob</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>inside appStateEnc</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>recurringExpenses</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Bills that repeat, and the day they fall.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>logged spending · the bill calendar</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>with every save</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>one entry per bill</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>inside the encrypted blob</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>inside appStateEnc</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>monthlySnapshots</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Net worth as it stood at each month end.</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>the trend line · beginning values</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>once a month, on the first open of a new month</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>one entry per month</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>inside the encrypted blob</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>inside appStateEnc</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>nwDaily</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Net worth captured when the app is opened.</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>the trend line · change in net worth</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>once a day, on the first open</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>one entry per day</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>inside the encrypted blob</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>inside appStateEnc</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>onboardingProfile</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>What the person told us at setup: birth year, retirement age, spending, Social Security, pension, filing status.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>birth year · retirement age · monthly spending · Social Security · pension · filing status</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>with every save</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>one per person</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>inside the encrypted blob</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>inside appStateEnc</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>retirementAssumptions</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>The plan's settings: return, claim age, contributions, draw.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>assumed return · Social Security claim age</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>with every save</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>one per person</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>inside the encrypted blob</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>inside appStateEnc</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>retirementScenarios</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Saved what-ifs.</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>the saved scenarios count</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>when a scenario is saved</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>one entry per scenario</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>inside the encrypted blob</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>inside appStateEnc</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>bigCosts</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>One-off costs ahead, with the year each falls.</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>big costs</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>with every save</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>one entry per cost</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>inside the encrypted blob</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>inside appStateEnc</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>goals · selectedGoals</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Goals: target, saved so far, date.</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>goals</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>with every save</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>one entry per goal</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>inside the encrypted blob</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>inside appStateEnc</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>budgetCategories · monthlyBudgetTarget · allocatedByMonth</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>The plan for spending, by category and by month.</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>typical monthly essentials · planned spending</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>with every save</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>one entry per category or month</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>inside the encrypted blob</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>inside appStateEnc</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>benchmarkReturns</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>The index returns the comparison uses.</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>benchmark return</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>when they are fetched</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>one entry per index and period</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>inside the encrypted blob</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>inside appStateEnc</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>snaptradeConnections</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Which brokerages are connected.</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>when a connection changes</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>one entry per connection</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>inside the encrypted blob</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>inside appStateEnc</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>estatePlan · badges · xp · streak · lastCheckIn</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Estate notes and the encouragement counters.</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>with every save</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>one per person</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>inside the encrypted blob</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>NOT SAVED</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>prices</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Prices are fetched fresh and held only on the device.</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>holding price · price fetched at</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>never written to the cloud</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>NOT SAVED</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>economic figures (inflation, the 10-year yield)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Fetched from a feed each time; deliberately left out of the sync.</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>inflation rate</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>never written to the cloud</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>NOT SAVED</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>transactions from a download</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>The activity read from an institution file stays on the device.</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>transaction amount · date · words</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>never written to the cloud</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -1975,7 +1975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2952,109 +2952,183 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>NOT SAVED</t>
+          <t>NOT SAVED — DEVICE ONLY</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>prices</t>
+          <t>snapshotDays</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Prices are fetched fresh and held only on the device.</t>
+          <t>THE DAILY RECORD: for each day, every account and every holding — units, price and value kept apart. This is what a beginning value is READ from instead of being back-solved.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>holding price · price fetched at</t>
+          <t>beginning value · change in account value · the performance walk</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>never written to the cloud</t>
+          <t>once a day, on the first open</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>one entry per day, per account, per holding</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>not sent at all</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>NOT SAVED</t>
+          <t>NOT SAVED — DEVICE ONLY</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>economic figures (inflation, the 10-year yield)</t>
+          <t>invDaily</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Fetched from a feed each time; deliberately left out of the sync.</t>
+          <t>Cash + investments captured daily — the baseline the Net worth return line is measured from.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>inflation rate</t>
+          <t>Return on cash + investments</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>never written to the cloud</t>
+          <t>once a day, on the first open</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>one entry per day</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>not sent at all</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
+          <t>NOT SAVED — DEVICE ONLY</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>transactions</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>The append-only ledger read from institution downloads: every buy, sell, contribution, withdrawal, dividend and interest line. Read by 32 places in the app.</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>contributions · withdrawals · income · realised gain · the change walk</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>when a file is imported or a connection syncs</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>one entry per transaction</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>not sent at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t>NOT SAVED</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>transactions from a download</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>The activity read from an institution file stays on the device.</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>transaction amount · date · words</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>prices</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Prices are fetched fresh and held only on the device.</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>holding price · price fetched at</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>never written to the cloud</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>NOT SAVED</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>economic figures (inflation, the 10-year yield)</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Fetched from a feed each time; deliberately left out of the sync.</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>inflation rate</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>never written to the cloud</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -469,450 +469,486 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Date file created</t>
+          <t>STANDING DECISION — how numbers are held and shown</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>Every number is held as a float internally. Decimals are SHOWN only for prices of stocks, bonds and options, for interest and dividend rates, and for expenses; everything else displays whole dollars. Rounding happens once, at the edge, never in the middle. Founder, 2026-08-22.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Date file last modified</t>
+          <t>Date file created</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22  (stamped by the build, not typed; unchanged when the file is only read)</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Date file last modified</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24  (stamped by the build, not typed; unchanged when the file is only read)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>Objective of this file</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>One row for every figure a person reads on screen, tied to the metric behind it, the engine that produces it, and the identifier that joins them — so a wrong number can be traced from the label on screen to its engine and formula in a minute. Serves objectives 3 and 4.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr"/>
-    </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TAB — Specification</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Everything a row must carry before its calculation can be written in code. The index tabs say what exists and where it is shown; this tab says what is still needed to say what each number IS.</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TAB — Reference</t>
+          <t>TAB — Specification</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>This tab. What the file is, what each tab holds, what each column means, and what it must comply with.</t>
+          <t>Everything a row must carry before its calculation can be written in code. The index tabs say what exists and where it is shown; this tab says what is still needed to say what each number IS.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TAB — multiple_screens</t>
+          <t>TAB — Reference</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Figures shown on more than one parent screen. A figure lives here ONCE, with every screen and every label it wears listed, so the same figure can never have two definitions.</t>
+          <t>This tab. What the file is, what each tab holds, what each column means, and what it must comply with.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TAB — home</t>
+          <t>TAB — multiple_screens</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Figures shown only on Home and the screens reached from it.</t>
+          <t>Figures shown on more than one parent screen. A figure lives here ONCE, with every screen and every label it wears listed, so the same figure can never have two definitions.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TAB — networth</t>
+          <t>TAB — home</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Figures shown only on Net worth and the screens reached from it.</t>
+          <t>Figures shown only on Home and the screens reached from it.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TAB — performance</t>
+          <t>TAB — networth</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Figures shown only on Performance and the screens reached from it.</t>
+          <t>Figures shown only on Net worth and the screens reached from it.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TAB — plan</t>
+          <t>TAB — performance</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Figures shown only on Plan and the screens reached from it.</t>
+          <t>Figures shown only on Performance and the screens reached from it.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TAB — cashflow</t>
+          <t>TAB — plan</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Figures shown only on Cash flow and the screens reached from it.</t>
+          <t>Figures shown only on Plan and the screens reached from it.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TAB — menu</t>
+          <t>TAB — cashflow</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Screens reachable only from the menu, and the figures on them.</t>
+          <t>Figures shown only on Cash flow and the screens reached from it.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TAB — database</t>
+          <t>TAB — menu</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>What the app saves in the cloud: where each thing is stored, what it holds, which figures depend on it, how often it is written and at what grain. Also names what is deliberately NOT saved.</t>
+          <t>Screens reachable only from the menu, and the figures on them.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>TAB — database</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>What the app saves in the cloud: where each thing is stored, what it holds, which figures depend on it, how often it is written and at what grain. Also names what is deliberately NOT saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>TAB — inputs</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>The raw values the engines need before any calculation happens.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr"/>
-    </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN — Metric ID</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>The identifier of the figure, per moneykeel_naming_spec_unique-identifier_v01.md. Given once, never changed, never reused.</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Parent Screen Name</t>
+          <t>COLUMN — Metric ID</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>One of: Home, Networth, Performance, Cashflow, Plan, Menu. Menu means reachable only from the menu.</t>
+          <t>The identifier of the figure, per moneykeel_naming_spec_unique-identifier_v01.md. Given once, never changed, never reused.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Secondary Screen Name</t>
+          <t>COLUMN — Parent Screen Name</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>The screen reached from the parent, or NA when the figure is on the parent screen itself.</t>
+          <t>One of: Home, Networth, Performance, Cashflow, Plan, Menu. Menu means reachable only from the menu.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name on Screen</t>
+          <t>COLUMN — Secondary Screen Name</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>The label copied exactly as it is worded on screen, including capitals. Where a figure wears different labels on different screens, all are listed.</t>
+          <t>The screen reached from the parent, or NA when the figure is on the parent screen itself.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name of Underlying Metric</t>
+          <t>COLUMN — Name on Screen</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>The metric's name in the code.</t>
+          <t>The label copied exactly as it is worded on screen, including capitals. Where a figure wears different labels on different screens, all are listed.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name of Underlying Engine</t>
+          <t>COLUMN — Name of Underlying Metric</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>The engine that produces the figure. NOT IN OLD MASTER means the engine exists in the code but has no row in the old master file.</t>
+          <t>The metric's name in the code.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (mathematical)</t>
+          <t>COLUMN — Name of Underlying Engine</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
+          <t>The engine that produces the figure. NOT IN OLD MASTER means the engine exists in the code but has no row in the old master file.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (in words)</t>
+          <t>COLUMN — Errors or findings to address</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
+          <t>What is known to be wrong or unproved about this figure, in plain English. Blank means nothing is on record yet — not that nothing is wrong.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Engine ID</t>
+          <t>COLUMN — Decisions made</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
+          <t>The rulings that govern this figure, and why. The standing display and rounding rule applies to every row and is stated once at the top of this tab.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Your name for it (72-metric file)</t>
+          <t>COLUMN — Formula (mathematical)</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
+          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Core screen?</t>
+          <t>COLUMN — Formula (in words)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Whether the screen is part of the 55-70 core, the agreed first scope.</t>
+          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Row status</t>
+          <t>COLUMN — Engine ID</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>VERIFIED with its date means a person read the screen and confirmed the chain. NOT STARTED means the screen has not been read yet. Nothing in between is claimed.</t>
+          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
-      <c r="B30" s="3" t="inlineStr"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>COLUMN — Your name for it (72-metric file)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Input ID</t>
+          <t>COLUMN — Core screen?</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>The identifier of a raw input, per the same standard.</t>
+          <t>Whether the screen is part of the 55-70 core, the agreed first scope.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Variable name</t>
+          <t>COLUMN — Row status</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>What the raw value is called.</t>
+          <t>VERIFIED with its date means a person read the screen and confirmed the chain. NOT STARTED means the screen has not been read yet. Nothing in between is claimed.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN — Source</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Which metric uses it</t>
+          <t>COLUMN — Input ID</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Every metric identifier that depends on this input.</t>
+          <t>The identifier of a raw input, per the same standard.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Which engine uses it</t>
+          <t>COLUMN — Variable name</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Every engine identifier that reads this input.</t>
+          <t>What the raw value is called.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
-      <c r="B36" s="3" t="inlineStr"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>COLUMN — Source</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Complies with — naming</t>
+          <t>COLUMN — Which metric uses it</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
+          <t>Every metric identifier that depends on this input.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Complies with — identifiers</t>
+          <t>COLUMN — Which engine uses it</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+          <t>Every engine identifier that reads this input.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Complies with — objectives</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>MoneyKeel/documents/standards/moneykeel_calc_spec_objectives-and-verification_v01.md</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="3" t="inlineStr"/>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Complies with — naming</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>COVERAGE — screens read so far</t>
+          <t>Complies with — identifiers</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>Complies with — objectives</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/standards/moneykeel_calc_spec_objectives-and-verification_v01.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>COVERAGE — screens read so far</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
           <t>COVERAGE — what that means</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Every screen in the app is listed on its tab. Only Home carries figures so far; the rest are marked NOT STARTED. A rising count is not completeness while screens remain unread.</t>
         </is>
@@ -3157,9 +3193,11 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="41" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="37" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="41" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3385,7 +3423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3397,9 +3435,11 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="41" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="37" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="41" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3450,15 +3490,25 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Errors or findings to address</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Decisions made</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -3514,10 +3564,16 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+          <t>Assets minus debts, computed each time and never stored as a third number that could disagree with its own halves. A genuine negative is shown, never floored at zero.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3570,13 +3626,23 @@
 The best-to-worst range re-runs the same plan at a lower and a higher return, so it reads as a range rather than a promise. It always contains the headline figure, and it is repeatable.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>The odds shown on Home, Plan and Cash flow are rounded to the nearest 5, while the compare tables still show them exact. One figure, two precisions — founder's open question.</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+          <t>One thousand futures, and the odds are rounded to the nearest 5. A genuine 100 or 0 is shown literally; 98 shows as 95, never as 100 (fix B6). The best-to-worst band was removed.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3629,12 +3695,14 @@
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3691,12 +3759,14 @@
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3749,12 +3819,14 @@
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3807,12 +3879,14 @@
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3861,12 +3935,14 @@
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3883,7 +3959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3895,9 +3971,11 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="41" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="37" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="41" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3948,15 +4026,25 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Errors or findings to address</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Decisions made</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -4009,13 +4097,19 @@
 Never fetched, unreadable, or dated in the future → STALE. Silence is not good news.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Prices are never synced, so freshness is per device. Two devices can legitimately disagree about how current a value is.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4068,12 +4162,14 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4126,12 +4222,14 @@
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4180,12 +4278,14 @@
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4222,12 +4322,14 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -4264,12 +4366,14 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -4306,12 +4410,14 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -4348,12 +4454,14 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -4390,12 +4498,14 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
         </is>
@@ -4412,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4424,9 +4534,11 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="41" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="37" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="41" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4477,15 +4589,25 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Errors or findings to address</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Decisions made</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -4540,13 +4662,19 @@
 THE LIMIT THAT MATTERS, and it is the mechanism behind the founder's F15: a daily point is ONE NUMBER — total net worth. There is no per-account daily history anywhere in the app, so "what was my Vanguard account worth in April" has no answer to read, and a beginning value gets BACK-SOLVED from today minus whatever the ledger claims happened. It also only ever starts the day the app was first opened: an account connected today has no yesterday, whatever the market did before that.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>The daily and monthly points are synced, but the DAILY RECORD they are checked against is not. On a second device the trend survives and the walk behind it does not.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4601,13 +4729,19 @@
 THE DEFECT IS WHAT THE BASELINE IS. It is whatever day the app happened to be opened, not a date a person chose. If the only stored point was written after a fall, the fall is invisible and the small recovery since reads as a gain — which is exactly how a −4.2% year showed as +2.0%.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>The line is labelled "Return on cash + investments" but is computed as (now − then) ÷ then with NO adjustment for money paid in or taken out. Move $50,000 in and it reports a gain. Either the label is wrong or the formula is — founder's call.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4662,13 +4796,19 @@
 THE LIMIT THAT MATTERS, and it is the mechanism behind the founder's F15: a daily point is ONE NUMBER — total net worth. There is no per-account daily history anywhere in the app, so "what was my Vanguard account worth in April" has no answer to read, and a beginning value gets BACK-SOLVED from today minus whatever the ledger claims happened. It also only ever starts the day the app was first opened: an account connected today has no yesterday, whatever the market did before that.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>The daily and monthly points are synced, but the DAILY RECORD they are checked against is not. On a second device the trend survives and the walk behind it does not.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4722,12 +4862,14 @@
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4779,13 +4921,23 @@
           <t>Add up the balances of every account whose class is Cash. Under the founder's 2026-08-04 rule that means checking, savings, high-yield savings and the uninvested sweep at a broker — and NOT money-market funds, which pay dividends and are measured with the investments.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Money-market funds are deliberately NOT counted as cash. Any institution that reports a sweep as a fund will therefore land in investments — worth watching per provider.</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+          <t>Cash means checking, savings, high-yield savings and the uninvested sweep at a broker. Money-market funds are investments, because they pay dividends and are measured with the investments (founder, 2026-08-04).</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4839,12 +4991,14 @@
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4898,12 +5052,14 @@
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4959,13 +5115,19 @@
 (If the pieces come to MORE than the broker's total, that is a pricing quirk rather than money, and it goes to the largest holding — putting it in cash would show you a negative cash balance, which reads worse than a rounding nudge.)</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Reported by the 54-item audit as one of the places a total and its parts can disagree; the reconciliation assertion now catches it, but the screen has no way to say so yet.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5020,12 +5182,14 @@
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5080,12 +5244,14 @@
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5138,12 +5304,14 @@
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5198,12 +5366,14 @@
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5252,12 +5422,14 @@
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5310,13 +5482,23 @@
 The larger wins deliberately. Someone may answer both and the two rarely agree, and understating spending is the direction that FLATTERS a plan — it makes the odds look better than they are. Taking the larger errs toward the cautious side.</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Money-market funds are deliberately NOT counted as cash. Any institution that reports a sweep as a fund will therefore land in investments — worth watching per provider.</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
+          <t>Cash means checking, savings, high-yield savings and the uninvested sweep at a broker. Money-market funds are investments, because they pay dividends and are measured with the investments (founder, 2026-08-04).</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5374,13 +5556,23 @@
 HOW IT DIFFERS FROM THE 25 x YARDSTICK reported by the odds engine: this one knows how long you plan for and what your money earns; the yardstick knows neither.</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>The Net worth screen builds this projection WITHOUT the person's big costs, while Cash flow, Budget, Goals and Social Security timing all include them. Same person, same day, two different nest eggs. Seen in the code; not yet confirmed on screen.</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
+          <t>The recommended nest egg is 25× the yearly spending not covered by guaranteed income, counted from the start of the retirement year — which is why it differs from an outside calculator.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5436,10 +5628,16 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
+          <t>Assets minus debts, computed each time and never stored as a third number that could disagree with its own halves. A genuine negative is shown, never floored at zero.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5497,10 +5695,16 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
+          <t>Assets minus debts, computed each time and never stored as a third number that could disagree with its own halves. A genuine negative is shown, never floored at zero.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5554,12 +5758,14 @@
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5612,12 +5818,14 @@
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5673,13 +5881,19 @@
 (If the pieces come to MORE than the broker's total, that is a pricing quirk rather than money, and it goes to the largest holding — putting it in cash would show you a negative cash balance, which reads worse than a rounding nudge.)</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Reported by the 54-item audit as one of the places a total and its parts can disagree; the reconciliation assertion now catches it, but the screen has no way to say so yet.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5732,12 +5946,14 @@
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5791,12 +6007,14 @@
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5849,12 +6067,14 @@
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5907,12 +6127,14 @@
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5965,12 +6187,14 @@
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6025,12 +6249,14 @@
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6083,12 +6309,14 @@
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6141,12 +6369,14 @@
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6199,12 +6429,14 @@
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6257,13 +6489,23 @@
 NO PRICE MEANS ZERO, NOT A GUESS. An unpriced holding contributes nothing and the screen says the price is missing — it is never valued at what it cost, which would silently report a gain of exactly zero.</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>OPTIONS: value is quantity × price with no contract multiplier. An option is 100 shares per contract unless the broker states otherwise, so an option position may be reported at one hundredth of its real value. The ledger normalises a TRADE so units × price equals the broker's cash figure, but the holdings path does not. TO VERIFY AND FIX.</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
+          <t>A price is a ratio, not money: it keeps eight decimal places and is never rounded to cents. Rounding a Treasury bill price of $0.9888 to $0.99 invented $276 of gain on one row.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6315,13 +6557,19 @@
           <t>Add the shares across every purchase lot. A position is the SUM OF ITS LOTS, never one stored figure — that is what makes gain-since-purchase possible.</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>OPTIONS: quantity is held in contracts for options and in shares for stock, in the same field, with nothing marking which. Anything multiplying quantity by price inherits the ambiguity.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6373,13 +6621,23 @@
           <t>Add shares × cost per share across every lot. A lot with no cost recorded contributes nothing, but its shares still count as owned.</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>OPTIONS: same contract-multiplier question as market value — cost per share × shares, with no ×100 for a contract. TO VERIFY.</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
+          <t>Cost basis comes from recorded lots. A lot with no cost is skipped rather than treated as free shares, because free shares would report the whole value as gain and tax it.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6431,13 +6689,23 @@
           <t>Add shares × cost per share across every lot. A lot with no cost recorded contributes nothing, but its shares still count as owned.</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>OPTIONS: same contract-multiplier question as market value — cost per share × shares, with no ×100 for a contract. TO VERIFY.</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
+          <t>Cost basis comes from recorded lots. A lot with no cost is skipped rather than treated as free shares, because free shares would report the whole value as gain and tax it.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6490,12 +6758,14 @@
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6549,13 +6819,19 @@
 A SALE WITH NO RECORDED BUY CONTRIBUTES NOTHING and is counted separately, so the screen can say how much it could not see. A cost is never invented — inventing one would report the entire sale as profit.</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Reads the transaction ledger, which is device-only. On a second device it reports nothing — not because nothing was sold, but because the record is elsewhere.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6609,13 +6885,23 @@
 An unreadable purchase date is treated as SHORT-term: the cautious side, since understating a tax bill is the worse mistake.</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>OPTIONS: gain per lot = shares × (price − cost), again with no contract multiplier. TO VERIFY. Separately: a lot with no recorded cost is skipped, so a position of skipped lots reports no gain at all rather than saying it cannot tell.</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
+          <t>Long-term is decided by DAYS, not calendar months (correction E7): 335 days used to count as long-term and be taxed at the lower rate.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6669,13 +6955,23 @@
 An unreadable purchase date is treated as SHORT-term: the cautious side, since understating a tax bill is the worse mistake.</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>OPTIONS: gain per lot = shares × (price − cost), again with no contract multiplier. TO VERIFY. Separately: a lot with no recorded cost is skipped, so a position of skipped lots reports no gain at all rather than saying it cannot tell.</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
+          <t>Long-term is decided by DAYS, not calendar months (correction E7): 335 days used to count as long-term and be taxed at the lower rate.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6728,12 +7024,14 @@
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6782,12 +7080,14 @@
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6840,13 +7140,23 @@
 NO PRICE MEANS ZERO, NOT A GUESS. An unpriced holding contributes nothing and the screen says the price is missing — it is never valued at what it cost, which would silently report a gain of exactly zero.</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>OPTIONS: value is quantity × price with no contract multiplier. An option is 100 shares per contract unless the broker states otherwise, so an option position may be reported at one hundredth of its real value. The ledger normalises a TRADE so units × price equals the broker's cash figure, but the holdings path does not. TO VERIFY AND FIX.</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
+          <t>A price is a ratio, not money: it keeps eight decimal places and is never rounded to cents. Rounding a Treasury bill price of $0.9888 to $0.99 invented $276 of gain on one row.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6899,12 +7209,14 @@
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6957,12 +7269,14 @@
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7015,12 +7329,14 @@
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7073,12 +7389,14 @@
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7131,12 +7449,14 @@
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7173,12 +7493,14 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -7215,12 +7537,14 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -7257,12 +7581,14 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -7279,7 +7605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -7291,9 +7617,11 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="41" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="37" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="41" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7344,15 +7672,25 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Errors or findings to address</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Decisions made</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -7408,13 +7746,23 @@
 And a real $500 loss produces exactly the same line. You cannot tell them apart, which is why a wrong deposit anywhere becomes a market movement that never happened.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Beginning values are read from the daily record, which never leaves the phone. On a new device there is no beginning, so the walk back-solves one or refuses.</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+          <t>The identity must close: ending = beginning + money in − money out + income − costs + market change. A direction stated by the institution never overrides a contradicting sign — a −$500 line marked IN is a reversal.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7470,13 +7818,23 @@
 And a real $500 loss produces exactly the same line. You cannot tell them apart, which is why a wrong deposit anywhere becomes a market movement that never happened.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Beginning values are read from the daily record, which never leaves the phone. On a new device there is no beginning, so the walk back-solves one or refuses.</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+          <t>The identity must close: ending = beginning + money in − money out + income − costs + market change. A direction stated by the institution never overrides a contradicting sign — a −$500 line marked IN is a reversal.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7532,13 +7890,23 @@
 And a real $500 loss produces exactly the same line. You cannot tell them apart, which is why a wrong deposit anywhere becomes a market movement that never happened.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Beginning values are read from the daily record, which never leaves the phone. On a new device there is no beginning, so the walk back-solves one or refuses.</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+          <t>The identity must close: ending = beginning + money in − money out + income − costs + market change. A direction stated by the institution never overrides a contradicting sign — a −$500 line marked IN is a reversal.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7594,13 +7962,23 @@
 And a real $500 loss produces exactly the same line. You cannot tell them apart, which is why a wrong deposit anywhere becomes a market movement that never happened.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Beginning values are read from the daily record, which never leaves the phone. On a new device there is no beginning, so the walk back-solves one or refuses.</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+          <t>The identity must close: ending = beginning + money in − money out + income − costs + market change. A direction stated by the institution never overrides a contradicting sign — a −$500 line marked IN is a reversal.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7656,12 +8034,14 @@
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7717,12 +8097,14 @@
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7778,12 +8160,14 @@
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7836,12 +8220,14 @@
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7896,10 +8282,16 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
+          <t>When the timing of money moving in or out drives the percentage more than the investments do, the figure is REFUSED and the dollar walk is shown instead.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7955,12 +8347,14 @@
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8016,12 +8410,14 @@
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8077,12 +8473,14 @@
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8119,12 +8517,14 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -8161,12 +8561,14 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -8203,12 +8605,14 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -8225,7 +8629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -8237,9 +8641,11 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="41" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="37" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="41" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8290,15 +8696,25 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Errors or findings to address</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Decisions made</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -8352,12 +8768,14 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8411,12 +8829,14 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8469,12 +8889,14 @@
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8526,12 +8948,14 @@
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8584,12 +9008,14 @@
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8638,12 +9064,14 @@
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8696,12 +9124,14 @@
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8758,12 +9188,14 @@
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8816,12 +9248,14 @@
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8876,10 +9310,16 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
+          <t>Each stream grows on its own rule: Social Security rises with inflation, a fixed pension stays flat. They are never inflated together (fix B1).</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8936,12 +9376,14 @@
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8996,10 +9438,16 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
+          <t>The same one dated table, after both earlier copies were deleted.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9054,10 +9502,16 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
+          <t>One dated table. Start age is 73 for those born 1951–1959 and 75 for those born 1960 or later; a Roth 401(k) is exempt (fix B4).</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9106,12 +9560,14 @@
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9166,10 +9622,16 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
+          <t>One dated table. Start age is 73 for those born 1951–1959 and 75 for those born 1960 or later; a Roth 401(k) is exempt (fix B4).</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9223,12 +9685,14 @@
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9283,10 +9747,16 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
+          <t>The amount a person types from their statement is the amount at THEIR full retirement age, not at 62 and not at 70 (fix B2). The full-retirement age itself comes from a birth-year table, to the month.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9340,12 +9810,14 @@
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9400,10 +9872,16 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
+          <t>The amount a person types from their statement is the amount at THEIR full retirement age, not at 62 and not at 70 (fix B2). The full-retirement age itself comes from a birth-year table, to the month.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9456,12 +9934,14 @@
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9514,12 +9994,14 @@
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9572,12 +10054,14 @@
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9630,12 +10114,14 @@
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9688,12 +10174,14 @@
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9746,12 +10234,14 @@
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9809,13 +10299,23 @@
 HOW IT DIFFERS FROM THE 25 x YARDSTICK reported by the odds engine: this one knows how long you plan for and what your money earns; the yardstick knows neither.</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>The Net worth screen builds this projection WITHOUT the person's big costs, while Cash flow, Budget, Goals and Social Security timing all include them. Same person, same day, two different nest eggs. Seen in the code; not yet confirmed on screen.</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
+          <t>The recommended nest egg is 25× the yearly spending not covered by guaranteed income, counted from the start of the retirement year — which is why it differs from an outside calculator.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9864,12 +10364,14 @@
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9922,12 +10424,14 @@
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9984,12 +10488,14 @@
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10044,12 +10550,14 @@
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10102,12 +10610,14 @@
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10161,12 +10671,14 @@
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10224,13 +10736,23 @@
 HOW IT DIFFERS FROM THE 25 x YARDSTICK reported by the odds engine: this one knows how long you plan for and what your money earns; the yardstick knows neither.</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>The Net worth screen builds this projection WITHOUT the person's big costs, while Cash flow, Budget, Goals and Social Security timing all include them. Same person, same day, two different nest eggs. Seen in the code; not yet confirmed on screen.</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
+          <t>The recommended nest egg is 25× the yearly spending not covered by guaranteed income, counted from the start of the retirement year — which is why it differs from an outside calculator.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10283,13 +10805,23 @@
 The best-to-worst range re-runs the same plan at a lower and a higher return, so it reads as a range rather than a promise. It always contains the headline figure, and it is repeatable.</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>The odds shown on Home, Plan and Cash flow are rounded to the nearest 5, while the compare tables still show them exact. One figure, two precisions — founder's open question.</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
+          <t>One thousand futures, and the odds are rounded to the nearest 5. A genuine 100 or 0 is shown literally; 98 shows as 95, never as 100 (fix B6). The best-to-worst band was removed.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10342,12 +10874,14 @@
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10400,12 +10934,14 @@
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10458,12 +10994,14 @@
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10500,12 +11038,14 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -10542,12 +11082,14 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -10584,12 +11126,14 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -10626,12 +11170,14 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
         </is>
@@ -10668,12 +11214,14 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -10690,7 +11238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -10702,9 +11250,11 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="41" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="37" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="41" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10755,15 +11305,25 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Errors or findings to address</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Decisions made</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -10816,12 +11376,14 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10874,12 +11436,14 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10927,12 +11491,14 @@
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10985,12 +11551,14 @@
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11038,12 +11606,14 @@
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11097,12 +11667,14 @@
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11156,12 +11728,14 @@
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11215,12 +11789,14 @@
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11273,12 +11849,14 @@
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11332,12 +11910,14 @@
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11391,12 +11971,14 @@
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11449,12 +12031,14 @@
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11507,12 +12091,14 @@
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11565,12 +12151,14 @@
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11624,12 +12212,14 @@
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11682,12 +12272,14 @@
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11740,12 +12332,14 @@
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11798,12 +12392,14 @@
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11856,12 +12452,14 @@
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11910,12 +12508,14 @@
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11968,12 +12568,14 @@
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12031,13 +12633,23 @@
 HOW IT DIFFERS FROM THE 25 x YARDSTICK reported by the odds engine: this one knows how long you plan for and what your money earns; the yardstick knows neither.</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>The Net worth screen builds this projection WITHOUT the person's big costs, while Cash flow, Budget, Goals and Social Security timing all include them. Same person, same day, two different nest eggs. Seen in the code; not yet confirmed on screen.</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
+          <t>The recommended nest egg is 25× the yearly spending not covered by guaranteed income, counted from the start of the retirement year — which is why it differs from an outside calculator.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12090,12 +12702,14 @@
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12149,12 +12763,14 @@
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12207,12 +12823,14 @@
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12267,10 +12885,16 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
+          <t>Withdrawals, including required ones, are NOT counted as guaranteed income — counting money coming out of the pot as income would count the same dollars twice (fix B5).</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12324,12 +12948,14 @@
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12382,12 +13008,14 @@
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12424,12 +13052,14 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -12466,12 +13096,14 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -12508,12 +13140,14 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -12550,12 +13184,14 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -12592,12 +13228,14 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
         </is>
@@ -12614,7 +13252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -12626,9 +13264,11 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="41" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="37" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="41" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12679,15 +13319,25 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Errors or findings to address</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Decisions made</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -12740,12 +13390,14 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12798,12 +13450,14 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12856,12 +13510,14 @@
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12914,12 +13570,14 @@
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12968,12 +13626,14 @@
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13026,12 +13686,14 @@
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13085,12 +13747,14 @@
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13143,12 +13807,14 @@
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13201,12 +13867,14 @@
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13259,12 +13927,14 @@
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13318,12 +13988,14 @@
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13377,12 +14049,14 @@
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13436,12 +14110,14 @@
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13494,12 +14170,14 @@
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13552,12 +14230,14 @@
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13609,13 +14289,23 @@
           <t>Cash + investments — everything except the house and the car. Selling the roof you live under is not a plan, so physical assets are excluded by CLASS, not by tax type. · Add up the balances of every account whose class is Cash. Under the founder's 2026-08-04 rule that means checking, savings, high-yield savings and the uninvested sweep at a broker — and NOT money-market funds, which pay dividends and are measured with the investments.</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Money-market funds are deliberately NOT counted as cash. Any institution that reports a sweep as a fund will therefore land in investments — worth watching per provider.</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
+          <t>Cash means checking, savings, high-yield savings and the uninvested sweep at a broker. Money-market funds are investments, because they pay dividends and are measured with the investments (founder, 2026-08-04).</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13668,12 +14358,14 @@
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13726,12 +14418,14 @@
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13784,12 +14478,14 @@
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13842,12 +14538,14 @@
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13900,12 +14598,14 @@
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13958,12 +14658,14 @@
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14016,12 +14718,14 @@
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14074,12 +14778,14 @@
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14132,12 +14838,14 @@
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14191,12 +14899,14 @@
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14251,10 +14961,16 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
+          <t>Explicit tables per filing status. A married band is not twice the single band — the 37% band starts at $768,700, not at double the single figure.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14309,10 +15025,16 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
+          <t>Explicit tables per filing status. A married band is not twice the single band — the 37% band starts at $768,700, not at double the single figure.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14365,12 +15087,14 @@
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14423,12 +15147,14 @@
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14465,12 +15191,14 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -14507,12 +15235,14 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -14549,12 +15279,14 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -14591,12 +15323,14 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -14633,12 +15367,14 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -14675,12 +15411,14 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -14717,12 +15455,14 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -498,7 +498,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24  (stamped by the build, not typed; unchanged when the file is only read)</t>
+          <t>2026-08-25  (stamped by the build, not typed; unchanged when the file is only read)</t>
         </is>
       </c>
     </row>
@@ -729,226 +729,238 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Errors or findings to address</t>
+          <t>COLUMN — Secondary calculations and decisions the engine makes</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>What is known to be wrong or unproved about this figure, in plain English. Blank means nothing is on record yet — not that nothing is wrong.</t>
+          <t>The judgements an engine must make BEFORE its headline figure exists: what class an asset is, what to call it on screen, which units apply, whether a value is fresh. Each of these is a formula of its own and needs its own row.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Decisions made</t>
+          <t>COLUMN — Errors or findings to address</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>The rulings that govern this figure, and why. The standing display and rounding rule applies to every row and is stated once at the top of this tab.</t>
+          <t>What is known to be wrong or unproved about this figure, in plain English. Blank means nothing is on record yet — not that nothing is wrong.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (mathematical)</t>
+          <t>COLUMN — Decisions made</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
+          <t>The rulings that govern this figure, and why. The standing display and rounding rule applies to every row and is stated once at the top of this tab.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (in words)</t>
+          <t>COLUMN — Formula (mathematical)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
+          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Engine ID</t>
+          <t>COLUMN — Formula (in words)</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
+          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Your name for it (72-metric file)</t>
+          <t>COLUMN — Engine ID</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
+          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Core screen?</t>
+          <t>COLUMN — Your name for it (72-metric file)</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Whether the screen is part of the 55-70 core, the agreed first scope.</t>
+          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>COLUMN — Core screen?</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Whether the screen is part of the 55-70 core, the agreed first scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t>COLUMN — Row status</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>VERIFIED with its date means a person read the screen and confirmed the chain. NOT STARTED means the screen has not been read yet. Nothing in between is claimed.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="3" t="inlineStr"/>
-    </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN — Input ID</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>The identifier of a raw input, per the same standard.</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Variable name</t>
+          <t>COLUMN — Input ID</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>What the raw value is called.</t>
+          <t>The identifier of a raw input, per the same standard.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Source</t>
+          <t>COLUMN — Variable name</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
+          <t>What the raw value is called.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Which metric uses it</t>
+          <t>COLUMN — Source</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Every metric identifier that depends on this input.</t>
+          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>COLUMN — Which metric uses it</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Every metric identifier that depends on this input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>COLUMN — Which engine uses it</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Every engine identifier that reads this input.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="3" t="inlineStr"/>
-    </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Complies with — naming</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Complies with — identifiers</t>
+          <t>Complies with — naming</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>Complies with — identifiers</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
           <t>Complies with — objectives</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>MoneyKeel/documents/standards/moneykeel_calc_spec_objectives-and-verification_v01.md</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr"/>
-      <c r="B43" s="3" t="inlineStr"/>
-    </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>COVERAGE — screens read so far</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>COVERAGE — screens read so far</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>COVERAGE — what that means</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Every screen in the app is listed on its tab. Only Home carries figures so far; the rest are marked NOT STARTED. A rising count is not completeness while screens remain unread.</t>
         </is>
@@ -965,7 +977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -973,7 +985,8 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1004,6 +1017,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Engine ID</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Row status</t>
         </is>
       </c>
@@ -1036,6 +1054,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>MK-XS-E-001 · MK-XS-E-003 · MK-NW-E-004 · MK-PL-E-008</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1068,6 +1091,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>MK-PL-E-008</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1100,6 +1128,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>MK-NW-E-006</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1132,6 +1165,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>MK-NW-E-023 · MK-NW-E-024</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1164,6 +1202,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>MK-HM-E-001 · MK-NW-E-023</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1196,6 +1239,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>MK-HM-E-001</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1228,6 +1276,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>MK-NW-E-025 · MK-NW-E-028</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1260,6 +1313,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>MK-PF-E-001</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1292,6 +1350,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>MK-PF-E-001</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1322,7 +1385,8 @@
           <t>LEDGER · the institution-words table</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -1356,6 +1420,11 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>MK-NW-E-016</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1388,6 +1457,11 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>MK-NW-E-017 · MK-NW-E-020</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1420,6 +1494,11 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>MK-NW-E-018 · MK-NW-E-019</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1452,6 +1531,11 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>MK-NW-E-007</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1484,6 +1568,11 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>MK-PL-E-018</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1516,6 +1605,11 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>MK-NW-E-008</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1548,6 +1642,11 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>MK-PL-E-009</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1580,6 +1679,11 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>MK-XS-E-002 · MK-NW-E-010</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1612,6 +1716,11 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>MK-PL-E-004</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1644,6 +1753,11 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>MK-PL-E-009 · MK-PL-E-010</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1674,7 +1788,8 @@
           <t>SS_CLAIM_FACTOR</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -1708,6 +1823,11 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>MK-PL-E-010</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1740,6 +1860,11 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>MK-CF-E-002</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1772,6 +1897,11 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>MK-CF-E-006 · MK-CF-E-007</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1804,6 +1934,11 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>MK-CF-E-007 · MK-MN-E-010</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1836,6 +1971,11 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>MK-MN-E-001</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1868,6 +2008,11 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>MK-MN-E-005</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1900,6 +2045,11 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>MK-XS-E-002 · MK-NW-E-010</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1932,6 +2082,11 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>MK-PL-E-004</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1964,6 +2119,11 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>MK-PL-E-015 · MK-MN-E-014</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
       </c>
@@ -1995,6 +2155,11 @@
         </is>
       </c>
       <c r="F32" t="inlineStr">
+        <is>
+          <t>MK-NW-E-001 · MK-PF-E-001</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3193,11 +3358,12 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="37" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="41" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="37" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="41" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3423,7 +3589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3435,11 +3601,12 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="37" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="41" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="37" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="41" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3490,25 +3657,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Secondary calculations and decisions the engine makes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Errors or findings to address</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Decisions made</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -3562,18 +3734,19 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>Assets minus debts, computed each time and never stored as a third number that could disagree with its own halves. A genuine negative is shown, never floored at zero.</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3626,23 +3799,24 @@
 The best-to-worst range re-runs the same plan at a lower and a higher return, so it reads as a range rather than a promise. It always contains the headline figure, and it is repeatable.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>The odds shown on Home, Plan and Cash flow are rounded to the nearest 5, while the compare tables still show them exact. One figure, two precisions — founder's open question.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>One thousand futures, and the odds are rounded to the nearest 5. A genuine 100 or 0 is shown literally; 98 shows as 95, never as 100 (fix B6). The best-to-worst band was removed.</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3697,12 +3871,13 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3761,12 +3936,13 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3821,12 +3997,13 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3881,12 +4058,13 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3937,12 +4115,13 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3959,7 +4138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3971,11 +4150,12 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="37" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="41" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="37" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="41" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4026,25 +4206,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Secondary calculations and decisions the engine makes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Errors or findings to address</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Decisions made</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -4099,17 +4284,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>DECIDES the moment a price stops being current.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Prices are never synced, so freshness is per device. Two devices can legitimately disagree about how current a value is.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4164,12 +4354,13 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4224,12 +4415,13 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4280,12 +4472,13 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4324,12 +4517,13 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -4368,12 +4562,13 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -4412,12 +4607,13 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -4456,12 +4652,13 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -4500,12 +4697,13 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
         </is>
@@ -4522,7 +4720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4534,11 +4732,12 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="37" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="41" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="37" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="41" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4589,25 +4788,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Secondary calculations and decisions the engine makes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Errors or findings to address</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Decisions made</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -4662,19 +4866,20 @@
 THE LIMIT THAT MATTERS, and it is the mechanism behind the founder's F15: a daily point is ONE NUMBER — total net worth. There is no per-account daily history anywhere in the app, so "what was my Vanguard account worth in April" has no answer to read, and a beginning value gets BACK-SOLVED from today minus whatever the ledger claims happened. It also only ever starts the day the app was first opened: an account connected today has no yesterday, whatever the market did before that.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>The daily and monthly points are synced, but the DAILY RECORD they are checked against is not. On a second device the trend survives and the walk behind it does not.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4729,19 +4934,20 @@
 THE DEFECT IS WHAT THE BASELINE IS. It is whatever day the app happened to be opened, not a date a person chose. If the only stored point was written after a fall, the fall is invisible and the small recovery since reads as a gain — which is exactly how a −4.2% year showed as +2.0%.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>The line is labelled "Return on cash + investments" but is computed as (now − then) ÷ then with NO adjustment for money paid in or taken out. Move $50,000 in and it reports a gain. Either the label is wrong or the formula is — founder's call.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4796,19 +5002,20 @@
 THE LIMIT THAT MATTERS, and it is the mechanism behind the founder's F15: a daily point is ONE NUMBER — total net worth. There is no per-account daily history anywhere in the app, so "what was my Vanguard account worth in April" has no answer to read, and a beginning value gets BACK-SOLVED from today minus whatever the ledger claims happened. It also only ever starts the day the app was first opened: an account connected today has no yesterday, whatever the market did before that.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>The daily and monthly points are synced, but the DAILY RECORD they are checked against is not. On a second device the trend survives and the walk behind it does not.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4864,12 +5071,13 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4923,21 +5131,26 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>DECIDES what counts as cash — and deliberately excludes money-market funds.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Money-market funds are deliberately NOT counted as cash. Any institution that reports a sweep as a fund will therefore land in investments — worth watching per provider.</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Cash means checking, savings, high-yield savings and the uninvested sweep at a broker. Money-market funds are investments, because they pay dividends and are measured with the investments (founder, 2026-08-04).</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4993,12 +5206,13 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5051,15 +5265,20 @@
 The totals must add to total assets — this is what the donut draws, so any leak shows as a wrong slice.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>DECIDES the class of every asset before it can group them, and DECIDES the words shown for each class. The classifying rule itself is engine MK-ST-E-xxx — see the asset-classification standard.</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5117,17 +5336,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>DECIDES which class each holding inside one account belongs to, then how much of the account total sits in each.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>Reported by the 54-item audit as one of the places a total and its parts can disagree; the reconciliation assertion now catches it, but the screen has no way to say so yet.</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5184,12 +5408,13 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5246,12 +5471,13 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5306,12 +5532,13 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5368,12 +5595,13 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5424,12 +5652,13 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5484,21 +5713,26 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>DECIDES what counts as cash — and deliberately excludes money-market funds.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>Money-market funds are deliberately NOT counted as cash. Any institution that reports a sweep as a fund will therefore land in investments — worth watching per provider.</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Cash means checking, savings, high-yield savings and the uninvested sweep at a broker. Money-market funds are investments, because they pay dividends and are measured with the investments (founder, 2026-08-04).</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5556,23 +5790,24 @@
 HOW IT DIFFERS FROM THE 25 x YARDSTICK reported by the odds engine: this one knows how long you plan for and what your money earns; the yardstick knows neither.</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
         <is>
           <t>The Net worth screen builds this projection WITHOUT the person's big costs, while Cash flow, Budget, Goals and Social Security timing all include them. Same person, same day, two different nest eggs. Seen in the code; not yet confirmed on screen.</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>The recommended nest egg is 25× the yearly spending not covered by guaranteed income, counted from the start of the retirement year — which is why it differs from an outside calculator.</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5626,18 +5861,19 @@
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>Assets minus debts, computed each time and never stored as a third number that could disagree with its own halves. A genuine negative is shown, never floored at zero.</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5693,18 +5929,19 @@
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>Assets minus debts, computed each time and never stored as a third number that could disagree with its own halves. A genuine negative is shown, never floored at zero.</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5757,15 +5994,20 @@
 A LIVE-PRICED account returns nothing: its value comes from today's prices, so staleness is not a question that applies to it. A value with no date recorded also returns nothing rather than being assumed fresh.</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>DECIDES whether a stated value is fresh enough to show without a warning.</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5820,12 +6062,13 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5883,17 +6126,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>DECIDES which class each holding inside one account belongs to, then how much of the account total sits in each.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>Reported by the 54-item audit as one of the places a total and its parts can disagree; the reconciliation assertion now catches it, but the screen has no way to say so yet.</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5948,12 +6196,13 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6009,12 +6258,13 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6066,15 +6316,20 @@
           <t>Reads the stored bond fields off the holding and computes its yields. A holding with none of them is not a bond and returns nothing.</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>DECIDES how a bond is NAMED on screen — issuer, or the identifying number, or a plain description; and DECIDES whether a line is a bond at all.</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6129,12 +6384,13 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6189,12 +6445,13 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6251,12 +6508,13 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6311,12 +6569,13 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6371,12 +6630,13 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6431,12 +6691,13 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6491,21 +6752,26 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>DECIDES whether a line is a share, a bond, an option, a crypto amount or a currency, because the units differ; and DECIDES the price to use when the feed has none.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>OPTIONS: value is quantity × price with no contract multiplier. An option is 100 shares per contract unless the broker states otherwise, so an option position may be reported at one hundredth of its real value. The ledger normalises a TRADE so units × price equals the broker's cash figure, but the holdings path does not. TO VERIFY AND FIX.</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>A price is a ratio, not money: it keeps eight decimal places and is never rounded to cents. Rounding a Treasury bill price of $0.9888 to $0.99 invented $276 of gain on one row.</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6557,19 +6823,20 @@
           <t>Add the shares across every purchase lot. A position is the SUM OF ITS LOTS, never one stored figure — that is what makes gain-since-purchase possible.</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
         <is>
           <t>OPTIONS: quantity is held in contracts for options and in shares for stock, in the same field, with nothing marking which. Anything multiplying quantity by price inherits the ambiguity.</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6621,23 +6888,24 @@
           <t>Add shares × cost per share across every lot. A lot with no cost recorded contributes nothing, but its shares still count as owned.</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
         <is>
           <t>OPTIONS: same contract-multiplier question as market value — cost per share × shares, with no ×100 for a contract. TO VERIFY.</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Cost basis comes from recorded lots. A lot with no cost is skipped rather than treated as free shares, because free shares would report the whole value as gain and tax it.</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6689,23 +6957,24 @@
           <t>Add shares × cost per share across every lot. A lot with no cost recorded contributes nothing, but its shares still count as owned.</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
         <is>
           <t>OPTIONS: same contract-multiplier question as market value — cost per share × shares, with no ×100 for a contract. TO VERIFY.</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Cost basis comes from recorded lots. A lot with no cost is skipped rather than treated as free shares, because free shares would report the whole value as gain and tax it.</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6760,12 +7029,13 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6819,19 +7089,20 @@
 A SALE WITH NO RECORDED BUY CONTRIBUTES NOTHING and is counted separately, so the screen can say how much it could not see. A cost is never invented — inventing one would report the entire sale as profit.</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
         <is>
           <t>Reads the transaction ledger, which is device-only. On a second device it reports nothing — not because nothing was sold, but because the record is elsewhere.</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6885,23 +7156,24 @@
 An unreadable purchase date is treated as SHORT-term: the cautious side, since understating a tax bill is the worse mistake.</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
         <is>
           <t>OPTIONS: gain per lot = shares × (price − cost), again with no contract multiplier. TO VERIFY. Separately: a lot with no recorded cost is skipped, so a position of skipped lots reports no gain at all rather than saying it cannot tell.</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Long-term is decided by DAYS, not calendar months (correction E7): 335 days used to count as long-term and be taxed at the lower rate.</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6955,23 +7227,24 @@
 An unreadable purchase date is treated as SHORT-term: the cautious side, since understating a tax bill is the worse mistake.</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
         <is>
           <t>OPTIONS: gain per lot = shares × (price − cost), again with no contract multiplier. TO VERIFY. Separately: a lot with no recorded cost is skipped, so a position of skipped lots reports no gain at all rather than saying it cannot tell.</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Long-term is decided by DAYS, not calendar months (correction E7): 335 days used to count as long-term and be taxed at the lower rate.</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7026,12 +7299,13 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7082,12 +7356,13 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7142,21 +7417,26 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t>DECIDES whether a line is a share, a bond, an option, a crypto amount or a currency, because the units differ; and DECIDES the price to use when the feed has none.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>OPTIONS: value is quantity × price with no contract multiplier. An option is 100 shares per contract unless the broker states otherwise, so an option position may be reported at one hundredth of its real value. The ledger normalises a TRADE so units × price equals the broker's cash figure, but the holdings path does not. TO VERIFY AND FIX.</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>A price is a ratio, not money: it keeps eight decimal places and is never rounded to cents. Rounding a Treasury bill price of $0.9888 to $0.99 invented $276 of gain on one row.</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7208,15 +7488,20 @@
           <t>Reads the stored bond fields off the holding and computes its yields. A holding with none of them is not a bond and returns nothing.</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>DECIDES how a bond is NAMED on screen — issuer, or the identifying number, or a plain description; and DECIDES whether a line is a bond at all.</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7268,15 +7553,20 @@
           <t>Reads the stored bond fields off the holding and computes its yields. A holding with none of them is not a bond and returns nothing.</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>DECIDES how a bond is NAMED on screen — issuer, or the identifying number, or a plain description; and DECIDES whether a line is a bond at all.</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7331,12 +7621,13 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7391,12 +7682,13 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7448,15 +7740,20 @@
           <t>Reads the stored bond fields off the holding and computes its yields. A holding with none of them is not a bond and returns nothing. · face value × coupon rate. NOT what the bond is worth today × the rate — a $10,000 bond paying 4% pays $400 whether it is trading at $9,800 or $11,000.</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>DECIDES how a bond is NAMED on screen — issuer, or the identifying number, or a plain description; and DECIDES whether a line is a bond at all.</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7495,12 +7792,13 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -7539,12 +7837,13 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -7583,12 +7882,13 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -7605,7 +7905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -7617,11 +7917,12 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="37" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="41" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="37" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="41" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7672,25 +7973,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Secondary calculations and decisions the engine makes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Errors or findings to address</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Decisions made</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -7746,23 +8052,24 @@
 And a real $500 loss produces exactly the same line. You cannot tell them apart, which is why a wrong deposit anywhere becomes a market movement that never happened.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Beginning values are read from the daily record, which never leaves the phone. On a new device there is no beginning, so the walk back-solves one or refuses.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>The identity must close: ending = beginning + money in − money out + income − costs + market change. A direction stated by the institution never overrides a contradicting sign — a −$500 line marked IN is a reversal.</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7818,23 +8125,24 @@
 And a real $500 loss produces exactly the same line. You cannot tell them apart, which is why a wrong deposit anywhere becomes a market movement that never happened.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Beginning values are read from the daily record, which never leaves the phone. On a new device there is no beginning, so the walk back-solves one or refuses.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>The identity must close: ending = beginning + money in − money out + income − costs + market change. A direction stated by the institution never overrides a contradicting sign — a −$500 line marked IN is a reversal.</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7890,23 +8198,24 @@
 And a real $500 loss produces exactly the same line. You cannot tell them apart, which is why a wrong deposit anywhere becomes a market movement that never happened.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Beginning values are read from the daily record, which never leaves the phone. On a new device there is no beginning, so the walk back-solves one or refuses.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>The identity must close: ending = beginning + money in − money out + income − costs + market change. A direction stated by the institution never overrides a contradicting sign — a −$500 line marked IN is a reversal.</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7962,23 +8271,24 @@
 And a real $500 loss produces exactly the same line. You cannot tell them apart, which is why a wrong deposit anywhere becomes a market movement that never happened.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Beginning values are read from the daily record, which never leaves the phone. On a new device there is no beginning, so the walk back-solves one or refuses.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>The identity must close: ending = beginning + money in − money out + income − costs + market change. A direction stated by the institution never overrides a contradicting sign — a −$500 line marked IN is a reversal.</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8036,12 +8346,13 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8099,12 +8410,13 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8162,12 +8474,13 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8222,12 +8535,13 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8280,18 +8594,19 @@
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>When the timing of money moving in or out drives the percentage more than the investments do, the figure is REFUSED and the dollar walk is shown instead.</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8349,12 +8664,13 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8412,12 +8728,13 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8475,12 +8792,13 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8519,12 +8837,13 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -8563,12 +8882,13 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -8607,12 +8927,13 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -8629,7 +8950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -8641,11 +8962,12 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="37" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="41" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="37" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="41" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8696,25 +9018,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Secondary calculations and decisions the engine makes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Errors or findings to address</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Decisions made</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -8770,12 +9097,13 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8831,12 +9159,13 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8891,12 +9220,13 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8950,12 +9280,13 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9010,12 +9341,13 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9066,12 +9398,13 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9126,12 +9459,13 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9190,12 +9524,13 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9250,12 +9585,13 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9308,18 +9644,19 @@
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>Each stream grows on its own rule: Social Security rises with inflation, a fixed pension stays flat. They are never inflated together (fix B1).</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9378,12 +9715,13 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9436,18 +9774,19 @@
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>The same one dated table, after both earlier copies were deleted.</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9500,18 +9839,19 @@
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>One dated table. Start age is 73 for those born 1951–1959 and 75 for those born 1960 or later; a Roth 401(k) is exempt (fix B4).</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9562,12 +9902,13 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9620,18 +9961,19 @@
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>One dated table. Start age is 73 for those born 1951–1959 and 75 for those born 1960 or later; a Roth 401(k) is exempt (fix B4).</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9684,15 +10026,20 @@
 A LIVE-PRICED account returns nothing: its value comes from today's prices, so staleness is not a question that applies to it. A value with no date recorded also returns nothing rather than being assumed fresh.</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>DECIDES whether a stated value is fresh enough to show without a warning.</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9745,18 +10092,19 @@
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>The amount a person types from their statement is the amount at THEIR full retirement age, not at 62 and not at 70 (fix B2). The full-retirement age itself comes from a birth-year table, to the month.</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9812,12 +10160,13 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9870,18 +10219,19 @@
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>The amount a person types from their statement is the amount at THEIR full retirement age, not at 62 and not at 70 (fix B2). The full-retirement age itself comes from a birth-year table, to the month.</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9936,12 +10286,13 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9996,12 +10347,13 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10056,12 +10408,13 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10116,12 +10469,13 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10176,12 +10530,13 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10236,12 +10591,13 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10299,23 +10655,24 @@
 HOW IT DIFFERS FROM THE 25 x YARDSTICK reported by the odds engine: this one knows how long you plan for and what your money earns; the yardstick knows neither.</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
         <is>
           <t>The Net worth screen builds this projection WITHOUT the person's big costs, while Cash flow, Budget, Goals and Social Security timing all include them. Same person, same day, two different nest eggs. Seen in the code; not yet confirmed on screen.</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>The recommended nest egg is 25× the yearly spending not covered by guaranteed income, counted from the start of the retirement year — which is why it differs from an outside calculator.</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10366,12 +10723,13 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10426,12 +10784,13 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10490,12 +10849,13 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10552,12 +10912,13 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10612,12 +10973,13 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10673,12 +11035,13 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10736,23 +11099,24 @@
 HOW IT DIFFERS FROM THE 25 x YARDSTICK reported by the odds engine: this one knows how long you plan for and what your money earns; the yardstick knows neither.</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
         <is>
           <t>The Net worth screen builds this projection WITHOUT the person's big costs, while Cash flow, Budget, Goals and Social Security timing all include them. Same person, same day, two different nest eggs. Seen in the code; not yet confirmed on screen.</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>The recommended nest egg is 25× the yearly spending not covered by guaranteed income, counted from the start of the retirement year — which is why it differs from an outside calculator.</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10805,23 +11169,24 @@
 The best-to-worst range re-runs the same plan at a lower and a higher return, so it reads as a range rather than a promise. It always contains the headline figure, and it is repeatable.</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
         <is>
           <t>The odds shown on Home, Plan and Cash flow are rounded to the nearest 5, while the compare tables still show them exact. One figure, two precisions — founder's open question.</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>One thousand futures, and the odds are rounded to the nearest 5. A genuine 100 or 0 is shown literally; 98 shows as 95, never as 100 (fix B6). The best-to-worst band was removed.</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10876,12 +11241,13 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10936,12 +11302,13 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10996,12 +11363,13 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11040,12 +11408,13 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -11084,12 +11453,13 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -11128,12 +11498,13 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -11172,12 +11543,13 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
         </is>
@@ -11216,12 +11588,13 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -11238,7 +11611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -11250,11 +11623,12 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="37" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="41" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="37" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="41" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11305,25 +11679,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Secondary calculations and decisions the engine makes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Errors or findings to address</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Decisions made</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -11378,12 +11757,13 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11438,12 +11818,13 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11493,12 +11874,13 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11553,12 +11935,13 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11608,12 +11991,13 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11669,12 +12053,13 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11730,12 +12115,13 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11791,12 +12177,13 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11851,12 +12238,13 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11912,12 +12300,13 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11973,12 +12362,13 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12033,12 +12423,13 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12093,12 +12484,13 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12153,12 +12545,13 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12214,12 +12607,13 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12274,12 +12668,13 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12334,12 +12729,13 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12394,12 +12790,13 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12454,12 +12851,13 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12510,12 +12908,13 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12570,12 +12969,13 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12633,23 +13033,24 @@
 HOW IT DIFFERS FROM THE 25 x YARDSTICK reported by the odds engine: this one knows how long you plan for and what your money earns; the yardstick knows neither.</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
         <is>
           <t>The Net worth screen builds this projection WITHOUT the person's big costs, while Cash flow, Budget, Goals and Social Security timing all include them. Same person, same day, two different nest eggs. Seen in the code; not yet confirmed on screen.</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>The recommended nest egg is 25× the yearly spending not covered by guaranteed income, counted from the start of the retirement year — which is why it differs from an outside calculator.</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12704,12 +13105,13 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12765,12 +13167,13 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12825,12 +13228,13 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12883,18 +13287,19 @@
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>Withdrawals, including required ones, are NOT counted as guaranteed income — counting money coming out of the pot as income would count the same dollars twice (fix B5).</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12950,12 +13355,13 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13010,12 +13416,13 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13054,12 +13461,13 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -13098,12 +13506,13 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -13142,12 +13551,13 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -13186,12 +13596,13 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -13230,12 +13641,13 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
         </is>
@@ -13252,7 +13664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -13264,11 +13676,12 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="37" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="41" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="37" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="41" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13319,25 +13732,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Secondary calculations and decisions the engine makes</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Errors or findings to address</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Decisions made</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -13392,12 +13810,13 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13452,12 +13871,13 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13512,12 +13932,13 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13572,12 +13993,13 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13628,12 +14050,13 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13688,12 +14111,13 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13749,12 +14173,13 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13809,12 +14234,13 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13869,12 +14295,13 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13929,12 +14356,13 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13990,12 +14418,13 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14051,12 +14480,13 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14112,12 +14542,13 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14172,12 +14603,13 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14232,12 +14664,13 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14291,21 +14724,26 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>DECIDES what counts as cash — and deliberately excludes money-market funds.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>Money-market funds are deliberately NOT counted as cash. Any institution that reports a sweep as a fund will therefore land in investments — worth watching per provider.</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Cash means checking, savings, high-yield savings and the uninvested sweep at a broker. Money-market funds are investments, because they pay dividends and are measured with the investments (founder, 2026-08-04).</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14360,12 +14798,13 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14420,12 +14859,13 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14480,12 +14920,13 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14540,12 +14981,13 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14600,12 +15042,13 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14660,12 +15103,13 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14720,12 +15164,13 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14780,12 +15225,13 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14840,12 +15286,13 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14901,12 +15348,13 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14959,18 +15407,19 @@
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>Explicit tables per filing status. A married band is not twice the single band — the 37% band starts at $768,700, not at double the single figure.</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15023,18 +15472,19 @@
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>Explicit tables per filing status. A married band is not twice the single band — the 37% band starts at $768,700, not at double the single figure.</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15089,12 +15539,13 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15149,12 +15600,13 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15193,12 +15645,13 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -15237,12 +15690,13 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -15281,12 +15735,13 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -15325,12 +15780,13 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -15369,12 +15825,13 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -15413,12 +15870,13 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -15457,12 +15915,13 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -741,226 +741,250 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Errors or findings to address</t>
+          <t>COLUMN — Questions for you (numbered)</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>What is known to be wrong or unproved about this figure, in plain English. Blank means nothing is on record yet — not that nothing is wrong.</t>
+          <t>My open questions about that engine or figure, each with a number that never changes. A number is never reused or renumbered, so an answer can always be matched to its question.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Decisions made</t>
+          <t>COLUMN — YOUR ANSWER — use the same number</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>The rulings that govern this figure, and why. The standing display and rounding rule applies to every row and is stated once at the top of this tab.</t>
+          <t>Answer here, starting each answer with the question number. Nothing else in the file needs to line up.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (mathematical)</t>
+          <t>COLUMN — Errors or findings to address</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
+          <t>What is known to be wrong or unproved about this figure, in plain English. Blank means nothing is on record yet — not that nothing is wrong.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (in words)</t>
+          <t>COLUMN — Decisions made</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
+          <t>The rulings that govern this figure, and why. The standing display and rounding rule applies to every row and is stated once at the top of this tab.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Engine ID</t>
+          <t>COLUMN — Formula (mathematical)</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
+          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Your name for it (72-metric file)</t>
+          <t>COLUMN — Formula (in words)</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
+          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Core screen?</t>
+          <t>COLUMN — Engine ID</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Whether the screen is part of the 55-70 core, the agreed first scope.</t>
+          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Row status</t>
+          <t>COLUMN — Your name for it (72-metric file)</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>VERIFIED with its date means a person read the screen and confirmed the chain. NOT STARTED means the screen has not been read yet. Nothing in between is claimed.</t>
+          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr"/>
-      <c r="B34" s="3" t="inlineStr"/>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>COLUMN — Core screen?</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Whether the screen is part of the 55-70 core, the agreed first scope.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Input ID</t>
+          <t>COLUMN — Row status</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>The identifier of a raw input, per the same standard.</t>
+          <t>VERIFIED with its date means a person read the screen and confirmed the chain. NOT STARTED means the screen has not been read yet. Nothing in between is claimed.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN — Variable name</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>What the raw value is called.</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Source</t>
+          <t>COLUMN — Input ID</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
+          <t>The identifier of a raw input, per the same standard.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Which metric uses it</t>
+          <t>COLUMN — Variable name</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Every metric identifier that depends on this input.</t>
+          <t>What the raw value is called.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Which engine uses it</t>
+          <t>COLUMN — Source</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Every engine identifier that reads this input.</t>
+          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="3" t="inlineStr"/>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>COLUMN — Which metric uses it</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Every metric identifier that depends on this input.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Complies with — naming</t>
+          <t>COLUMN — Which engine uses it</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
+          <t>Every engine identifier that reads this input.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Complies with — identifiers</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Complies with — objectives</t>
+          <t>Complies with — naming</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/standards/moneykeel_calc_spec_objectives-and-verification_v01.md</t>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="3" t="inlineStr"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Complies with — identifiers</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>Complies with — objectives</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/standards/moneykeel_calc_spec_objectives-and-verification_v01.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
           <t>COVERAGE — screens read so far</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>COVERAGE — what that means</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Every screen in the app is listed on its tab. Only Home carries figures so far; the rest are marked NOT STARTED. A rising count is not completeness while screens remain unread.</t>
         </is>
@@ -3361,9 +3385,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="37" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="41" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="41" customWidth="1" min="14" max="14"/>
+    <col width="41" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3589,7 +3615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3604,9 +3630,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="37" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="41" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="41" customWidth="1" min="14" max="14"/>
+    <col width="41" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3672,15 +3700,25 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Questions for you (numbered)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -3741,12 +3779,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3810,13 +3850,19 @@
           <t>One thousand futures, and the odds are rounded to the nearest 5. A genuine 100 or 0 is shown literally; 98 shows as 95, never as 100 (fix B6). The best-to-worst band was removed.</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Q19 — The odds are rounded to the nearest 5 on screen but shown exact in the compare tables. Round everywhere, or show exact everywhere?</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3872,12 +3918,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3937,12 +3985,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -3998,12 +4048,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4059,12 +4111,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4116,12 +4170,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4138,7 +4194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4153,9 +4209,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="37" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="41" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="41" customWidth="1" min="14" max="14"/>
+    <col width="41" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4221,15 +4279,25 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Questions for you (numbered)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -4293,13 +4361,19 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Q22 — How old is too old for a price before the screen warns? Today it is a fixed limit in the code; you have never set it.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4355,12 +4429,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4416,12 +4492,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4473,12 +4551,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4518,12 +4598,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -4563,12 +4645,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -4608,12 +4692,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -4653,12 +4739,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -4698,12 +4786,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
         </is>
@@ -4720,7 +4810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4735,9 +4825,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="37" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="41" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="41" customWidth="1" min="14" max="14"/>
+    <col width="41" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4803,15 +4895,25 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Questions for you (numbered)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -4873,13 +4975,19 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Q32 — The trend survives on a new device but the walk behind it does not. Should the trend say so, or show quietly?</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4941,13 +5049,19 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Q17 — "Return on cash + investments" counts money you paid in as a gain. Is the LABEL wrong, or the FORMULA? Fixing the formula means removing deposits and withdrawals before measuring.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5010,12 +5124,14 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5072,12 +5188,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5144,13 +5262,19 @@
           <t>Cash means checking, savings, high-yield savings and the uninvested sweep at a broker. Money-market funds are investments, because they pay dividends and are measured with the investments (founder, 2026-08-04).</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Q16 — Does foreign-currency cash count towards Cash, or sit apart until it is converted?</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5207,12 +5331,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5272,13 +5398,22 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Q10 — What order of evidence decides an asset's class? Draft: the institution's own class field, then the shape of the identifier (option symbols, nine-character bond numbers, currency codes), then words in the name, then ask you.
+Q11 — When nothing matches: refuse the line and ask, or park it as unclassified? Parking keeps the totals right and hides a gap; refusing is honest and stops the import.
+Q12 — Does the person's own answer always win and stick, even when the next sync disagrees? That is today's rule for holdings — confirm it holds for every class.
+Q13 — Commodities: is a fund that tracks gold (GLD) simply a fund with a "commodity" label for allocation, and do you want PHYSICAL metal — weight, unit, purity, storage, spot price — supported at launch?</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5345,13 +5480,19 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Q14 — What should a MIXED account be called on screen, when it holds several classes at once?</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5409,12 +5550,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5472,12 +5615,14 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5533,12 +5678,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5596,12 +5743,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5653,12 +5802,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5727,12 +5878,14 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5801,13 +5954,19 @@
           <t>The recommended nest egg is 25× the yearly spending not covered by guaranteed income, counted from the start of the retirement year — which is why it differs from an outside calculator.</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Q18 — Net worth projects the pot WITHOUT your big costs; Cash flow, Budget, Goals and Social Security timing all include them. Which is right for the Net worth screen?</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5868,12 +6027,14 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5936,12 +6097,14 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6001,13 +6164,19 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Q23 — Same question for a value you typed by hand: after how long should the app ask you to check it?</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6062,13 +6231,19 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Q15 — An institution word we do not recognise: refuse the line and ask you, or book it as unclassified with no direction? The old sign-guess is what minted the $1.4 million.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6136,12 +6311,14 @@
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6197,12 +6374,14 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6259,12 +6438,14 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6323,13 +6504,21 @@
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Q01 — Is Quantity for a bond the FACE amount (e.g. 227,000) with the price quoted per $100 of face, or the number of bonds? It decides how value and gain are worked out.
+Q02 — How should a bond be NAMED on screen? Draft: "US Treasury 4.25% Nov 2029", with the identifying number shown as a detail rather than the headline. Approve or rewrite.
+Q03 — Certificates of deposit: under Fixed Income, or their own class? They carry a term, a rate and an early-withdrawal penalty that a bond does not.</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6384,13 +6573,19 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Q04 — "Annual income" on a bond: the last twelve months actually received, or the forward estimate from today's coupon? Both are defensible and they differ.</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6446,12 +6641,14 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6508,13 +6705,19 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Q05 — Accrued interest: do we work it out ourselves — which needs a day-count rule per bond type — or only show what the institution gives us?</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6570,12 +6773,14 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6631,12 +6836,14 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6692,12 +6899,14 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6765,13 +6974,21 @@
           <t>A price is a ratio, not money: it keeps eight decimal places and is never rounded to cents. Rounding a Treasury bill price of $0.9888 to $0.99 invented $276 of gain on one row.</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Q06 — Options: is quantity held in CONTRACTS with the price per share (so value = contracts x 100 x price), or is the price already per contract? Today neither is applied and the value may be a hundredth of the truth.
+Q07 — Crypto: how many decimal places should a quantity keep? Some coins are held in very small fractions.
+Q08 — Foreign currency: is this cash held at an institution, or currency trading? And should that tab's "Dividend" row be "Interest"?</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6830,13 +7047,19 @@
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Q09 — Should the app store the UNIT beside every quantity — shares, contracts, coins, units of face, currency units — so nothing can be multiplied by the wrong price? Today one field holds all of them with nothing marking which.</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6900,12 +7123,14 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6969,12 +7194,14 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7030,12 +7257,14 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7096,13 +7325,19 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Q21 — On a second device the ledger is absent, so this reads nothing. Until history syncs, should it refuse in words rather than show a figure that looks like zero?</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7167,13 +7402,19 @@
           <t>Long-term is decided by DAYS, not calendar months (correction E7): 335 days used to count as long-term and be taxed at the lower rate.</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Q20 — A lot with no recorded purchase price is skipped, so its gain is simply absent. Should the screen SAY so — "gain not counted for N shares, no purchase price on record" — rather than quietly reporting less?</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7239,12 +7480,14 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7300,12 +7543,14 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7357,12 +7602,14 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7431,12 +7678,14 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7496,12 +7745,14 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7561,12 +7812,14 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7622,12 +7875,14 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7683,12 +7938,14 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7748,12 +8005,14 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7793,12 +8052,14 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -7838,12 +8099,14 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -7883,12 +8146,14 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -7905,7 +8170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -7920,9 +8185,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="37" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="41" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="41" customWidth="1" min="14" max="14"/>
+    <col width="41" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7988,15 +8255,25 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Questions for you (numbered)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -8064,12 +8341,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8137,12 +8416,14 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8210,12 +8491,14 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8283,12 +8566,14 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8347,12 +8632,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8411,12 +8698,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8475,12 +8764,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8535,13 +8826,19 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Q33 — Which index should each asset class be compared against, and should the person be able to change it?</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8601,12 +8898,14 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8665,12 +8964,14 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8729,12 +9030,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8793,12 +9096,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8838,12 +9143,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -8883,12 +9190,14 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -8928,12 +9237,14 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -8950,7 +9261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -8965,9 +9276,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="37" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="41" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="41" customWidth="1" min="14" max="14"/>
+    <col width="41" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9033,15 +9346,25 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Questions for you (numbered)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -9098,12 +9421,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9160,12 +9485,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9221,12 +9548,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9281,12 +9610,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9342,12 +9673,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9399,12 +9732,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9460,12 +9795,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9525,12 +9862,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9586,12 +9925,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9651,12 +9992,14 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9716,12 +10059,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9781,12 +10126,14 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9845,13 +10192,19 @@
           <t>One dated table. Start age is 73 for those born 1951–1959 and 75 for those born 1960 or later; a Roth 401(k) is exempt (fix B4).</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Q31 — Required withdrawals are estimated from balances we hold. When an institution states its own required figure, does theirs win?</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9903,12 +10256,14 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9968,12 +10323,14 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10034,12 +10391,14 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10099,12 +10458,14 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10161,12 +10522,14 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10226,12 +10589,14 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10287,12 +10652,14 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10348,12 +10715,14 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10409,12 +10778,14 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10470,12 +10841,14 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10531,12 +10904,14 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10592,12 +10967,14 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10667,12 +11044,14 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10724,12 +11103,14 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10785,12 +11166,14 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10850,12 +11233,14 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10913,12 +11298,14 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10974,12 +11361,14 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11036,12 +11425,14 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11111,12 +11502,14 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11181,12 +11574,14 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11242,12 +11637,14 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11302,13 +11699,19 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Q26 — What education inflation rate should the college projection use, and should it be visible and editable on the screen?</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11364,12 +11767,14 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11409,12 +11814,14 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -11454,12 +11861,14 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -11499,12 +11908,14 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -11544,12 +11955,14 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
         </is>
@@ -11589,12 +12002,14 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -11611,7 +12026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -11626,9 +12041,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="37" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="41" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="41" customWidth="1" min="14" max="14"/>
+    <col width="41" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11694,15 +12111,25 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Questions for you (numbered)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -11758,12 +12185,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11819,12 +12248,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11875,12 +12306,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11936,12 +12369,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11992,12 +12427,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12054,12 +12491,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12116,12 +12555,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12178,12 +12619,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12239,12 +12682,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12301,12 +12746,14 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12363,12 +12810,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12424,12 +12873,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12485,12 +12936,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12546,12 +12999,14 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12608,12 +13063,14 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12669,12 +13126,14 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12730,12 +13189,14 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12791,12 +13252,14 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12852,12 +13315,14 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12909,12 +13374,14 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12970,12 +13437,14 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13045,12 +13514,14 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13106,12 +13577,14 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13168,12 +13641,14 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13229,12 +13704,14 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13293,13 +13770,19 @@
           <t>Withdrawals, including required ones, are NOT counted as guaranteed income — counting money coming out of the pot as income would count the same dollars twice (fix B5).</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Q30 — The draw from savings is shown as one figure a month. Should it hold steady in today's dollars, or rise with inflation each year?</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13356,12 +13839,14 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13417,12 +13902,14 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13462,12 +13949,14 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -13507,12 +13996,14 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -13552,12 +14043,14 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -13597,12 +14090,14 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -13642,12 +14137,14 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
         </is>
@@ -13664,7 +14161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -13679,9 +14176,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="37" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="41" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="41" customWidth="1" min="14" max="14"/>
+    <col width="41" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13747,15 +14246,25 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Questions for you (numbered)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER — use the same number</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -13811,12 +14320,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13872,12 +14383,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13933,12 +14446,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13994,12 +14509,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14051,12 +14568,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14112,12 +14631,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14174,12 +14695,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14234,13 +14757,19 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Q27 — "Typical free cash to save" uses the middle of recent months. How many months should it look back, and should a one-off windfall be excluded?</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14296,12 +14825,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14357,12 +14888,14 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14419,12 +14952,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14481,12 +15016,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14543,12 +15080,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14604,12 +15143,14 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14665,12 +15206,14 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14738,12 +15281,14 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14798,13 +15343,19 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Q25 — How many years of income should the default life-cover estimate replace, and does it assume the mortgage is cleared?</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14860,12 +15411,14 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14921,12 +15474,14 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14981,13 +15536,19 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Q28 — How many months of essentials should the app treat as safe by default — and is that number yours to set per person, or one figure for everyone?</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15043,12 +15604,14 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15104,12 +15667,14 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15165,12 +15730,14 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15225,13 +15792,19 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Q29 — What size of shock should the test use by default, and should it be a fixed dollar figure or a share of the person's spending?</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15287,12 +15860,14 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15349,12 +15924,14 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15413,13 +15990,19 @@
           <t>Explicit tables per filing status. A married band is not twice the single band — the 37% band starts at $768,700, not at double the single figure.</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Q24 — State tax is applied to taxable accounts only. Do you want a state rate captured per person, or to keep the single blended figure we use now?</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15479,12 +16062,14 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15540,12 +16125,14 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15601,12 +16188,14 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15646,12 +16235,14 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -15691,12 +16282,14 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -15736,12 +16329,14 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -15781,12 +16376,14 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -15826,12 +16423,14 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -15871,12 +16470,14 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -15916,12 +16517,14 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Whether the screen is part of the 55-70 core, the agreed first scope.</t>
+          <t>Whether the screen is part of the 55-70 core, the agreed first scope. Currently NOT DETERMINED on every row: the core list has never been written down, so no row can honestly claim to be in or out of it.</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -3922,7 +3922,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -3989,7 +3989,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -4052,7 +4052,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -4115,7 +4115,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -4174,7 +4174,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -4370,7 +4370,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -4496,7 +4496,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -4555,7 +4555,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -4602,7 +4602,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -4649,7 +4649,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -4696,7 +4696,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -4743,7 +4743,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -4790,7 +4790,7 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -4984,7 +4984,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -5128,7 +5128,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -5192,7 +5192,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -5271,7 +5271,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -5335,7 +5335,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -5410,7 +5410,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -5489,7 +5489,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -5554,7 +5554,7 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -5619,7 +5619,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -5682,7 +5682,7 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -5747,7 +5747,7 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -5806,7 +5806,7 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -5882,7 +5882,7 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -5963,7 +5963,7 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -6031,7 +6031,7 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -6101,7 +6101,7 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -6173,7 +6173,7 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -6240,7 +6240,7 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -6315,7 +6315,7 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -6378,7 +6378,7 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -6442,7 +6442,7 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -6515,7 +6515,7 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -6582,7 +6582,7 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -6645,7 +6645,7 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -6714,7 +6714,7 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -6777,7 +6777,7 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -6840,7 +6840,7 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -6903,7 +6903,7 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -6985,7 +6985,7 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -7056,7 +7056,7 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -7127,7 +7127,7 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -7198,7 +7198,7 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -7261,7 +7261,7 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -7334,7 +7334,7 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -7411,7 +7411,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -7484,7 +7484,7 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -7547,7 +7547,7 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -7606,7 +7606,7 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -7682,7 +7682,7 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -7749,7 +7749,7 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -7816,7 +7816,7 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -7879,7 +7879,7 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -7942,7 +7942,7 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -8009,7 +8009,7 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -8056,7 +8056,7 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -8103,7 +8103,7 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -8150,7 +8150,7 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -8345,7 +8345,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -8420,7 +8420,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -8495,7 +8495,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -8570,7 +8570,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -8636,7 +8636,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -8702,7 +8702,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -8768,7 +8768,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -8835,7 +8835,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -8902,7 +8902,7 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -8968,7 +8968,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -9034,7 +9034,7 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -9100,7 +9100,7 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -9147,7 +9147,7 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -9194,7 +9194,7 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -9241,7 +9241,7 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -9425,7 +9425,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -9489,7 +9489,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -9552,7 +9552,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -9614,7 +9614,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -9677,7 +9677,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -9736,7 +9736,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -9799,7 +9799,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -9866,7 +9866,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -9929,7 +9929,7 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -9996,7 +9996,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -10063,7 +10063,7 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -10130,7 +10130,7 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -10201,7 +10201,7 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -10260,7 +10260,7 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -10327,7 +10327,7 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -10395,7 +10395,7 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -10462,7 +10462,7 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -10526,7 +10526,7 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -10593,7 +10593,7 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -10656,7 +10656,7 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -10719,7 +10719,7 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -10782,7 +10782,7 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -10845,7 +10845,7 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -10908,7 +10908,7 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -10971,7 +10971,7 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -11048,7 +11048,7 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -11107,7 +11107,7 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -11170,7 +11170,7 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -11237,7 +11237,7 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -11302,7 +11302,7 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -11365,7 +11365,7 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -11429,7 +11429,7 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -11506,7 +11506,7 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -11578,7 +11578,7 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -11641,7 +11641,7 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -11708,7 +11708,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -11771,7 +11771,7 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -11818,7 +11818,7 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -11865,7 +11865,7 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -11912,7 +11912,7 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -11959,7 +11959,7 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -12006,7 +12006,7 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -12189,7 +12189,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -12252,7 +12252,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -12310,7 +12310,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -12373,7 +12373,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -12431,7 +12431,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -12495,7 +12495,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -12559,7 +12559,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -12623,7 +12623,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -12686,7 +12686,7 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -12750,7 +12750,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -12814,7 +12814,7 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -12877,7 +12877,7 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -12940,7 +12940,7 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -13003,7 +13003,7 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -13067,7 +13067,7 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -13130,7 +13130,7 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -13193,7 +13193,7 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -13256,7 +13256,7 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -13319,7 +13319,7 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -13378,7 +13378,7 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -13441,7 +13441,7 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -13518,7 +13518,7 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -13581,7 +13581,7 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -13645,7 +13645,7 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -13708,7 +13708,7 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -13779,7 +13779,7 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -13843,7 +13843,7 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -13906,7 +13906,7 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -13953,7 +13953,7 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -14000,7 +14000,7 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -14047,7 +14047,7 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -14094,7 +14094,7 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -14141,7 +14141,7 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -14324,7 +14324,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -14387,7 +14387,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -14450,7 +14450,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -14513,7 +14513,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -14572,7 +14572,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -14635,7 +14635,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -14699,7 +14699,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -14766,7 +14766,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -14829,7 +14829,7 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -14892,7 +14892,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -14956,7 +14956,7 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -15020,7 +15020,7 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -15084,7 +15084,7 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -15147,7 +15147,7 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -15210,7 +15210,7 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -15285,7 +15285,7 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -15352,7 +15352,7 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -15415,7 +15415,7 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -15478,7 +15478,7 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -15545,7 +15545,7 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -15608,7 +15608,7 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -15671,7 +15671,7 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -15734,7 +15734,7 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -15801,7 +15801,7 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -15864,7 +15864,7 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -15928,7 +15928,7 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -15999,7 +15999,7 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -16066,7 +16066,7 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -16129,7 +16129,7 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -16192,7 +16192,7 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -16239,7 +16239,7 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -16286,7 +16286,7 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -16333,7 +16333,7 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -16380,7 +16380,7 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -16427,7 +16427,7 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -16474,7 +16474,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -16521,7 +16521,7 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -81,7 +81,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -526,7 +528,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Everything a row must carry before its calculation can be written in code. The index tabs say what exists and where it is shown; this tab says what is still needed to say what each number IS.</t>
+          <t>Everything a row must carry before its calculation can be written in code, NUMBERED S01 upwards so a piece of work can be named by its number. The last column says where each one stands in this file today.</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -3395,212 +3397,446 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>What is needed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Why it is needed, and whether the file carries it today</t>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Why it is needed</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Where it stands in this file today</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>SECTION — WHAT THE NUMBER IS</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
           <t>The formula</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>The actual rules in plain English, followable by hand. Nothing in the index tabs carries it.</t>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>The actual rules, both as arithmetic and in plain English, followable by hand.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>DONE — 163 of 163 rows carry both forms.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>The inputs, one by one</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Every input named separately, with its unit, and where it comes from: the person typed it, an institution download, a connected provider, or another engine.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PART DONE — an inputs tab of 31 rows exists, but no row names ITS OWN inputs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
           <t>The decisions and assumptions applied</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Rounding, timing conventions, inflation, which balance is used, which date wins. Each labelled with whose decision it was — the founder's, the person's, or built in. This is the fourth link of objective 4.</t>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Rounding, timing conventions, inflation, which balance is used, which date wins — each labelled with whose decision it was: the founder's, the person's, or built in. The fourth link of objective 4.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>PART DONE — 32 of 163 rows, and none says whose decision it was.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
           <t>What comes out</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Dollars, a percentage, a date, a count or a range; its unit and its rounding.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>MISSING.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
           <t>What it says when it cannot be computed</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>The exact refusal. This is where wrong numbers get invented, so the refusal is part of the specification, not an afterthought.</t>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>The exact refusal. This is where wrong numbers get invented, so it is part of the specification, not an afterthought.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>MISSING.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
           <t>The grain</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Whether the figure is per holding, per account, per person or per household. Without it a total and a single line look identical.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>MISSING.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
           <t>The period</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>As of when, and over what window — this month, twelve months, since the person owned it.</t>
         </is>
       </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>MISSING.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>SECTION — WHAT PROVES IT</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
           <t>Worked examples</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>These inputs give this answer. Rung 2 re-runs them through the real engine on every build.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>MISSING.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
           <t>An example for every case</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>One per case the grid names: input missing, input degraded, a different shape per institution, time-bounded, related events, account type. This is rung 3, the floor for every calculation.</t>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>One per case the grid names: input missing, input degraded, a different shape per institution, time-bounded, related events, account type. Rung 3, the floor for every calculation.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>MISSING.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Verification level</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Whether this engine is marked for rung 4 (the written formula made executable and checked against the code on generated inputs) and rung 5 (laws that must hold for every input). Marked by the founder, recommended by me.</t>
         </is>
       </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>MISSING — the column does not exist yet.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>SECTION — WHAT CONNECTS IT</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
           <t>Which engines feed this engine</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>The engines it depends on. Without this, build order and the one-door design cannot be worked out — a metric points at an engine today, but engines do not point at each other.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>MISSING.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>Where it is implemented</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>The file and function that carry it, so file and code can be checked against each other on every build.</t>
         </is>
       </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>MISSING.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>SECTION — GOVERNANCE</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
           <t>The founder's verdict</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>His approval of the row. A row counts as documented only when he has approved it, so without this column the coverage count is meaningless.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>MISSING — the column does not exist yet.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>Lifecycle</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Live, cut, or superseded by another identifier. Identifiers are never reused, so a retired one must say what replaced it.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>MISSING.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>SECTION — NOT ON THE ORIGINAL LIST, STILL NEEDED</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Your name for it, from the 72-metric file</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>The bridge between the founder's vocabulary and the code's. Today only four of his seventy-two names appear anywhere in the old master.</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>MISSING — 0 of 163 rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>The duplication pass</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Figures that are the same thing under two identifiers — the Net worth figure that also sits on Plan. Objective 1 made real, and it must happen before the deeper columns are filled or the work gets done twice.</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>NOT STARTED — the founder flagged it; rows now exist, so it is due.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Which screens are the 55-70 core</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>The agreed first scope has never been written down, so no row can honestly say whether it is in or out.</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED on every row.</t>
         </is>
       </c>
     </row>

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -828,250 +828,262 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Questions for you (numbered)</t>
+          <t>COLUMN — Same figure as (S16)</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>My open questions about that engine or figure, each with a number that never changes. A number is never reused or renumbered, so an answer can always be matched to its question.</t>
+          <t>Where the same figure appears under more than one identifier, the row names the surviving identifier and why. Nothing is deleted: identifiers are never reused, so a folded row stays visible and says what it became.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — YOUR ANSWER — use the same number</t>
+          <t>COLUMN — Questions for you (numbered)</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Answer here, starting each answer with the question number. Nothing else in the file needs to line up.</t>
+          <t>My open questions about that engine or figure, each with a number that never changes. A number is never reused or renumbered, so an answer can always be matched to its question.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Errors or findings to address</t>
+          <t>COLUMN — YOUR ANSWER — use the same number</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>What is known to be wrong or unproved about this figure, in plain English. Blank means nothing is on record yet — not that nothing is wrong.</t>
+          <t>Answer here, starting each answer with the question number. Nothing else in the file needs to line up.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Decisions made (S03)</t>
+          <t>COLUMN — Errors or findings to address</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>The rulings and assumptions that govern this figure, each marked with WHOSE decision it was: [Founder] his own ruling, [The person] something the user set, [Built in] an assumption nobody chose on a screen — which is usually why a number looks wrong. The standing display and rounding rule applies to every row and is stated at the top of this tab.</t>
+          <t>What is known to be wrong or unproved about this figure, in plain English. Blank means nothing is on record yet — not that nothing is wrong.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (mathematical)</t>
+          <t>COLUMN — Decisions made (S03)</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
+          <t>The rulings and assumptions that govern this figure, each marked with WHOSE decision it was: [Founder] his own ruling, [The person] something the user set, [Built in] an assumption nobody chose on a screen — which is usually why a number looks wrong. The standing display and rounding rule applies to every row and is stated at the top of this tab.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (in words)</t>
+          <t>COLUMN — Formula (mathematical)</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
+          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Engine ID</t>
+          <t>COLUMN — Formula (in words)</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
+          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Your name for it (72-metric file)</t>
+          <t>COLUMN — Engine ID</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
+          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Core screen?</t>
+          <t>COLUMN — Your name for it (72-metric file)</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Whether the screen is part of the 55-70 core, the agreed first scope. Currently NOT DETERMINED on every row: the core list has never been written down, so no row can honestly claim to be in or out of it.</t>
+          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>COLUMN — Core screen?</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Whether the screen is part of the 55-70 core, the agreed first scope. Currently NOT DETERMINED on every row: the core list has never been written down, so no row can honestly claim to be in or out of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
           <t>COLUMN — Row status</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>VERIFIED with its date means a person read the screen and confirmed the chain. NOT STARTED means the screen has not been read yet. Nothing in between is claimed.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr"/>
-      <c r="B43" s="3" t="inlineStr"/>
-    </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN — Input ID</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>The identifier of a raw input, per the same standard.</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Variable name</t>
+          <t>COLUMN — Input ID</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>What the raw value is called.</t>
+          <t>The identifier of a raw input, per the same standard.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Source</t>
+          <t>COLUMN — Variable name</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
+          <t>What the raw value is called.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Which metric uses it</t>
+          <t>COLUMN — Source</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Every metric identifier that depends on this input.</t>
+          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>COLUMN — Which metric uses it</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Every metric identifier that depends on this input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t>COLUMN — Which engine uses it</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Every engine identifier that reads this input.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr"/>
-      <c r="B49" s="3" t="inlineStr"/>
-    </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Complies with — naming</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Complies with — identifiers</t>
+          <t>Complies with — naming</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>Complies with — identifiers</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
           <t>Complies with — objectives</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>MoneyKeel/documents/standards/moneykeel_calc_spec_objectives-and-verification_v01.md</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr"/>
-      <c r="B53" s="3" t="inlineStr"/>
-    </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>COVERAGE — screens read so far</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>COVERAGE — screens read so far</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
           <t>COVERAGE — what that means</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>Every screen in the app is listed on its tab. Only Home carries figures so far; the rest are marked NOT STARTED. A rising count is not completeness while screens remain unread.</t>
         </is>
@@ -4402,11 +4414,12 @@
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="37" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="36" customWidth="1" min="19" max="19"/>
-    <col width="41" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="41" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="41" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4459,7 +4472,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>DONE — 163 of 163 rows carry both forms.</t>
+          <t>COMPLETE — 163 of 163 carry both forms.</t>
         </is>
       </c>
     </row>
@@ -4476,12 +4489,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Every input named separately, with its unit, and where it comes from: the person typed it, an institution download, a connected provider, or another engine.</t>
+          <t>Every input named, with its unit and where it comes from.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>DONE where it is on record — every row carries its own inputs; 72 read NOT DETERMINED because the old master never held an input list for that engine.</t>
+          <t>PARTIAL — every row carries a cell; 91 name their inputs, 72 read NOT DETERMINED because the old master never held an input list for that engine.</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4511,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Rounding, timing conventions, inflation, which balance is used, which date wins — each labelled with whose decision it was: the founder's, the person's, or built in. The fourth link of objective 4.</t>
+          <t>Each marked with whose decision it was: the founder's, the person's, or built in.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>DONE — every row now carries its decisions and assumptions marked [Founder], [The person] or [Built in]; 126 read NOT DETERMINED, meaning no assumption is on record yet.</t>
+          <t>PARTIAL — every row carries a cell; 37 name a real decision, 126 read NOT DETERMINED.</t>
         </is>
       </c>
     </row>
@@ -4520,12 +4533,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Dollars, a percentage, a date, a count or a range; its unit and its rounding.</t>
+          <t>Dollars, a percentage, a date, a count; its unit and its rounding.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>DONE — 163 of 163, derived by rule from the label and formula and marked as derived. Needs confirming, not trusting.</t>
+          <t>COMPLETE — 163 of 163, derived by rule from the label and formula and marked as derived. Confirm rather than trust.</t>
         </is>
       </c>
     </row>
@@ -4542,12 +4555,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>The exact refusal. This is where wrong numbers get invented, so it is part of the specification, not an afterthought.</t>
+          <t>The exact refusal — where wrong numbers get invented.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>PART DONE — 126 of 163 written; 37 read NOT DETERMINED because that engine has not been read for its refusal yet.</t>
+          <t>PARTIAL — 126 of 163 written; 37 read NOT DETERMINED because that engine has not been read for its refusal yet.</t>
         </is>
       </c>
     </row>
@@ -4564,12 +4577,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Whether the figure is per holding, per account, per person or per household. Without it a total and a single line look identical.</t>
+          <t>One figure per holding, account, debt, goal, category, month or person.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>DONE — 163 of 163, derived by rule and marked as derived.</t>
+          <t>COMPLETE — 163 of 163, derived by rule and marked as derived.</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4599,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>As of when, and over what window — this month, twelve months, since the person owned it.</t>
+          <t>As of when, and over what window.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>DONE — 163 of 163, derived by rule and marked as derived.</t>
+          <t>COMPLETE — 163 of 163, derived by rule and marked as derived.</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4636,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>MISSING.</t>
+          <t>NOT STARTED — waits on the founder's answers to the numbered questions, since an example needs the rule settled first.</t>
         </is>
       </c>
     </row>
@@ -4640,12 +4653,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>One per case the grid names: input missing, input degraded, a different shape per institution, time-bounded, related events, account type. Rung 3, the floor for every calculation.</t>
+          <t>One per case the grid names: missing, degraded, per institution, time-bounded, related events, account type. Rung 3.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>MISSING.</t>
+          <t>NOT STARTED — the biggest single piece of work, and it belongs in the per-family detail files rather than here.</t>
         </is>
       </c>
     </row>
@@ -4662,12 +4675,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Whether this engine is marked for rung 4 (the written formula made executable and checked against the code on generated inputs) and rung 5 (laws that must hold for every input). Marked by the founder, recommended by me.</t>
+          <t>Which engines are marked for rung 4 and rung 5. Marked by the founder, recommended by me.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>MISSING — the column does not exist yet.</t>
+          <t>NOT STARTED — the column does not exist yet.</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4707,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>The engines it depends on. Without this, build order and the one-door design cannot be worked out — a metric points at an engine today, but engines do not point at each other.</t>
+          <t>The engines it depends on — without it, build order and the one-door design cannot be worked out.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>DONE — read from the code itself, not from any document. 90 rows name their dependencies; the rest read raw values only or have no source line on record.</t>
+          <t>COMPLETE — read from the code itself, not from any document. 90 rows name their dependencies; the rest read raw values only.</t>
         </is>
       </c>
     </row>
@@ -4721,7 +4734,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>MISSING.</t>
+          <t>NOT STARTED.</t>
         </is>
       </c>
     </row>
@@ -4748,12 +4761,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>His approval of the row. A row counts as documented only when he has approved it, so without this column the coverage count is meaningless.</t>
+          <t>A row counts as documented only when he has approved it.</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>MISSING — the column does not exist yet.</t>
+          <t>NOT STARTED — the column does not exist yet, so the coverage count means nothing until it does.</t>
         </is>
       </c>
     </row>
@@ -4770,12 +4783,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Live, cut, or superseded by another identifier. Identifiers are never reused, so a retired one must say what replaced it.</t>
+          <t>Live, cut, or superseded by another identifier.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>MISSING.</t>
+          <t>NOT STARTED.</t>
         </is>
       </c>
     </row>
@@ -4802,12 +4815,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>The bridge between the founder's vocabulary and the code's. Today only four of his seventy-two names appear anywhere in the old master.</t>
+          <t>The bridge between the founder's vocabulary and the code's.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>MISSING — 0 of 163 rows.</t>
+          <t>NOT STARTED — 0 of 163 rows.</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4837,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Figures that are the same thing under two identifiers — the Net worth figure that also sits on Plan. Objective 1 made real, and it must happen before the deeper columns are filled or the work gets done twice.</t>
+          <t>Figures that are the same thing under two identifiers.</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>NOT STARTED — the founder flagged it; rows now exist, so it is due.</t>
+          <t>COMPLETE — every group judged one at a time. 11 figures were being shown under 24 identifiers; the 13 folded rows now name the identifier that survives and why. 18 groups were checked and are NOT duplicates — one engine legitimately producing several figures — and say so, so the question is not asked twice. Two mis-assigned engines were found and recorded as findings.</t>
         </is>
       </c>
     </row>
@@ -4846,12 +4859,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>The agreed first scope has never been written down, so no row can honestly say whether it is in or out.</t>
+          <t>The agreed first scope has never been written down.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>READY FOR THE FOUNDER — the core_screens tab lists all 49 screens with my recommendation (39 yes, 5 no, 5 borderline) and a column for his decision.</t>
+          <t>READY FOR THE FOUNDER — the core_screens tab lists all 49 screens with my recommendation (39 in, 5 out, 5 borderline) and a column for his decision.</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4887,11 +4900,12 @@
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="37" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="36" customWidth="1" min="19" max="19"/>
-    <col width="41" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="41" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="41" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4987,25 +5001,30 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>Same figure as (S16)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Questions for you (numbered)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YOUR ANSWER — use the same number</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -5095,15 +5114,20 @@
           <t>[Founder] Assets minus debts, computed each time and never stored as a third number that could disagree with its own halves. A genuine negative is shown, never floored at zero.</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>THE SURVIVING IDENTIFIER for this figure. Folded in: MK-NW-M-016. Net worth. "Net worth so far" during setup is the same figure as the headline, mid-way through entry.</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5198,19 +5222,20 @@
 [Built in] The assumed rate of return, which the person can change on the cockpit.</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
         <is>
           <t>Q19 — The odds are rounded to the nearest 5 on screen but shown exact in the compare tables. Round everywhere, or show exact everywhere?</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5302,12 +5327,13 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5403,12 +5429,13 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5500,12 +5527,13 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5594,15 +5622,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>THE SURVIVING IDENTIFIER for this figure. Folded in: MK-CF-M-018. Money in this month. "In (take-home)" on Cash flow is the same figure as "Income" on Home.</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5690,12 +5723,13 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -5712,7 +5746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5733,11 +5767,12 @@
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="37" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="36" customWidth="1" min="19" max="19"/>
-    <col width="41" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="41" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="41" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5833,25 +5868,30 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>Same figure as (S16)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Questions for you (numbered)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YOUR ANSWER — use the same number</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -5949,19 +5989,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
         <is>
           <t>Q22 — How old is too old for a price before the screen warns? Today it is a fixed limit in the code; you have never set it.</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6053,12 +6094,13 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6147,15 +6189,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>THE SAME FIGURE AS MK-MN-M-015 — The insights list. Home shows the top three of the same list the Insights screen shows in full.</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6243,12 +6290,13 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6295,12 +6343,13 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -6347,12 +6396,13 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -6399,12 +6449,13 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -6451,12 +6502,13 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -6503,12 +6555,13 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
         </is>
@@ -6525,7 +6578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:X49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6546,11 +6599,12 @@
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="37" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="36" customWidth="1" min="19" max="19"/>
-    <col width="41" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="41" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="41" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6646,25 +6700,30 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>Same figure as (S16)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Questions for you (numbered)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YOUR ANSWER — use the same number</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -6760,19 +6819,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
         <is>
           <t>Q32 — The trend survives on a new device but the walk behind it does not. Should the trend say so, or show quietly?</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6868,19 +6928,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
         <is>
           <t>Q17 — "Return on cash + investments" counts money you paid in as a gain. Is the LABEL wrong, or the FORMULA? Fixing the formula means removing deposits and withdrawals before measuring.</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -6979,12 +7040,13 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7077,12 +7139,13 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7179,19 +7242,20 @@
           <t>[Founder] Cash means checking, savings, high-yield savings and the uninvested sweep at a broker. Money-market funds are investments, because they pay dividends and are measured with the investments (founder, 2026-08-04).</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
         <is>
           <t>Q16 — Does foreign-currency cash count towards Cash, or sit apart until it is converted?</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7275,7 +7339,11 @@
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>This row names ACCOUNT_SHARE_OF_TOTAL, but personal property is its own total, not a share of one.</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
@@ -7284,12 +7352,13 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7383,7 +7452,8 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
         <is>
           <t>Q10 — What order of evidence decides an asset's class? Draft: the institution's own class field, then the shape of the identifier (option symbols, nine-character bond numbers, currency codes), then words in the name, then ask you.
 Q11 — When nothing matches: refuse the line and ask, or park it as unclassified? Parking keeps the totals right and hides a gap; refusing is honest and stops the import.
@@ -7391,14 +7461,14 @@
 Q13 — Commodities: is a fund that tracks gold (GLD) simply a fund with a "commodity" label for allocation, and do you want PHYSICAL metal — weight, unit, purity, storage, spot price — supported at launch?</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7499,19 +7569,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
         <is>
           <t>Q14 — What should a MIXED account be called on screen, when it holds several classes at once?</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7605,12 +7676,13 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7704,12 +7776,13 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7801,12 +7874,13 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7900,12 +7974,13 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -7993,12 +8068,13 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8099,12 +8175,13 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8207,17 +8284,22 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
+          <t>THE SAME FIGURE AS MK-PL-M-033 — The projected pot at retirement, shown on Net worth as "on track for $X by age Y" and on the cockpit as "your $X grows to $Y". One figure, two screens — the founder spotted this one himself.</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>Q18 — Net worth projects the pot WITHOUT your big costs; Cash flow, Budget, Goals and Social Security timing all include them. Which is right for the Net worth screen?</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8307,15 +8389,20 @@
           <t>[Founder] Assets minus debts, computed each time and never stored as a third number that could disagree with its own halves. A genuine negative is shown, never floored at zero.</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>THE SAME FIGURE AS MK-XS-M-001 — Net worth. "Net worth so far" during setup is the same figure as the headline, mid-way through entry.</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8410,12 +8497,13 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8511,17 +8599,22 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
+          <t>THE SURVIVING IDENTIFIER for this figure. Folded in: MK-PL-M-016. An account's value. The balance listed under required withdrawals is the same figure as Market value on account detail.</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>Q23 — Same question for a value you typed by hand: after how long should the app ask you to check it?</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8610,19 +8703,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
         <is>
           <t>Q15 — An institution word we do not recognise: refuse the line and ask you, or book it as unclassified with no direction? The old sign-guess is what minted the $1.4 million.</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8726,12 +8820,13 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8823,12 +8918,13 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -8921,12 +9017,13 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9019,21 +9116,22 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
         <is>
           <t>Q01 — Is Quantity for a bond the FACE amount (e.g. 227,000) with the price quoted per $100 of face, or the number of bonds? It decides how value and gain are worked out.
 Q02 — How should a bond be NAMED on screen? Draft: "US Treasury 4.25% Nov 2029", with the identifying number shown as a detail rather than the headline. Approve or rewrite.
 Q03 — Certificates of deposit: under Fixed Income, or their own class? They carry a term, a rate and an early-withdrawal penalty that a bond does not.</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9124,17 +9222,22 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
+          <t>THE SURVIVING IDENTIFIER for this figure. Folded in: MK-NW-M-043. The coupon a bond pays in a year. "Interest payments" on account detail and "COUPON / YR" on the bonds screen.</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
           <t>Q04 — "Annual income" on a bond: the last twelve months actually received, or the forward estimate from today's coupon? Both are defensible and they differ.</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9226,12 +9329,13 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9322,19 +9426,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
         <is>
           <t>Q05 — Accrued interest: do we work it out ourselves — which needs a day-count rule per bond type — or only show what the institution gives us?</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9426,12 +9531,13 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9523,12 +9629,13 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9620,12 +9727,13 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9724,20 +9832,25 @@
         </is>
       </c>
       <c r="S31" t="inlineStr">
+        <is>
+          <t>THE SURVIVING IDENTIFIER for this figure. Folded in: MK-NW-M-040. A holding's current value, on holding detail and again while itemising an account.</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
         <is>
           <t>Q06 — Options: is quantity held in CONTRACTS with the price per share (so value = contracts x 100 x price), or is the price already per contract? Today neither is applied and the value may be a hundredth of the truth.
 Q07 — Crypto: how many decimal places should a quantity keep? Some coins are held in very small fractions.
 Q08 — Foreign currency: is this cash held at an institution, or currency trading? And should that tab's "Dividend" row be "Interest"?</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9830,19 +9943,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
         <is>
           <t>Q09 — Should the app store the UNIT beside every quantity — shares, contracts, coins, units of face, currency units — so nothing can be multiplied by the wrong price? Today one field holds all of them with nothing marking which.</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -9938,12 +10052,13 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10039,12 +10154,13 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10136,12 +10252,13 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10236,19 +10353,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
         <is>
           <t>Q21 — On a second device the ledger is absent, so this reads nothing. Until history syncs, should it refuse in words rather than show a figure that looks like zero?</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10343,19 +10461,20 @@
           <t>[Founder] Long-term is decided by DAYS, not calendar months (correction E7): 335 days used to count as long-term and be taxed at the lower rate.</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
         <is>
           <t>Q20 — A lot with no recorded purchase price is skipped, so its gain is simply absent. Should the screen SAY so — "gain not counted for N shares, no purchase price on record" — rather than quietly reporting less?</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10453,12 +10572,13 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10550,12 +10670,13 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10643,12 +10764,13 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10746,15 +10868,20 @@
           <t>[Founder] A price is a ratio, not money: it keeps eight decimal places and is never rounded to cents. Rounding a Treasury bill price of $0.9888 to $0.99 invented $276 of gain on one row.</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>THE SAME FIGURE AS MK-NW-M-030 — A holding's current value, on holding detail and again while itemising an account.</t>
+        </is>
+      </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10850,12 +10977,13 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -10951,12 +11079,13 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11045,15 +11174,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>THE SAME FIGURE AS MK-NW-M-024 — The coupon a bond pays in a year. "Interest payments" on account detail and "COUPON / YR" on the bonds screen.</t>
+        </is>
+      </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11145,12 +11279,13 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11246,12 +11381,13 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11298,12 +11434,13 @@
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -11350,12 +11487,13 @@
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -11402,12 +11540,13 @@
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -11424,7 +11563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -11445,11 +11584,12 @@
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="37" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="36" customWidth="1" min="19" max="19"/>
-    <col width="41" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="41" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="41" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11545,25 +11685,30 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>Same figure as (S16)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Questions for you (numbered)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YOUR ANSWER — use the same number</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -11660,15 +11805,20 @@
           <t>[Founder] The identity must close: ending = beginning + money in − money out + income − costs + market change. A direction stated by the institution never overrides a contradicting sign — a −$500 line marked IN is a reversal.</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>THE SURVIVING IDENTIFIER for this figure. Folded in: MK-PF-M-003. The ending value, shown as its own line and again inside the heading "HOW $X BECAME $Y". Same screen, same figure, twice.</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11768,12 +11918,13 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11870,15 +12021,20 @@
           <t>[Founder] The identity must close: ending = beginning + money in − money out + income − costs + market change. A direction stated by the institution never overrides a contradicting sign — a −$500 line marked IN is a reversal.</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>THE SAME FIGURE AS MK-PF-M-001 — The ending value, shown as its own line and again inside the heading "HOW $X BECAME $Y". Same screen, same figure, twice.</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -11978,12 +12134,13 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12078,12 +12235,13 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12178,12 +12336,13 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12278,12 +12437,13 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12372,19 +12532,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
         <is>
           <t>Q33 — Which index should each asset class be compared against, and should the person be able to change it?</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12476,12 +12637,13 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12576,12 +12738,13 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12676,12 +12839,13 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12776,12 +12940,13 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -12828,12 +12993,13 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -12880,12 +13046,13 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -12932,12 +13099,13 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -12954,7 +13122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W43"/>
+  <dimension ref="A1:X43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -12975,11 +13143,12 @@
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="37" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="36" customWidth="1" min="19" max="19"/>
-    <col width="41" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="41" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="41" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13075,25 +13244,30 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>Same figure as (S16)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Questions for you (numbered)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YOUR ANSWER — use the same number</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -13186,12 +13360,13 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13284,12 +13459,13 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13381,12 +13557,13 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13477,12 +13654,13 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13574,12 +13752,13 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13667,12 +13846,13 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13764,12 +13944,13 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13865,12 +14046,13 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -13962,12 +14144,13 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14060,12 +14243,13 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14158,15 +14342,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>THE SURVIVING IDENTIFIER for this figure. Folded in: MK-PL-M-029. What is being saved each month towards retirement — "Monthly saving until then" and "Retirement saving $X/mo now".</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14258,12 +14447,13 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14352,19 +14542,20 @@
           <t>[Founder] One dated table. Start age is 73 for those born 1951–1959 and 75 for those born 1960 or later; a Roth 401(k) is exempt (fix B4).</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
         <is>
           <t>Q31 — Required withdrawals are estimated from balances we hold. When an institution states its own required figure, does theirs win?</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14452,12 +14643,13 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14549,12 +14741,13 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14648,15 +14841,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>THE SAME FIGURE AS MK-NW-M-018 — An account's value. The balance listed under required withdrawals is the same figure as Market value on account detail.</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14750,12 +14948,13 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14845,15 +15044,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>THE SAME FIGURE AS MK-CF-M-011 — Guaranteed income being received now. Shown four ways: "You receive $X/mo" on Social Security timing, "incl. Social Security $X/mo" on the cockpit, as a source on Cash flow, and as a list on Monthly income. One figure, four identifiers.</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -14946,12 +15150,13 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15044,12 +15249,13 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15141,12 +15347,13 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15238,12 +15445,13 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15335,12 +15543,13 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15432,12 +15641,13 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15529,12 +15739,13 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15638,12 +15849,13 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15731,12 +15943,13 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15828,12 +16041,13 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -15926,15 +16140,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>THE SAME FIGURE AS MK-PL-M-011 — What is being saved each month towards retirement — "Monthly saving until then" and "Retirement saving $X/mo now".</t>
+        </is>
+      </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -16019,7 +16238,11 @@
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>This row names DEBT_PICTURE, but "Extra on debt $X/mo" is an amount the person chose on a dial, not a figure that engine produces.</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr">
         <is>
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
@@ -16028,12 +16251,13 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -16125,12 +16349,13 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -16220,15 +16445,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>THE SAME FIGURE AS MK-CF-M-011 — Guaranteed income being received now. Shown four ways: "You receive $X/mo" on Social Security timing, "incl. Social Security $X/mo" on the cockpit, as a source on Cash flow, and as a list on Monthly income. One figure, four identifiers.</t>
+        </is>
+      </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -16329,15 +16559,20 @@
 [The person] The retirement age in their plan.</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>THE SURVIVING IDENTIFIER for this figure. Folded in: MK-NW-M-015. The projected pot at retirement, shown on Net worth as "on track for $X by age Y" and on the cockpit as "your $X grows to $Y". One figure, two screens — the founder spotted this one himself.</t>
+        </is>
+      </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -16435,12 +16670,13 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -16532,12 +16768,13 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -16626,19 +16863,20 @@
           <t>[Built in] Inflation comes from a published feed, with a fallback figure when the feed is silent.</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
         <is>
           <t>Q26 — What education inflation rate should the college projection use, and should it be visible and editable on the screen?</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -16730,12 +16968,13 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -16782,12 +17021,13 @@
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -16834,12 +17074,13 @@
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -16886,12 +17127,13 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -16938,12 +17180,13 @@
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
         </is>
@@ -16990,12 +17233,13 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -17012,7 +17256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W34"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -17033,11 +17277,12 @@
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="37" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="36" customWidth="1" min="19" max="19"/>
-    <col width="41" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="41" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="41" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17133,25 +17378,30 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>Same figure as (S16)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Questions for you (numbered)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YOUR ANSWER — use the same number</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -17243,12 +17493,13 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -17340,12 +17591,13 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -17432,12 +17684,13 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -17529,12 +17782,13 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -17621,12 +17875,13 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -17719,12 +17974,13 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -17817,12 +18073,13 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -17915,12 +18172,13 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -18012,12 +18270,13 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -18110,12 +18369,13 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -18205,15 +18465,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>THE SURVIVING IDENTIFIER for this figure. Folded in: MK-PL-M-018, MK-PL-M-032, MK-CF-M-024. Guaranteed income being received now. Shown four ways: "You receive $X/mo" on Social Security timing, "incl. Social Security $X/mo" on the cockpit, as a source on Cash flow, and as a list on Monthly income. One figure, four identifiers.</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -18305,12 +18570,13 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -18402,12 +18668,13 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -18499,12 +18766,13 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -18594,15 +18862,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>THE SURVIVING IDENTIFIER for this figure. Folded in: MK-MN-M-007. Spending against plan for a category — the same comparison on Cash flow and on the expense screen. CONFIRM: the expense screen adds the amount being typed, which may make it a different figure.</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -18694,12 +18967,13 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -18791,12 +19065,13 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -18885,15 +19160,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>THE SAME FIGURE AS MK-XS-M-006 — Money in this month. "In (take-home)" on Cash flow is the same figure as "Income" on Home.</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -18985,12 +19265,13 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -19078,12 +19359,13 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -19175,12 +19457,13 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -19284,12 +19567,13 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -19381,12 +19665,13 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -19476,15 +19761,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>THE SAME FIGURE AS MK-CF-M-011 — Guaranteed income being received now. Shown four ways: "You receive $X/mo" on Social Security timing, "incl. Social Security $X/mo" on the cockpit, as a source on Cash flow, and as a list on Monthly income. One figure, four identifiers.</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -19576,12 +19866,13 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -19670,19 +19961,20 @@
           <t>[Founder] Withdrawals, including required ones, are NOT counted as guaranteed income — counting money coming out of the pot as income would count the same dollars twice (fix B5).</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
         <is>
           <t>Q30 — The draw from savings is shown as one figure a month. Should it hold steady in today's dollars, or rise with inflation each year?</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -19775,12 +20067,13 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -19872,12 +20165,13 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -19924,12 +20218,13 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -19976,12 +20271,13 @@
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -20028,12 +20324,13 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -20080,12 +20377,13 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -20132,12 +20430,13 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — the same screen as /invest, reached by a second route</t>
         </is>
@@ -20154,7 +20453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W38"/>
+  <dimension ref="A1:X38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -20175,11 +20474,12 @@
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="37" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="36" customWidth="1" min="19" max="19"/>
-    <col width="41" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="41" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="41" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20275,25 +20575,30 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>Same figure as (S16)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Questions for you (numbered)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YOUR ANSWER — use the same number</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Your name for it (72-metric file)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Core screen?</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Row status</t>
         </is>
@@ -20385,12 +20690,13 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -20482,12 +20788,13 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -20579,12 +20886,13 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -20676,12 +20984,13 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -20769,12 +21078,13 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -20866,12 +21176,13 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -20961,15 +21272,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>THE SAME FIGURE AS MK-CF-M-015 — Spending against plan for a category — the same comparison on Cash flow and on the expense screen. CONFIRM: the expense screen adds the amount being typed, which may make it a different figure.</t>
+        </is>
+      </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -21058,19 +21374,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
         <is>
           <t>Q27 — "Typical free cash to save" uses the middle of recent months. How many months should it look back, and should a one-off windfall be excluded?</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -21162,12 +21479,13 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -21259,12 +21577,13 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -21357,12 +21676,13 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -21455,12 +21775,13 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -21553,12 +21874,13 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -21650,12 +21972,13 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -21744,15 +22067,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>THE SURVIVING IDENTIFIER for this figure. Folded in: MK-HM-M-003. The insights list. Home shows the top three of the same list the Insights screen shows in full.</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -21852,12 +22180,13 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -21946,19 +22275,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
         <is>
           <t>Q25 — How many years of income should the default life-cover estimate replace, and does it assume the mortgage is cleared?</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -22050,12 +22380,13 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -22147,12 +22478,13 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -22241,19 +22573,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
         <is>
           <t>Q28 — How many months of essentials should the app treat as safe by default — and is that number yours to set per person, or one figure for everyone?</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -22345,12 +22678,13 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -22442,12 +22776,13 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -22539,12 +22874,13 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -22633,19 +22969,20 @@
           <t>NOT DETERMINED — no assumption recorded for this figure yet.</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr">
         <is>
           <t>Q29 — What size of shock should the test use by default, and should it be a fixed dollar figure or a share of the person's spending?</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -22737,12 +23074,13 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -22835,12 +23173,13 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -22929,19 +23268,20 @@
           <t>[Founder] Explicit tables per filing status. A married band is not twice the single band — the 37% band starts at $768,700, not at double the single figure.</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
         <is>
           <t>Q24 — State tax is applied to taxable accounts only. Do you want a state rate captured per person, or to keep the single blended figure we use now?</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -23033,12 +23373,13 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -23130,12 +23471,13 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -23227,12 +23569,13 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -23279,12 +23622,13 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -23331,12 +23675,13 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -23383,12 +23728,13 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -23435,12 +23781,13 @@
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -23487,12 +23834,13 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -23539,12 +23887,13 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>
@@ -23591,12 +23940,13 @@
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
         <is>
           <t>READ 2026-08-22 — no calculated figure on this screen</t>
         </is>

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -19,6 +19,7 @@
     <sheet name="inputs" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="database" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="core_screens" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="reconciliation" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +44,10 @@
     <font>
       <b val="1"/>
       <color rgb="001F3864"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
@@ -73,16 +78,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -450,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -632,458 +640,470 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TAB — core_screens</t>
+          <t>TAB — reconciliation</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Every screen in the app, its parent, my recommendation on whether it belongs to the 55-70 core, and a column for the founder to decide. Until this is decided, no row in the file can honestly claim to be in scope (S17).</t>
+          <t>The input map checked in BOTH directions: what the inputs tab says uses each input, against what each engine actually names in its own input list. Where the two disagree the row says so. The section at the foot lists inputs an engine names that appear nowhere on the inputs tab.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TAB — database</t>
+          <t>TAB — core_screens</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>What the app saves in the cloud: where each thing is stored, what it holds, which figures depend on it, how often it is written and at what grain. Also names what is deliberately NOT saved.</t>
+          <t>Every screen in the app, its parent, my recommendation on whether it belongs to the 55-70 core, and a column for the founder to decide. Until this is decided, no row in the file can honestly claim to be in scope (S17).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>TAB — database</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>What the app saves in the cloud: where each thing is stored, what it holds, which figures depend on it, how often it is written and at what grain. Also names what is deliberately NOT saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>TAB — inputs</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>The raw values the engines need before any calculation happens.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="3" t="inlineStr"/>
-    </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN — Metric ID</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>The identifier of the figure, per moneykeel_naming_spec_unique-identifier_v01.md. Given once, never changed, never reused.</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Parent Screen Name</t>
+          <t>COLUMN — Metric ID</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>One of: Home, Networth, Performance, Cashflow, Plan, Menu. Menu means reachable only from the menu.</t>
+          <t>The identifier of the figure, per moneykeel_naming_spec_unique-identifier_v01.md. Given once, never changed, never reused.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Secondary Screen Name</t>
+          <t>COLUMN — Parent Screen Name</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>The screen reached from the parent, or NA when the figure is on the parent screen itself.</t>
+          <t>One of: Home, Networth, Performance, Cashflow, Plan, Menu. Menu means reachable only from the menu.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name on Screen</t>
+          <t>COLUMN — Secondary Screen Name</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>The label copied exactly as it is worded on screen, including capitals. Where a figure wears different labels on different screens, all are listed.</t>
+          <t>The screen reached from the parent, or NA when the figure is on the parent screen itself.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name of Underlying Metric</t>
+          <t>COLUMN — Name on Screen</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>The metric's name in the code.</t>
+          <t>The label copied exactly as it is worded on screen, including capitals. Where a figure wears different labels on different screens, all are listed.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name of Underlying Engine</t>
+          <t>COLUMN — Name of Underlying Metric</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>The engine that produces the figure. NOT IN OLD MASTER means the engine exists in the code but has no row in the old master file.</t>
+          <t>The metric's name in the code.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Inputs it needs (S02)</t>
+          <t>COLUMN — Name of Underlying Engine</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Every input the engine reads, named. Carried from the old master where it has a row there.</t>
+          <t>The engine that produces the figure. NOT IN OLD MASTER means the engine exists in the code but has no row in the old master file.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — What comes out (S04)</t>
+          <t>COLUMN — Inputs it needs (S02)</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Dollars, a percentage, a date, a count; how it is held and how it is shown. Marked "derived by rule" where it was worked out from the label and formula rather than read from the engine — those need confirming.</t>
+          <t>Every input the engine reads, named. Carried from the old master where it has a row there.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — What it says when it cannot be computed (S05)</t>
+          <t>COLUMN — What comes out (S04)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>The refusal. Written where the engine has been read; NOT DETERMINED where it has not, rather than guessed.</t>
+          <t>Dollars, a percentage, a date, a count; how it is held and how it is shown. Marked "derived by rule" where it was worked out from the label and formula rather than read from the engine — those need confirming.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Grain (S06)</t>
+          <t>COLUMN — What it says when it cannot be computed (S05)</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>One figure per what: holding, account, debt, goal, category, month, or person.</t>
+          <t>The refusal. Written where the engine has been read; NOT DETERMINED where it has not, rather than guessed.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Period (S07)</t>
+          <t>COLUMN — Grain (S06)</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>As of when, and over what window.</t>
+          <t>One figure per what: holding, account, debt, goal, category, month, or person.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Engines it depends on (S11)</t>
+          <t>COLUMN — Period (S07)</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>The engines this one calls, read from the code itself. "None found" means it reads raw values only.</t>
+          <t>As of when, and over what window.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Secondary calculations and decisions the engine makes</t>
+          <t>COLUMN — Engines it depends on (S11)</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>The judgements an engine must make BEFORE its headline figure exists: what class an asset is, what to call it on screen, which units apply, whether a value is fresh. Each of these is a formula of its own and needs its own row.</t>
+          <t>The engines this one calls, read from the code itself. "None found" means it reads raw values only.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Same figure as (S16)</t>
+          <t>COLUMN — Secondary calculations and decisions the engine makes</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Where the same figure appears under more than one identifier, the row names the surviving identifier and why. Nothing is deleted: identifiers are never reused, so a folded row stays visible and says what it became.</t>
+          <t>The judgements an engine must make BEFORE its headline figure exists: what class an asset is, what to call it on screen, which units apply, whether a value is fresh. Each of these is a formula of its own and needs its own row.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Questions for you (numbered)</t>
+          <t>COLUMN — Same figure as (S16)</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>My open questions about that engine or figure, each with a number that never changes. A number is never reused or renumbered, so an answer can always be matched to its question.</t>
+          <t>Where the same figure appears under more than one identifier, the row names the surviving identifier and why. Nothing is deleted: identifiers are never reused, so a folded row stays visible and says what it became.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — YOUR ANSWER — use the same number</t>
+          <t>COLUMN — Questions for you (numbered)</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Answer here, starting each answer with the question number. Nothing else in the file needs to line up.</t>
+          <t>My open questions about that engine or figure, each with a number that never changes. A number is never reused or renumbered, so an answer can always be matched to its question.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Errors or findings to address</t>
+          <t>COLUMN — YOUR ANSWER — use the same number</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>What is known to be wrong or unproved about this figure, in plain English. Blank means nothing is on record yet — not that nothing is wrong.</t>
+          <t>Answer here, starting each answer with the question number. Nothing else in the file needs to line up.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Decisions made (S03)</t>
+          <t>COLUMN — Errors or findings to address</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>The rulings and assumptions that govern this figure, each marked with WHOSE decision it was: [Founder] his own ruling, [The person] something the user set, [Built in] an assumption nobody chose on a screen — which is usually why a number looks wrong. The standing display and rounding rule applies to every row and is stated at the top of this tab.</t>
+          <t>What is known to be wrong or unproved about this figure, in plain English. Blank means nothing is on record yet — not that nothing is wrong.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (mathematical)</t>
+          <t>COLUMN — Decisions made (S03)</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
+          <t>The rulings and assumptions that govern this figure, each marked with WHOSE decision it was: [Founder] his own ruling, [The person] something the user set, [Built in] an assumption nobody chose on a screen — which is usually why a number looks wrong. The standing display and rounding rule applies to every row and is stated at the top of this tab.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (in words)</t>
+          <t>COLUMN — Formula (mathematical)</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
+          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Engine ID</t>
+          <t>COLUMN — Formula (in words)</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
+          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Your name for it (72-metric file)</t>
+          <t>COLUMN — Engine ID</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
+          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Core screen?</t>
+          <t>COLUMN — Your name for it (72-metric file)</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Whether the screen is part of the 55-70 core, the agreed first scope. Currently NOT DETERMINED on every row: the core list has never been written down, so no row can honestly claim to be in or out of it.</t>
+          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>COLUMN — Core screen?</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Whether the screen is part of the 55-70 core, the agreed first scope. Currently NOT DETERMINED on every row: the core list has never been written down, so no row can honestly claim to be in or out of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
           <t>COLUMN — Row status</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>VERIFIED with its date means a person read the screen and confirmed the chain. NOT STARTED means the screen has not been read yet. Nothing in between is claimed.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="3" t="inlineStr"/>
-    </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN — Input ID</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>The identifier of a raw input, per the same standard.</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Variable name</t>
+          <t>COLUMN — Input ID</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>What the raw value is called.</t>
+          <t>The identifier of a raw input, per the same standard.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Source</t>
+          <t>COLUMN — Variable name</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
+          <t>What the raw value is called.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Which metric uses it</t>
+          <t>COLUMN — Source</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Every metric identifier that depends on this input.</t>
+          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>COLUMN — Which metric uses it</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Every metric identifier that depends on this input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>COLUMN — Which engine uses it</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Every engine identifier that reads this input.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr"/>
-      <c r="B50" s="3" t="inlineStr"/>
-    </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Complies with — naming</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Complies with — identifiers</t>
+          <t>Complies with — naming</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>Complies with — identifiers</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
           <t>Complies with — objectives</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>MoneyKeel/documents/standards/moneykeel_calc_spec_objectives-and-verification_v01.md</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
-      <c r="B54" s="3" t="inlineStr"/>
-    </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>COVERAGE — screens read so far</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>COVERAGE — screens read so far</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
           <t>COVERAGE — what that means</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>Every screen in the app is listed on its tab. Only Home carries figures so far; the rest are marked NOT STARTED. A rising count is not completeness while screens remain unread.</t>
         </is>
@@ -4381,6 +4401,2587 @@
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E96"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Input ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Engines the inputs tab says use it</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Engines that actually name it in their own input list</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>account balance</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>NET_WORTH · REQUIRED_WITHDRAWAL · TOTAL_CASH · TOTAL_INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>ACCOUNT_SHARE_OF_TOTAL · ACCOUNT_SPLIT · ALLOCATION_BY_CLASS · DEBT_PICTURE · NET_WORTH · PLANNED_SPENDING · TOTAL_CASH · TOTAL_INVESTABLE · TOTAL_INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — declared but not naming it: REQUIRED_WITHDRAWAL  |  naming it but not declared: ACCOUNT_SHARE_OF_TOTAL, ACCOUNT_SPLIT, ALLOCATION_BY_CLASS, DEBT_PICTURE, PLANNED_SPENDING, TOTAL_INVESTABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>account type (taxable, pre-tax, Roth)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>REQUIRED_WITHDRAWAL · TAX_TREATMENT</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>DECLARED BUT NEVER NAMED — the inputs tab says these engines use it, but no engine names it in its own input list. Unproved in one direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>institution name</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>ACCOUNT_SPLIT</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>DECLARED BUT NEVER NAMED — the inputs tab says these engines use it, but no engine names it in its own input list. Unproved in one direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>holding quantity (shares)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_MARKET_VALUE · HOLDING_SHARES</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_COST_BASIS · HOLDING_MARKET_VALUE · HOLDING_SHARES</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — naming it but not declared: HOLDING_COST_BASIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-005</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>holding price</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_MARKET_VALUE · PRICE_FRESHNESS</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_CAP_GAINS · HOLDING_MARKET_VALUE · PERFORMANCE_TABLE</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — declared but not naming it: PRICE_FRESHNESS  |  naming it but not declared: HOLDING_CAP_GAINS, PERFORMANCE_TABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-006</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>price fetched at</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>PRICE_FRESHNESS</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>PRICE_FRESHNESS</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>AGREES — both directions name the same engines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-007</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>purchase price and date (per lot)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_CAP_GAINS · HOLDING_COST_BASIS</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_CAP_GAINS · HOLDING_COST_BASIS · HOLDING_SHARES</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — naming it but not declared: HOLDING_SHARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-008</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>transaction amount</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>LEDGER · NW_CHANGE_WALK</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>LOOK_BACK · RETIREMENT_INCOME_NOW · SS_BENEFIT_AT_AGE · SS_CLAIM_FACTOR</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — declared but not naming it: LEDGER, NW_CHANGE_WALK  |  naming it but not declared: LOOK_BACK, RETIREMENT_INCOME_NOW, SS_BENEFIT_AT_AGE, SS_CLAIM_FACTOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-009</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>transaction date</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>LEDGER · NW_CHANGE_WALK</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>DECLARED BUT NEVER NAMED — the inputs tab says these engines use it, but no engine names it in its own input list. Unproved in one direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-010</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>transaction words (the institution's own wording)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>LEDGER · the institution-words table</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>DECLARED BUT NEVER NAMED — the inputs tab says these engines use it, but no engine names it in its own input list. Unproved in one direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-011</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>bond face value</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>BOND_FACTS</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>BOND_COUPON · BOND_FACTS · BOND_YIELD_TO_MATURITY</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — naming it but not declared: BOND_COUPON, BOND_YIELD_TO_MATURITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-012</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>bond coupon rate</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>BOND_COUPON · BOND_CURRENT_YIELD</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>BOND_COUPON · BOND_CURRENT_YIELD · BOND_FACTS · BOND_YIELD_TO_MATURITY</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — naming it but not declared: BOND_FACTS, BOND_YIELD_TO_MATURITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-013</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>bond maturity date</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>BOND_YEARS_LEFT · BOND_YIELD_TO_MATURITY</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>BOND_YEARS_LEFT · BOND_YIELD_TO_MATURITY</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>AGREES — both directions name the same engines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-014</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>debt balance</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_PICTURE</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_PICTURE · NET_WORTH</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — naming it but not declared: NET_WORTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-015</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>debt interest rate</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_PAYOFF</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_PICTURE · NET_WORTH</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — declared but not naming it: DEBT_PAYOFF  |  naming it but not declared: DEBT_PICTURE, NET_WORTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-016</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>debt minimum payment</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_REQUIRED_PAYMENT</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_PICTURE · DEBT_REQUIRED_PAYMENT · NET_WORTH · SPENDING_BY_KIND</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — naming it but not declared: DEBT_PICTURE, NET_WORTH, SPENDING_BY_KIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-017</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>birth year</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>RMD_START_AGE · SS_BENEFIT_AT_AGE</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>SS_BENEFIT_AT_AGE · SS_CLAIM_FACTOR · WHAT_THE_PLAN_STILL_NEEDS · WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — declared but not naming it: RMD_START_AGE  |  naming it but not declared: SS_CLAIM_FACTOR, WHAT_THE_PLAN_STILL_NEEDS, WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-018</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>retirement age</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>POT_AT_RETIREMENT · WILL_IT_LAST_RESULT</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>SS_BENEFIT_AT_AGE · SS_CLAIM_FACTOR</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — declared but not naming it: POT_AT_RETIREMENT, WILL_IT_LAST_RESULT  |  naming it but not declared: SS_BENEFIT_AT_AGE, SS_CLAIM_FACTOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-019</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>monthly spending in retirement</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>DECLARED BUT NEVER NAMED — the inputs tab says these engines use it, but no engine names it in its own input list. Unproved in one direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-020</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Social Security monthly amount</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME_NOW · SS_BENEFIT_AT_AGE</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>SS_BENEFIT_AT_AGE · SS_CLAIM_FACTOR</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — declared but not naming it: RETIREMENT_INCOME_NOW  |  naming it but not declared: SS_CLAIM_FACTOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-021</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Social Security claim age</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>SS_CLAIM_FACTOR</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>SS_BENEFIT_AT_AGE · SS_CLAIM_FACTOR</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — naming it but not declared: SS_BENEFIT_AT_AGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-022</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>pension monthly amount</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME_NOW</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — declared but not naming it: RETIREMENT_INCOME_NOW  |  naming it but not declared: RETIREMENT_INCOME</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-023</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>salary and other income</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL_INCOME</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>RENTAL_INCOME_A_YEAR</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — declared but not naming it: TOTAL_INCOME  |  naming it but not declared: RENTAL_INCOME_A_YEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-024</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>logged spending</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>PLANNED_SPENDING · SPENDING_BY_KIND</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>PLANNED_SPENDING · RETIREMENT_SPENDING · TOTAL_CASH · WHAT_THE_PLAN_STILL_NEEDS · WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — declared but not naming it: SPENDING_BY_KIND  |  naming it but not declared: RETIREMENT_SPENDING, TOTAL_CASH, WHAT_THE_PLAN_STILL_NEEDS, WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-025</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>typical monthly essentials</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>JOB_SAFETY_RUNWAY · PLANNED_SPENDING</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>DECLARED BUT NEVER NAMED — the inputs tab says these engines use it, but no engine names it in its own input list. Unproved in one direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-026</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>big costs (amount and year)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>BIG_COSTS</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>DECLARED BUT NEVER NAMED — the inputs tab says these engines use it, but no engine names it in its own input list. Unproved in one direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-027</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>goals (target, saved, date)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>GOAL_PROGRESS</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>DECLARED BUT NEVER NAMED — the inputs tab says these engines use it, but no engine names it in its own input list. Unproved in one direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-028</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>assumed return</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>POT_AT_RETIREMENT · WILL_IT_LAST_RESULT</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>ACCOUNT_SHARE_OF_TOTAL</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — declared but not naming it: POT_AT_RETIREMENT, WILL_IT_LAST_RESULT  |  naming it but not declared: ACCOUNT_SHARE_OF_TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-029</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>inflation rate</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>DECLARED BUT NEVER NAMED — the inputs tab says these engines use it, but no engine names it in its own input list. Unproved in one direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-030</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>tax filing status and age</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>TAXABLE_INCOME · TAX_ON_CONVERSION</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>PLANNED_SPENDING · TOTAL_CASH</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — declared but not naming it: TAXABLE_INCOME, TAX_ON_CONVERSION  |  naming it but not declared: PLANNED_SPENDING, TOTAL_CASH</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-031</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>daily and monthly snapshots</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_WALK · TREND_SERIES</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_PCT · TREND_SERIES</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — declared but not naming it: NW_CHANGE_WALK  |  naming it but not declared: NW_CHANGE_PCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>GAPS — inputs an engine names that are on NO row of the inputs tab.</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Each one is either a missing input, or the same input under another name.</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>and how often each arrives → the matching frequency</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>any split → accountClassBreakdown</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>ALLOCATION_BY_CLASS</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>baseline date → sinceKey</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_PCT</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>chosen → monthly_payment</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_REQUIRED_PAYMENT · SPENDING_BY_KIND</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>debt paid down → debtPrincipal</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_WALK</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>dividends → dividends</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_WALK</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>do they receive it now → incomeSources</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME_NOW</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>each account's class → assetClassOf</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>ALLOCATION_BY_CLASS · PLANNED_SPENDING · TOTAL_CASH · TOTAL_INVESTABLE · TOTAL_INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>each holding's benchmark return → rows[].benchReturn</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>BENCHMARK_RETURN_BLENDED</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>each holding's return → rows[].periodReturn</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>VALUE_WEIGHTED_RETURN</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>each part → its own engine above</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL_INCOME</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>each source → ri_ss</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>ending value → ending</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_WALK</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>every debt → debts</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_PICTURE · NET_WORTH</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>everything → WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_RESULT</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>gross → gross</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>TAXABLE_INCOME</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>guaranteed income → RETIREMENT_INCOME, SS_BENEFIT_AT_AGE</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>holdings → positions[]</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>ACCOUNT_SPLIT</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>how far back → months</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>LOOK_BACK</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>how they file → status</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>TAXABLE_INCOME</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>interest → interest</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_WALK</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>is a range wanted → withBand</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_RESULT</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>its value → rows[].marketValue</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>BENCHMARK_RETURN_BLENDED · VALUE_WEIGHTED_RETURN</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>money in → contributions</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_WALK</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>money out → withdrawals</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_WALK</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>money that counts toward retirement → NEST_EGG</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>WHAT_THE_PLAN_STILL_NEEDS</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>money to leave behind → legacyTarget</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>now → now</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>PRICE_FRESHNESS</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>optionally one account → opts.accountId</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>REALISED_GAIN</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>optionally one ticker → opts.ticker</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>REALISED_GAIN</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>options → option_holdings[]</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>ACCOUNT_SPLIT</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>or the three summary figures → b_fixed, b_nonmonthly, b_flexible</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_REQUIRED_PAYMENT · SPENDING_BY_KIND</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>percent or dollars → employerMatchMode</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>EMPLOYER_MATCH</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>return and swing → EXPECTED_RETURN_BLENDED, EXPECTED_SWING_BLENDED</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>ri_annuities</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>ri_other</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>ri_rmd</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>ri_withdrawals</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>shape → paymentShape</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_REQUIRED_PAYMENT · SPENDING_BY_KIND</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>starting value → beginning</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_WALK</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>the account → a</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>ACCOUNT_SPLIT · HAND_VALUE_AGE</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>the categories → spendCats</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_REQUIRED_PAYMENT · SPENDING_BY_KIND</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>the chosen chip → period</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>PERFORMANCE_TABLE</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>the dates in this sync → activityDates</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>HISTORY_DEPTH</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>the holding → position/account</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>BOND_COUPON · BOND_FACTS</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>the holdings → positions</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>PERFORMANCE_TABLE</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>the ledger → txns</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>REALISED_GAIN</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>the match → employerMatchValue</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>EMPLOYER_MATCH</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>the pot → NEST_EGG</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>the same inputs → inp</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>POT_AT_RETIREMENT</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>their own contribution → c_401k</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>EMPLOYER_MATCH</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>their own overrides → the Plan screen</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>today → now</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>BOND_YEARS_LEFT · HAND_VALUE_AGE · HOLDING_CAP_GAINS · PERFORMANCE_TABLE</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>today → opts.now</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>REALISED_GAIN</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>today's value → currentInvestable</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_PCT</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>value → value</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>BOND_YIELD_TO_MATURITY</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>what it is worth → value</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>BOND_CURRENT_YIELD</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>what we knew → existing</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>HISTORY_DEPTH</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>when the value was set → value_as_of</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>HAND_VALUE_AGE</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>where it might have gone → toSeries</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>LOOK_BACK</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>where it sat → fromSeries</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>LOOK_BACK</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>NO ID</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>where they will live → the location answer</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_SPENDING</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4489,12 +7090,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Every input named, with its unit and where it comes from.</t>
+          <t>Every input named, with its INPUT IDENTIFIER beside it, its unit and where it comes from.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>PARTIAL — every row carries a cell; 91 name their inputs, 72 read NOT DETERMINED because the old master never held an input list for that engine.</t>
+          <t>PARTIAL — 59 rows name inputs carrying their identifiers; 72 rows name at least one input that appears nowhere on the inputs tab, and say so in the cell. The reconciliation tab checks both directions and is where the gap is counted.</t>
         </is>
       </c>
     </row>
@@ -5079,7 +7680,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>everything owned → grossAssets · everything owed → grossDebt</t>
+          <t>everything owned → grossAssets  [MK-XS-I-001] · everything owed → grossDebt  [MK-XS-I-014]</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -5182,7 +7783,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>everything → WILL_IT_LAST_INPUTS · is a range wanted → withBand</t>
+          <t>everything → WILL_IT_LAST_INPUTS  [NO INPUT ID — not on the inputs tab] · is a range wanted → withBand  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -5289,7 +7890,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>each account's class → assetClassOf · each account's money → balance</t>
+          <t>each account's class → assetClassOf  [NO INPUT ID — not on the inputs tab] · each account's money → balance  [MK-XS-I-001]</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -5391,7 +7992,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>each holding's return → rows[].periodReturn · its value → rows[].marketValue</t>
+          <t>each holding's return → rows[].periodReturn  [NO INPUT ID — not on the inputs tab] · its value → rows[].marketValue  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -5946,7 +8547,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>when it was fetched → fetchedAt · now → now</t>
+          <t>when it was fetched → fetchedAt  [MK-XS-I-006] · now → now  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -6780,7 +9381,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>monthly snapshots → monthly · daily points → daily</t>
+          <t>monthly snapshots → monthly  [MK-XS-I-031] · daily points → daily  [MK-XS-I-031]</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -6889,7 +9490,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stored history → daily · today's value → currentInvestable · baseline date → sinceKey</t>
+          <t>stored history → daily  [MK-XS-I-031] · today's value → currentInvestable  [NO INPUT ID — not on the inputs tab] · baseline date → sinceKey  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -6998,7 +9599,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>monthly snapshots → monthly · daily points → daily</t>
+          <t>monthly snapshots → monthly  [MK-XS-I-031] · daily points → daily  [MK-XS-I-031]</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -7101,7 +9702,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>each balance → balance · each assumed return → target_return</t>
+          <t>each balance → balance  [MK-XS-I-001] · each assumed return → target_return  [MK-XS-I-028]</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -7199,7 +9800,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>each account's class → assetClassOf · each account's money → balance</t>
+          <t>each account's class → assetClassOf  [NO INPUT ID — not on the inputs tab] · each account's money → balance  [MK-XS-I-001]</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7310,7 +9911,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>each balance → balance · each assumed return → target_return</t>
+          <t>each balance → balance  [MK-XS-I-001] · each assumed return → target_return  [MK-XS-I-028]</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -7413,7 +10014,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>each account's class → assetClassOf · each account's money → balance · any split → accountClassBreakdown</t>
+          <t>each account's class → assetClassOf  [NO INPUT ID — not on the inputs tab] · each account's money → balance  [MK-XS-I-001] · any split → accountClassBreakdown  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7526,7 +10127,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>the account → a · its total → balance · uninvested → cash_balance · holdings → positions[] · options → option_holdings[]</t>
+          <t>the account → a  [NO INPUT ID — not on the inputs tab] · its total → balance  [MK-XS-I-001] · uninvested → cash_balance  [MK-XS-I-001] · holdings → positions[]  [NO INPUT ID — not on the inputs tab] · options → option_holdings[]  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -7638,7 +10239,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>every debt → debts · rates → interest_rate_apr · payments → the minimum and chosen payments</t>
+          <t>every debt → debts  [NO INPUT ID — not on the inputs tab] · rates → interest_rate_apr  [MK-XS-I-015] · payments → the minimum and chosen payments  [MK-XS-I-016]</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -7738,7 +10339,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>every debt → debts · rates → interest_rate_apr · payments → the minimum and chosen payments</t>
+          <t>every debt → debts  [NO INPUT ID — not on the inputs tab] · rates → interest_rate_apr  [MK-XS-I-015] · payments → the minimum and chosen payments  [MK-XS-I-016]</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -7836,7 +10437,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>shape → paymentShape · minimum → minimum_monthly_payment · chosen → monthly_payment</t>
+          <t>shape → paymentShape  [NO INPUT ID — not on the inputs tab] · minimum → minimum_monthly_payment  [MK-XS-I-016] · chosen → monthly_payment  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -7936,7 +10537,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>every debt → debts · rates → interest_rate_apr · payments → the minimum and chosen payments</t>
+          <t>every debt → debts  [NO INPUT ID — not on the inputs tab] · rates → interest_rate_apr  [MK-XS-I-015] · payments → the minimum and chosen payments  [MK-XS-I-016]</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -8129,7 +10730,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>each account's class → assetClassOf · each account's money → balance · the categories → SPENDING_BY_KIND · the single figure → monthlySpending</t>
+          <t>each account's class → assetClassOf  [NO INPUT ID — not on the inputs tab] · each account's money → balance  [MK-XS-I-001] · the categories → SPENDING_BY_KIND  [MK-XS-I-024] · the single figure → monthlySpending  [MK-XS-I-024, MK-XS-I-030]</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -8241,7 +10842,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>the same inputs → inp</t>
+          <t>the same inputs → inp  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -8354,7 +10955,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>everything owned → grossAssets · everything owed → grossDebt</t>
+          <t>everything owned → grossAssets  [MK-XS-I-001] · everything owed → grossDebt  [MK-XS-I-014]</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8459,7 +11060,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>everything owned → grossAssets · everything owed → grossDebt · every debt → debts · rates → interest_rate_apr · payments → the minimum and chosen payments</t>
+          <t>everything owned → grossAssets  [MK-XS-I-001] · everything owed → grossDebt  [MK-XS-I-014] · every debt → debts  [NO INPUT ID — not on the inputs tab] · rates → interest_rate_apr  [MK-XS-I-015] · payments → the minimum and chosen payments  [MK-XS-I-016]</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8558,7 +11159,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>the account → a · when the value was set → value_as_of · today → now</t>
+          <t>the account → a  [NO INPUT ID — not on the inputs tab] · when the value was set → value_as_of  [NO INPUT ID — not on the inputs tab] · today → now  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8774,7 +11375,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>the account → a · its total → balance · uninvested → cash_balance · holdings → positions[] · options → option_holdings[]</t>
+          <t>the account → a  [NO INPUT ID — not on the inputs tab] · its total → balance  [MK-XS-I-001] · uninvested → cash_balance  [MK-XS-I-001] · holdings → positions[]  [NO INPUT ID — not on the inputs tab] · options → option_holdings[]  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -8979,7 +11580,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>what we knew → existing · the dates in this sync → activityDates</t>
+          <t>what we knew → existing  [NO INPUT ID — not on the inputs tab] · the dates in this sync → activityDates  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9077,7 +11678,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>the holding → position/account</t>
+          <t>the holding → position/account  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -9185,7 +11786,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>face value → face · coupon rate → couponRate</t>
+          <t>face value → face  [MK-XS-I-011] · coupon rate → couponRate  [MK-XS-I-012]</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -9291,7 +11892,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>maturity → maturity · today → now</t>
+          <t>maturity → maturity  [MK-XS-I-013] · today → now  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -9391,7 +11992,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>coupon → annualCoupon · face → face · value → value · years left → yearsToMaturity</t>
+          <t>coupon → annualCoupon  [MK-XS-I-012] · face → face  [MK-XS-I-011] · value → value  [NO INPUT ID — not on the inputs tab] · years left → yearsToMaturity  [MK-XS-I-013]</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -9493,7 +12094,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>coupon → annualCoupon · what it is worth → value</t>
+          <t>coupon → annualCoupon  [MK-XS-I-012] · what it is worth → value  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -9788,7 +12389,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>shares → totalShares · price → the latest close</t>
+          <t>shares → totalShares  [MK-XS-I-004] · price → the latest close  [MK-XS-I-005]</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -9904,7 +12505,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>each lot's shares → lots[].shares</t>
+          <t>each lot's shares → lots[].shares  [MK-XS-I-004, MK-XS-I-007]</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -10010,7 +12611,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>each lot's shares and cost → lots[].shares, lots[].cost_per_share</t>
+          <t>each lot's shares and cost → lots[].shares, lots[].cost_per_share  [MK-XS-I-004, MK-XS-I-007]</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -10112,7 +12713,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>each lot's shares and cost → lots[].shares, lots[].cost_per_share</t>
+          <t>each lot's shares and cost → lots[].shares, lots[].cost_per_share  [MK-XS-I-004, MK-XS-I-007]</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -10314,7 +12915,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>the ledger → txns · optionally one ticker → opts.ticker · optionally one account → opts.accountId · today → opts.now</t>
+          <t>the ledger → txns  [NO INPUT ID — not on the inputs tab] · optionally one ticker → opts.ticker  [NO INPUT ID — not on the inputs tab] · optionally one account → opts.accountId  [NO INPUT ID — not on the inputs tab] · today → opts.now  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -10422,7 +13023,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>each lot → lots[] · price → the latest close · today → now</t>
+          <t>each lot → lots[]  [MK-XS-I-007] · price → the latest close  [MK-XS-I-005] · today → now  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -10530,7 +13131,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>each lot → lots[] · price → the latest close · today → now</t>
+          <t>each lot → lots[]  [MK-XS-I-007] · price → the latest close  [MK-XS-I-005] · today → now  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -10825,7 +13426,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>shares → totalShares · price → the latest close</t>
+          <t>shares → totalShares  [MK-XS-I-004] · price → the latest close  [MK-XS-I-005]</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -10935,7 +13536,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>the holding → position/account</t>
+          <t>the holding → position/account  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -11037,7 +13638,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>the holding → position/account</t>
+          <t>the holding → position/account  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -11139,7 +13740,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>face value → face · coupon rate → couponRate</t>
+          <t>face value → face  [MK-XS-I-011] · coupon rate → couponRate  [MK-XS-I-012]</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -11241,7 +13842,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>coupon → annualCoupon · what it is worth → value</t>
+          <t>coupon → annualCoupon  [MK-XS-I-012] · what it is worth → value  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -11339,7 +13940,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>the holding → position/account · face value → face · coupon rate → couponRate</t>
+          <t>the holding → position/account  [NO INPUT ID — not on the inputs tab] · face value → face  [MK-XS-I-011] · coupon rate → couponRate  [MK-XS-I-012]</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -11766,7 +14367,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>starting value → beginning · ending value → ending · money in → contributions · money out → withdrawals · dividends → dividends · interest → interest · debt paid down → debtPrincipal</t>
+          <t>starting value → beginning  [NO INPUT ID — not on the inputs tab] · ending value → ending  [NO INPUT ID — not on the inputs tab] · money in → contributions  [NO INPUT ID — not on the inputs tab] · money out → withdrawals  [NO INPUT ID — not on the inputs tab] · dividends → dividends  [NO INPUT ID — not on the inputs tab] · interest → interest  [NO INPUT ID — not on the inputs tab] · debt paid down → debtPrincipal  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -11876,7 +14477,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>starting value → beginning · ending value → ending · money in → contributions · money out → withdrawals · dividends → dividends · interest → interest · debt paid down → debtPrincipal</t>
+          <t>starting value → beginning  [NO INPUT ID — not on the inputs tab] · ending value → ending  [NO INPUT ID — not on the inputs tab] · money in → contributions  [NO INPUT ID — not on the inputs tab] · money out → withdrawals  [NO INPUT ID — not on the inputs tab] · dividends → dividends  [NO INPUT ID — not on the inputs tab] · interest → interest  [NO INPUT ID — not on the inputs tab] · debt paid down → debtPrincipal  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -11982,7 +14583,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>starting value → beginning · ending value → ending · money in → contributions · money out → withdrawals · dividends → dividends · interest → interest · debt paid down → debtPrincipal</t>
+          <t>starting value → beginning  [NO INPUT ID — not on the inputs tab] · ending value → ending  [NO INPUT ID — not on the inputs tab] · money in → contributions  [NO INPUT ID — not on the inputs tab] · money out → withdrawals  [NO INPUT ID — not on the inputs tab] · dividends → dividends  [NO INPUT ID — not on the inputs tab] · interest → interest  [NO INPUT ID — not on the inputs tab] · debt paid down → debtPrincipal  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -12092,7 +14693,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>starting value → beginning · ending value → ending · money in → contributions · money out → withdrawals · dividends → dividends · interest → interest · debt paid down → debtPrincipal</t>
+          <t>starting value → beginning  [NO INPUT ID — not on the inputs tab] · ending value → ending  [NO INPUT ID — not on the inputs tab] · money in → contributions  [NO INPUT ID — not on the inputs tab] · money out → withdrawals  [NO INPUT ID — not on the inputs tab] · dividends → dividends  [NO INPUT ID — not on the inputs tab] · interest → interest  [NO INPUT ID — not on the inputs tab] · debt paid down → debtPrincipal  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -12197,7 +14798,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>the holdings → positions · prices → priceOf(ticker) · the chosen chip → period · today → now</t>
+          <t>the holdings → positions  [NO INPUT ID — not on the inputs tab] · prices → priceOf(ticker)  [MK-XS-I-005] · the chosen chip → period  [NO INPUT ID — not on the inputs tab] · today → now  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -12298,7 +14899,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>the holdings → positions · prices → priceOf(ticker) · the chosen chip → period · today → now</t>
+          <t>the holdings → positions  [NO INPUT ID — not on the inputs tab] · prices → priceOf(ticker)  [MK-XS-I-005] · the chosen chip → period  [NO INPUT ID — not on the inputs tab] · today → now  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -12399,7 +15000,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>the holdings → positions · prices → priceOf(ticker) · the chosen chip → period · today → now</t>
+          <t>the holdings → positions  [NO INPUT ID — not on the inputs tab] · prices → priceOf(ticker)  [MK-XS-I-005] · the chosen chip → period  [NO INPUT ID — not on the inputs tab] · today → now  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -12497,7 +15098,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>each holding's benchmark return → rows[].benchReturn · its value → rows[].marketValue</t>
+          <t>each holding's benchmark return → rows[].benchReturn  [NO INPUT ID — not on the inputs tab] · its value → rows[].marketValue  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -12700,7 +15301,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>the amount → amount · where it sat → fromSeries · where it might have gone → toSeries · how far back → months</t>
+          <t>the amount → amount  [MK-XS-I-008] · where it sat → fromSeries  [NO INPUT ID — not on the inputs tab] · where it might have gone → toSeries  [NO INPUT ID — not on the inputs tab] · how far back → months  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -12801,7 +15402,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>the amount → amount · where it sat → fromSeries · where it might have gone → toSeries · how far back → months</t>
+          <t>the amount → amount  [MK-XS-I-008] · where it sat → fromSeries  [NO INPUT ID — not on the inputs tab] · where it might have gone → toSeries  [NO INPUT ID — not on the inputs tab] · how far back → months  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -12902,7 +15503,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>the amount → amount · where it sat → fromSeries · where it might have gone → toSeries · how far back → months</t>
+          <t>the amount → amount  [MK-XS-I-008] · where it sat → fromSeries  [NO INPUT ID — not on the inputs tab] · where it might have gone → toSeries  [NO INPUT ID — not on the inputs tab] · how far back → months  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -13322,7 +15923,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>their age → birthYear or age · what they spend → monthlySpending · money that counts toward retirement → NEST_EGG</t>
+          <t>their age → birthYear or age  [MK-XS-I-017] · what they spend → monthlySpending  [MK-XS-I-024] · money that counts toward retirement → NEST_EGG  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -13421,7 +16022,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>their age → birthYear or age · what they spend → monthlySpending · money that counts toward retirement → NEST_EGG</t>
+          <t>their age → birthYear or age  [MK-XS-I-017] · what they spend → monthlySpending  [MK-XS-I-024] · money that counts toward retirement → NEST_EGG  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -14008,7 +16609,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>their age → birthYear · the pot → NEST_EGG · return and swing → EXPECTED_RETURN_BLENDED, EXPECTED_SWING_BLENDED · spending → RETIREMENT_SPENDING · guaranteed income → RETIREMENT_INCOME, SS_BENEFIT_AT_AGE · money to leave behind → legacyTarget · their own overrides → the Plan screen</t>
+          <t>their age → birthYear  [MK-XS-I-017] · the pot → NEST_EGG  [NO INPUT ID — not on the inputs tab] · return and swing → EXPECTED_RETURN_BLENDED, EXPECTED_SWING_BLENDED  [NO INPUT ID — not on the inputs tab] · spending → RETIREMENT_SPENDING  [MK-XS-I-024] · guaranteed income → RETIREMENT_INCOME, SS_BENEFIT_AT_AGE  [NO INPUT ID — not on the inputs tab] · money to leave behind → legacyTarget  [NO INPUT ID — not on the inputs tab] · their own overrides → the Plan screen  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -14106,7 +16707,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>the answer → the retirement-spending question · where they will live → the location answer</t>
+          <t>the answer → the retirement-spending question  [MK-XS-I-024] · where they will live → the location answer  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -14307,7 +16908,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>their age → birthYear · the pot → NEST_EGG · return and swing → EXPECTED_RETURN_BLENDED, EXPECTED_SWING_BLENDED · spending → RETIREMENT_SPENDING · guaranteed income → RETIREMENT_INCOME, SS_BENEFIT_AT_AGE · money to leave behind → legacyTarget · their own overrides → the Plan screen</t>
+          <t>their age → birthYear  [MK-XS-I-017] · the pot → NEST_EGG  [NO INPUT ID — not on the inputs tab] · return and swing → EXPECTED_RETURN_BLENDED, EXPECTED_SWING_BLENDED  [NO INPUT ID — not on the inputs tab] · spending → RETIREMENT_SPENDING  [MK-XS-I-024] · guaranteed income → RETIREMENT_INCOME, SS_BENEFIT_AT_AGE  [NO INPUT ID — not on the inputs tab] · money to leave behind → legacyTarget  [NO INPUT ID — not on the inputs tab] · their own overrides → the Plan screen  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -14802,7 +17403,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>the account → a · when the value was set → value_as_of · today → now</t>
+          <t>the account → a  [NO INPUT ID — not on the inputs tab] · when the value was set → value_as_of  [NO INPUT ID — not on the inputs tab] · today → now  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -14908,7 +17509,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>statement amount at their full retirement age (typed from their ssa.gov statement) → statement monthly · claim age (the slider) → the factor's input · birth year (setup) → the anchor</t>
+          <t>statement amount at their full retirement age (typed from their ssa.gov statement) → statement monthly  [MK-XS-I-008, MK-XS-I-018, MK-XS-I-020] · claim age (the slider) → the factor's input  [MK-XS-I-021] · birth year (setup) → the anchor  [MK-XS-I-017]</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -15009,7 +17610,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>do they receive it now → incomeSources · the amounts → retirementIncomeMonthly</t>
+          <t>do they receive it now → incomeSources  [NO INPUT ID — not on the inputs tab] · the amounts → retirementIncomeMonthly  [MK-XS-I-008]</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -15111,7 +17712,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>claim age (the slider, 62–70) → months early or late vs their full retirement age · birth year (their setup answer) → the full retirement age it anchors to · statement amount at their full retirement age (typed from their ssa.gov statement) → statement monthly · claim age (the slider) → the factor's input · birth year (setup) → the anchor</t>
+          <t>claim age (the slider, 62–70) → months early or late vs their full retirement age  [MK-XS-I-018, MK-XS-I-021] · birth year (their setup answer) → the full retirement age it anchors to  [MK-XS-I-017, MK-XS-I-018] · statement amount at their full retirement age (typed from their ssa.gov statement) → statement monthly  [MK-XS-I-008, MK-XS-I-018, MK-XS-I-020] · claim age (the slider) → the factor's input  [MK-XS-I-021] · birth year (setup) → the anchor  [MK-XS-I-017]</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -15805,7 +18406,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>the same inputs → inp</t>
+          <t>the same inputs → inp  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -16105,7 +18706,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>their age → birthYear · the pot → NEST_EGG · return and swing → EXPECTED_RETURN_BLENDED, EXPECTED_SWING_BLENDED · spending → RETIREMENT_SPENDING · guaranteed income → RETIREMENT_INCOME, SS_BENEFIT_AT_AGE · money to leave behind → legacyTarget · their own overrides → the Plan screen</t>
+          <t>their age → birthYear  [MK-XS-I-017] · the pot → NEST_EGG  [NO INPUT ID — not on the inputs tab] · return and swing → EXPECTED_RETURN_BLENDED, EXPECTED_SWING_BLENDED  [NO INPUT ID — not on the inputs tab] · spending → RETIREMENT_SPENDING  [MK-XS-I-024] · guaranteed income → RETIREMENT_INCOME, SS_BENEFIT_AT_AGE  [NO INPUT ID — not on the inputs tab] · money to leave behind → legacyTarget  [NO INPUT ID — not on the inputs tab] · their own overrides → the Plan screen  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -16209,7 +18810,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>every debt → debts · rates → interest_rate_apr · payments → the minimum and chosen payments</t>
+          <t>every debt → debts  [NO INPUT ID — not on the inputs tab] · rates → interest_rate_apr  [MK-XS-I-015] · payments → the minimum and chosen payments  [MK-XS-I-016]</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -16410,7 +19011,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>do they receive it now → incomeSources · the amounts → retirementIncomeMonthly</t>
+          <t>do they receive it now → incomeSources  [NO INPUT ID — not on the inputs tab] · the amounts → retirementIncomeMonthly  [MK-XS-I-008]</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -16518,7 +19119,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>the same inputs → inp</t>
+          <t>the same inputs → inp  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -16627,7 +19228,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>everything → WILL_IT_LAST_INPUTS · is a range wanted → withBand</t>
+          <t>everything → WILL_IT_LAST_INPUTS  [NO INPUT ID — not on the inputs tab] · is a range wanted → withBand  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -17936,7 +20537,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>each part → its own engine above</t>
+          <t>each part → its own engine above  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -18035,7 +20636,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>each part → its own engine above</t>
+          <t>each part → its own engine above  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -18134,7 +20735,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>each part → its own engine above</t>
+          <t>each part → its own engine above  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -18331,7 +20932,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>each rental → rentalList</t>
+          <t>each rental → rentalList  [MK-XS-I-023]</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -18430,7 +21031,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>do they receive it now → incomeSources · the amounts → retirementIncomeMonthly</t>
+          <t>do they receive it now → incomeSources  [NO INPUT ID — not on the inputs tab] · the amounts → retirementIncomeMonthly  [MK-XS-I-008]</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -18630,7 +21231,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>the categories → spendCats · or the three summary figures → b_fixed, b_nonmonthly, b_flexible</t>
+          <t>the categories → spendCats  [NO INPUT ID — not on the inputs tab] · or the three summary figures → b_fixed, b_nonmonthly, b_flexible  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -18728,7 +21329,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>the categories → spendCats · or the three summary figures → b_fixed, b_nonmonthly, b_flexible</t>
+          <t>the categories → spendCats  [NO INPUT ID — not on the inputs tab] · or the three summary figures → b_fixed, b_nonmonthly, b_flexible  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -18827,7 +21428,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>the categories → SPENDING_BY_KIND · the single figure → monthlySpending</t>
+          <t>the categories → SPENDING_BY_KIND  [MK-XS-I-024] · the single figure → monthlySpending  [MK-XS-I-024, MK-XS-I-030]</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -19227,7 +21828,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>the categories → spendCats · or the three summary figures → b_fixed, b_nonmonthly, b_flexible · shape → paymentShape · minimum → minimum_monthly_payment · chosen → monthly_payment</t>
+          <t>the categories → spendCats  [NO INPUT ID — not on the inputs tab] · or the three summary figures → b_fixed, b_nonmonthly, b_flexible  [NO INPUT ID — not on the inputs tab] · shape → paymentShape  [NO INPUT ID — not on the inputs tab] · minimum → minimum_monthly_payment  [MK-XS-I-016] · chosen → monthly_payment  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -19523,7 +22124,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>the same inputs → inp</t>
+          <t>the same inputs → inp  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -19627,7 +22228,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>each source → ri_ss · ri_pension · ri_withdrawals · ri_rmd · ri_annuities · ri_other · and how often each arrives → the matching frequency</t>
+          <t>each source → ri_ss  [NO INPUT ID — not on the inputs tab] · ri_pension  [MK-XS-I-022] · ri_withdrawals  [NO INPUT ID — not on the inputs tab] · ri_rmd  [NO INPUT ID — not on the inputs tab] · ri_annuities  [NO INPUT ID — not on the inputs tab] · ri_other  [NO INPUT ID — not on the inputs tab] · and how often each arrives → the matching frequency  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -19726,7 +22327,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>do they receive it now → incomeSources · the amounts → retirementIncomeMonthly</t>
+          <t>do they receive it now → incomeSources  [NO INPUT ID — not on the inputs tab] · the amounts → retirementIncomeMonthly  [MK-XS-I-008]</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -20029,7 +22630,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>each part → its own engine above</t>
+          <t>each part → its own engine above  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -21237,7 +23838,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>the categories → SPENDING_BY_KIND · the single figure → monthlySpending</t>
+          <t>the categories → SPENDING_BY_KIND  [MK-XS-I-024] · the single figure → monthlySpending  [MK-XS-I-024, MK-XS-I-030]</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -21638,7 +24239,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>each part → its own engine above</t>
+          <t>each part → its own engine above  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -21737,7 +24338,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>each part → its own engine above</t>
+          <t>each part → its own engine above  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -21836,7 +24437,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>each part → its own engine above</t>
+          <t>each part → its own engine above  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -21934,7 +24535,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>the match → employerMatchValue · percent or dollars → employerMatchMode · their own contribution → c_401k</t>
+          <t>the match → employerMatchValue  [NO INPUT ID — not on the inputs tab] · percent or dollars → employerMatchMode  [NO INPUT ID — not on the inputs tab] · their own contribution → c_401k  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -22134,7 +24735,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>each account's class → assetClassOf · each account's money → balance · each account's class → assetClassOf · each account's money → balance</t>
+          <t>each account's class → assetClassOf  [NO INPUT ID — not on the inputs tab] · each account's money → balance  [MK-XS-I-001] · each account's class → assetClassOf  [NO INPUT ID — not on the inputs tab] · each account's money → balance  [MK-XS-I-001]</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -22640,7 +25241,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>the categories → spendCats · or the three summary figures → b_fixed, b_nonmonthly, b_flexible</t>
+          <t>the categories → spendCats  [NO INPUT ID — not on the inputs tab] · or the three summary figures → b_fixed, b_nonmonthly, b_flexible  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -23135,7 +25736,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>the categories → SPENDING_BY_KIND · the single figure → monthlySpending</t>
+          <t>the categories → SPENDING_BY_KIND  [MK-XS-I-024] · the single figure → monthlySpending  [MK-XS-I-024, MK-XS-I-030]</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -23233,7 +25834,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>gross → gross · how they file → status</t>
+          <t>gross → gross  [NO INPUT ID — not on the inputs tab] · how they file → status  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -23335,7 +25936,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>gross → gross · how they file → status</t>
+          <t>gross → gross  [NO INPUT ID — not on the inputs tab] · how they file → status  [NO INPUT ID — not on the inputs tab]</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -824,12 +824,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Engines it depends on (S11)</t>
+          <t>COLUMN — Dependency (S11)</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>The engines this one calls, read from the code itself. "None found" means it reads raw values only.</t>
+          <t>The engines this one leans on, each named by ITS identifier and by the output it gives. Read from the code itself, never from a document. "None" means the engine reads raw inputs only.</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MK-XS-E-001 · MK-XS-E-003 · MK-NW-E-004 · MK-PL-E-008</t>
+          <t>MK-XS-E-001 · MK-XS-E-009 · MK-NW-E-004 · MK-PL-E-006</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MK-PL-E-008</t>
+          <t>MK-PL-E-006</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MK-NW-E-006</t>
+          <t>MK-XS-E-015</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MK-NW-E-023 · MK-NW-E-024</t>
+          <t>MK-XS-E-022 · MK-NW-E-022</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MK-HM-E-001 · MK-NW-E-023</t>
+          <t>MK-HM-E-001 · MK-NW-E-022</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MK-NW-E-025 · MK-NW-E-028</t>
+          <t>MK-NW-E-023 · MK-NW-E-026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MK-NW-E-016</t>
+          <t>MK-NW-E-015</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MK-NW-E-017 · MK-NW-E-020</t>
+          <t>MK-NW-E-016 · MK-NW-E-019</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MK-NW-E-018 · MK-NW-E-019</t>
+          <t>MK-NW-E-017 · MK-NW-E-018</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MK-NW-E-007</t>
+          <t>MK-NW-E-006</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MK-PL-E-018</t>
+          <t>MK-PL-E-015</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MK-NW-E-008</t>
+          <t>MK-NW-E-007</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MK-PL-E-009</t>
+          <t>MK-XS-E-040</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MK-XS-E-002 · MK-NW-E-010</t>
+          <t>MK-XS-E-007 · MK-NW-E-009</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MK-PL-E-004</t>
+          <t>MK-XS-E-006</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MK-PL-E-009 · MK-PL-E-010</t>
+          <t>MK-XS-E-040 · MK-PL-E-007</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1931,7 +1931,11 @@
           <t>SS_CLAIM_FACTOR</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>MK-XS-E-046</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
@@ -1966,7 +1970,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MK-PL-E-010</t>
+          <t>MK-PL-E-007</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2003,7 +2007,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MK-CF-E-002</t>
+          <t>MK-XS-E-044</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2040,7 +2044,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MK-CF-E-006 · MK-CF-E-007</t>
+          <t>MK-XS-E-021 · MK-CF-E-004</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2077,7 +2081,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MK-CF-E-007 · MK-MN-E-010</t>
+          <t>MK-CF-E-004 · MK-MN-E-010</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2188,7 +2192,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MK-XS-E-002 · MK-NW-E-010</t>
+          <t>MK-XS-E-007 · MK-NW-E-009</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2225,7 +2229,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MK-PL-E-004</t>
+          <t>MK-XS-E-006</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2262,7 +2266,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MK-PL-E-015 · MK-MN-E-014</t>
+          <t>MK-PL-E-012 · MK-MN-E-014</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -6994,7 +6998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -7011,7 +7015,7 @@
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="35" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
-    <col width="29" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="37" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
@@ -7308,12 +7312,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>The engines it depends on — without it, build order and the one-door design cannot be worked out.</t>
+          <t>Each dependency named by ITS engine identifier and by the output it gives, so a chain can be followed without knowing any engine by name.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>COMPLETE — read from the code itself, not from any document. 90 rows name their dependencies; the rest read raw values only.</t>
+          <t>COMPLETE — read from the code itself, not from any document. 64 rows name a dependency by identifier; the rest read raw inputs only.</t>
         </is>
       </c>
     </row>
@@ -7428,42 +7432,64 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>The duplication pass</t>
+          <t>The reconciliation engine</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Figures that are the same thing under two identifiers.</t>
+          <t>Both records kept independently and checked against each other as a build gate — an input an engine names that is on no row, an input declared that no engine names, an engine identifier that does not exist, an engine no metric reaches. Founder, 2026-08-25: never generate one list from the other; agreement by construction hides the orphan.</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>COMPLETE — every group judged one at a time. 11 figures were being shown under 24 identifiers; the 13 folded rows now name the identifier that survives and why. 18 groups were checked and are NOT duplicates — one engine legitimately producing several figures — and say so, so the question is not asked twice. Two mis-assigned engines were found and recorded as findings.</t>
+          <t>NOT STARTED — the reconciliation tab is today a report, run by hand. It has to become code with a test.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>The duplication pass</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Figures that are the same thing under two identifiers.</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>COMPLETE — every group judged one at a time. 11 figures were being shown under 24 identifiers; the 13 folded rows now name the identifier that survives and why. 18 groups were checked and are NOT duplicates — one engine legitimately producing several figures — and say so, so the question is not asked twice. Two mis-assigned engines were found and recorded as findings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>S17</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Which screens are the 55-70 core</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>The agreed first scope has never been written down.</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>READY FOR THE FOUNDER — the core_screens tab lists all 49 screens with my recommendation (39 in, 5 out, 5 borderline) and a column for his decision.</t>
         </is>
@@ -7497,7 +7523,7 @@
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="35" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
-    <col width="29" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="37" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
@@ -7582,7 +7608,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Engines it depends on</t>
+          <t>Dependency — engine ID → the output it uses</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -7705,7 +7731,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -7767,7 +7793,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MK-XS-E-002</t>
+          <t>MK-XS-E-007</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7808,7 +7834,11 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>NEST_EGG · ODDS_DISPLAY · RETIREMENT_SPENDING · WILL_IT_LAST · WILL_IT_LAST_INPUTS</t>
+          <t>MK-XS-E-002 (NEST_EGG) → What is my retirement pot worth?
+MK-XS-E-003 (ODDS_DISPLAY) → The retirement odds a person actually sees. Answers: 0, 5, 10 … 100 — the exact simulation
+MK-XS-E-004 (RETIREMENT_SPENDING) → What will be spent each month in retirement?
+MK-XS-E-005 (WILL_IT_LAST) → Will my money last?
+MK-XS-E-006 (WILL_IT_LAST_INPUTS) → What goes into working out the odds?</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -7875,7 +7905,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MK-XS-E-003</t>
+          <t>MK-XS-E-009</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7915,7 +7945,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ASSET_CLASS_OF_ACCOUNT</t>
+          <t>MK-XS-E-008 (ASSET_CLASS_OF_ACCOUNT) → What kind of thing is this account — cash, a bond, shares, or something else?</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -7973,7 +8003,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MK-XS-E-004</t>
+          <t>MK-XS-E-010</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8017,7 +8047,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -8075,7 +8105,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MK-XS-E-005</t>
+          <t>MK-XS-E-011</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8173,7 +8203,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MK-XS-E-006</t>
+          <t>MK-XS-E-012</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8364,7 +8394,7 @@
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="35" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
-    <col width="29" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="37" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
@@ -8449,7 +8479,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Engines it depends on</t>
+          <t>Dependency — engine ID → the output it uses</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -8572,7 +8602,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>FETCH_PRICES</t>
+          <t>MK-XS-E-013 (FETCH_PRICES) → What are these holdings worth?</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -9196,7 +9226,7 @@
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="35" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
-    <col width="29" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="37" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
@@ -9281,7 +9311,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Engines it depends on</t>
+          <t>Dependency — engine ID → the output it uses</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -9406,7 +9436,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>SNAPSHOT_READ_ALL</t>
+          <t>MK-XS-E-014 (SNAPSHOT_READ_ALL) → What history do we hold?</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -9515,7 +9545,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -9624,7 +9654,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>SNAPSHOT_READ_ALL</t>
+          <t>MK-XS-E-014 (SNAPSHOT_READ_ALL) → What history do we hold?</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -9727,7 +9757,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -9825,7 +9855,8 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ACCOUNT_SPLIT · ASSET_CLASS_OF_ACCOUNT</t>
+          <t>MK-XS-E-015 (ACCOUNT_SPLIT) → This one brokerage account holds several different things — how much of it is each?
+MK-XS-E-008 (ASSET_CLASS_OF_ACCOUNT) → What kind of thing is this account — cash, a bond, shares, or something else?</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -9936,7 +9967,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -10039,7 +10070,8 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>ACCOUNT_SPLIT · ASSET_CLASS_OF_ACCOUNT</t>
+          <t>MK-XS-E-015 (ACCOUNT_SPLIT) → This one brokerage account holds several different things — how much of it is each?
+MK-XS-E-008 (ASSET_CLASS_OF_ACCOUNT) → What kind of thing is this account — cash, a bond, shares, or something else?</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -10108,7 +10140,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MK-NW-E-006</t>
+          <t>MK-XS-E-015</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -10152,7 +10184,8 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ASSET_CLASS_OF_ACCOUNT · CLASS_FROM_NAME_TEXT</t>
+          <t>MK-XS-E-008 (ASSET_CLASS_OF_ACCOUNT) → What kind of thing is this account — cash, a bond, shares, or something else?
+MK-XS-E-016 (CLASS_FROM_NAME_TEXT) → Reading the NAME alone, is this cash, a money-market fund, or a CD / T-bill?</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -10222,7 +10255,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MK-NW-E-007</t>
+          <t>MK-NW-E-006</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -10264,7 +10297,8 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>DEBT_MINIMUM_TOTAL · DEBT_PAYMENTS_ACTUAL</t>
+          <t>MK-XS-E-017 (DEBT_MINIMUM_TOTAL) → What must I pay across all debts to stay current?
+MK-XS-E-018 (DEBT_PAYMENTS_ACTUAL) → What is actually going out on debt each month?</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -10322,7 +10356,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MK-NW-E-007</t>
+          <t>MK-NW-E-006</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10364,7 +10398,8 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>DEBT_MINIMUM_TOTAL · DEBT_PAYMENTS_ACTUAL</t>
+          <t>MK-XS-E-017 (DEBT_MINIMUM_TOTAL) → What must I pay across all debts to stay current?
+MK-XS-E-018 (DEBT_PAYMENTS_ACTUAL) → What is actually going out on debt each month?</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -10422,7 +10457,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MK-NW-E-008</t>
+          <t>MK-NW-E-007</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10462,7 +10497,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>DEBT_SHAPE</t>
+          <t>MK-XS-E-019 (DEBT_SHAPE) → How is THIS debt repaid?</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -10520,7 +10555,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MK-NW-E-007</t>
+          <t>MK-NW-E-006</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10562,7 +10597,8 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>DEBT_MINIMUM_TOTAL · DEBT_PAYMENTS_ACTUAL</t>
+          <t>MK-XS-E-017 (DEBT_MINIMUM_TOTAL) → What must I pay across all debts to stay current?
+MK-XS-E-018 (DEBT_PAYMENTS_ACTUAL) → What is actually going out on debt each month?</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -10714,7 +10750,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MK-NW-E-009</t>
+          <t>MK-NW-E-008</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10755,7 +10791,10 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>ACCOUNT_SPLIT · ASSET_CLASS_OF_ACCOUNT · READ_A_NUMBER · SPENDING_BY_KIND</t>
+          <t>MK-XS-E-015 (ACCOUNT_SPLIT) → This one brokerage account holds several different things — how much of it is each?
+MK-XS-E-008 (ASSET_CLASS_OF_ACCOUNT) → What kind of thing is this account — cash, a bond, shares, or something else?
+MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?
+MK-XS-E-021 (SPENDING_BY_KIND) → What is spent each month, split by kind?</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -10821,7 +10860,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MK-NW-E-010</t>
+          <t>MK-NW-E-009</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10867,7 +10906,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>WILL_IT_LAST</t>
+          <t>MK-XS-E-005 (WILL_IT_LAST) → Will my money last?</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -10980,7 +11019,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -11042,7 +11081,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MK-NW-E-011</t>
+          <t>MK-NW-E-010</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -11085,7 +11124,8 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>DEBT_MINIMUM_TOTAL · DEBT_PAYMENTS_ACTUAL</t>
+          <t>MK-XS-E-017 (DEBT_MINIMUM_TOTAL) → What must I pay across all debts to stay current?
+MK-XS-E-018 (DEBT_PAYMENTS_ACTUAL) → What is actually going out on debt each month?</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -11143,7 +11183,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MK-NW-E-012</t>
+          <t>MK-NW-E-011</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -11184,7 +11224,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -11254,7 +11294,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MK-NW-E-013</t>
+          <t>MK-NW-E-012</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -11356,7 +11396,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MK-NW-E-006</t>
+          <t>MK-XS-E-015</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -11400,7 +11440,8 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>ASSET_CLASS_OF_ACCOUNT · CLASS_FROM_NAME_TEXT</t>
+          <t>MK-XS-E-008 (ASSET_CLASS_OF_ACCOUNT) → What kind of thing is this account — cash, a bond, shares, or something else?
+MK-XS-E-016 (CLASS_FROM_NAME_TEXT) → Reading the NAME alone, is this cash, a money-market fund, or a CD / T-bill?</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -11466,7 +11507,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MK-NW-E-014</t>
+          <t>MK-NW-E-013</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -11564,7 +11605,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MK-NW-E-015</t>
+          <t>MK-NW-E-014</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -11605,7 +11646,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -11663,7 +11704,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MK-NW-E-016</t>
+          <t>MK-NW-E-015</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -11703,7 +11744,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -11771,7 +11812,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MK-NW-E-017</t>
+          <t>MK-NW-E-016</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -11811,7 +11852,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -11877,7 +11918,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MK-NW-E-018</t>
+          <t>MK-NW-E-017</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -11917,7 +11958,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -11975,7 +12016,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MK-NW-E-019</t>
+          <t>MK-NW-E-018</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -12017,7 +12058,8 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>BOND_COUPON · BOND_YEARS_LEFT</t>
+          <t>MK-NW-E-016 (BOND_COUPON) → How much income does this bond pay in a year?
+MK-NW-E-017 (BOND_YEARS_LEFT) → How long until this bond pays back?</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -12079,7 +12121,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MK-NW-E-020</t>
+          <t>MK-NW-E-019</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -12119,7 +12161,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>BOND_COUPON</t>
+          <t>MK-NW-E-016 (BOND_COUPON) → How much income does this bond pay in a year?</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -12177,7 +12219,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MK-NW-E-021</t>
+          <t>MK-NW-E-020</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -12275,7 +12317,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MK-NW-E-022</t>
+          <t>MK-NW-E-021</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -12373,7 +12415,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MK-NW-E-023</t>
+          <t>MK-NW-E-022</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -12414,7 +12456,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>HOLDING_SHARES</t>
+          <t>MK-XS-E-022 (HOLDING_SHARES) → How many shares of this do I own?</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -12490,7 +12532,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MK-NW-E-024</t>
+          <t>MK-XS-E-022</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -12530,7 +12572,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -12596,7 +12638,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MK-NW-E-025</t>
+          <t>MK-NW-E-023</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -12636,7 +12678,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -12698,7 +12740,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MK-NW-E-025</t>
+          <t>MK-NW-E-023</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -12738,7 +12780,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -12800,7 +12842,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MK-NW-E-026</t>
+          <t>MK-NW-E-024</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -12898,7 +12940,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>MK-NW-E-027</t>
+          <t>MK-NW-E-025</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -12940,7 +12982,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -13006,7 +13048,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MK-NW-E-028</t>
+          <t>MK-NW-E-026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -13048,7 +13090,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -13114,7 +13156,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MK-NW-E-028</t>
+          <t>MK-NW-E-026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -13156,7 +13198,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -13218,7 +13260,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MK-NW-E-029</t>
+          <t>MK-NW-E-027</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -13410,7 +13452,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MK-NW-E-023</t>
+          <t>MK-NW-E-022</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -13451,7 +13493,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>HOLDING_SHARES</t>
+          <t>MK-XS-E-022 (HOLDING_SHARES) → How many shares of this do I own?</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -13521,7 +13563,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MK-NW-E-016</t>
+          <t>MK-NW-E-015</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -13561,7 +13603,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -13623,7 +13665,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>MK-NW-E-016</t>
+          <t>MK-NW-E-015</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -13663,7 +13705,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -13725,7 +13767,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MK-NW-E-017</t>
+          <t>MK-NW-E-016</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -13765,7 +13807,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
@@ -13827,7 +13869,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>MK-NW-E-020</t>
+          <t>MK-NW-E-019</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -13867,7 +13909,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>BOND_COUPON</t>
+          <t>MK-NW-E-016 (BOND_COUPON) → How much income does this bond pay in a year?</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -13925,7 +13967,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>MK-NW-E-030</t>
+          <t>MK-NW-E-028</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -13965,7 +14007,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>NOT DETERMINED</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -14181,7 +14223,7 @@
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="35" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
-    <col width="29" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="37" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
@@ -14266,7 +14308,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Engines it depends on</t>
+          <t>Dependency — engine ID → the output it uses</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -14392,7 +14434,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -14502,7 +14544,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -14608,7 +14650,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -14718,7 +14760,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -14823,7 +14865,16 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>BENCHMARK_FOR_KIND · HOLDING_COST_BASIS · HOLDING_FIRST_BOUGHT · HOLDING_MARKET_VALUE · HOLDING_TOTAL_ROI · HOLDING_UNREALISED_GAIN · PERIOD_RETURN · PERIOD_START_DATE · PRICE_LATEST · RETURN_SINCE_A_DATE</t>
+          <t>MK-XS-E-023 (BENCHMARK_FOR_KIND) → What should this holding be compared against?
+MK-NW-E-023 (HOLDING_COST_BASIS) → What did I pay for this in total?
+MK-XS-E-024 (HOLDING_FIRST_BOUGHT) → When did I first buy this?
+MK-NW-E-022 (HOLDING_MARKET_VALUE) → What is this holding worth right now?
+MK-XS-E-025 (HOLDING_TOTAL_ROI) → How much am I up on this in percentage terms, since I bought it?
+MK-XS-E-026 (HOLDING_UNREALISED_GAIN) → How much am I up or down on this?
+MK-XS-E-027 (PERIOD_RETURN) → What did this holding do over the chosen period?
+MK-XS-E-028 (PERIOD_START_DATE) → Which date does the chosen period start from?
+MK-XS-E-029 (PRICE_LATEST) → What is the most recent price we hold for this?
+MK-XS-E-030 (RETURN_SINCE_A_DATE) → What did this do between a given date and today?</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -14924,7 +14975,16 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>BENCHMARK_FOR_KIND · HOLDING_COST_BASIS · HOLDING_FIRST_BOUGHT · HOLDING_MARKET_VALUE · HOLDING_TOTAL_ROI · HOLDING_UNREALISED_GAIN · PERIOD_RETURN · PERIOD_START_DATE · PRICE_LATEST · RETURN_SINCE_A_DATE</t>
+          <t>MK-XS-E-023 (BENCHMARK_FOR_KIND) → What should this holding be compared against?
+MK-NW-E-023 (HOLDING_COST_BASIS) → What did I pay for this in total?
+MK-XS-E-024 (HOLDING_FIRST_BOUGHT) → When did I first buy this?
+MK-NW-E-022 (HOLDING_MARKET_VALUE) → What is this holding worth right now?
+MK-XS-E-025 (HOLDING_TOTAL_ROI) → How much am I up on this in percentage terms, since I bought it?
+MK-XS-E-026 (HOLDING_UNREALISED_GAIN) → How much am I up or down on this?
+MK-XS-E-027 (PERIOD_RETURN) → What did this holding do over the chosen period?
+MK-XS-E-028 (PERIOD_START_DATE) → Which date does the chosen period start from?
+MK-XS-E-029 (PRICE_LATEST) → What is the most recent price we hold for this?
+MK-XS-E-030 (RETURN_SINCE_A_DATE) → What did this do between a given date and today?</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -15025,7 +15085,16 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>BENCHMARK_FOR_KIND · HOLDING_COST_BASIS · HOLDING_FIRST_BOUGHT · HOLDING_MARKET_VALUE · HOLDING_TOTAL_ROI · HOLDING_UNREALISED_GAIN · PERIOD_RETURN · PERIOD_START_DATE · PRICE_LATEST · RETURN_SINCE_A_DATE</t>
+          <t>MK-XS-E-023 (BENCHMARK_FOR_KIND) → What should this holding be compared against?
+MK-NW-E-023 (HOLDING_COST_BASIS) → What did I pay for this in total?
+MK-XS-E-024 (HOLDING_FIRST_BOUGHT) → When did I first buy this?
+MK-NW-E-022 (HOLDING_MARKET_VALUE) → What is this holding worth right now?
+MK-XS-E-025 (HOLDING_TOTAL_ROI) → How much am I up on this in percentage terms, since I bought it?
+MK-XS-E-026 (HOLDING_UNREALISED_GAIN) → How much am I up or down on this?
+MK-XS-E-027 (PERIOD_RETURN) → What did this holding do over the chosen period?
+MK-XS-E-028 (PERIOD_START_DATE) → Which date does the chosen period start from?
+MK-XS-E-029 (PRICE_LATEST) → What is the most recent price we hold for this?
+MK-XS-E-030 (RETURN_SINCE_A_DATE) → What did this do between a given date and today?</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -15123,7 +15192,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -15326,7 +15395,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PRICE_FACTOR_OVER_WINDOW</t>
+          <t>MK-XS-E-031 (PRICE_FACTOR_OVER_WINDOW) → By what multiple did this price move over the last N months?</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -15427,7 +15496,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PRICE_FACTOR_OVER_WINDOW</t>
+          <t>MK-XS-E-031 (PRICE_FACTOR_OVER_WINDOW) → By what multiple did this price move over the last N months?</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -15528,7 +15597,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PRICE_FACTOR_OVER_WINDOW</t>
+          <t>MK-XS-E-031 (PRICE_FACTOR_OVER_WINDOW) → By what multiple did this price move over the last N months?</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -15740,7 +15809,7 @@
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="35" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
-    <col width="29" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="37" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
@@ -15825,7 +15894,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Engines it depends on</t>
+          <t>Dependency — engine ID → the output it uses</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -15948,7 +16017,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>NEST_EGG</t>
+          <t>MK-XS-E-002 (NEST_EGG) → What is my retirement pot worth?</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -16047,7 +16116,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>NEST_EGG</t>
+          <t>MK-XS-E-002 (NEST_EGG) → What is my retirement pot worth?</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -16590,7 +16659,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MK-PL-E-004</t>
+          <t>MK-XS-E-006</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -16634,7 +16703,21 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>EFFECTIVE_TAX_RATE · EXPECTED_RETURN_BLENDED · EXPECTED_SWING_BLENDED · FILING_STATUS · GUARANTEED_OUTSIDE_STREAMS · MONTHLY_SAVING · NEST_EGG · REPORTED_RETURN · RETIREMENT_SPENDING · SPLIT_BY_HOW_IT_IS_TAXED · SS_BENEFIT_AT_AGE · STATE_TAX_RATE · SWING_FROM_RETURN · TAX_OVER65_COUNT · TOTAL_INCOME</t>
+          <t>MK-XS-E-032 (EFFECTIVE_TAX_RATE) → What share of my income actually goes in tax?
+MK-XS-E-033 (EXPECTED_RETURN_BLENDED) → What return should I expect on everything I hold together?
+MK-XS-E-034 (EXPECTED_SWING_BLENDED) → How much does a year's return typically swing around that average?
+MK-XS-E-035 (FILING_STATUS) → How does this person file?
+MK-XS-E-036 (GUARANTEED_OUTSIDE_STREAMS) → The plan's guaranteed-income input as separate streams of OUTSIDE money only. Answers: zer
+MK-XS-E-037 (MONTHLY_SAVING) → How much goes in each month?
+MK-XS-E-002 (NEST_EGG) → What is my retirement pot worth?
+MK-XS-E-038 (REPORTED_RETURN) → What return did the person say they actually earned over the past year?
+MK-XS-E-004 (RETIREMENT_SPENDING) → What will be spent each month in retirement?
+MK-XS-E-039 (SPLIT_BY_HOW_IT_IS_TAXED) → How is the retirement money split by the tax that will be owed on it?
+MK-XS-E-040 (SS_BENEFIT_AT_AGE) → The monthly Social Security check at a chosen claim age, in today's dollars. Answers: a wh
+MK-XS-E-041 (STATE_TAX_RATE) → What state tax rate applies?
+MK-XS-E-042 (SWING_FROM_RETURN) → How much might a year's return swing, judged from the return alone?
+MK-XS-E-043 (TAX_OVER65_COUNT) → How many people on the tax return are 65 or older — the input the over-65 deduction needs 
+MK-XS-E-044 (TOTAL_INCOME) → What is the whole household income for the year, before tax?</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -16692,7 +16775,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MK-PL-E-005</t>
+          <t>MK-XS-E-004</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -16732,7 +16815,8 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>COST_OF_LIVING · READ_A_NUMBER</t>
+          <t>MK-XS-E-045 (COST_OF_LIVING) → How much more or less does life cost where they plan to live?
+MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -16790,7 +16874,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MK-PL-E-006</t>
+          <t>MK-PL-E-004</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -16889,7 +16973,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MK-PL-E-004</t>
+          <t>MK-XS-E-006</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -16933,7 +17017,21 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>EFFECTIVE_TAX_RATE · EXPECTED_RETURN_BLENDED · EXPECTED_SWING_BLENDED · FILING_STATUS · GUARANTEED_OUTSIDE_STREAMS · MONTHLY_SAVING · NEST_EGG · REPORTED_RETURN · RETIREMENT_SPENDING · SPLIT_BY_HOW_IT_IS_TAXED · SS_BENEFIT_AT_AGE · STATE_TAX_RATE · SWING_FROM_RETURN · TAX_OVER65_COUNT · TOTAL_INCOME</t>
+          <t>MK-XS-E-032 (EFFECTIVE_TAX_RATE) → What share of my income actually goes in tax?
+MK-XS-E-033 (EXPECTED_RETURN_BLENDED) → What return should I expect on everything I hold together?
+MK-XS-E-034 (EXPECTED_SWING_BLENDED) → How much does a year's return typically swing around that average?
+MK-XS-E-035 (FILING_STATUS) → How does this person file?
+MK-XS-E-036 (GUARANTEED_OUTSIDE_STREAMS) → The plan's guaranteed-income input as separate streams of OUTSIDE money only. Answers: zer
+MK-XS-E-037 (MONTHLY_SAVING) → How much goes in each month?
+MK-XS-E-002 (NEST_EGG) → What is my retirement pot worth?
+MK-XS-E-038 (REPORTED_RETURN) → What return did the person say they actually earned over the past year?
+MK-XS-E-004 (RETIREMENT_SPENDING) → What will be spent each month in retirement?
+MK-XS-E-039 (SPLIT_BY_HOW_IT_IS_TAXED) → How is the retirement money split by the tax that will be owed on it?
+MK-XS-E-040 (SS_BENEFIT_AT_AGE) → The monthly Social Security check at a chosen claim age, in today's dollars. Answers: a wh
+MK-XS-E-041 (STATE_TAX_RATE) → What state tax rate applies?
+MK-XS-E-042 (SWING_FROM_RETURN) → How much might a year's return swing, judged from the return alone?
+MK-XS-E-043 (TAX_OVER65_COUNT) → How many people on the tax return are 65 or older — the input the over-65 deduction needs 
+MK-XS-E-044 (TOTAL_INCOME) → What is the whole household income for the year, before tax?</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -16995,7 +17093,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MK-PL-E-007</t>
+          <t>MK-PL-E-005</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -17093,7 +17191,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MK-PL-E-008</t>
+          <t>MK-PL-E-006</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -17289,7 +17387,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MK-PL-E-008</t>
+          <t>MK-PL-E-006</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -17387,7 +17485,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MK-NW-E-012</t>
+          <t>MK-NW-E-011</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -17428,7 +17526,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>None found in the code — it reads raw values only</t>
+          <t>None — this engine reads raw inputs only</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -17494,7 +17592,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MK-PL-E-009</t>
+          <t>MK-XS-E-040</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -17534,7 +17632,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>SS_CLAIM_FACTOR</t>
+          <t>MK-XS-E-046 (SS_CLAIM_FACTOR) → How much of the statement amount a claim age actually pays, anchored at the person's OWN f</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -17594,7 +17692,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MK-PL-E-010</t>
+          <t>MK-PL-E-007</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -17635,7 +17733,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>RETIREMENT_INCOME</t>
+          <t>MK-XS-E-047 (RETIREMENT_INCOME) → How much retirement income arrives monthly?</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -17697,7 +17795,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MK-PL-E-011</t>
+          <t>MK-PL-E-008</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -17737,7 +17835,8 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>SS_CLAIM_FACTOR · SS_FULL_RETIREMENT_AGE</t>
+          <t>MK-XS-E-048 (SS_FULL_RETIREMENT_AGE) → The person's own Social Security full retirement age. Answers: 66 (born through 1954) · 66
+MK-XS-E-046 (SS_CLAIM_FACTOR) → How much of the statement amount a claim age actually pays, anchored at the person's OWN f</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -17796,7 +17895,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MK-PL-E-012</t>
+          <t>MK-PL-E-009</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -17895,7 +17994,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MK-PL-E-013</t>
+          <t>MK-PL-E-010</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -17993,7 +18092,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MK-PL-E-014</t>
+          <t>MK-PL-E-011</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -18091,7 +18190,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MK-PL-E-015</t>
+          <t>MK-PL-E-012</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -18189,7 +18288,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MK-PL-E-016</t>
+          <t>MK-PL-E-013</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -18287,7 +18386,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MK-PL-E-014</t>
+          <t>MK-PL-E-011</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -18385,7 +18484,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MK-NW-E-010</t>
+          <t>MK-NW-E-009</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -18431,7 +18530,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>WILL_IT_LAST</t>
+          <t>MK-XS-E-005 (WILL_IT_LAST) → Will my money last?</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -18589,7 +18688,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MK-PL-E-017</t>
+          <t>MK-PL-E-014</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -18687,7 +18786,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MK-PL-E-004</t>
+          <t>MK-XS-E-006</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -18731,7 +18830,21 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>EFFECTIVE_TAX_RATE · EXPECTED_RETURN_BLENDED · EXPECTED_SWING_BLENDED · FILING_STATUS · GUARANTEED_OUTSIDE_STREAMS · MONTHLY_SAVING · NEST_EGG · REPORTED_RETURN · RETIREMENT_SPENDING · SPLIT_BY_HOW_IT_IS_TAXED · SS_BENEFIT_AT_AGE · STATE_TAX_RATE · SWING_FROM_RETURN · TAX_OVER65_COUNT · TOTAL_INCOME</t>
+          <t>MK-XS-E-032 (EFFECTIVE_TAX_RATE) → What share of my income actually goes in tax?
+MK-XS-E-033 (EXPECTED_RETURN_BLENDED) → What return should I expect on everything I hold together?
+MK-XS-E-034 (EXPECTED_SWING_BLENDED) → How much does a year's return typically swing around that average?
+MK-XS-E-035 (FILING_STATUS) → How does this person file?
+MK-XS-E-036 (GUARANTEED_OUTSIDE_STREAMS) → The plan's guaranteed-income input as separate streams of OUTSIDE money only. Answers: zer
+MK-XS-E-037 (MONTHLY_SAVING) → How much goes in each month?
+MK-XS-E-002 (NEST_EGG) → What is my retirement pot worth?
+MK-XS-E-038 (REPORTED_RETURN) → What return did the person say they actually earned over the past year?
+MK-XS-E-004 (RETIREMENT_SPENDING) → What will be spent each month in retirement?
+MK-XS-E-039 (SPLIT_BY_HOW_IT_IS_TAXED) → How is the retirement money split by the tax that will be owed on it?
+MK-XS-E-040 (SS_BENEFIT_AT_AGE) → The monthly Social Security check at a chosen claim age, in today's dollars. Answers: a wh
+MK-XS-E-041 (STATE_TAX_RATE) → What state tax rate applies?
+MK-XS-E-042 (SWING_FROM_RETURN) → How much might a year's return swing, judged from the return alone?
+MK-XS-E-043 (TAX_OVER65_COUNT) → How many people on the tax return are 65 or older — the input the over-65 deduction needs 
+MK-XS-E-044 (TOTAL_INCOME) → What is the whole household income for the year, before tax?</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -18793,7 +18906,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MK-NW-E-007</t>
+          <t>MK-NW-E-006</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -18835,7 +18948,8 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>DEBT_MINIMUM_TOTAL · DEBT_PAYMENTS_ACTUAL</t>
+          <t>MK-XS-E-017 (DEBT_MINIMUM_TOTAL) → What must I pay across all debts to stay current?
+MK-XS-E-018 (DEBT_PAYMENTS_ACTUAL) → What is actually going out on debt each month?</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -18897,7 +19011,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MK-PL-E-018</t>
+          <t>MK-PL-E-015</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -18995,7 +19109,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MK-PL-E-010</t>
+          <t>MK-PL-E-007</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -19036,7 +19150,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>RETIREMENT_INCOME</t>
+          <t>MK-XS-E-047 (RETIREMENT_INCOME) → How much retirement income arrives monthly?</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -19098,7 +19212,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MK-NW-E-010</t>
+          <t>MK-NW-E-009</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -19144,7 +19258,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>WILL_IT_LAST</t>
+          <t>MK-XS-E-005 (WILL_IT_LAST) → Will my money last?</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -19212,7 +19326,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MK-XS-E-002</t>
+          <t>MK-XS-E-007</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -19253,7 +19367,11 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>NEST_EGG · ODDS_DISPLAY · RETIREMENT_SPENDING · WILL_IT_LAST · WILL_IT_LAST_INPUTS</t>
+          <t>MK-XS-E-002 (NEST_EGG) → What is my retirement pot worth?
+MK-XS-E-003 (ODDS_DISPLAY) → The retirement odds a person actually sees. Answers: 0, 5, 10 … 100 — the exact simulation
+MK-XS-E-004 (RETIREMENT_SPENDING) → What will be spent each month in retirement?
+MK-XS-E-005 (WILL_IT_LAST) → Will my money last?
+MK-XS-E-006 (WILL_IT_LAST_INPUTS) → What goes into working out the odds?</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
@@ -19316,7 +19434,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>MK-PL-E-019</t>
+          <t>MK-PL-E-016</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -19414,7 +19532,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MK-PL-E-020</t>
+          <t>MK-PL-E-017</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -19516,7 +19634,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MK-PL-E-020</t>
+          <t>MK-PL-E-017</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -19874,7 +19992,7 @@
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="35" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
-    <col width="29" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="37" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
@@ -19959,7 +20077,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Engines it depends on</t>
+          <t>Dependency — engine ID → the output it uses</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -20330,7 +20448,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MK-XS-E-005</t>
+          <t>MK-XS-E-011</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -20521,7 +20639,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MK-CF-E-002</t>
+          <t>MK-XS-E-044</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -20562,7 +20680,13 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>EQUITY_THIS_YEAR · OTHER_INCOME · READ_A_NUMBER · RENTAL_INCOME_A_YEAR · RETIREMENT_INCOME_NOW · SALARY_A_YEAR · TIPS_A_YEAR</t>
+          <t>MK-XS-E-049 (EQUITY_THIS_YEAR) → How much equity vests this year?
+MK-XS-E-050 (OTHER_INCOME) → What else comes in?
+MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?
+MK-XS-E-051 (RENTAL_INCOME_A_YEAR) → What do the rentals net over a year?
+MK-PL-E-007 (RETIREMENT_INCOME_NOW) → How much retirement income is arriving TODAY?
+MK-XS-E-052 (SALARY_A_YEAR) → What is the salary for the year?
+MK-XS-E-053 (TIPS_A_YEAR) → What do tips come to over the year?</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -20620,7 +20744,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MK-CF-E-002</t>
+          <t>MK-XS-E-044</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -20661,7 +20785,13 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>EQUITY_THIS_YEAR · OTHER_INCOME · READ_A_NUMBER · RENTAL_INCOME_A_YEAR · RETIREMENT_INCOME_NOW · SALARY_A_YEAR · TIPS_A_YEAR</t>
+          <t>MK-XS-E-049 (EQUITY_THIS_YEAR) → How much equity vests this year?
+MK-XS-E-050 (OTHER_INCOME) → What else comes in?
+MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?
+MK-XS-E-051 (RENTAL_INCOME_A_YEAR) → What do the rentals net over a year?
+MK-PL-E-007 (RETIREMENT_INCOME_NOW) → How much retirement income is arriving TODAY?
+MK-XS-E-052 (SALARY_A_YEAR) → What is the salary for the year?
+MK-XS-E-053 (TIPS_A_YEAR) → What do tips come to over the year?</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -20719,7 +20849,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MK-CF-E-002</t>
+          <t>MK-XS-E-044</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -20760,7 +20890,13 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>EQUITY_THIS_YEAR · OTHER_INCOME · READ_A_NUMBER · RENTAL_INCOME_A_YEAR · RETIREMENT_INCOME_NOW · SALARY_A_YEAR · TIPS_A_YEAR</t>
+          <t>MK-XS-E-049 (EQUITY_THIS_YEAR) → How much equity vests this year?
+MK-XS-E-050 (OTHER_INCOME) → What else comes in?
+MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?
+MK-XS-E-051 (RENTAL_INCOME_A_YEAR) → What do the rentals net over a year?
+MK-PL-E-007 (RETIREMENT_INCOME_NOW) → How much retirement income is arriving TODAY?
+MK-XS-E-052 (SALARY_A_YEAR) → What is the salary for the year?
+MK-XS-E-053 (TIPS_A_YEAR) → What do tips come to over the year?</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -20818,7 +20954,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MK-CF-E-003</t>
+          <t>MK-CF-E-002</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -20916,7 +21052,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MK-CF-E-004</t>
+          <t>MK-XS-E-051</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -20957,7 +21093,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>RENTALS</t>
+          <t>MK-XS-E-054 (RENTALS) → What rental properties are there, and what does each bring in?</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -21015,7 +21151,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MK-PL-E-010</t>
+          <t>MK-PL-E-007</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21056,7 +21192,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>RETIREMENT_INCOME</t>
+          <t>MK-XS-E-047 (RETIREMENT_INCOME) → How much retirement income arrives monthly?</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -21118,7 +21254,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MK-CF-E-005</t>
+          <t>MK-CF-E-003</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -21216,7 +21352,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MK-CF-E-006</t>
+          <t>MK-XS-E-021</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -21256,7 +21392,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>READ_A_NUMBER</t>
+          <t>MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -21314,7 +21450,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MK-CF-E-006</t>
+          <t>MK-XS-E-021</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -21354,7 +21490,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>READ_A_NUMBER</t>
+          <t>MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -21412,7 +21548,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MK-CF-E-007</t>
+          <t>MK-CF-E-004</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -21453,7 +21589,8 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>READ_A_NUMBER · SPENDING_BY_KIND</t>
+          <t>MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?
+MK-XS-E-021 (SPENDING_BY_KIND) → What is spent each month, split by kind?</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -21515,7 +21652,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MK-CF-E-008</t>
+          <t>MK-CF-E-005</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -21613,7 +21750,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MK-CF-E-009</t>
+          <t>MK-CF-E-006</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -21711,7 +21848,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MK-XS-E-006</t>
+          <t>MK-XS-E-012</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -21813,7 +21950,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MK-CF-E-010</t>
+          <t>MK-CF-E-007</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -21853,7 +21990,8 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>DEBT_SHAPE · READ_A_NUMBER</t>
+          <t>MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?
+MK-XS-E-019 (DEBT_SHAPE) → How is THIS debt repaid?</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -22005,7 +22143,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MK-CF-E-011</t>
+          <t>MK-CF-E-008</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -22103,7 +22241,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MK-NW-E-010</t>
+          <t>MK-NW-E-009</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -22149,7 +22287,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>WILL_IT_LAST</t>
+          <t>MK-XS-E-005 (WILL_IT_LAST) → Will my money last?</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -22213,7 +22351,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MK-CF-E-012</t>
+          <t>MK-XS-E-047</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -22253,7 +22391,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>READ_A_NUMBER</t>
+          <t>MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -22311,7 +22449,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MK-PL-E-010</t>
+          <t>MK-PL-E-007</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -22352,7 +22490,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>RETIREMENT_INCOME</t>
+          <t>MK-XS-E-047 (RETIREMENT_INCOME) → How much retirement income arrives monthly?</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -22414,7 +22552,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MK-CF-E-013</t>
+          <t>MK-CF-E-009</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -22512,7 +22650,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MK-CF-E-014</t>
+          <t>MK-CF-E-010</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -22614,7 +22752,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MK-CF-E-002</t>
+          <t>MK-XS-E-044</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -22655,7 +22793,13 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>EQUITY_THIS_YEAR · OTHER_INCOME · READ_A_NUMBER · RENTAL_INCOME_A_YEAR · RETIREMENT_INCOME_NOW · SALARY_A_YEAR · TIPS_A_YEAR</t>
+          <t>MK-XS-E-049 (EQUITY_THIS_YEAR) → How much equity vests this year?
+MK-XS-E-050 (OTHER_INCOME) → What else comes in?
+MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?
+MK-XS-E-051 (RENTAL_INCOME_A_YEAR) → What do the rentals net over a year?
+MK-PL-E-007 (RETIREMENT_INCOME_NOW) → How much retirement income is arriving TODAY?
+MK-XS-E-052 (SALARY_A_YEAR) → What is the salary for the year?
+MK-XS-E-053 (TIPS_A_YEAR) → What do tips come to over the year?</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -22713,7 +22857,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MK-CF-E-015</t>
+          <t>MK-CF-E-011</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -23071,7 +23215,7 @@
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="35" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
-    <col width="29" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="37" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
@@ -23156,7 +23300,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Engines it depends on</t>
+          <t>Dependency — engine ID → the output it uses</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -23822,7 +23966,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MK-CF-E-007</t>
+          <t>MK-CF-E-004</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -23863,7 +24007,8 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>READ_A_NUMBER · SPENDING_BY_KIND</t>
+          <t>MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?
+MK-XS-E-021 (SPENDING_BY_KIND) → What is spent each month, split by kind?</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -24223,7 +24368,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MK-CF-E-002</t>
+          <t>MK-XS-E-044</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -24264,7 +24409,13 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>EQUITY_THIS_YEAR · OTHER_INCOME · READ_A_NUMBER · RENTAL_INCOME_A_YEAR · RETIREMENT_INCOME_NOW · SALARY_A_YEAR · TIPS_A_YEAR</t>
+          <t>MK-XS-E-049 (EQUITY_THIS_YEAR) → How much equity vests this year?
+MK-XS-E-050 (OTHER_INCOME) → What else comes in?
+MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?
+MK-XS-E-051 (RENTAL_INCOME_A_YEAR) → What do the rentals net over a year?
+MK-PL-E-007 (RETIREMENT_INCOME_NOW) → How much retirement income is arriving TODAY?
+MK-XS-E-052 (SALARY_A_YEAR) → What is the salary for the year?
+MK-XS-E-053 (TIPS_A_YEAR) → What do tips come to over the year?</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -24322,7 +24473,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MK-CF-E-002</t>
+          <t>MK-XS-E-044</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -24363,7 +24514,13 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>EQUITY_THIS_YEAR · OTHER_INCOME · READ_A_NUMBER · RENTAL_INCOME_A_YEAR · RETIREMENT_INCOME_NOW · SALARY_A_YEAR · TIPS_A_YEAR</t>
+          <t>MK-XS-E-049 (EQUITY_THIS_YEAR) → How much equity vests this year?
+MK-XS-E-050 (OTHER_INCOME) → What else comes in?
+MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?
+MK-XS-E-051 (RENTAL_INCOME_A_YEAR) → What do the rentals net over a year?
+MK-PL-E-007 (RETIREMENT_INCOME_NOW) → How much retirement income is arriving TODAY?
+MK-XS-E-052 (SALARY_A_YEAR) → What is the salary for the year?
+MK-XS-E-053 (TIPS_A_YEAR) → What do tips come to over the year?</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -24421,7 +24578,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MK-CF-E-002</t>
+          <t>MK-XS-E-044</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -24462,7 +24619,13 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>EQUITY_THIS_YEAR · OTHER_INCOME · READ_A_NUMBER · RENTAL_INCOME_A_YEAR · RETIREMENT_INCOME_NOW · SALARY_A_YEAR · TIPS_A_YEAR</t>
+          <t>MK-XS-E-049 (EQUITY_THIS_YEAR) → How much equity vests this year?
+MK-XS-E-050 (OTHER_INCOME) → What else comes in?
+MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?
+MK-XS-E-051 (RENTAL_INCOME_A_YEAR) → What do the rentals net over a year?
+MK-PL-E-007 (RETIREMENT_INCOME_NOW) → How much retirement income is arriving TODAY?
+MK-XS-E-052 (SALARY_A_YEAR) → What is the salary for the year?
+MK-XS-E-053 (TIPS_A_YEAR) → What do tips come to over the year?</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -24560,7 +24723,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>READ_A_NUMBER</t>
+          <t>MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -24760,7 +24923,9 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>ACCOUNT_SPLIT · ASSET_CLASS_OF_ACCOUNT · IS_PHYSICAL_ASSET</t>
+          <t>MK-XS-E-055 (IS_PHYSICAL_ASSET) → Is this something physical you own rather than money you could spend?
+MK-XS-E-015 (ACCOUNT_SPLIT) → This one brokerage account holds several different things — how much of it is each?
+MK-XS-E-008 (ASSET_CLASS_OF_ACCOUNT) → What kind of thing is this account — cash, a bond, shares, or something else?</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -25226,7 +25391,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MK-CF-E-006</t>
+          <t>MK-XS-E-021</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -25266,7 +25431,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>READ_A_NUMBER</t>
+          <t>MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -25720,7 +25885,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MK-CF-E-007</t>
+          <t>MK-CF-E-004</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -25761,7 +25926,8 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>READ_A_NUMBER · SPENDING_BY_KIND</t>
+          <t>MK-XS-E-020 (READ_A_NUMBER) → What number did the person actually type?
+MK-XS-E-021 (SPENDING_BY_KIND) → What is spent each month, split by kind?</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -25859,7 +26025,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>TAX_DEDUCTION</t>
+          <t>MK-XS-E-056 (TAX_DEDUCTION) → What amount of income is tax-free before the brackets start. Answers: $16,100 single · $32</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -25961,7 +26127,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>TAX_DEDUCTION</t>
+          <t>MK-XS-E-056 (TAX_DEDUCTION) → What amount of income is tax-free before the brackets start. Answers: $16,100 single · $32</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -20,7 +20,8 @@
     <sheet name="database" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="core_screens" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="reconciliation" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="engines_from_code" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="engines" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="engines_from_code" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -641,482 +642,494 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TAB — engines_from_code</t>
+          <t>TAB — engines</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Every exported function in the calculation code, read from the code itself and never from a document, matched back to its engine name, its identifier and the metric identifiers that reach it. This is where an engine nobody reaches, and a calculation nobody documented, become visible.</t>
+          <t>One row per engine identifier — the definitive list every dependency and every figure points at. Carries where the engine is implemented, what it answers, and which figures reach it.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TAB — reconciliation</t>
+          <t>TAB — engines_from_code</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>The input map checked in BOTH directions: what the inputs tab says uses each input, against what each engine actually names in its own input list. Where the two disagree the row says so. The section at the foot lists inputs an engine names that appear nowhere on the inputs tab.</t>
+          <t>Every exported function in the calculation code, read from the code itself and never from a document, matched back to its engine name, its identifier and the metric identifiers that reach it. This is where an engine nobody reaches, and a calculation nobody documented, become visible.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TAB — core_screens</t>
+          <t>TAB — reconciliation</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Every screen in the app, its parent, my recommendation on whether it belongs to the 55-70 core, and a column for the founder to decide. Until this is decided, no row in the file can honestly claim to be in scope (S17).</t>
+          <t>The input map checked in BOTH directions: what the inputs tab says uses each input, against what each engine actually names in its own input list. Where the two disagree the row says so. The section at the foot lists inputs an engine names that appear nowhere on the inputs tab.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TAB — database</t>
+          <t>TAB — core_screens</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>What the app saves in the cloud: where each thing is stored, what it holds, which figures depend on it, how often it is written and at what grain. Also names what is deliberately NOT saved.</t>
+          <t>Every screen in the app, its parent, my recommendation on whether it belongs to the 55-70 core, and a column for the founder to decide. Until this is decided, no row in the file can honestly claim to be in scope (S17).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>TAB — database</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>What the app saves in the cloud: where each thing is stored, what it holds, which figures depend on it, how often it is written and at what grain. Also names what is deliberately NOT saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>TAB — inputs</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>The raw values the engines need before any calculation happens.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="3" t="inlineStr"/>
-    </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN — Metric ID</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>The identifier of the figure, per moneykeel_naming_spec_unique-identifier_v01.md. Given once, never changed, never reused.</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Parent Screen Name</t>
+          <t>COLUMN — Metric ID</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>One of: Home, Networth, Performance, Cashflow, Plan, Menu. Menu means reachable only from the menu.</t>
+          <t>The identifier of the figure, per moneykeel_naming_spec_unique-identifier_v01.md. Given once, never changed, never reused.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Secondary Screen Name</t>
+          <t>COLUMN — Parent Screen Name</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>The screen reached from the parent, or NA when the figure is on the parent screen itself.</t>
+          <t>One of: Home, Networth, Performance, Cashflow, Plan, Menu. Menu means reachable only from the menu.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name on Screen</t>
+          <t>COLUMN — Secondary Screen Name</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>The label copied exactly as it is worded on screen, including capitals. Where a figure wears different labels on different screens, all are listed.</t>
+          <t>The screen reached from the parent, or NA when the figure is on the parent screen itself.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name of Underlying Metric</t>
+          <t>COLUMN — Name on Screen</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>The metric's name in the code.</t>
+          <t>The label copied exactly as it is worded on screen, including capitals. Where a figure wears different labels on different screens, all are listed.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name of Underlying Engine</t>
+          <t>COLUMN — Name of Underlying Metric</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>The engine that produces the figure. NOT IN OLD MASTER means the engine exists in the code but has no row in the old master file.</t>
+          <t>The metric's name in the code.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Inputs it needs (S02)</t>
+          <t>COLUMN — Name of Underlying Engine</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Every input the engine reads, named. Carried from the old master where it has a row there.</t>
+          <t>The engine that produces the figure. NOT IN OLD MASTER means the engine exists in the code but has no row in the old master file.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — What comes out (S04)</t>
+          <t>COLUMN — Inputs it needs (S02)</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Dollars, a percentage, a date, a count; how it is held and how it is shown. Marked "derived by rule" where it was worked out from the label and formula rather than read from the engine — those need confirming.</t>
+          <t>Every input the engine reads, named. Carried from the old master where it has a row there.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — What it says when it cannot be computed (S05)</t>
+          <t>COLUMN — What comes out (S04)</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>The refusal. Written where the engine has been read; NOT DETERMINED where it has not, rather than guessed.</t>
+          <t>Dollars, a percentage, a date, a count; how it is held and how it is shown. Marked "derived by rule" where it was worked out from the label and formula rather than read from the engine — those need confirming.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Grain (S06)</t>
+          <t>COLUMN — What it says when it cannot be computed (S05)</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>One figure per what: holding, account, debt, goal, category, month, or person.</t>
+          <t>The refusal. Written where the engine has been read; NOT DETERMINED where it has not, rather than guessed.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Period (S07)</t>
+          <t>COLUMN — Grain (S06)</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>As of when, and over what window.</t>
+          <t>One figure per what: holding, account, debt, goal, category, month, or person.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Dependency (S11)</t>
+          <t>COLUMN — Period (S07)</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>The engines this one leans on, each named by ITS identifier and by the output it gives. Read from the code itself, never from a document. "None" means the engine reads raw inputs only.</t>
+          <t>As of when, and over what window.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Secondary calculations and decisions the engine makes</t>
+          <t>COLUMN — Dependency (S11)</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>The judgements an engine must make BEFORE its headline figure exists: what class an asset is, what to call it on screen, which units apply, whether a value is fresh. Each of these is a formula of its own and needs its own row.</t>
+          <t>The engines this one leans on, each named by ITS identifier and by the output it gives. Read from the code itself, never from a document. "None" means the engine reads raw inputs only.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Same figure as (S16)</t>
+          <t>COLUMN — Secondary calculations and decisions the engine makes</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Where the same figure appears under more than one identifier, the row names the surviving identifier and why. Nothing is deleted: identifiers are never reused, so a folded row stays visible and says what it became.</t>
+          <t>The judgements an engine must make BEFORE its headline figure exists: what class an asset is, what to call it on screen, which units apply, whether a value is fresh. Each of these is a formula of its own and needs its own row.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Questions for you (numbered)</t>
+          <t>COLUMN — Same figure as (S16)</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>My open questions about that engine or figure, each with a number that never changes. A number is never reused or renumbered, so an answer can always be matched to its question.</t>
+          <t>Where the same figure appears under more than one identifier, the row names the surviving identifier and why. Nothing is deleted: identifiers are never reused, so a folded row stays visible and says what it became.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — YOUR ANSWER — use the same number</t>
+          <t>COLUMN — Questions for you (numbered)</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Answer here, starting each answer with the question number. Nothing else in the file needs to line up.</t>
+          <t>My open questions about that engine or figure, each with a number that never changes. A number is never reused or renumbered, so an answer can always be matched to its question.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Errors or findings to address</t>
+          <t>COLUMN — YOUR ANSWER — use the same number</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>What is known to be wrong or unproved about this figure, in plain English. Blank means nothing is on record yet — not that nothing is wrong.</t>
+          <t>Answer here, starting each answer with the question number. Nothing else in the file needs to line up.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Decisions made (S03)</t>
+          <t>COLUMN — Errors or findings to address</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>The rulings and assumptions that govern this figure, each marked with WHOSE decision it was: [Founder] his own ruling, [The person] something the user set, [Built in] an assumption nobody chose on a screen — which is usually why a number looks wrong. The standing display and rounding rule applies to every row and is stated at the top of this tab.</t>
+          <t>What is known to be wrong or unproved about this figure, in plain English. Blank means nothing is on record yet — not that nothing is wrong.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (mathematical)</t>
+          <t>COLUMN — Decisions made (S03)</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
+          <t>The rulings and assumptions that govern this figure, each marked with WHOSE decision it was: [Founder] his own ruling, [The person] something the user set, [Built in] an assumption nobody chose on a screen — which is usually why a number looks wrong. The standing display and rounding rule applies to every row and is stated at the top of this tab.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (in words)</t>
+          <t>COLUMN — Formula (mathematical)</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
+          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Engine ID</t>
+          <t>COLUMN — Formula (in words)</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
+          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Your name for it (72-metric file)</t>
+          <t>COLUMN — Engine ID</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
+          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Core screen?</t>
+          <t>COLUMN — Your name for it (72-metric file)</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Whether the screen is part of the 55-70 core, the agreed first scope. Currently NOT DETERMINED on every row: the core list has never been written down, so no row can honestly claim to be in or out of it.</t>
+          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>COLUMN — Core screen?</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Whether the screen is part of the 55-70 core, the agreed first scope. Currently NOT DETERMINED on every row: the core list has never been written down, so no row can honestly claim to be in or out of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>COLUMN — Row status</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>VERIFIED with its date means a person read the screen and confirmed the chain. NOT STARTED means the screen has not been read yet. Nothing in between is claimed.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
-      <c r="B46" s="3" t="inlineStr"/>
-    </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN — Input ID</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>The identifier of a raw input, per the same standard.</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Variable name</t>
+          <t>COLUMN — Input ID</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>What the raw value is called.</t>
+          <t>The identifier of a raw input, per the same standard.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Source</t>
+          <t>COLUMN — Variable name</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
+          <t>What the raw value is called.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Which metric uses it</t>
+          <t>COLUMN — Source</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Every metric identifier that depends on this input.</t>
+          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>COLUMN — Which metric uses it</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Every metric identifier that depends on this input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
           <t>COLUMN — Which engine uses it</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>Every engine identifier that reads this input.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
-      <c r="B52" s="3" t="inlineStr"/>
-    </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Complies with — naming</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Complies with — identifiers</t>
+          <t>Complies with — naming</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>Complies with — identifiers</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
           <t>Complies with — objectives</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>MoneyKeel/documents/standards/moneykeel_calc_spec_objectives-and-verification_v01.md</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr"/>
-      <c r="B56" s="3" t="inlineStr"/>
-    </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>COVERAGE — screens read so far</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>COVERAGE — screens read so far</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
           <t>COVERAGE — what that means</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>Every screen in the app is listed on its tab. Only Home carries figures so far; the rest are marked NOT STARTED. A rising count is not completeness while screens remain unread.</t>
         </is>
@@ -1133,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2320,6 +2333,635 @@
         </is>
       </c>
       <c r="G32" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MK-XS-I-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>spending categories the person set up</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Typed by the person when they set up their budget</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>planned spending · spending by kind</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PLANNED_SPENDING · SPENDING_BY_KIND</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>MK-XS-E-021 · MK-CF-E-004</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MK-XS-I-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>the date a hand-typed value was set</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Typed by the person, stamped when they save it</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>account value and its freshness</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>HAND_VALUE_AGE</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>MK-NW-E-011</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MK-XS-I-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>option positions — contracts, strike, expiry, put or call</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>An institution download, a connection, or typed</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>a holding’s value and gain when it is an option</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>HOLDING_MARKET_VALUE · HOLDING_CAP_GAINS</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>MK-NW-E-022 · MK-NW-E-026</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MK-XS-I-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>annuity income</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Typed by the person</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>guaranteed income · the retirement paycheck</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME · RETIREMENT_INCOME_NOW</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>MK-XS-E-047 · MK-PL-E-007</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MK-XS-I-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>other guaranteed income</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Typed by the person</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>guaranteed income · the retirement paycheck</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>MK-XS-E-047</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MK-XS-I-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>required-withdrawal income stream (ri_rmd)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Worked out from balances, not typed</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>the retirement paycheck. RULE B5: it must NOT count as guaranteed income — money coming OUT of the pot cannot fund the pot</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>MK-XS-E-047</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MK-XS-I-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>withdrawal income stream (ri_withdrawals)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Worked out from the plan, not typed</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>the retirement paycheck. RULE B5: excluded from guaranteed income for the same reason</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>MK-XS-E-047</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MK-XS-I-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>how often each income arrives</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Typed by the person</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>which months an income lands in</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME · TOTAL_INCOME</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>MK-XS-E-044 · MK-XS-E-047</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MK-XS-I-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>whether a stream is already being received</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Typed by the person</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>guaranteed income now, as against guaranteed income later</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME_NOW</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>MK-PL-E-007</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MK-XS-I-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>the payment the person chose to make on a debt</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Typed by the person, and it can exceed the minimum</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>payoff date · money out</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>DEBT_PAYOFF · DEBT_REQUIRED_PAYMENT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>MK-NW-E-007 · MK-PL-E-015</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MK-XS-I-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>how a stream is paid — monthly, yearly or one lump</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Typed by the person</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>how an income is spread across the year</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>MK-XS-E-047</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MK-XS-I-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>their own retirement contribution</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Typed by the person</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>take-home pay · the pot at retirement</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>TOTAL_INCOME · POT_AT_RETIREMENT</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>MK-NW-E-009 · MK-XS-E-044</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MK-XS-I-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>the person’s own plan overrides</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Set by the person on the Plan screen</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>every plan figure they have overridden</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>MK-XS-E-006</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MK-XS-I-045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>where they will live in retirement</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Typed by the person</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>cost of living where they retire</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RETIREMENT_SPENDING</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>MK-XS-E-004</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MK-XS-I-046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>how the employer match is expressed — percent or dollars</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Typed by the person</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>the employer match</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>EMPLOYER_MATCH</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>MK-MN-E-007</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MK-XS-I-047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>money to leave behind</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Typed by the person</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>the odds — the pot may not be run to zero</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_INPUTS · WILL_IT_LAST_RESULT</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>MK-XS-E-006 · MK-XS-E-007</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MK-XS-I-048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>the person’s own asset-class answer</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Typed by the person, and it outranks the institution</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>what class a holding is counted as</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ALLOCATION_BY_CLASS · ASSET_CLASS_OF_ACCOUNT</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>MK-XS-E-008 · MK-NW-E-005</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>VERIFIED 2026-08-22</t>
         </is>
@@ -4430,7 +5072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4485,12 +5127,12 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>ACCOUNT_SHARE_OF_TOTAL · ACCOUNT_SPLIT · ALLOCATION_BY_CLASS · DEBT_PICTURE · NET_WORTH · PLANNED_SPENDING · TOTAL_CASH · TOTAL_INVESTABLE · TOTAL_INVESTMENTS</t>
+          <t>ACCOUNT_SHARE_OF_TOTAL · ACCOUNT_SPLIT · ALLOCATION_BY_CLASS · BOND_CURRENT_YIELD · BOND_YIELD_TO_MATURITY · DEBT_PICTURE · HAND_VALUE_AGE · NET_WORTH · PLANNED_SPENDING · POT_AT_RETIREMENT · TOTAL_CASH · TOTAL_INVESTABLE · TOTAL_INVESTMENTS</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>PARTLY AGREES — declared but not naming it: REQUIRED_WITHDRAWAL  |  naming it but not declared: ACCOUNT_SHARE_OF_TOTAL, ACCOUNT_SPLIT, ALLOCATION_BY_CLASS, DEBT_PICTURE, PLANNED_SPENDING, TOTAL_INVESTABLE</t>
+          <t>PARTLY AGREES — declared but not naming it: REQUIRED_WITHDRAWAL  |  naming it but not declared: ACCOUNT_SHARE_OF_TOTAL, ACCOUNT_SPLIT, ALLOCATION_BY_CLASS, BOND_CURRENT_YIELD, BOND_YIELD_TO_MATURITY, DEBT_PICTURE, HAND_VALUE_AGE, PLANNED_SPENDING, POT_AT_RETIREMENT, TOTAL_INVESTABLE</t>
         </is>
       </c>
     </row>
@@ -4566,12 +5208,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>HOLDING_COST_BASIS · HOLDING_MARKET_VALUE · HOLDING_SHARES</t>
+          <t>ACCOUNT_SPLIT · BOND_COUPON · BOND_FACTS · HOLDING_COST_BASIS · HOLDING_MARKET_VALUE · HOLDING_SHARES · PERFORMANCE_TABLE</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>PARTLY AGREES — naming it but not declared: HOLDING_COST_BASIS</t>
+          <t>PARTLY AGREES — naming it but not declared: ACCOUNT_SPLIT, BOND_COUPON, BOND_FACTS, HOLDING_COST_BASIS, PERFORMANCE_TABLE</t>
         </is>
       </c>
     </row>
@@ -4674,12 +5316,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>LOOK_BACK · RETIREMENT_INCOME_NOW · SS_BENEFIT_AT_AGE · SS_CLAIM_FACTOR</t>
+          <t>LOOK_BACK · REALISED_GAIN · RETIREMENT_INCOME_NOW · SS_BENEFIT_AT_AGE · SS_CLAIM_FACTOR</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>PARTLY AGREES — declared but not naming it: LEDGER, NW_CHANGE_WALK  |  naming it but not declared: LOOK_BACK, RETIREMENT_INCOME_NOW, SS_BENEFIT_AT_AGE, SS_CLAIM_FACTOR</t>
+          <t>PARTLY AGREES — declared but not naming it: LEDGER, NW_CHANGE_WALK  |  naming it but not declared: LOOK_BACK, REALISED_GAIN, RETIREMENT_INCOME_NOW, SS_BENEFIT_AT_AGE, SS_CLAIM_FACTOR</t>
         </is>
       </c>
     </row>
@@ -4998,12 +5640,12 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>SS_BENEFIT_AT_AGE · SS_CLAIM_FACTOR</t>
+          <t>RETIREMENT_INCOME · SS_BENEFIT_AT_AGE · SS_CLAIM_FACTOR</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>PARTLY AGREES — declared but not naming it: RETIREMENT_INCOME_NOW  |  naming it but not declared: SS_CLAIM_FACTOR</t>
+          <t>PARTLY AGREES — declared but not naming it: RETIREMENT_INCOME_NOW  |  naming it but not declared: RETIREMENT_INCOME, SS_CLAIM_FACTOR</t>
         </is>
       </c>
     </row>
@@ -5079,12 +5721,12 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>RENTAL_INCOME_A_YEAR</t>
+          <t>RENTAL_INCOME_A_YEAR · TAXABLE_INCOME</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>PARTLY AGREES — declared but not naming it: TOTAL_INCOME  |  naming it but not declared: RENTAL_INCOME_A_YEAR</t>
+          <t>PARTLY AGREES — declared but not naming it: TOTAL_INCOME  |  naming it but not declared: RENTAL_INCOME_A_YEAR, TAXABLE_INCOME</t>
         </is>
       </c>
     </row>
@@ -5268,12 +5910,12 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>PLANNED_SPENDING · TOTAL_CASH</t>
+          <t>PLANNED_SPENDING · TAXABLE_INCOME · TOTAL_CASH</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>PARTLY AGREES — declared but not naming it: TAXABLE_INCOME, TAX_ON_CONVERSION  |  naming it but not declared: PLANNED_SPENDING, TOTAL_CASH</t>
+          <t>PARTLY AGREES — declared but not naming it: TAX_ON_CONVERSION  |  naming it but not declared: PLANNED_SPENDING, TOTAL_CASH</t>
         </is>
       </c>
     </row>
@@ -5295,213 +5937,245 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>NW_CHANGE_PCT · TREND_SERIES</t>
+          <t>NW_CHANGE_PCT · NW_CHANGE_WALK · TREND_SERIES</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>PARTLY AGREES — declared but not naming it: NW_CHANGE_WALK  |  naming it but not declared: NW_CHANGE_PCT</t>
+          <t>PARTLY AGREES — naming it but not declared: NW_CHANGE_PCT</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n"/>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-032</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>spending categories the person set up</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>PLANNED_SPENDING · SPENDING_BY_KIND</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_REQUIRED_PAYMENT · PLANNED_SPENDING · SPENDING_BY_KIND · TOTAL_CASH</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>PARTLY AGREES — naming it but not declared: DEBT_REQUIRED_PAYMENT, TOTAL_CASH</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>GAPS — inputs an engine names that are on NO row of the inputs tab.</t>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-I-033</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Each one is either a missing input, or the same input under another name.</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
+          <t>the date a hand-typed value was set</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>HAND_VALUE_AGE</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>HAND_VALUE_AGE</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>AGREES — both directions name the same engines.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>NO ID</t>
+          <t>MK-XS-I-034</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>and how often each arrives → the matching frequency</t>
+          <t>option positions — contracts, strike, expiry, put or call</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HOLDING_CAP_GAINS · HOLDING_MARKET_VALUE</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>RETIREMENT_INCOME</t>
+          <t>ACCOUNT_SPLIT</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+          <t>PARTLY AGREES — declared but not naming it: HOLDING_CAP_GAINS, HOLDING_MARKET_VALUE  |  naming it but not declared: ACCOUNT_SPLIT</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>NO ID</t>
+          <t>MK-XS-I-035</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>any split → accountClassBreakdown</t>
+          <t>annuity income</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RETIREMENT_INCOME · RETIREMENT_INCOME_NOW</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>ALLOCATION_BY_CLASS</t>
+          <t>RETIREMENT_INCOME</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+          <t>PARTLY AGREES — declared but not naming it: RETIREMENT_INCOME_NOW</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>NO ID</t>
+          <t>MK-XS-I-036</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>baseline date → sinceKey</t>
+          <t>other guaranteed income</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RETIREMENT_INCOME</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>NW_CHANGE_PCT</t>
+          <t>RETIREMENT_INCOME</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+          <t>AGREES — both directions name the same engines.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>NO ID</t>
+          <t>MK-XS-I-037</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>chosen → monthly_payment</t>
+          <t>required-withdrawal income stream (ri_rmd)</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RETIREMENT_INCOME</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>DEBT_REQUIRED_PAYMENT · SPENDING_BY_KIND</t>
+          <t>RETIREMENT_INCOME</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+          <t>AGREES — both directions name the same engines.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>NO ID</t>
+          <t>MK-XS-I-038</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>debt paid down → debtPrincipal</t>
+          <t>withdrawal income stream (ri_withdrawals)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RETIREMENT_INCOME</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>NW_CHANGE_WALK</t>
+          <t>RETIREMENT_INCOME</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+          <t>AGREES — both directions name the same engines.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>NO ID</t>
+          <t>MK-XS-I-039</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>dividends → dividends</t>
+          <t>how often each income arrives</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RETIREMENT_INCOME · TOTAL_INCOME</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>NW_CHANGE_WALK</t>
+          <t>RETIREMENT_INCOME</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+          <t>PARTLY AGREES — declared but not naming it: TOTAL_INCOME</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>NO ID</t>
+          <t>MK-XS-I-040</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>do they receive it now → incomeSources</t>
+          <t>whether a stream is already being received</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RETIREMENT_INCOME_NOW</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -5511,1494 +6185,247 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+          <t>AGREES — both directions name the same engines.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>NO ID</t>
+          <t>MK-XS-I-041</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>each account's class → assetClassOf</t>
+          <t>the payment the person chose to make on a debt</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEBT_PAYOFF · DEBT_REQUIRED_PAYMENT</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>ALLOCATION_BY_CLASS · PLANNED_SPENDING · TOTAL_CASH · TOTAL_INVESTABLE · TOTAL_INVESTMENTS</t>
+          <t>DEBT_REQUIRED_PAYMENT · SPENDING_BY_KIND</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+          <t>PARTLY AGREES — declared but not naming it: DEBT_PAYOFF  |  naming it but not declared: SPENDING_BY_KIND</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>NO ID</t>
+          <t>MK-XS-I-042</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>each holding's benchmark return → rows[].benchReturn</t>
+          <t>how a stream is paid — monthly, yearly or one lump</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RETIREMENT_INCOME</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>BENCHMARK_RETURN_BLENDED</t>
+          <t>DEBT_REQUIRED_PAYMENT · SPENDING_BY_KIND</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+          <t>PARTLY AGREES — declared but not naming it: RETIREMENT_INCOME  |  naming it but not declared: DEBT_REQUIRED_PAYMENT, SPENDING_BY_KIND</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>NO ID</t>
+          <t>MK-XS-I-043</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>each holding's return → rows[].periodReturn</t>
+          <t>their own retirement contribution</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>POT_AT_RETIREMENT · TOTAL_INCOME</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>VALUE_WEIGHTED_RETURN</t>
+          <t>EMPLOYER_MATCH</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+          <t>PARTLY AGREES — declared but not naming it: POT_AT_RETIREMENT, TOTAL_INCOME  |  naming it but not declared: EMPLOYER_MATCH</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>NO ID</t>
+          <t>MK-XS-I-044</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>each part → its own engine above</t>
+          <t>the person’s own plan overrides</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WILL_IT_LAST_INPUTS</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>TOTAL_INCOME</t>
+          <t>WILL_IT_LAST_INPUTS</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+          <t>AGREES — both directions name the same engines.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>NO ID</t>
+          <t>MK-XS-I-045</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>each source → ri_ss</t>
+          <t>where they will live in retirement</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RETIREMENT_SPENDING</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>RETIREMENT_INCOME</t>
+          <t>RETIREMENT_SPENDING</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+          <t>AGREES — both directions name the same engines.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>NO ID</t>
+          <t>MK-XS-I-046</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>ending value → ending</t>
+          <t>how the employer match is expressed — percent or dollars</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>EMPLOYER_MATCH</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>NW_CHANGE_WALK</t>
+          <t>EMPLOYER_MATCH</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+          <t>AGREES — both directions name the same engines.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>NO ID</t>
+          <t>MK-XS-I-047</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>every debt → debts</t>
+          <t>money to leave behind</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WILL_IT_LAST_INPUTS · WILL_IT_LAST_RESULT</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>DEBT_PICTURE · NET_WORTH</t>
+          <t>WILL_IT_LAST_INPUTS</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+          <t>PARTLY AGREES — declared but not naming it: WILL_IT_LAST_RESULT</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>NO ID</t>
+          <t>MK-XS-I-048</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>everything → WILL_IT_LAST_INPUTS</t>
+          <t>the person’s own asset-class answer</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ALLOCATION_BY_CLASS · ASSET_CLASS_OF_ACCOUNT</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>WILL_IT_LAST_RESULT</t>
+          <t>ALLOCATION_BY_CLASS · PLANNED_SPENDING · TOTAL_CASH · TOTAL_INVESTABLE · TOTAL_INVESTMENTS</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
+          <t>PARTLY AGREES — declared but not naming it: ASSET_CLASS_OF_ACCOUNT  |  naming it but not declared: PLANNED_SPENDING, TOTAL_CASH, TOTAL_INVESTABLE, TOTAL_INVESTMENTS</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>gross → gross</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>TAXABLE_INCOME</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
+      <c r="A50" s="3" t="n"/>
+      <c r="B50" s="3" t="n"/>
+      <c r="C50" s="3" t="n"/>
+      <c r="D50" s="3" t="n"/>
+      <c r="E50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>GAPS — inputs an engine names that are on NO row of the inputs tab.</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>guaranteed income → RETIREMENT_INCOME, SS_BENEFIT_AT_AGE</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>WILL_IT_LAST_INPUTS</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>holdings → positions[]</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>ACCOUNT_SPLIT</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>how far back → months</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>LOOK_BACK</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>how they file → status</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>TAXABLE_INCOME</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>interest → interest</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>NW_CHANGE_WALK</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>is a range wanted → withBand</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>WILL_IT_LAST_RESULT</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>its value → rows[].marketValue</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>BENCHMARK_RETURN_BLENDED · VALUE_WEIGHTED_RETURN</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>money in → contributions</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>NW_CHANGE_WALK</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>money out → withdrawals</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>NW_CHANGE_WALK</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>money that counts toward retirement → NEST_EGG</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>WHAT_THE_PLAN_STILL_NEEDS</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>money to leave behind → legacyTarget</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>WILL_IT_LAST_INPUTS</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>now → now</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>PRICE_FRESHNESS</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>optionally one account → opts.accountId</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>REALISED_GAIN</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>optionally one ticker → opts.ticker</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>REALISED_GAIN</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>options → option_holdings[]</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>ACCOUNT_SPLIT</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>or the three summary figures → b_fixed, b_nonmonthly, b_flexible</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>DEBT_REQUIRED_PAYMENT · SPENDING_BY_KIND</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>percent or dollars → employerMatchMode</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>EMPLOYER_MATCH</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>return and swing → EXPECTED_RETURN_BLENDED, EXPECTED_SWING_BLENDED</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>WILL_IT_LAST_INPUTS</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>ri_annuities</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>RETIREMENT_INCOME</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>ri_other</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>RETIREMENT_INCOME</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>ri_rmd</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>RETIREMENT_INCOME</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>ri_withdrawals</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>RETIREMENT_INCOME</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>shape → paymentShape</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>DEBT_REQUIRED_PAYMENT · SPENDING_BY_KIND</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>starting value → beginning</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>NW_CHANGE_WALK</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>the account → a</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>ACCOUNT_SPLIT · HAND_VALUE_AGE</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>the categories → spendCats</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>DEBT_REQUIRED_PAYMENT · SPENDING_BY_KIND</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>the chosen chip → period</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>PERFORMANCE_TABLE</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>the dates in this sync → activityDates</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>HISTORY_DEPTH</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>the holding → position/account</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>BOND_COUPON · BOND_FACTS</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>the holdings → positions</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>PERFORMANCE_TABLE</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>the ledger → txns</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>REALISED_GAIN</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>the match → employerMatchValue</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>EMPLOYER_MATCH</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>the pot → NEST_EGG</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>WILL_IT_LAST_INPUTS</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>the same inputs → inp</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>POT_AT_RETIREMENT</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>their own contribution → c_401k</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>EMPLOYER_MATCH</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>their own overrides → the Plan screen</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>WILL_IT_LAST_INPUTS</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>today → now</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>BOND_YEARS_LEFT · HAND_VALUE_AGE · HOLDING_CAP_GAINS · PERFORMANCE_TABLE</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>today → opts.now</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>REALISED_GAIN</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>today's value → currentInvestable</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>NW_CHANGE_PCT</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>value → value</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>BOND_YIELD_TO_MATURITY</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>what it is worth → value</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>BOND_CURRENT_YIELD</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>what we knew → existing</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>HISTORY_DEPTH</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>when the value was set → value_as_of</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>HAND_VALUE_AGE</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>where it might have gone → toSeries</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>LOOK_BACK</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>where it sat → fromSeries</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>LOOK_BACK</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>NO ID</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>where they will live → the location answer</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>RETIREMENT_SPENDING</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>MISSING FROM THE INPUTS TAB — add it, or point it at the input it already is.</t>
-        </is>
-      </c>
+          <t>Each one is either a missing input, or the same input under another name.</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7006,6 +6433,4380 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F136"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Engine ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Engine name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Where it is implemented (S12)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>What it answers</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Metric identifiers that reach it</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>How it is reached</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-E-001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — the by-month grid, src/domain/cashflow</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-001 · MK-CF-M-002</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-E-002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — the equity schedule, src/domain/income</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-009</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-E-003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — the received list, src/domain/income</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-012</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-E-004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>PLANNED_SPENDING</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/budget/index.ts:45</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>What does this person plan to spend each month?</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-015 · MK-MN-M-007 · MK-MN-M-026</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Named by 3 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-E-005</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — the big-bill radar, src/domain/cashflow</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-016</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-E-006</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — the unusual-spend check, src/domain/budget</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-017</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-E-007</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>SPENDING_BY_KIND · DEBT_REQUIRED_PAYMENT</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-019</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-E-008</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — plan commitments, src/domain/planning</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-021</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-E-009</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>the by-month grid</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-025</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-E-010</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_PAYCHECK</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-026</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-E-011</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>THE_BILL_CALENDAR</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-028</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>MK-HM-E-001</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>PRICE_FRESHNESS</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>src/services/marketData.ts:60</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>How old is the price we are showing?</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>MK-HM-M-001</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>MK-HM-E-002</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — milestoneCrossed, src/domain/milestones.ts</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>MK-HM-M-002</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>MK-HM-E-003</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — useInsights, src/domain/insights</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>MK-HM-M-003 · MK-MN-M-015</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-E-001</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>BIG_COSTS</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-M-001 · MK-MN-M-002</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-E-002</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>CONTRIBUTION_ROOM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-M-003 · MK-MN-M-004 · MK-MN-M-029</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Named by 3 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-E-003</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>CREDIT_USE</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-M-006</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-E-004</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>GOAL_CAPACITY</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-M-008</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-E-005</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>GOAL_PROGRESS</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-M-009</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-E-006</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>SINKING_FUNDS</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-M-010</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-E-007</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>EMPLOYER_MATCH</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/income/onboarding.ts:263</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>How much does the employer add each month?</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-M-014</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-E-008</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL_INVESTABLE · TOTAL_CASH</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-M-016</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-E-009</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>INSURANCE_NEED</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-M-017 · MK-MN-M-018 · MK-MN-M-019</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Named by 3 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-E-010</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>JOB_SAFETY_RUNWAY</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-M-020</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-E-011</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>ALTERNATIVES_TOTAL</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-M-022</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-E-012</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>ALTERNATIVES_GROWTH</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-M-023</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-E-013</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>STRESS_TEST</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-M-024 · MK-MN-M-025</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-E-014</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>TAXABLE_INCOME</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/income/tax.ts:110</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>What income is taxed, given how this person files?</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-M-027 · MK-MN-M-028</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-E-015</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — the outflow watch, src/domain/insights</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>MK-MN-M-030</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-001</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>TREND_SERIES</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/history.ts:43</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>What points does the net-worth graph draw?</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-001 · MK-NW-M-003</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-002</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_PCT</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/history.ts:118</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>What is my return on cash and investments since the baseline?</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-002</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-003</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>ACCOUNT_SHARE_OF_TOTAL</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:663</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>How much of everything sits in each account, and what return do they blend to?</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-004</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-004</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL_CASH</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:271</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>How much actual cash do I have?</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-005</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-005</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>ALLOCATION_BY_CLASS</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:502</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>How much money sits in each of the seven classes?</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-007</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-006</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_PICTURE</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/debt/index.ts:214</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>What is the whole debt picture?</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-009 · MK-NW-M-010 · MK-NW-M-012</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Named by 3 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-007</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_REQUIRED_PAYMENT</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/debt/index.ts:44</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>What must I pay on this each month?</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-011</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-008</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL_CASH · PLANNED_SPENDING</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-014</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-009</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>POT_AT_RETIREMENT</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/index.ts:324</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>What will the pot be worth at retirement, and how big does it need to be?</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-022 · MK-NW-M-015 · MK-PL-M-026 · MK-PL-M-033</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Named by 4 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-010</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>NET_WORTH · DEBT_PICTURE</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-017</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-011</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>HAND_VALUE_AGE</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:97</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>How old is this hand-entered value?</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-018 · MK-PL-M-016</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-012</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>the ledger sum of interest and dividends for the account</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-019</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-013</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>the ledger sum for that holding</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-021</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-014</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>HISTORY_DEPTH</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>src/services/sync/snaptrade.ts:284</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>How far back does this source's activity history go?</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-022</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-015</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>BOND_FACTS</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/bonds/index.ts:16</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>What are this holding's bond facts?</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-023 · MK-NW-M-041 · MK-NW-M-042</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Named by 3 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-016</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>BOND_COUPON</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/bonds/index.ts:21</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>How much income does this bond pay in a year?</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-024 · MK-NW-M-043</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-017</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>BOND_YEARS_LEFT</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/bonds/index.ts:24</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>How long until this bond pays back?</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-025</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-018</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>BOND_YIELD_TO_MATURITY</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/bonds/index.ts:33</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>What will this bond earn me a year if I hold it to the end?</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-026</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-019</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>BOND_CURRENT_YIELD</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/bonds/index.ts:29</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>What is this bond paying me, measured against what it is worth today?</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-027 · MK-NW-M-044</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-020</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>BOND_RATE_SENSITIVITY</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-028</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-021</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>the price feed, with its freshness</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-029</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-022</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_MARKET_VALUE</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:47</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>What is this holding worth right now?</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-030 · MK-NW-M-040</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-023</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_COST_BASIS</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:40</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>What did I pay for this in total?</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-032 · MK-NW-M-033</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-024</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>the ledger sum of dividends over twelve months</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-034</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-025</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>REALISED_GAIN</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/realized.ts:14</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>How much profit have I actually taken?</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-035</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-026</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_CAP_GAINS</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:63</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>If I sold this today, how much of the gain is long-term and how much short-term?</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-036 · MK-NW-M-037</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-027</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>the account balance being itemised</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-038</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-E-028</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>BOND_FACTS · BOND_COUPON</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-045</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>MK-PF-E-001</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>NW_CHANGE_WALK</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/history.ts:144</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>My net worth changed since last time — what actually caused it?</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>MK-PF-M-001 · MK-PF-M-002 · MK-PF-M-003 · MK-PF-M-004</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Named by 4 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>MK-PF-E-002</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>PERFORMANCE_TABLE</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:191</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>What is the full picture for every holding?</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>MK-PF-M-005 · MK-PF-M-006 · MK-PF-M-007</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Named by 3 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>MK-PF-E-003</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>BENCHMARK_RETURN_BLENDED</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:293</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>What would the matching benchmarks have done over the same period?</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>MK-PF-M-008</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>MK-PF-E-004</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>MODIFIED_DIETZ (Calculation Module code/engines/window-return.ts)</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>MK-PF-M-009</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>MK-PF-E-005</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>LOOK_BACK</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/lookBack.ts:32</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>What if I had moved this money?</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>MK-PF-M-010 · MK-PF-M-011 · MK-PF-M-012</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Named by 3 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-001</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>WHAT_THE_PLAN_STILL_NEEDS</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/planning/hub.ts:44</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Is there enough to show this person their own odds?</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-001 · MK-PL-M-002</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-002</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — retirementPaycheckYear, src/domain/paycheck</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-003 · MK-PL-M-004 · MK-PL-M-005</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Named by 3 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-003</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — saved scenarios, src/domain/scenarios</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-007</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-004</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>GUARANTEED_STREAMS (engines: B1 rebuild)</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-010</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-005</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>RMD_START_AGE (Calculation Module code/engines/rmd.ts)</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-012</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-006</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>REQUIRED_WITHDRAWAL</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-013 · MK-PL-M-015</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-007</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME_NOW</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/income/onboarding.ts:191</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>How much retirement income is arriving TODAY?</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-011 · MK-CF-M-024 · MK-PL-M-018 · MK-PL-M-032</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Named by 4 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-008</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>SS_CLAIM_FACTOR · SS_BENEFIT_AT_AGE</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-019</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-009</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>SS_LIFETIME_TOTAL</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-020</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-010</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>the worked example used until a real statement goes in</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-021</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-011</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>the amount the person chose</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>On the screen itself — no engine file</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-022 · MK-PL-M-025 · MK-PL-M-030</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Named by 3 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-012</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>TAX_ON_CONVERSION</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-023</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-013</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>PRE_TAX_BALANCE</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-024</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-014</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>the amounts the person chose</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>On the screen itself — no engine file</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-028</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-015</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_PAYOFF</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-031</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-016</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>the age the person chose</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>On the screen itself — no engine file</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-035</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-E-017</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>EDUCATION_COST</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-036 · MK-PL-M-037</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-001</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>NET_WORTH</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/networth/index.ts:12</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>What is this household worth?</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-016 · MK-XS-M-001</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-002</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>NEST_EGG</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:548</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>What is my retirement pot worth?</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-003</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>ODDS_DISPLAY</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/willItLast.ts:55</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>The retirement odds a person actually sees. Answers: 0, 5, 10 … 100 — the exact simulation</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-004</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_SPENDING</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/index.ts:49</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>What will be spent each month in retirement?</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-009</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-005</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/index.ts:156</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Will my money last?</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-006</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/willItLast.ts:62</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>What goes into working out the odds?</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-008 · MK-PL-M-011 · MK-PL-M-029</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>Named by 3 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-007</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_RESULT</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/willItLast.ts:149</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>What are the odds, and can we honestly show them?</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-034 · MK-XS-M-002</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-008</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>ASSET_CLASS_OF_ACCOUNT</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:221</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>What kind of thing is this account — cash, a bond, shares, or something else?</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-009</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL_INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:291</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>How much do I have invested?</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-M-003</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-010</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>VALUE_WEIGHTED_RETURN</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:283</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>How did everything I hold do over the chosen period?</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-M-004</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-011</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — budgetVsActual, src/domain/budget</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-004 · MK-XS-M-005</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-012</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>NOT IN OLD MASTER — incomeMonthlyGrid, src/domain/income</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>NOT DETERMINED — no source line on record</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-018 · MK-XS-M-006</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-013</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>FETCH_PRICES</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>src/services/marketData.ts:71</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>What are these holdings worth?</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-014</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>SNAPSHOT_READ_ALL</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/history.ts:107</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>What history do we hold?</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-015</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>ACCOUNT_SPLIT</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:401</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>This one brokerage account holds several different things — how much of it is each?</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-008 · MK-NW-M-020</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>Named by 2 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-016</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>CLASS_FROM_NAME_TEXT</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:193</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Reading the NAME alone, is this cash, a money-market fund, or a CD / T-bill?</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-017</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_MINIMUM_TOTAL</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/debt/index.ts:55</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>What must I pay across all debts to stay current?</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-018</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_PAYMENTS_ACTUAL</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/debt/index.ts:59</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>What is actually going out on debt each month?</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-019</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_SHAPE</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/debt/index.ts:38</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>How is THIS debt repaid?</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-020</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>READ_A_NUMBER</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/_shared/num.ts:4</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>What number did the person actually type?</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-021</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>SPENDING_BY_KIND</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/budget/index.ts:72</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>What is spent each month, split by kind?</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-013 · MK-CF-M-014 · MK-MN-M-021</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>Named by 3 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-022</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_SHARES</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:37</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>How many shares of this do I own?</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>MK-NW-M-031</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-023</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>BENCHMARK_FOR_KIND</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:167</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>What should this holding be compared against?</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-024</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_FIRST_BOUGHT</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:146</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>When did I first buy this?</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-025</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_TOTAL_ROI</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:89</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>How much am I up on this in percentage terms, since I bought it?</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-026</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_UNREALISED_GAIN</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:51</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>How much am I up or down on this?</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-027</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>PERIOD_RETURN</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:122</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>What did this holding do over the chosen period?</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-028</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>PERIOD_START_DATE</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:96</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Which date does the chosen period start from?</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-029</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>PRICE_LATEST</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:117</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>What is the most recent price we hold for this?</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-030</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>RETURN_SINCE_A_DATE</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:137</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>What did this do between a given date and today?</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-031</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>PRICE_FACTOR_OVER_WINDOW</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/performance/lookBack.ts:19</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>By what multiple did this price move over the last N months?</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-032</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>EFFECTIVE_TAX_RATE</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/income/tax.ts:130</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>What share of my income actually goes in tax?</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-033</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>EXPECTED_RETURN_BLENDED</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:638</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>What return should I expect on everything I hold together?</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-034</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>EXPECTED_SWING_BLENDED</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:597</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>How much does a year's return typically swing around that average?</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-035</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>FILING_STATUS</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/income/onboarding.ts:354</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>How does this person file?</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-036</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>GUARANTEED_OUTSIDE_STREAMS</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/income/onboarding.ts:227</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>The plan's guaranteed-income input as separate streams of OUTSIDE money only. Answers: zer</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-037</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>MONTHLY_SAVING</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:695</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>How much goes in each month?</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-038</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>REPORTED_RETURN</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:108</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>What return did the person say they actually earned over the past year?</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-039</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>SPLIT_BY_HOW_IT_IS_TAXED</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/decumulation/index.ts:11</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>How is the retirement money split by the tax that will be owed on it?</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-040</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>SS_BENEFIT_AT_AGE</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/ssTiming.ts:54</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>The monthly Social Security check at a chosen claim age, in today's dollars. Answers: a wh</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>MK-PL-M-017</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-041</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>STATE_TAX_RATE</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/income/onboarding.ts:358</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>What state tax rate applies?</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-042</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>SWING_FROM_RETURN</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/willItLast.ts:19</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>How much might a year's return swing, judged from the return alone?</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-043</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>TAX_OVER65_COUNT</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/income/onboarding.ts:405</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How many people on the tax return are 65 or older — the input the over-65 deduction needs </t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-044</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL_INCOME</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/income/onboarding.ts:337</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>What is the whole household income for the year, before tax?</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-006 · MK-CF-M-007 · MK-CF-M-008 · MK-CF-M-027 · MK-MN-M-011 · MK-MN-M-012 · MK-MN-M-013</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>Named by 7 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-045</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>COST_OF_LIVING</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/col.ts:53</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>How much more or less does life cost where they plan to live?</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-046</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>SS_CLAIM_FACTOR</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/ssTiming.ts:34</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>How much of the statement amount a claim age actually pays, anchored at the person's OWN f</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-047</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/income/onboarding.ts:213</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>How much retirement income arrives monthly?</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-023</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-048</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>SS_FULL_RETIREMENT_AGE</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/ssTiming.ts:23</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>The person's own Social Security full retirement age. Answers: 66 (born through 1954) · 66</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-049</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>EQUITY_THIS_YEAR</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/income/onboarding.ts:114</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>How much equity vests this year?</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-050</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>OTHER_INCOME</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/income/onboarding.ts:161</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>What else comes in?</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-051</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>RENTAL_INCOME_A_YEAR</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/income/onboarding.ts:142</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>What do the rentals net over a year?</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>MK-CF-M-010</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>Named by 1 figure(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-052</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>SALARY_A_YEAR</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/income/onboarding.ts:331</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>What is the salary for the year?</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-053</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>TIPS_A_YEAR</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/income/onboarding.ts:204</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>What do tips come to over the year?</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-054</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>RENTALS</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/income/onboarding.ts:129</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>What rental properties are there, and what does each bring in?</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-055</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>IS_PHYSICAL_ASSET</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:253</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>Is this something physical you own rather than money you could spend?</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>MK-XS-E-056</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>TAX_DEDUCTION</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>src/domain/income/tax.ts:105</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>What amount of income is tax-free before the brackets start. Answers: $16,100 single · $32</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>Only as another engine’s dependency — no figure names it directly</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8779,12 +12580,12 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-004 · MK-NW-M-006</t>
+          <t>MK-NW-M-004</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>MAPPED — reached by 2 metric identifier(s).</t>
+          <t>MAPPED — reached by 1 metric identifier(s).</t>
         </is>
       </c>
     </row>
@@ -8954,12 +12755,12 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>MK-NW-M-009 · MK-NW-M-010 · MK-NW-M-012 · MK-PL-M-030</t>
+          <t>MK-NW-M-009 · MK-NW-M-010 · MK-NW-M-012</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>MAPPED — reached by 4 metric identifier(s).</t>
+          <t>MAPPED — reached by 3 metric identifier(s).</t>
         </is>
       </c>
     </row>
@@ -23525,7 +27326,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>NOT STARTED.</t>
+          <t>PARTIAL — the engines tab carries the file and line for every engine identifier that has one on record; the rest read NOT DETERMINED, and the ones worked out on a screen say so.</t>
         </is>
       </c>
     </row>
@@ -23633,7 +27434,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>NOT STARTED — the reconciliation tab is today a report, run by hand. It has to become code with a test.</t>
+          <t>COMPLETE — moneykeel_reconcile.py runs at the end of every build and STOPS it on a structural break: a duplicate identifier, a reference to an engine or input that does not exist, a fold pointing nowhere, a question number used twice. Findings that are real but unresolved — orphan and dead inputs — are counted every build rather than failing it, and must reach zero before the module is called done. Today: 0 breaks, 9 open findings.</t>
         </is>
       </c>
     </row>
@@ -23995,7 +27796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>everything → WILL_IT_LAST_INPUTS  [NO INPUT ID — not on the inputs tab] · is a range wanted → withBand  [NO INPUT ID — not on the inputs tab]</t>
+          <t>everything → WILL_IT_LAST_INPUTS  [NOT AN INPUT — another engine’s answer; see the dependency column] · is a range wanted → withBand  [NOT AN INPUT — a setting or a filter, not data anyone supplies]</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -24106,7 +27907,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>each account's class → assetClassOf  [NO INPUT ID — not on the inputs tab] · each account's money → balance  [MK-XS-I-001]</t>
+          <t>each account's class → assetClassOf  [MK-XS-I-048] · each account's money → balance  [MK-XS-I-001]</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -24208,7 +28009,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>each holding's return → rows[].periodReturn  [NO INPUT ID — not on the inputs tab] · its value → rows[].marketValue  [NO INPUT ID — not on the inputs tab]</t>
+          <t>each holding's return → rows[].periodReturn  [NOT AN INPUT — another engine’s answer; see the dependency column] · its value → rows[].marketValue  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -24763,7 +28564,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>when it was fetched → fetchedAt  [MK-XS-I-006] · now → now  [NO INPUT ID — not on the inputs tab]</t>
+          <t>when it was fetched → fetchedAt  [MK-XS-I-006] · now → now  [NOT AN INPUT — a setting or a filter, not data anyone supplies]</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -25706,7 +29507,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stored history → daily  [MK-XS-I-031] · today's value → currentInvestable  [NO INPUT ID — not on the inputs tab] · baseline date → sinceKey  [NO INPUT ID — not on the inputs tab]</t>
+          <t>stored history → daily  [MK-XS-I-031] · today's value → currentInvestable  [NOT AN INPUT — another engine’s answer; see the dependency column] · baseline date → sinceKey  [MK-XS-I-031]</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -26016,7 +29817,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>each account's class → assetClassOf  [NO INPUT ID — not on the inputs tab] · each account's money → balance  [MK-XS-I-001]</t>
+          <t>each account's class → assetClassOf  [MK-XS-I-048] · each account's money → balance  [MK-XS-I-001]</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -26107,28 +29908,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ACCOUNT_SHARE_OF_TOTAL</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MK-NW-E-003</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>assets = Σ(balance of every account);  share of an account = balance ÷ assets</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Each account's share = its balance ÷ the total, so the shares add to 100. The blended return is weighted by money, not an average of the rates.
-No money at all → every share is 0 and a stated default return is used, rather than dividing by nothing.</t>
-        </is>
-      </c>
+          <t>worked out on the screen: the sum of the accounts in the personal-property section</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>each balance → balance  [MK-XS-I-001] · each assumed return → target_return  [MK-XS-I-028]</t>
+          <t>NOT DETERMINED — no input list on record for this engine</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -26138,12 +29926,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Adds up to $0 when there is nothing to add. Zero and "nothing recorded yet" look identical on screen — worth a decision.</t>
+          <t>Inherits the refusal of the figures it is built from: if either side is missing, this line is not shown.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>One figure per account  [derived by rule — confirm]</t>
+          <t>One figure per person — or per household when two people share one record  [derived by rule — confirm]</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -26153,13 +29941,13 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>None — this engine reads raw inputs only</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>This row names ACCOUNT_SHARE_OF_TOTAL, but personal property is its own total, not a share of one.</t>
+          <t>CORRECTED 2026-08-25 — this row used to name ACCOUNT_SHARE_OF_TOTAL. Personal property is its own total, worked out on the screen, not a share of a total.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -26231,7 +30019,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>each account's class → assetClassOf  [NO INPUT ID — not on the inputs tab] · each account's money → balance  [MK-XS-I-001] · any split → accountClassBreakdown  [NO INPUT ID — not on the inputs tab]</t>
+          <t>each account's class → assetClassOf  [MK-XS-I-048] · each account's money → balance  [MK-XS-I-001] · any split → accountClassBreakdown  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -26345,7 +30133,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>the account → a  [NO INPUT ID — not on the inputs tab] · its total → balance  [MK-XS-I-001] · uninvested → cash_balance  [MK-XS-I-001] · holdings → positions[]  [NO INPUT ID — not on the inputs tab] · options → option_holdings[]  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the account → a  [MK-XS-I-001] · its total → balance  [MK-XS-I-001] · uninvested → cash_balance  [MK-XS-I-001] · holdings → positions[]  [MK-XS-I-004] · options → option_holdings[]  [MK-XS-I-034]</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -26458,7 +30246,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>every debt → debts  [NO INPUT ID — not on the inputs tab] · rates → interest_rate_apr  [MK-XS-I-015] · payments → the minimum and chosen payments  [MK-XS-I-016]</t>
+          <t>every debt → debts  [MK-XS-I-014] · rates → interest_rate_apr  [MK-XS-I-015] · payments → the minimum and chosen payments  [MK-XS-I-016]</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -26559,7 +30347,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>every debt → debts  [NO INPUT ID — not on the inputs tab] · rates → interest_rate_apr  [MK-XS-I-015] · payments → the minimum and chosen payments  [MK-XS-I-016]</t>
+          <t>every debt → debts  [MK-XS-I-014] · rates → interest_rate_apr  [MK-XS-I-015] · payments → the minimum and chosen payments  [MK-XS-I-016]</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -26658,7 +30446,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>shape → paymentShape  [NO INPUT ID — not on the inputs tab] · minimum → minimum_monthly_payment  [MK-XS-I-016] · chosen → monthly_payment  [NO INPUT ID — not on the inputs tab]</t>
+          <t>shape → paymentShape  [MK-XS-I-042] · minimum → minimum_monthly_payment  [MK-XS-I-016] · chosen → monthly_payment  [MK-XS-I-041]</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -26758,7 +30546,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>every debt → debts  [NO INPUT ID — not on the inputs tab] · rates → interest_rate_apr  [MK-XS-I-015] · payments → the minimum and chosen payments  [MK-XS-I-016]</t>
+          <t>every debt → debts  [MK-XS-I-014] · rates → interest_rate_apr  [MK-XS-I-015] · payments → the minimum and chosen payments  [MK-XS-I-016]</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -26952,7 +30740,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>each account's class → assetClassOf  [NO INPUT ID — not on the inputs tab] · each account's money → balance  [MK-XS-I-001] · the categories → SPENDING_BY_KIND  [MK-XS-I-024] · the single figure → monthlySpending  [MK-XS-I-024, MK-XS-I-030]</t>
+          <t>each account's class → assetClassOf  [MK-XS-I-048] · each account's money → balance  [MK-XS-I-001] · the categories → SPENDING_BY_KIND  [MK-XS-I-032] · the single figure → monthlySpending  [MK-XS-I-024, MK-XS-I-030]</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -27067,7 +30855,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>the same inputs → inp  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the same inputs → inp  [MK-XS-I-001]</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -27285,7 +31073,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>everything owned → grossAssets  [MK-XS-I-001] · everything owed → grossDebt  [MK-XS-I-014] · every debt → debts  [NO INPUT ID — not on the inputs tab] · rates → interest_rate_apr  [MK-XS-I-015] · payments → the minimum and chosen payments  [MK-XS-I-016]</t>
+          <t>everything owned → grossAssets  [MK-XS-I-001] · everything owed → grossDebt  [MK-XS-I-014] · every debt → debts  [MK-XS-I-014] · rates → interest_rate_apr  [MK-XS-I-015] · payments → the minimum and chosen payments  [MK-XS-I-016]</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -27385,7 +31173,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>the account → a  [NO INPUT ID — not on the inputs tab] · when the value was set → value_as_of  [NO INPUT ID — not on the inputs tab] · today → now  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the account → a  [MK-XS-I-001] · when the value was set → value_as_of  [MK-XS-I-033] · today → now  [NOT AN INPUT — a setting or a filter, not data anyone supplies]</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -27601,7 +31389,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>the account → a  [NO INPUT ID — not on the inputs tab] · its total → balance  [MK-XS-I-001] · uninvested → cash_balance  [MK-XS-I-001] · holdings → positions[]  [NO INPUT ID — not on the inputs tab] · options → option_holdings[]  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the account → a  [MK-XS-I-001] · its total → balance  [MK-XS-I-001] · uninvested → cash_balance  [MK-XS-I-001] · holdings → positions[]  [MK-XS-I-004] · options → option_holdings[]  [MK-XS-I-034]</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -27807,7 +31595,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>what we knew → existing  [NO INPUT ID — not on the inputs tab] · the dates in this sync → activityDates  [NO INPUT ID — not on the inputs tab]</t>
+          <t>what we knew → existing  [NOT AN INPUT — another engine’s answer; see the dependency column] · the dates in this sync → activityDates  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -27905,7 +31693,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>the holding → position/account  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the holding → position/account  [MK-XS-I-004]</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -28119,7 +31907,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>maturity → maturity  [MK-XS-I-013] · today → now  [NO INPUT ID — not on the inputs tab]</t>
+          <t>maturity → maturity  [MK-XS-I-013] · today → now  [NOT AN INPUT — a setting or a filter, not data anyone supplies]</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -28219,7 +32007,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>coupon → annualCoupon  [MK-XS-I-012] · face → face  [MK-XS-I-011] · value → value  [NO INPUT ID — not on the inputs tab] · years left → yearsToMaturity  [MK-XS-I-013]</t>
+          <t>coupon → annualCoupon  [MK-XS-I-012] · face → face  [MK-XS-I-011] · value → value  [MK-XS-I-001] · years left → yearsToMaturity  [MK-XS-I-013]</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -28322,7 +32110,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>coupon → annualCoupon  [MK-XS-I-012] · what it is worth → value  [NO INPUT ID — not on the inputs tab]</t>
+          <t>coupon → annualCoupon  [MK-XS-I-012] · what it is worth → value  [MK-XS-I-001]</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -29143,7 +32931,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>the ledger → txns  [NO INPUT ID — not on the inputs tab] · optionally one ticker → opts.ticker  [NO INPUT ID — not on the inputs tab] · optionally one account → opts.accountId  [NO INPUT ID — not on the inputs tab] · today → opts.now  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the ledger → txns  [MK-XS-I-008] · optionally one ticker → opts.ticker  [NOT AN INPUT — a setting or a filter, not data anyone supplies] · optionally one account → opts.accountId  [NOT AN INPUT — a setting or a filter, not data anyone supplies] · today → opts.now  [NOT AN INPUT — a setting or a filter, not data anyone supplies]</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -29251,7 +33039,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>each lot → lots[]  [MK-XS-I-007] · price → the latest close  [MK-XS-I-005] · today → now  [NO INPUT ID — not on the inputs tab]</t>
+          <t>each lot → lots[]  [MK-XS-I-007] · price → the latest close  [MK-XS-I-005] · today → now  [NOT AN INPUT — a setting or a filter, not data anyone supplies]</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -29359,7 +33147,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>each lot → lots[]  [MK-XS-I-007] · price → the latest close  [MK-XS-I-005] · today → now  [NO INPUT ID — not on the inputs tab]</t>
+          <t>each lot → lots[]  [MK-XS-I-007] · price → the latest close  [MK-XS-I-005] · today → now  [NOT AN INPUT — a setting or a filter, not data anyone supplies]</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -29764,7 +33552,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>the holding → position/account  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the holding → position/account  [MK-XS-I-004]</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -29866,7 +33654,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>the holding → position/account  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the holding → position/account  [MK-XS-I-004]</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -30070,7 +33858,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>coupon → annualCoupon  [MK-XS-I-012] · what it is worth → value  [NO INPUT ID — not on the inputs tab]</t>
+          <t>coupon → annualCoupon  [MK-XS-I-012] · what it is worth → value  [MK-XS-I-001]</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -30168,7 +33956,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>the holding → position/account  [NO INPUT ID — not on the inputs tab] · face value → face  [MK-XS-I-011] · coupon rate → couponRate  [MK-XS-I-012]</t>
+          <t>the holding → position/account  [MK-XS-I-004] · face value → face  [MK-XS-I-011] · coupon rate → couponRate  [MK-XS-I-012]</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -30595,7 +34383,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>starting value → beginning  [NO INPUT ID — not on the inputs tab] · ending value → ending  [NO INPUT ID — not on the inputs tab] · money in → contributions  [NO INPUT ID — not on the inputs tab] · money out → withdrawals  [NO INPUT ID — not on the inputs tab] · dividends → dividends  [NO INPUT ID — not on the inputs tab] · interest → interest  [NO INPUT ID — not on the inputs tab] · debt paid down → debtPrincipal  [NO INPUT ID — not on the inputs tab]</t>
+          <t>starting value → beginning  [MK-XS-I-031] · ending value → ending  [NOT AN INPUT — another engine’s answer; see the dependency column] · money in → contributions  [NOT AN INPUT — another engine’s answer; see the dependency column] · money out → withdrawals  [NOT AN INPUT — another engine’s answer; see the dependency column] · dividends → dividends  [NOT AN INPUT — another engine’s answer; see the dependency column] · interest → interest  [NOT AN INPUT — another engine’s answer; see the dependency column] · debt paid down → debtPrincipal  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -30705,7 +34493,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>starting value → beginning  [NO INPUT ID — not on the inputs tab] · ending value → ending  [NO INPUT ID — not on the inputs tab] · money in → contributions  [NO INPUT ID — not on the inputs tab] · money out → withdrawals  [NO INPUT ID — not on the inputs tab] · dividends → dividends  [NO INPUT ID — not on the inputs tab] · interest → interest  [NO INPUT ID — not on the inputs tab] · debt paid down → debtPrincipal  [NO INPUT ID — not on the inputs tab]</t>
+          <t>starting value → beginning  [MK-XS-I-031] · ending value → ending  [NOT AN INPUT — another engine’s answer; see the dependency column] · money in → contributions  [NOT AN INPUT — another engine’s answer; see the dependency column] · money out → withdrawals  [NOT AN INPUT — another engine’s answer; see the dependency column] · dividends → dividends  [NOT AN INPUT — another engine’s answer; see the dependency column] · interest → interest  [NOT AN INPUT — another engine’s answer; see the dependency column] · debt paid down → debtPrincipal  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -30811,7 +34599,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>starting value → beginning  [NO INPUT ID — not on the inputs tab] · ending value → ending  [NO INPUT ID — not on the inputs tab] · money in → contributions  [NO INPUT ID — not on the inputs tab] · money out → withdrawals  [NO INPUT ID — not on the inputs tab] · dividends → dividends  [NO INPUT ID — not on the inputs tab] · interest → interest  [NO INPUT ID — not on the inputs tab] · debt paid down → debtPrincipal  [NO INPUT ID — not on the inputs tab]</t>
+          <t>starting value → beginning  [MK-XS-I-031] · ending value → ending  [NOT AN INPUT — another engine’s answer; see the dependency column] · money in → contributions  [NOT AN INPUT — another engine’s answer; see the dependency column] · money out → withdrawals  [NOT AN INPUT — another engine’s answer; see the dependency column] · dividends → dividends  [NOT AN INPUT — another engine’s answer; see the dependency column] · interest → interest  [NOT AN INPUT — another engine’s answer; see the dependency column] · debt paid down → debtPrincipal  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -30921,7 +34709,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>starting value → beginning  [NO INPUT ID — not on the inputs tab] · ending value → ending  [NO INPUT ID — not on the inputs tab] · money in → contributions  [NO INPUT ID — not on the inputs tab] · money out → withdrawals  [NO INPUT ID — not on the inputs tab] · dividends → dividends  [NO INPUT ID — not on the inputs tab] · interest → interest  [NO INPUT ID — not on the inputs tab] · debt paid down → debtPrincipal  [NO INPUT ID — not on the inputs tab]</t>
+          <t>starting value → beginning  [MK-XS-I-031] · ending value → ending  [NOT AN INPUT — another engine’s answer; see the dependency column] · money in → contributions  [NOT AN INPUT — another engine’s answer; see the dependency column] · money out → withdrawals  [NOT AN INPUT — another engine’s answer; see the dependency column] · dividends → dividends  [NOT AN INPUT — another engine’s answer; see the dependency column] · interest → interest  [NOT AN INPUT — another engine’s answer; see the dependency column] · debt paid down → debtPrincipal  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -31026,7 +34814,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>the holdings → positions  [NO INPUT ID — not on the inputs tab] · prices → priceOf(ticker)  [MK-XS-I-005] · the chosen chip → period  [NO INPUT ID — not on the inputs tab] · today → now  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the holdings → positions  [MK-XS-I-004] · prices → priceOf(ticker)  [MK-XS-I-005] · the chosen chip → period  [NOT AN INPUT — a setting or a filter, not data anyone supplies] · today → now  [NOT AN INPUT — a setting or a filter, not data anyone supplies]</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -31136,7 +34924,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>the holdings → positions  [NO INPUT ID — not on the inputs tab] · prices → priceOf(ticker)  [MK-XS-I-005] · the chosen chip → period  [NO INPUT ID — not on the inputs tab] · today → now  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the holdings → positions  [MK-XS-I-004] · prices → priceOf(ticker)  [MK-XS-I-005] · the chosen chip → period  [NOT AN INPUT — a setting or a filter, not data anyone supplies] · today → now  [NOT AN INPUT — a setting or a filter, not data anyone supplies]</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -31246,7 +35034,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>the holdings → positions  [NO INPUT ID — not on the inputs tab] · prices → priceOf(ticker)  [MK-XS-I-005] · the chosen chip → period  [NO INPUT ID — not on the inputs tab] · today → now  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the holdings → positions  [MK-XS-I-004] · prices → priceOf(ticker)  [MK-XS-I-005] · the chosen chip → period  [NOT AN INPUT — a setting or a filter, not data anyone supplies] · today → now  [NOT AN INPUT — a setting or a filter, not data anyone supplies]</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -31353,7 +35141,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>each holding's benchmark return → rows[].benchReturn  [NO INPUT ID — not on the inputs tab] · its value → rows[].marketValue  [NO INPUT ID — not on the inputs tab]</t>
+          <t>each holding's benchmark return → rows[].benchReturn  [NOT AN INPUT — another engine’s answer; see the dependency column] · its value → rows[].marketValue  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -31556,7 +35344,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>the amount → amount  [MK-XS-I-008] · where it sat → fromSeries  [NO INPUT ID — not on the inputs tab] · where it might have gone → toSeries  [NO INPUT ID — not on the inputs tab] · how far back → months  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the amount → amount  [MK-XS-I-008] · where it sat → fromSeries  [NOT AN INPUT — another engine’s answer; see the dependency column] · where it might have gone → toSeries  [NOT AN INPUT — another engine’s answer; see the dependency column] · how far back → months  [NOT AN INPUT — a setting or a filter, not data anyone supplies]</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -31657,7 +35445,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>the amount → amount  [MK-XS-I-008] · where it sat → fromSeries  [NO INPUT ID — not on the inputs tab] · where it might have gone → toSeries  [NO INPUT ID — not on the inputs tab] · how far back → months  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the amount → amount  [MK-XS-I-008] · where it sat → fromSeries  [NOT AN INPUT — another engine’s answer; see the dependency column] · where it might have gone → toSeries  [NOT AN INPUT — another engine’s answer; see the dependency column] · how far back → months  [NOT AN INPUT — a setting or a filter, not data anyone supplies]</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -31758,7 +35546,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>the amount → amount  [MK-XS-I-008] · where it sat → fromSeries  [NO INPUT ID — not on the inputs tab] · where it might have gone → toSeries  [NO INPUT ID — not on the inputs tab] · how far back → months  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the amount → amount  [MK-XS-I-008] · where it sat → fromSeries  [NOT AN INPUT — another engine’s answer; see the dependency column] · where it might have gone → toSeries  [NOT AN INPUT — another engine’s answer; see the dependency column] · how far back → months  [NOT AN INPUT — a setting or a filter, not data anyone supplies]</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -32178,7 +35966,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>their age → birthYear or age  [MK-XS-I-017] · what they spend → monthlySpending  [MK-XS-I-024] · money that counts toward retirement → NEST_EGG  [NO INPUT ID — not on the inputs tab]</t>
+          <t>their age → birthYear or age  [MK-XS-I-017] · what they spend → monthlySpending  [MK-XS-I-024] · money that counts toward retirement → NEST_EGG  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -32277,7 +36065,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>their age → birthYear or age  [MK-XS-I-017] · what they spend → monthlySpending  [MK-XS-I-024] · money that counts toward retirement → NEST_EGG  [NO INPUT ID — not on the inputs tab]</t>
+          <t>their age → birthYear or age  [MK-XS-I-017] · what they spend → monthlySpending  [MK-XS-I-024] · money that counts toward retirement → NEST_EGG  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -32864,7 +36652,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>their age → birthYear  [MK-XS-I-017] · the pot → NEST_EGG  [NO INPUT ID — not on the inputs tab] · return and swing → EXPECTED_RETURN_BLENDED, EXPECTED_SWING_BLENDED  [NO INPUT ID — not on the inputs tab] · spending → RETIREMENT_SPENDING  [MK-XS-I-024] · guaranteed income → RETIREMENT_INCOME, SS_BENEFIT_AT_AGE  [NO INPUT ID — not on the inputs tab] · money to leave behind → legacyTarget  [NO INPUT ID — not on the inputs tab] · their own overrides → the Plan screen  [NO INPUT ID — not on the inputs tab]</t>
+          <t>their age → birthYear  [MK-XS-I-017] · the pot → NEST_EGG  [NOT AN INPUT — another engine’s answer; see the dependency column] · return and swing → EXPECTED_RETURN_BLENDED, EXPECTED_SWING_BLENDED  [NOT AN INPUT — another engine’s answer; see the dependency column] · spending → RETIREMENT_SPENDING  [MK-XS-I-024] · guaranteed income → RETIREMENT_INCOME, SS_BENEFIT_AT_AGE  [NOT AN INPUT — another engine’s answer; see the dependency column] · money to leave behind → legacyTarget  [MK-XS-I-047] · their own overrides → the Plan screen  [MK-XS-I-044]</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -32976,7 +36764,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>the answer → the retirement-spending question  [MK-XS-I-024] · where they will live → the location answer  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the answer → the retirement-spending question  [MK-XS-I-024] · where they will live → the location answer  [MK-XS-I-045]</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -33178,7 +36966,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>their age → birthYear  [MK-XS-I-017] · the pot → NEST_EGG  [NO INPUT ID — not on the inputs tab] · return and swing → EXPECTED_RETURN_BLENDED, EXPECTED_SWING_BLENDED  [NO INPUT ID — not on the inputs tab] · spending → RETIREMENT_SPENDING  [MK-XS-I-024] · guaranteed income → RETIREMENT_INCOME, SS_BENEFIT_AT_AGE  [NO INPUT ID — not on the inputs tab] · money to leave behind → legacyTarget  [NO INPUT ID — not on the inputs tab] · their own overrides → the Plan screen  [NO INPUT ID — not on the inputs tab]</t>
+          <t>their age → birthYear  [MK-XS-I-017] · the pot → NEST_EGG  [NOT AN INPUT — another engine’s answer; see the dependency column] · return and swing → EXPECTED_RETURN_BLENDED, EXPECTED_SWING_BLENDED  [NOT AN INPUT — another engine’s answer; see the dependency column] · spending → RETIREMENT_SPENDING  [MK-XS-I-024] · guaranteed income → RETIREMENT_INCOME, SS_BENEFIT_AT_AGE  [NOT AN INPUT — another engine’s answer; see the dependency column] · money to leave behind → legacyTarget  [MK-XS-I-047] · their own overrides → the Plan screen  [MK-XS-I-044]</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -33687,7 +37475,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>the account → a  [NO INPUT ID — not on the inputs tab] · when the value was set → value_as_of  [NO INPUT ID — not on the inputs tab] · today → now  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the account → a  [MK-XS-I-001] · when the value was set → value_as_of  [MK-XS-I-033] · today → now  [NOT AN INPUT — a setting or a filter, not data anyone supplies]</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -33894,7 +37682,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>do they receive it now → incomeSources  [NO INPUT ID — not on the inputs tab] · the amounts → retirementIncomeMonthly  [MK-XS-I-008]</t>
+          <t>do they receive it now → incomeSources  [MK-XS-I-040] · the amounts → retirementIncomeMonthly  [MK-XS-I-008]</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -34691,7 +38479,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>the same inputs → inp  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the same inputs → inp  [MK-XS-I-001]</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -34991,7 +38779,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>their age → birthYear  [MK-XS-I-017] · the pot → NEST_EGG  [NO INPUT ID — not on the inputs tab] · return and swing → EXPECTED_RETURN_BLENDED, EXPECTED_SWING_BLENDED  [NO INPUT ID — not on the inputs tab] · spending → RETIREMENT_SPENDING  [MK-XS-I-024] · guaranteed income → RETIREMENT_INCOME, SS_BENEFIT_AT_AGE  [NO INPUT ID — not on the inputs tab] · money to leave behind → legacyTarget  [NO INPUT ID — not on the inputs tab] · their own overrides → the Plan screen  [NO INPUT ID — not on the inputs tab]</t>
+          <t>their age → birthYear  [MK-XS-I-017] · the pot → NEST_EGG  [NOT AN INPUT — another engine’s answer; see the dependency column] · return and swing → EXPECTED_RETURN_BLENDED, EXPECTED_SWING_BLENDED  [NOT AN INPUT — another engine’s answer; see the dependency column] · spending → RETIREMENT_SPENDING  [MK-XS-I-024] · guaranteed income → RETIREMENT_INCOME, SS_BENEFIT_AT_AGE  [NOT AN INPUT — another engine’s answer; see the dependency column] · money to leave behind → legacyTarget  [MK-XS-I-047] · their own overrides → the Plan screen  [MK-XS-I-044]</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -35087,29 +38875,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DEBT_PICTURE</t>
+          <t>the amount the person chose</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MK-NW-E-006</t>
+          <t>MK-PL-E-011</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>owed = Σ(remaining balance);  monthly debt payments = Σ(required payment of each debt)</t>
+          <t>the value typed by the person</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Total the balances. Find the highest-rate debt. Add up separately the balances above the rate we treat as dangerous.
-TWO MONTHLY FIGURES ARE KEPT DELIBERATELY: the minimum that must be paid to stay current, and what is actually going out. Confusing them misstates affordability in one direction or the other.
-No debts gives zero and nothing to point at.</t>
+          <t>A number the person entered; no calculation.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>every debt → debts  [NO INPUT ID — not on the inputs tab] · rates → interest_rate_apr  [MK-XS-I-015] · payments → the minimum and chosen payments  [MK-XS-I-016]</t>
+          <t>NOT DETERMINED — no input list on record for this engine</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -35119,7 +38905,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Adds up to $0 when there is nothing to add. Zero and "nothing recorded yet" look identical on screen — worth a decision.</t>
+          <t>Nothing to compute — the person either entered it or has not, and the screen shows it only when they have.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -35134,14 +38920,13 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>MK-XS-E-017 (DEBT_MINIMUM_TOTAL) → What must I pay across all debts to stay current?
-MK-XS-E-018 (DEBT_PAYMENTS_ACTUAL) → What is actually going out on debt each month?</t>
+          <t>NOT DETERMINED</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>This row names DEBT_PICTURE, but "Extra on debt $X/mo" is an amount the person chose on a dial, not a figure that engine produces.</t>
+          <t>CORRECTED 2026-08-25 — this row used to name DEBT_PICTURE. "Extra on debt $X/mo" is an amount the person chose on a dial, not a figure that engine produces.</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -35311,7 +39096,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>do they receive it now → incomeSources  [NO INPUT ID — not on the inputs tab] · the amounts → retirementIncomeMonthly  [MK-XS-I-008]</t>
+          <t>do they receive it now → incomeSources  [MK-XS-I-040] · the amounts → retirementIncomeMonthly  [MK-XS-I-008]</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -35419,7 +39204,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>the same inputs → inp  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the same inputs → inp  [MK-XS-I-001]</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -35528,7 +39313,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>everything → WILL_IT_LAST_INPUTS  [NO INPUT ID — not on the inputs tab] · is a range wanted → withBand  [NO INPUT ID — not on the inputs tab]</t>
+          <t>everything → WILL_IT_LAST_INPUTS  [NOT AN INPUT — another engine’s answer; see the dependency column] · is a range wanted → withBand  [NOT AN INPUT — a setting or a filter, not data anyone supplies]</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -36841,7 +40626,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>each part → its own engine above  [NO INPUT ID — not on the inputs tab]</t>
+          <t>each part → its own engine above  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -36946,7 +40731,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>each part → its own engine above  [NO INPUT ID — not on the inputs tab]</t>
+          <t>each part → its own engine above  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -37051,7 +40836,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>each part → its own engine above  [NO INPUT ID — not on the inputs tab]</t>
+          <t>each part → its own engine above  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -37353,7 +41138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>do they receive it now → incomeSources  [NO INPUT ID — not on the inputs tab] · the amounts → retirementIncomeMonthly  [MK-XS-I-008]</t>
+          <t>do they receive it now → incomeSources  [MK-XS-I-040] · the amounts → retirementIncomeMonthly  [MK-XS-I-008]</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -37553,7 +41338,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>the categories → spendCats  [NO INPUT ID — not on the inputs tab] · or the three summary figures → b_fixed, b_nonmonthly, b_flexible  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the categories → spendCats  [MK-XS-I-032] · or the three summary figures → b_fixed, b_nonmonthly, b_flexible  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -37651,7 +41436,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>the categories → spendCats  [NO INPUT ID — not on the inputs tab] · or the three summary figures → b_fixed, b_nonmonthly, b_flexible  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the categories → spendCats  [MK-XS-I-032] · or the three summary figures → b_fixed, b_nonmonthly, b_flexible  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -37750,7 +41535,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>the categories → SPENDING_BY_KIND  [MK-XS-I-024] · the single figure → monthlySpending  [MK-XS-I-024, MK-XS-I-030]</t>
+          <t>the categories → SPENDING_BY_KIND  [MK-XS-I-032] · the single figure → monthlySpending  [MK-XS-I-024, MK-XS-I-030]</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -38151,7 +41936,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>the categories → spendCats  [NO INPUT ID — not on the inputs tab] · or the three summary figures → b_fixed, b_nonmonthly, b_flexible  [NO INPUT ID — not on the inputs tab] · shape → paymentShape  [NO INPUT ID — not on the inputs tab] · minimum → minimum_monthly_payment  [MK-XS-I-016] · chosen → monthly_payment  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the categories → spendCats  [MK-XS-I-032] · or the three summary figures → b_fixed, b_nonmonthly, b_flexible  [NOT AN INPUT — another engine’s answer; see the dependency column] · shape → paymentShape  [MK-XS-I-042] · minimum → minimum_monthly_payment  [MK-XS-I-016] · chosen → monthly_payment  [MK-XS-I-041]</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -38448,7 +42233,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>the same inputs → inp  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the same inputs → inp  [MK-XS-I-001]</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -38552,7 +42337,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>each source → ri_ss  [NO INPUT ID — not on the inputs tab] · ri_pension  [MK-XS-I-022] · ri_withdrawals  [NO INPUT ID — not on the inputs tab] · ri_rmd  [NO INPUT ID — not on the inputs tab] · ri_annuities  [NO INPUT ID — not on the inputs tab] · ri_other  [NO INPUT ID — not on the inputs tab] · and how often each arrives → the matching frequency  [NO INPUT ID — not on the inputs tab]</t>
+          <t>each source → ri_ss  [MK-XS-I-020] · ri_pension  [MK-XS-I-022] · ri_withdrawals  [MK-XS-I-038] · ri_rmd  [MK-XS-I-037] · ri_annuities  [MK-XS-I-035] · ri_other  [MK-XS-I-036] · and how often each arrives → the matching frequency  [MK-XS-I-039]</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -38651,7 +42436,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>do they receive it now → incomeSources  [NO INPUT ID — not on the inputs tab] · the amounts → retirementIncomeMonthly  [MK-XS-I-008]</t>
+          <t>do they receive it now → incomeSources  [MK-XS-I-040] · the amounts → retirementIncomeMonthly  [MK-XS-I-008]</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -38954,7 +42739,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>each part → its own engine above  [NO INPUT ID — not on the inputs tab]</t>
+          <t>each part → its own engine above  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -40168,7 +43953,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>the categories → SPENDING_BY_KIND  [MK-XS-I-024] · the single figure → monthlySpending  [MK-XS-I-024, MK-XS-I-030]</t>
+          <t>the categories → SPENDING_BY_KIND  [MK-XS-I-032] · the single figure → monthlySpending  [MK-XS-I-024, MK-XS-I-030]</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -40570,7 +44355,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>each part → its own engine above  [NO INPUT ID — not on the inputs tab]</t>
+          <t>each part → its own engine above  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -40675,7 +44460,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>each part → its own engine above  [NO INPUT ID — not on the inputs tab]</t>
+          <t>each part → its own engine above  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -40780,7 +44565,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>each part → its own engine above  [NO INPUT ID — not on the inputs tab]</t>
+          <t>each part → its own engine above  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -40884,7 +44669,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>the match → employerMatchValue  [NO INPUT ID — not on the inputs tab] · percent or dollars → employerMatchMode  [NO INPUT ID — not on the inputs tab] · their own contribution → c_401k  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the match → employerMatchValue  [NOT AN INPUT — another engine’s answer; see the dependency column] · percent or dollars → employerMatchMode  [MK-XS-I-046] · their own contribution → c_401k  [MK-XS-I-043]</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -41084,7 +44869,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>each account's class → assetClassOf  [NO INPUT ID — not on the inputs tab] · each account's money → balance  [MK-XS-I-001] · each account's class → assetClassOf  [NO INPUT ID — not on the inputs tab] · each account's money → balance  [MK-XS-I-001]</t>
+          <t>each account's class → assetClassOf  [MK-XS-I-048] · each account's money → balance  [MK-XS-I-001] · each account's class → assetClassOf  [MK-XS-I-048] · each account's money → balance  [MK-XS-I-001]</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -41592,7 +45377,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>the categories → spendCats  [NO INPUT ID — not on the inputs tab] · or the three summary figures → b_fixed, b_nonmonthly, b_flexible  [NO INPUT ID — not on the inputs tab]</t>
+          <t>the categories → spendCats  [MK-XS-I-032] · or the three summary figures → b_fixed, b_nonmonthly, b_flexible  [NOT AN INPUT — another engine’s answer; see the dependency column]</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -42087,7 +45872,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>the categories → SPENDING_BY_KIND  [MK-XS-I-024] · the single figure → monthlySpending  [MK-XS-I-024, MK-XS-I-030]</t>
+          <t>the categories → SPENDING_BY_KIND  [MK-XS-I-032] · the single figure → monthlySpending  [MK-XS-I-024, MK-XS-I-030]</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -42186,7 +45971,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>gross → gross  [NO INPUT ID — not on the inputs tab] · how they file → status  [NO INPUT ID — not on the inputs tab]</t>
+          <t>gross → gross  [MK-XS-I-023] · how they file → status  [MK-XS-I-030]</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -42288,7 +46073,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>gross → gross  [NO INPUT ID — not on the inputs tab] · how they file → status  [NO INPUT ID — not on the inputs tab]</t>
+          <t>gross → gross  [MK-XS-I-023] · how they file → status  [MK-XS-I-030]</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -26985,7 +26985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -27441,42 +27441,86 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>The duplication pass</t>
+          <t>Duplicate calculations in the CODE</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Figures that are the same thing under two identifiers.</t>
+          <t>S16 compared the figures on screens, so it could only see engines a figure names. Two functions in different files that compute the same thing, named by no figure, are invisible to it — alternativesSummary and alternativesTotal both total the same holdings. A second pass is needed over the code itself.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>COMPLETE — every group judged one at a time. 11 figures were being shown under 24 identifiers; the 13 folded rows now name the identifier that survives and why. 18 groups were checked and are NOT duplicates — one engine legitimately producing several figures — and say so, so the question is not asked twice. Two mis-assigned engines were found and recorded as findings.</t>
+          <t>NOT STARTED — found while answering a question about S16, not by S16.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Engine names that exist nowhere</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Twenty engine names in this file were assigned while reading a screen and have no engine row anywhere. Every one now says so on its row rather than looking documented.</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>FLAGGED — the names are marked; each still needs a row of its own, or to be pointed at an engine that already exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>The duplication pass</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Figures that are the same thing under two identifiers.</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>COMPLETE — every group judged one at a time. 11 figures were being shown under 24 identifiers; the 13 folded rows now name the identifier that survives and why. 18 groups were checked and are NOT duplicates — one engine legitimately producing several figures — and say so, so the question is not asked twice. Two mis-assigned engines were found and recorded as findings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>S17</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Which screens are the 55-70 core</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>The agreed first scope has never been written down.</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>READY FOR THE FOUNDER — the core_screens tab lists all 49 screens with my recommendation (39 in, 5 out, 5 borderline) and a column for his decision.</t>
         </is>
@@ -32188,7 +32232,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BOND_RATE_SENSITIVITY</t>
+          <t>BOND_RATE_SENSITIVITY  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -37160,7 +37204,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>REQUIRED_WITHDRAWAL</t>
+          <t>REQUIRED_WITHDRAWAL  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -37356,7 +37400,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>REQUIRED_WITHDRAWAL</t>
+          <t>REQUIRED_WITHDRAWAL  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -37864,7 +37908,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SS_LIFETIME_TOTAL</t>
+          <t>SS_LIFETIME_TOTAL  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -38159,7 +38203,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TAX_ON_CONVERSION</t>
+          <t>TAX_ON_CONVERSION  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -38257,7 +38301,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PRE_TAX_BALANCE</t>
+          <t>PRE_TAX_BALANCE  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -38977,7 +39021,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>DEBT_PAYOFF</t>
+          <t>DEBT_PAYOFF  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -39498,7 +39542,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>EDUCATION_COST</t>
+          <t>EDUCATION_COST  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -39600,7 +39644,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>EDUCATION_COST</t>
+          <t>EDUCATION_COST  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -42616,7 +42660,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RETIREMENT_PAYCHECK</t>
+          <t>RETIREMENT_PAYCHECK  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -42823,7 +42867,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>THE_BILL_CALENDAR</t>
+          <t>THE_BILL_CALENDAR  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -43348,7 +43392,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BIG_COSTS</t>
+          <t>BIG_COSTS  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -43446,7 +43490,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BIG_COSTS</t>
+          <t>BIG_COSTS  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -43544,7 +43588,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CONTRIBUTION_ROOM</t>
+          <t>CONTRIBUTION_ROOM  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -43642,7 +43686,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CONTRIBUTION_ROOM</t>
+          <t>CONTRIBUTION_ROOM  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -43834,7 +43878,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CREDIT_USE</t>
+          <t>CREDIT_USE  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -44036,7 +44080,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GOAL_CAPACITY</t>
+          <t>GOAL_CAPACITY  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -44138,7 +44182,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GOAL_PROGRESS</t>
+          <t>GOAL_PROGRESS  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -44236,7 +44280,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SINKING_FUNDS</t>
+          <t>SINKING_FUNDS  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -44957,7 +45001,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>INSURANCE_NEED</t>
+          <t>INSURANCE_NEED  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -45059,7 +45103,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>INSURANCE_NEED</t>
+          <t>INSURANCE_NEED  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -45157,7 +45201,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>INSURANCE_NEED</t>
+          <t>INSURANCE_NEED  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -45255,7 +45299,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JOB_SAFETY_RUNWAY</t>
+          <t>JOB_SAFETY_RUNWAY  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -45455,7 +45499,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ALTERNATIVES_TOTAL</t>
+          <t>ALTERNATIVES_TOTAL  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -45553,7 +45597,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ALTERNATIVES_GROWTH</t>
+          <t>ALTERNATIVES_GROWTH  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -45651,7 +45695,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>STRESS_TEST</t>
+          <t>STRESS_TEST  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -45753,7 +45797,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>STRESS_TEST</t>
+          <t>STRESS_TEST  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -46151,7 +46195,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CONTRIBUTION_ROOM</t>
+          <t>CONTRIBUTION_ROOM  [NAME ASSIGNED HERE — no engine row exists for it yet]</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -886,12 +886,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Every function that feeds it</t>
+          <t>COLUMN — Dependent functions</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Every function whose output reaches this one, however many steps away.</t>
+          <t>A dependent function is one whose output is used by another function, in a chain that ends at a screen. These columns list the dependent functions behind this one: those one step below it, how many there are in total, and all of them however many steps away.</t>
         </is>
       </c>
     </row>
@@ -10904,17 +10904,17 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Fed directly by (one step)</t>
+          <t>Dependent functions — one step below</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>How many functions feed it in total</t>
+          <t>Dependent functions — how many in total</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Every function that feeds it</t>
+          <t>Dependent functions — all of them</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -11254,12 +11254,12 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -11317,12 +11317,12 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -11443,12 +11443,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -11767,12 +11767,12 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -11830,12 +11830,12 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -12343,12 +12343,12 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -12406,12 +12406,12 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -12980,12 +12980,12 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -13043,12 +13043,12 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -13106,12 +13106,12 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -13234,12 +13234,12 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -13486,12 +13486,12 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -13746,12 +13746,12 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -14335,12 +14335,12 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
@@ -14597,12 +14597,12 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
@@ -15065,12 +15065,12 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
@@ -15380,12 +15380,12 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
@@ -15443,12 +15443,12 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
@@ -15707,12 +15707,12 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
@@ -15770,12 +15770,12 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
@@ -15833,12 +15833,12 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
@@ -16022,12 +16022,12 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
@@ -16085,12 +16085,12 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
@@ -16148,12 +16148,12 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
@@ -16211,12 +16211,12 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
@@ -16657,12 +16657,12 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L91" s="3" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
@@ -16783,12 +16783,12 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
@@ -16846,12 +16846,12 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
@@ -16972,12 +16972,12 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
@@ -17035,12 +17035,12 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L97" s="3" t="inlineStr">
@@ -17161,12 +17161,12 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L99" s="3" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L103" s="3" t="inlineStr">
@@ -17604,12 +17604,12 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr">
@@ -17795,12 +17795,12 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L109" s="3" t="inlineStr">
@@ -17921,12 +17921,12 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L111" s="3" t="inlineStr">
@@ -18116,12 +18116,12 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr">
@@ -18179,12 +18179,12 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L115" s="3" t="inlineStr">
@@ -18308,12 +18308,12 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L117" s="3" t="inlineStr">
@@ -19030,12 +19030,12 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr">
@@ -19093,12 +19093,12 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L129" s="3" t="inlineStr">
@@ -19283,12 +19283,12 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr">
@@ -19794,12 +19794,12 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr">
@@ -19857,12 +19857,12 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L141" s="3" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr">
@@ -19983,12 +19983,12 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L143" s="3" t="inlineStr">
@@ -20046,12 +20046,12 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr">
@@ -20172,12 +20172,12 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr">
@@ -20424,12 +20424,12 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L150" s="3" t="inlineStr">
@@ -20487,12 +20487,12 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L151" s="3" t="inlineStr">
@@ -20550,12 +20550,12 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr">
@@ -20740,12 +20740,12 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L155" s="3" t="inlineStr">
@@ -21006,12 +21006,12 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L159" s="3" t="inlineStr">
@@ -21132,12 +21132,12 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L161" s="3" t="inlineStr">
@@ -21514,12 +21514,12 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L167" s="3" t="inlineStr">
@@ -21703,12 +21703,12 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr">
@@ -21766,12 +21766,12 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L171" s="3" t="inlineStr">
@@ -21829,12 +21829,12 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr">
@@ -22020,12 +22020,12 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L175" s="3" t="inlineStr">
@@ -22288,12 +22288,12 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L179" s="3" t="inlineStr">
@@ -22679,12 +22679,12 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L185" s="3" t="inlineStr">
@@ -22868,12 +22868,12 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr">
@@ -23057,12 +23057,12 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L191" s="3" t="inlineStr">
@@ -23120,12 +23120,12 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr">
@@ -23183,12 +23183,12 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L193" s="3" t="inlineStr">
@@ -23246,12 +23246,12 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr">
@@ -23309,12 +23309,12 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L195" s="3" t="inlineStr">
@@ -23372,12 +23372,12 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr">
@@ -23757,12 +23757,12 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr">
@@ -23883,12 +23883,12 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr">
@@ -24074,12 +24074,12 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L207" s="3" t="inlineStr">
@@ -24137,12 +24137,12 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr">
@@ -24200,12 +24200,12 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L209" s="3" t="inlineStr">
@@ -24263,12 +24263,12 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr">
@@ -24326,12 +24326,12 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L211" s="3" t="inlineStr">
@@ -24389,12 +24389,12 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr">
@@ -24839,12 +24839,12 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L219" s="3" t="inlineStr">
@@ -24902,12 +24902,12 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr">
@@ -25217,12 +25217,12 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L225" s="3" t="inlineStr">
@@ -25280,12 +25280,12 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L226" s="3" t="inlineStr">
@@ -25343,12 +25343,12 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K227" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L227" s="3" t="inlineStr">
@@ -25659,12 +25659,12 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr">
@@ -25722,12 +25722,12 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K233" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L233" s="3" t="inlineStr">
@@ -25849,12 +25849,12 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K235" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L235" s="3" t="inlineStr">
@@ -25975,12 +25975,12 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K237" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L237" s="3" t="inlineStr">
@@ -26038,12 +26038,12 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K238" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L238" s="3" t="inlineStr">
@@ -26418,12 +26418,12 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L244" s="3" t="inlineStr">
@@ -26758,12 +26758,12 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K249" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L249" s="3" t="inlineStr">
@@ -26821,12 +26821,12 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K250" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L250" s="3" t="inlineStr">
@@ -26884,12 +26884,12 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L251" s="3" t="inlineStr">
@@ -27012,12 +27012,12 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K253" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L253" s="3" t="inlineStr">
@@ -27075,12 +27075,12 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K254" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L254" s="3" t="inlineStr">
@@ -27138,12 +27138,12 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K255" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L255" s="3" t="inlineStr">
@@ -27393,12 +27393,12 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L259" s="3" t="inlineStr">
@@ -27520,12 +27520,12 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K261" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L261" s="3" t="inlineStr">
@@ -27583,12 +27583,12 @@
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L262" s="3" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L263" s="3" t="inlineStr">
@@ -27772,12 +27772,12 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K265" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L265" s="3" t="inlineStr">
@@ -27961,12 +27961,12 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L268" s="3" t="inlineStr">
@@ -28024,12 +28024,12 @@
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K269" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L269" s="3" t="inlineStr">
@@ -28276,12 +28276,12 @@
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K273" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L273" s="3" t="inlineStr">
@@ -28403,12 +28403,12 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K275" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L275" s="3" t="inlineStr">
@@ -28466,12 +28466,12 @@
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L276" s="3" t="inlineStr">
@@ -28656,12 +28656,12 @@
       </c>
       <c r="J279" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K279" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L279" s="3" t="inlineStr">
@@ -28719,12 +28719,12 @@
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K280" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L280" s="3" t="inlineStr">
@@ -28782,12 +28782,12 @@
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K281" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L281" s="3" t="inlineStr">
@@ -29117,12 +29117,12 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K286" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L286" s="3" t="inlineStr">
@@ -29180,12 +29180,12 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K287" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L287" s="3" t="inlineStr">
@@ -29307,12 +29307,12 @@
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K289" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L289" s="3" t="inlineStr">
@@ -29433,12 +29433,12 @@
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K291" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L291" s="3" t="inlineStr">
@@ -29625,12 +29625,12 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K294" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L294" s="3" t="inlineStr">
@@ -29688,12 +29688,12 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K295" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L295" s="3" t="inlineStr">
@@ -29814,12 +29814,12 @@
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K297" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L297" s="3" t="inlineStr">
@@ -29940,12 +29940,12 @@
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K299" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L299" s="3" t="inlineStr">
@@ -30066,12 +30066,12 @@
       </c>
       <c r="J301" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K301" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L301" s="3" t="inlineStr">
@@ -30129,12 +30129,12 @@
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K302" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L302" s="3" t="inlineStr">
@@ -30320,12 +30320,12 @@
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K305" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L305" s="3" t="inlineStr">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K306" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L306" s="3" t="inlineStr">
@@ -30446,12 +30446,12 @@
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K307" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L307" s="3" t="inlineStr">
@@ -30509,12 +30509,12 @@
       </c>
       <c r="J308" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K308" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L308" s="3" t="inlineStr">
@@ -30703,12 +30703,12 @@
       </c>
       <c r="J311" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K311" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L311" s="3" t="inlineStr">
@@ -30892,12 +30892,12 @@
       </c>
       <c r="J314" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K314" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L314" s="3" t="inlineStr">
@@ -30955,12 +30955,12 @@
       </c>
       <c r="J315" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K315" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L315" s="3" t="inlineStr">
@@ -31145,12 +31145,12 @@
       </c>
       <c r="J318" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K318" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L318" s="3" t="inlineStr">
@@ -31208,12 +31208,12 @@
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K319" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L319" s="3" t="inlineStr">
@@ -31401,12 +31401,12 @@
       </c>
       <c r="J322" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K322" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L322" s="3" t="inlineStr">
@@ -31661,12 +31661,12 @@
       </c>
       <c r="J326" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L326" s="3" t="inlineStr">
@@ -31915,12 +31915,12 @@
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L330" s="3" t="inlineStr">
@@ -31978,12 +31978,12 @@
       </c>
       <c r="J331" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K331" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L331" s="3" t="inlineStr">
@@ -32105,12 +32105,12 @@
       </c>
       <c r="J333" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K333" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L333" s="3" t="inlineStr">
@@ -32235,12 +32235,12 @@
       </c>
       <c r="J335" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K335" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L335" s="3" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="J340" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K340" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L340" s="3" t="inlineStr">
@@ -32614,12 +32614,12 @@
       </c>
       <c r="J341" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K341" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L341" s="3" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="J342" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K342" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L342" s="3" t="inlineStr">
@@ -32740,12 +32740,12 @@
       </c>
       <c r="J343" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K343" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L343" s="3" t="inlineStr">
@@ -32803,12 +32803,12 @@
       </c>
       <c r="J344" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K344" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L344" s="3" t="inlineStr">
@@ -33193,12 +33193,12 @@
       </c>
       <c r="J350" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L350" s="3" t="inlineStr">
@@ -33256,12 +33256,12 @@
       </c>
       <c r="J351" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K351" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L351" s="3" t="inlineStr">
@@ -33900,12 +33900,12 @@
       </c>
       <c r="J361" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K361" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L361" s="3" t="inlineStr">
@@ -33963,12 +33963,12 @@
       </c>
       <c r="J362" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K362" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L362" s="3" t="inlineStr">
@@ -34026,12 +34026,12 @@
       </c>
       <c r="J363" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K363" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L363" s="3" t="inlineStr">
@@ -34089,12 +34089,12 @@
       </c>
       <c r="J364" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K364" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L364" s="3" t="inlineStr">
@@ -34286,12 +34286,12 @@
       </c>
       <c r="J367" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K367" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L367" s="3" t="inlineStr">
@@ -34412,12 +34412,12 @@
       </c>
       <c r="J369" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K369" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L369" s="3" t="inlineStr">
@@ -34538,12 +34538,12 @@
       </c>
       <c r="J371" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K371" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L371" s="3" t="inlineStr">
@@ -34601,12 +34601,12 @@
       </c>
       <c r="J372" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K372" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L372" s="3" t="inlineStr">
@@ -34664,12 +34664,12 @@
       </c>
       <c r="J373" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K373" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L373" s="3" t="inlineStr">
@@ -34727,12 +34727,12 @@
       </c>
       <c r="J374" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K374" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L374" s="3" t="inlineStr">
@@ -34790,12 +34790,12 @@
       </c>
       <c r="J375" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K375" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L375" s="3" t="inlineStr">
@@ -34853,12 +34853,12 @@
       </c>
       <c r="J376" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K376" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L376" s="3" t="inlineStr">
@@ -34916,12 +34916,12 @@
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K377" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L377" s="3" t="inlineStr">
@@ -35043,12 +35043,12 @@
       </c>
       <c r="J379" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K379" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L379" s="3" t="inlineStr">
@@ -35371,12 +35371,12 @@
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr">
@@ -35565,12 +35565,12 @@
       </c>
       <c r="J387" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K387" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L387" s="3" t="inlineStr">
@@ -35628,12 +35628,12 @@
       </c>
       <c r="J388" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L388" s="3" t="inlineStr">
@@ -36006,12 +36006,12 @@
       </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K394" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L394" s="3" t="inlineStr">
@@ -36069,12 +36069,12 @@
       </c>
       <c r="J395" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K395" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L395" s="3" t="inlineStr">
@@ -36132,12 +36132,12 @@
       </c>
       <c r="J396" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K396" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L396" s="3" t="inlineStr">
@@ -36195,12 +36195,12 @@
       </c>
       <c r="J397" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K397" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L397" s="3" t="inlineStr">
@@ -36321,12 +36321,12 @@
       </c>
       <c r="J399" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K399" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L399" s="3" t="inlineStr">
@@ -36384,12 +36384,12 @@
       </c>
       <c r="J400" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K400" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L400" s="3" t="inlineStr">
@@ -36447,12 +36447,12 @@
       </c>
       <c r="J401" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K401" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L401" s="3" t="inlineStr">
@@ -36581,12 +36581,12 @@
       </c>
       <c r="J403" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K403" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L403" s="3" t="inlineStr">
@@ -36715,12 +36715,12 @@
       </c>
       <c r="J405" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K405" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L405" s="3" t="inlineStr">
@@ -37041,12 +37041,12 @@
       </c>
       <c r="J410" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K410" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L410" s="3" t="inlineStr">
@@ -37246,12 +37246,12 @@
       </c>
       <c r="J413" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K413" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L413" s="3" t="inlineStr">
@@ -37504,12 +37504,12 @@
       </c>
       <c r="J417" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K417" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L417" s="3" t="inlineStr">
@@ -37567,12 +37567,12 @@
       </c>
       <c r="J418" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K418" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L418" s="3" t="inlineStr">
@@ -37695,12 +37695,12 @@
       </c>
       <c r="J420" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K420" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L420" s="3" t="inlineStr">
@@ -38148,12 +38148,12 @@
       </c>
       <c r="J427" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K427" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L427" s="3" t="inlineStr">
@@ -38211,12 +38211,12 @@
       </c>
       <c r="J428" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K428" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L428" s="3" t="inlineStr">
@@ -38409,12 +38409,12 @@
       </c>
       <c r="J431" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K431" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L431" s="3" t="inlineStr">
@@ -38472,12 +38472,12 @@
       </c>
       <c r="J432" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K432" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L432" s="3" t="inlineStr">
@@ -38599,12 +38599,12 @@
       </c>
       <c r="J434" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K434" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L434" s="3" t="inlineStr">
@@ -39051,12 +39051,12 @@
       </c>
       <c r="J441" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K441" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L441" s="3" t="inlineStr">
@@ -39185,12 +39185,12 @@
       </c>
       <c r="J443" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K443" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L443" s="3" t="inlineStr">
@@ -39248,12 +39248,12 @@
       </c>
       <c r="J444" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K444" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L444" s="3" t="inlineStr">
@@ -39644,12 +39644,12 @@
       </c>
       <c r="J450" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K450" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L450" s="3" t="inlineStr">
@@ -39707,12 +39707,12 @@
       </c>
       <c r="J451" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K451" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L451" s="3" t="inlineStr">
@@ -39899,12 +39899,12 @@
       </c>
       <c r="J454" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K454" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L454" s="3" t="inlineStr">
@@ -39962,12 +39962,12 @@
       </c>
       <c r="J455" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K455" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L455" s="3" t="inlineStr">
@@ -40025,12 +40025,12 @@
       </c>
       <c r="J456" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K456" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L456" s="3" t="inlineStr">
@@ -40088,12 +40088,12 @@
       </c>
       <c r="J457" s="3" t="inlineStr">
         <is>
-          <t>Nothing — it is the start of its own chain</t>
+          <t>None — no dependent function stands behind it</t>
         </is>
       </c>
       <c r="K457" s="3" t="inlineStr">
         <is>
-          <t>Nothing feeds it — it reads its inputs and answers</t>
+          <t>No dependent function — it reads its inputs and answers</t>
         </is>
       </c>
       <c r="L457" s="3" t="inlineStr">

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -22,6 +22,7 @@
     <sheet name="reconciliation" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="engines" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="functions_from_code" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="functions_summary" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -80,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -93,6 +94,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -460,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -654,542 +658,554 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TAB — functions_from_code</t>
+          <t>TAB — functions_summary</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Every function in the calculation code, read from the code itself, sorted into the four categories by what it actually does. 1 ACTION does something and displays nothing. 2 DISPLAYED lands on a screen. 3 DEPENDENT feeds a chain that ends at a screen. 4 BRINGS DATA IN fetches from outside the app. A function that can reach a screen can put a wrong number in front of a person; one that cannot, cannot.</t>
+          <t>A count per category: how many functions there are, how many are handed nothing at all, how many are handed nothing but reach into the stored data, and how many never say what they give back.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TAB — reconciliation</t>
+          <t>TAB — functions_from_code</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>The input map checked in BOTH directions: what the inputs tab says uses each input, against what each engine actually names in its own input list. Where the two disagree the row says so. The section at the foot lists inputs an engine names that appear nowhere on the inputs tab.</t>
+          <t>Every function in the calculation code, read from the code itself, sorted into the four categories by what it actually does. 1 ACTION does something and displays nothing. 2 DISPLAYED lands on a screen. 3 DEPENDENT feeds a chain that ends at a screen. 4 BRINGS DATA IN fetches from outside the app. A function that can reach a screen can put a wrong number in front of a person; one that cannot, cannot.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TAB — core_screens</t>
+          <t>TAB — reconciliation</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Every screen in the app, its parent, my recommendation on whether it belongs to the 55-70 core, and a column for the founder to decide. Until this is decided, no row in the file can honestly claim to be in scope (S17).</t>
+          <t>The input map checked in BOTH directions: what the inputs tab says uses each input, against what each engine actually names in its own input list. Where the two disagree the row says so. The section at the foot lists inputs an engine names that appear nowhere on the inputs tab.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TAB — database</t>
+          <t>TAB — core_screens</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>What the app saves in the cloud: where each thing is stored, what it holds, which figures depend on it, how often it is written and at what grain. Also names what is deliberately NOT saved.</t>
+          <t>Every screen in the app, its parent, my recommendation on whether it belongs to the 55-70 core, and a column for the founder to decide. Until this is decided, no row in the file can honestly claim to be in scope (S17).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>TAB — database</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>What the app saves in the cloud: where each thing is stored, what it holds, which figures depend on it, how often it is written and at what grain. Also names what is deliberately NOT saved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>TAB — inputs</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>The raw values the engines need before any calculation happens.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="3" t="inlineStr"/>
-    </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN — Metric ID</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>The identifier of the figure, per moneykeel_naming_spec_unique-identifier_v01.md. Given once, never changed, never reused.</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Parent Screen Name</t>
+          <t>COLUMN — Metric ID</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>One of: Home, Networth, Performance, Cashflow, Plan, Menu. Menu means reachable only from the menu.</t>
+          <t>The identifier of the figure, per moneykeel_naming_spec_unique-identifier_v01.md. Given once, never changed, never reused.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Secondary Screen Name</t>
+          <t>COLUMN — Parent Screen Name</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>The screen reached from the parent, or NA when the figure is on the parent screen itself.</t>
+          <t>One of: Home, Networth, Performance, Cashflow, Plan, Menu. Menu means reachable only from the menu.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name on Screen</t>
+          <t>COLUMN — Secondary Screen Name</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>The label copied exactly as it is worded on screen, including capitals. Where a figure wears different labels on different screens, all are listed.</t>
+          <t>The screen reached from the parent, or NA when the figure is on the parent screen itself.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name of Underlying Metric</t>
+          <t>COLUMN — Name on Screen</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>The metric's name in the code.</t>
+          <t>The label copied exactly as it is worded on screen, including capitals. Where a figure wears different labels on different screens, all are listed.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Name of Underlying Engine</t>
+          <t>COLUMN — Name of Underlying Metric</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>The engine that produces the figure. NOT IN OLD MASTER means the engine exists in the code but has no row in the old master file.</t>
+          <t>The metric's name in the code.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Inputs it needs (S02)</t>
+          <t>COLUMN — Name of Underlying Engine</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Every input the engine reads, named. Carried from the old master where it has a row there.</t>
+          <t>The engine that produces the figure. NOT IN OLD MASTER means the engine exists in the code but has no row in the old master file.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — What comes out (S04)</t>
+          <t>COLUMN — Inputs it needs (S02)</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Dollars, a percentage, a date, a count; how it is held and how it is shown. Marked "derived by rule" where it was worked out from the label and formula rather than read from the engine — those need confirming.</t>
+          <t>Every input the engine reads, named. Carried from the old master where it has a row there.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — What it says when it cannot be computed (S05)</t>
+          <t>COLUMN — What comes out (S04)</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>The refusal. Written where the engine has been read; NOT DETERMINED where it has not, rather than guessed.</t>
+          <t>Dollars, a percentage, a date, a count; how it is held and how it is shown. Marked "derived by rule" where it was worked out from the label and formula rather than read from the engine — those need confirming.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Grain (S06)</t>
+          <t>COLUMN — What it says when it cannot be computed (S05)</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>One figure per what: holding, account, debt, goal, category, month, or person.</t>
+          <t>The refusal. Written where the engine has been read; NOT DETERMINED where it has not, rather than guessed.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Period (S07)</t>
+          <t>COLUMN — Grain (S06)</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>As of when, and over what window.</t>
+          <t>One figure per what: holding, account, debt, goal, category, month, or person.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Dependency (S11)</t>
+          <t>COLUMN — Period (S07)</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>The engines this one leans on, each named by ITS identifier and by the output it gives. Read from the code itself, never from a document. "None" means the engine reads raw inputs only.</t>
+          <t>As of when, and over what window.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Secondary calculations and decisions the engine makes</t>
+          <t>COLUMN — Dependency (S11)</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>The judgements an engine must make BEFORE its headline figure exists: what class an asset is, what to call it on screen, which units apply, whether a value is fresh. Each of these is a formula of its own and needs its own row.</t>
+          <t>The engines this one leans on, each named by ITS identifier and by the output it gives. Read from the code itself, never from a document. "None" means the engine reads raw inputs only.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Function ID</t>
+          <t>COLUMN — Secondary calculations and decisions the engine makes</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Every function in the code carries one, MK-[family]-F-[number]. The family comes from the folder the code sits in.</t>
+          <t>The judgements an engine must make BEFORE its headline figure exists: what class an asset is, what to call it on screen, which units apply, whether a value is fresh. Each of these is a formula of its own and needs its own row.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — What it is handed / what it gives back</t>
+          <t>COLUMN — Function ID</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Read from the function's own signature: the values passed to it, whether it also reads the stored data, and what it returns. NOT DECLARED means the code does not say what comes back.</t>
+          <t>Every function in the code carries one, MK-[family]-F-[number]. The family comes from the folder the code sits in.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Label on screen</t>
+          <t>COLUMN — What it is handed / what it gives back</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>For a function whose answer is displayed, the words printed beside it, found by following the name the screen stores the answer in. NOT FOUND means a screen calls it but the label could not be traced automatically and needs reading.</t>
+          <t>Read from the function's own signature: the values passed to it, whether it also reads the stored data, and what it returns. NOT DECLARED means the code does not say what comes back.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Dependent functions</t>
+          <t>COLUMN — Label on screen</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>A dependent function is one whose output is used by another function, in a chain that ends at a screen. These columns list the dependent functions behind this one: those one step below it, how many there are in total, and all of them however many steps away.</t>
+          <t>For a function whose answer is displayed, the words printed beside it, found by following the name the screen stores the answer in. NOT FOUND means a screen calls it but the label could not be traced automatically and needs reading.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — The chain, ending in this function</t>
+          <t>COLUMN — Dependent functions</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Read left to right. The function that shows the answer sits at the END, and everything feeding it comes before it. A loop is marked where a chain turns back on itself. Chains are cut at five levels and eight paths, and say so.</t>
+          <t>A dependent function is one whose output is used by another function, in a chain that ends at a screen. These columns list the dependent functions behind this one: those one step below it, how many there are in total, and all of them however many steps away.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Same figure as (S16)</t>
+          <t>COLUMN — The chain, ending in this function</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Where the same figure appears under more than one identifier, the row names the surviving identifier and why. Nothing is deleted: identifiers are never reused, so a folded row stays visible and says what it became.</t>
+          <t>Read left to right. The function that shows the answer sits at the END, and everything feeding it comes before it. A loop is marked where a chain turns back on itself. Chains are cut at five levels and eight paths, and say so.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Questions for you (numbered)</t>
+          <t>COLUMN — Same figure as (S16)</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>My open questions about that engine or figure, each with a number that never changes. A number is never reused or renumbered, so an answer can always be matched to its question.</t>
+          <t>Where the same figure appears under more than one identifier, the row names the surviving identifier and why. Nothing is deleted: identifiers are never reused, so a folded row stays visible and says what it became.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — YOUR ANSWER — use the same number</t>
+          <t>COLUMN — Questions for you (numbered)</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Answer here, starting each answer with the question number. Nothing else in the file needs to line up.</t>
+          <t>My open questions about that engine or figure, each with a number that never changes. A number is never reused or renumbered, so an answer can always be matched to its question.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Errors or findings to address</t>
+          <t>COLUMN — YOUR ANSWER — use the same number</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>What is known to be wrong or unproved about this figure, in plain English. Blank means nothing is on record yet — not that nothing is wrong.</t>
+          <t>Answer here, starting each answer with the question number. Nothing else in the file needs to line up.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Decisions made (S03)</t>
+          <t>COLUMN — Errors or findings to address</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>The rulings and assumptions that govern this figure, each marked with WHOSE decision it was: [Founder] his own ruling, [The person] something the user set, [Built in] an assumption nobody chose on a screen — which is usually why a number looks wrong. The standing display and rounding rule applies to every row and is stated at the top of this tab.</t>
+          <t>What is known to be wrong or unproved about this figure, in plain English. Blank means nothing is on record yet — not that nothing is wrong.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (mathematical)</t>
+          <t>COLUMN — Decisions made (S03)</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
+          <t>The rulings and assumptions that govern this figure, each marked with WHOSE decision it was: [Founder] his own ruling, [The person] something the user set, [Built in] an assumption nobody chose on a screen — which is usually why a number looks wrong. The standing display and rounding rule applies to every row and is stated at the top of this tab.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (in words)</t>
+          <t>COLUMN — Formula (mathematical)</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
+          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Engine ID</t>
+          <t>COLUMN — Formula (in words)</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
+          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Your name for it (72-metric file)</t>
+          <t>COLUMN — Engine ID</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
+          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Core screen?</t>
+          <t>COLUMN — Your name for it (72-metric file)</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Whether the screen is part of the 55-70 core, the agreed first scope. Currently NOT DETERMINED on every row: the core list has never been written down, so no row can honestly claim to be in or out of it.</t>
+          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>COLUMN — Core screen?</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Whether the screen is part of the 55-70 core, the agreed first scope. Currently NOT DETERMINED on every row: the core list has never been written down, so no row can honestly claim to be in or out of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
           <t>COLUMN — Row status</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>VERIFIED with its date means a person read the screen and confirmed the chain. NOT STARTED means the screen has not been read yet. Nothing in between is claimed.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
-      <c r="B52" s="3" t="inlineStr"/>
-    </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN — Input ID</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>The identifier of a raw input, per the same standard.</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Variable name</t>
+          <t>COLUMN — Input ID</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>What the raw value is called.</t>
+          <t>The identifier of a raw input, per the same standard.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Source</t>
+          <t>COLUMN — Variable name</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
+          <t>What the raw value is called.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Which metric uses it</t>
+          <t>COLUMN — Source</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Every metric identifier that depends on this input.</t>
+          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>COLUMN — Which metric uses it</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Every metric identifier that depends on this input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
           <t>COLUMN — Which engine uses it</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Every engine identifier that reads this input.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr"/>
-      <c r="B58" s="3" t="inlineStr"/>
-    </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Complies with — naming</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Complies with — identifiers</t>
+          <t>Complies with — naming</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>Complies with — identifiers</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
           <t>Complies with — objectives</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>MoneyKeel/documents/standards/moneykeel_calc_spec_objectives-and-verification_v01.md</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr"/>
-      <c r="B62" s="3" t="inlineStr"/>
-    </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>COVERAGE — screens read so far</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>COVERAGE — screens read so far</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
           <t>COVERAGE — what that means</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>Every screen in the app is listed on its tab. Only Home carries figures so far; the rest are marked NOT STARTED. A rising count is not completeness while screens remain unread.</t>
         </is>
@@ -46975,6 +46991,226 @@
         <is>
           <t>—</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Functions</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Handed nothing, and reads no stored data</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Handed nothing, but reads the stored data</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Does not declare what it gives back</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Neither: nothing in, nothing declared out</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>A function handed nothing that reads no stored data has its answer from a constant, the clock, or something the code does not show. A function that does not declare what it gives back cannot be checked for returning the right shape. Both are counted here rather than described.</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1 · ACTION</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2 · DISPLAYED</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>228</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2 · DISPLAYED (presentation only)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>3 · DEPENDENT</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>3 · DEPENDENT (feeds an action only)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>4 · BRINGS DATA IN</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>455</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -11292,7 +11292,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>NOT FOUND — a screen calls it but no label was found near the call</t>
+          <t>Bonds &amp; alternatives — recorded on their own pages   (PerformanceScreen.tsx)</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>In   (CashFlowScreen.tsx)</t>
+          <t>In (take-home)   (CashFlowScreen.tsx)</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Set a target date to track on-track / behind.   (GoalsScreen.tsx)</t>
+          <t>Allocate to this goal ›   (GoalsScreen.tsx)</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Your contribution   (modules.tsx)</t>
+          <t>Your contribution (per month)   (modules.tsx)</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>NOT FOUND — a screen calls it but no label was found near the call</t>
+          <t>Bonds &amp; alternatives — recorded on their own pages   (PerformanceScreen.tsx)</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>You are   (HoldingDetailScreen.tsx)</t>
+          <t>Name (optional)   (PerformanceScreen.tsx) · You are   (HoldingDetailScreen.tsx)</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Ending market value   (PerformanceScreen.tsx) · Wealth generated   (PerformanceScreen.tsx)</t>
+          <t>Ending market value   (PerformanceScreen.tsx) · Ending market value (today)   (PerformanceScreen.tsx) · Wealth generated   (PerformanceScreen.tsx)</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -16302,7 +16302,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>IF YOU SOLD TODAY   (HoldingDetailScreen.tsx)</t>
+          <t>Gain — long-term (held over 1 yr)   (HoldingDetailScreen.tsx) · Gain — short-term (under 1 yr)   (HoldingDetailScreen.tsx)</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>Annuity / other   (modules.tsx) · Capital needed   (modules.tsx) · Leave behind   (modules.tsx) · To fund from savings   (modules.tsx) · What are you saving for   (modules.tsx) · Your retirement outlook   (modules.tsx)</t>
+          <t>Annuity / other   (modules.tsx) · Capital needed   (modules.tsx) · Leave behind (your legacy goal)   (modules.tsx) · To fund from savings   (modules.tsx) · What are you saving for?   (modules.tsx) · Your retirement outlook   (modules.tsx)</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -18191,7 +18191,7 @@
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>NOT FOUND — a screen calls it but no label was found near the call</t>
+          <t>Your credit score (optional)   (CreditScreen.tsx)</t>
         </is>
       </c>
       <c r="J93" s="3" t="inlineStr">
@@ -18347,7 +18347,7 @@
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>Amount   (LookBackScreen.tsx) · Estimated benefit   (RetirementCockpit.tsx) · How much   (modules.tsx) · How much per month   (modules.tsx) · Leave blank to use a 40-hour week.   (modules.tsx) · Market price   (modules.tsx)</t>
+          <t>Amount   (LookBackScreen.tsx) · Break this into specific stocks, bonds, options…   (NetWorthScreen.tsx) · Estimated benefit   (RetirementCockpit.tsx) · HOW MUCH WILL YOU INVEST PER YEAR?   (modules.tsx) · How much   (modules.tsx) · How much (this disbursement)   (modules.tsx)</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr">
@@ -18425,7 +18425,7 @@
       </c>
       <c r="I96" s="3" t="inlineStr">
         <is>
-          <t>How long should your money last   (modules.tsx) · Operating expense / mo   (modules.tsx) · Projected to last to age   (modules.tsx) · Set by month   (modules.tsx) · Surplus by month   (modules.tsx) · Your contribution   (modules.tsx)</t>
+          <t>How long should your money last?   (modules.tsx) · Operating expense / mo   (modules.tsx) · Projected to last to age   (modules.tsx) · Set by month   (modules.tsx) · Surplus by month   (modules.tsx) · Your contribution (per month)   (modules.tsx)</t>
         </is>
       </c>
       <c r="J96" s="3" t="inlineStr">
@@ -18737,7 +18737,7 @@
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>Yield on today's value   (AccountDetailScreen.tsx)</t>
+          <t>Yield on today   (AccountDetailScreen.tsx)</t>
         </is>
       </c>
       <c r="J100" s="3" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>NOT FOUND — a screen calls it but no label was found near the call</t>
+          <t>Add a debt →   (NetWorthScreen.tsx)</t>
         </is>
       </c>
       <c r="J103" s="3" t="inlineStr">
@@ -20154,7 +20154,7 @@
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>WHAT COUNTS TOWARD RETIREMENT   (PlanInputs.tsx)</t>
+          <t>Test retiring earlier, saving more, market ups &amp; downs.   (RetirementCockpit.tsx) · WHAT COUNTS TOWARD RETIREMENT   (PlanInputs.tsx) · What counts toward retirement?   (RetirementCockpit.tsx)</t>
         </is>
       </c>
       <c r="J118" s="3" t="inlineStr">
@@ -21513,7 +21513,7 @@
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>Annual vesting cash flow   (modules.tsx) · Monthly   (modules.tsx) · Monthly cash flow   (modules.tsx)</t>
+          <t>Annual vesting cash flow   (modules.tsx) · Monthly (retirement)   (modules.tsx) · Monthly cash flow   (modules.tsx)</t>
         </is>
       </c>
       <c r="J135" s="3" t="inlineStr">
@@ -22453,7 +22453,7 @@
       </c>
       <c r="I147" s="3" t="inlineStr">
         <is>
-          <t>Annual vesting cash flow   (modules.tsx) · Annuity / other   (modules.tsx) · Available / yr   (modules.tsx) · Capital needed   (modules.tsx) · Critical   (modules.tsx) · Do you manage money with a partner   (modules.tsx)</t>
+          <t>Annual vesting cash flow   (modules.tsx) · Annuity / other   (modules.tsx) · Available / yr   (modules.tsx) · Capital needed   (modules.tsx) · Count money you receive to live on. We won't tax this.   (modules.tsx) · Critical   (modules.tsx)</t>
         </is>
       </c>
       <c r="J147" s="3" t="inlineStr">
@@ -23638,7 +23638,7 @@
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>Complete   (RewardsScreen.tsx)</t>
+          <t>Complete! 🎉   (RewardsScreen.tsx)</t>
         </is>
       </c>
       <c r="J162" s="3" t="inlineStr">
@@ -27820,7 +27820,7 @@
       </c>
       <c r="I215" s="3" t="inlineStr">
         <is>
-          <t>NOT FOUND — a screen calls it but no label was found near the call</t>
+          <t>Pay off over (years)   (modules.tsx)</t>
         </is>
       </c>
       <c r="J215" s="3" t="inlineStr">
@@ -29778,7 +29778,7 @@
       </c>
       <c r="I240" s="3" t="inlineStr">
         <is>
-          <t>ACCOUNTS   (TaxOrganizerScreen.tsx) · Amount   (BudgetScreen.tsx) · Annual vesting cash flow   (modules.tsx) · Annuity / other   (modules.tsx) · Available / yr   (modules.tsx) · COUPON / YR   (BondsScreen.tsx)</t>
+          <t>ACCOUNTS (year-end)   (TaxOrganizerScreen.tsx) · Allocate to this goal ›   (GoalsScreen.tsx) · Amount   (BudgetScreen.tsx) · Annual vesting cash flow   (modules.tsx) · Annuity / other   (modules.tsx) · Available / yr   (modules.tsx)</t>
         </is>
       </c>
       <c r="J240" s="3" t="inlineStr">
@@ -31448,7 +31448,7 @@
       </c>
       <c r="I261" s="3" t="inlineStr">
         <is>
-          <t>WILL MY MONEY LAST   (HomeScreen.tsx)</t>
+          <t>WILL MY MONEY LAST?   (HomeScreen.tsx)</t>
         </is>
       </c>
       <c r="J261" s="3" t="inlineStr">
@@ -32462,7 +32462,7 @@
       </c>
       <c r="I274" s="3" t="inlineStr">
         <is>
-          <t>Extra / month   (BudgetScreen.tsx) · No budget yet   (BudgetScreen.tsx) · Payoff plan   (BudgetScreen.tsx) · Your monthly plan   (BudgetScreen.tsx)</t>
+          <t>Add any loans or credit cards to plan your payoff.   (BudgetScreen.tsx) · Extra / month   (BudgetScreen.tsx) · Extra / month (beyond minimums)   (GoalsScreen.tsx) · Income (take-home)   (BudgetScreen.tsx) · Payoff plan   (BudgetScreen.tsx) · Tap “Set limits” to plan what you'll spend, by category.   (BudgetScreen.tsx)</t>
         </is>
       </c>
       <c r="J274" s="3" t="inlineStr">
@@ -33254,7 +33254,7 @@
       </c>
       <c r="I284" s="3" t="inlineStr">
         <is>
-          <t>Your monthly plan   (BudgetScreen.tsx)</t>
+          <t>Income (take-home)   (BudgetScreen.tsx)</t>
         </is>
       </c>
       <c r="J284" s="3" t="inlineStr">
@@ -35142,7 +35142,7 @@
       </c>
       <c r="I308" s="3" t="inlineStr">
         <is>
-          <t>Certain months   (modules.tsx)</t>
+          <t>Certain months   (modules.tsx) · HOW MUCH WILL YOU INVEST PER YEAR?   (modules.tsx) · When does it land? (pick the months)   (modules.tsx) · When is it due? (pick the months)   (modules.tsx)</t>
         </is>
       </c>
       <c r="J308" s="3" t="inlineStr">
@@ -36084,7 +36084,7 @@
       </c>
       <c r="I320" s="3" t="inlineStr">
         <is>
-          <t>Everything in MoneyKeel   (TopBar.tsx) · WILL MY MONEY LAST   (HomeScreen.tsx)</t>
+          <t>WILL MY MONEY LAST?   (HomeScreen.tsx) · YOUR FIVE TABS — same order as the bar below   (TopBar.tsx)</t>
         </is>
       </c>
       <c r="J320" s="3" t="inlineStr">
@@ -37034,7 +37034,7 @@
       </c>
       <c r="I332" s="3" t="inlineStr">
         <is>
-          <t>Required Minimum Distributions   (RetirementCockpit.tsx) · WHAT IT BUYS LATER   (RothScreen.tsx) · Yours starts in   (RequiredWithdrawalsScreen.tsx)</t>
+          <t>Required Minimum Distributions   (RetirementCockpit.tsx) · Required withdrawal — first   (DrawSteerSheet.tsx) · WHAT IT BUYS LATER   (RothScreen.tsx) · Yours starts in   (RequiredWithdrawalsScreen.tsx)</t>
         </is>
       </c>
       <c r="J332" s="3" t="inlineStr">
@@ -37273,7 +37273,7 @@
       </c>
       <c r="I335" s="3" t="inlineStr">
         <is>
-          <t>Operating expense / mo   (modules.tsx) · Set by month   (modules.tsx) · Surplus by month   (modules.tsx) · Your contribution   (modules.tsx) · Your retirement outlook   (modules.tsx)</t>
+          <t>Operating expense / mo   (modules.tsx) · Set by month   (modules.tsx) · Surplus by month   (modules.tsx) · Your contribution (per month)   (modules.tsx) · Your retirement outlook   (modules.tsx)</t>
         </is>
       </c>
       <c r="J335" s="3" t="inlineStr">
@@ -37351,7 +37351,7 @@
       </c>
       <c r="I336" s="3" t="inlineStr">
         <is>
-          <t>Required Minimum Distributions   (RetirementCockpit.tsx) · Roth conversion   (RothScreen.tsx) · Suggested withdrawal order   (RetirementCockpit.tsx) · WHAT IT BUYS LATER   (RothScreen.tsx) · WHAT THIS IS   (RequiredWithdrawalsScreen.tsx) · Yours starts in   (RequiredWithdrawalsScreen.tsx)</t>
+          <t>Required Minimum Distributions   (RetirementCockpit.tsx) · Required withdrawal — first   (DrawSteerSheet.tsx) · Roth conversion   (RothScreen.tsx) · Suggested withdrawal order   (RetirementCockpit.tsx) · WHAT IT BUYS LATER   (RothScreen.tsx) · WHAT THIS IS   (RequiredWithdrawalsScreen.tsx)</t>
         </is>
       </c>
       <c r="J336" s="3" t="inlineStr">
@@ -37664,7 +37664,7 @@
       </c>
       <c r="I340" s="3" t="inlineStr">
         <is>
-          <t>Required Minimum Distributions   (RetirementCockpit.tsx)</t>
+          <t>Roth conversion window:   (RetirementCockpit.tsx)</t>
         </is>
       </c>
       <c r="J340" s="3" t="inlineStr">
@@ -41461,7 +41461,7 @@
       </c>
       <c r="I388" s="3" t="inlineStr">
         <is>
-          <t>NOT FOUND — a screen calls it but no label was found near the call</t>
+          <t>Can I spend more?   (SpendMoreControl.tsx)</t>
         </is>
       </c>
       <c r="J388" s="3" t="inlineStr">
@@ -41617,7 +41617,7 @@
       </c>
       <c r="I390" s="3" t="inlineStr">
         <is>
-          <t>NOT FOUND — a screen calls it but no label was found near the call</t>
+          <t>When should I claim Social Security?   (ClaimAgeRow.tsx)</t>
         </is>
       </c>
       <c r="J390" s="3" t="inlineStr">
@@ -42639,7 +42639,7 @@
       </c>
       <c r="I403" s="3" t="inlineStr">
         <is>
-          <t>Everything in MoneyKeel   (TopBar.tsx)</t>
+          <t>YOUR FIVE TABS — same order as the bar below   (TopBar.tsx)</t>
         </is>
       </c>
       <c r="J403" s="3" t="inlineStr">
@@ -42717,7 +42717,7 @@
       </c>
       <c r="I404" s="3" t="inlineStr">
         <is>
-          <t>Itemized   (modules.tsx) · Net   (modules.tsx) · Net Worth   (modules.tsx) · Surplus / year   (modules.tsx) · Take-home   (modules.tsx) · Take-home / year   (modules.tsx)</t>
+          <t>Income (take-home)   (BudgetScreen.tsx) · Itemized   (modules.tsx) · Net   (modules.tsx) · Net Worth   (modules.tsx) · Surplus / year   (modules.tsx) · Take-home   (modules.tsx)</t>
         </is>
       </c>
       <c r="J404" s="3" t="inlineStr">
@@ -42881,7 +42881,7 @@
       </c>
       <c r="I406" s="3" t="inlineStr">
         <is>
-          <t>Required Minimum Distributions   (RetirementCockpit.tsx) · Suggested withdrawal order   (RetirementCockpit.tsx) · Where your money sits   (RetirementCockpit.tsx) · Yours starts in   (RequiredWithdrawalsScreen.tsx)</t>
+          <t>Healthcare:   (RetirementCockpit.tsx) · Required Minimum Distributions   (RetirementCockpit.tsx) · Required withdrawal — first   (DrawSteerSheet.tsx) · Roth conversion window:   (RetirementCockpit.tsx) · Suggested withdrawal order   (RetirementCockpit.tsx) · Where your money sits   (RetirementCockpit.tsx)</t>
         </is>
       </c>
       <c r="J406" s="3" t="inlineStr">
@@ -43282,7 +43282,7 @@
       </c>
       <c r="I411" s="3" t="inlineStr">
         <is>
-          <t>Self-employment income   (modules.tsx) · WHAT'S TAKEN OUT   (modules.tsx)</t>
+          <t>Count money you receive to live on. We won't tax this.   (modules.tsx) · Each month: tax · spending · savings   (modules.tsx) · How often?   (modules.tsx) · WHAT'S TAKEN OUT   (modules.tsx)</t>
         </is>
       </c>
       <c r="J411" s="3" t="inlineStr">
@@ -44008,7 +44008,7 @@
       </c>
       <c r="I420" s="3" t="inlineStr">
         <is>
-          <t>NOT FOUND — a screen calls it but no label was found near the call</t>
+          <t>Activity ›   (PerformanceScreen.tsx)</t>
         </is>
       </c>
       <c r="J420" s="3" t="inlineStr">
@@ -44242,7 +44242,7 @@
       </c>
       <c r="I423" s="3" t="inlineStr">
         <is>
-          <t>DEBT-TO-INCOME   (GoalsScreen.tsx) · Your monthly plan   (BudgetScreen.tsx)</t>
+          <t>DEBT-TO-INCOME   (GoalsScreen.tsx) · Income (take-home)   (BudgetScreen.tsx)</t>
         </is>
       </c>
       <c r="J423" s="3" t="inlineStr">
@@ -44320,7 +44320,7 @@
       </c>
       <c r="I424" s="3" t="inlineStr">
         <is>
-          <t>Net Worth   (modules.tsx) · Operating expense / mo   (modules.tsx) · STUDENT LOAN OUTLOOK   (GoalsScreen.tsx) · Total income / yr   (modules.tsx) · Total value   (modules.tsx) · YOUR INCOME   (IncomeManagerScreen.tsx)</t>
+          <t>Net Worth   (modules.tsx) · Operating expense / mo   (modules.tsx) · Pay off over (years)   (modules.tsx) · STUDENT LOAN OUTLOOK   (GoalsScreen.tsx) · Total income / yr   (modules.tsx) · Total value   (modules.tsx)</t>
         </is>
       </c>
       <c r="J424" s="3" t="inlineStr">
@@ -46563,7 +46563,7 @@
       </c>
       <c r="I452" s="3" t="inlineStr">
         <is>
-          <t>NOT FOUND — a screen calls it but no label was found near the call</t>
+          <t>Why this order?   (CashFlowScreen.tsx) · Why? ›   (CashFlowScreen.tsx)</t>
         </is>
       </c>
       <c r="J452" s="3" t="inlineStr">
@@ -46644,7 +46644,7 @@
       </c>
       <c r="I453" s="3" t="inlineStr">
         <is>
-          <t>From your portfolio   (RetirementCockpit.tsx) · You plan to spend   (RetirementCockpit.tsx)</t>
+          <t>From your portfolio   (RetirementCockpit.tsx) · WILL YOUR MONEY LAST?   (RetirementCockpit.tsx) · You plan to spend   (RetirementCockpit.tsx)</t>
         </is>
       </c>
       <c r="J453" s="3" t="inlineStr">

--- a/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_master_calculation-master_v01.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B65"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -902,310 +902,322 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — What it is handed / what it gives back</t>
+          <t>COLUMN — What it is for</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Read from the function's own signature: the values passed to it, whether it also reads the stored data, and what it returns. NOT DECLARED means the code does not say what comes back.</t>
+          <t>The purpose of the function in one sentence, taken from the note written above it in the code, or from the old inventory when the code carries none. NOT DETERMINED where neither exists — never invented.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Label on screen</t>
+          <t>COLUMN — What it is handed / what it gives back</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>For a function whose answer is displayed, the words printed beside it, found by following the name the screen stores the answer in. NOT FOUND means a screen calls it but the label could not be traced automatically and needs reading.</t>
+          <t>Read from the function's own signature: the values passed to it, whether it also reads the stored data, and what it returns. NOT DECLARED means the code does not say what comes back.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Dependent functions</t>
+          <t>COLUMN — Label on screen</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>A dependent function is one whose output is used by another function, in a chain that ends at a screen. These columns list the dependent functions behind this one: those one step below it, how many there are in total, and all of them however many steps away.</t>
+          <t>For a function whose answer is displayed, the words printed beside it, found by following the name the screen stores the answer in. NOT FOUND means a screen calls it but the label could not be traced automatically and needs reading.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — The chain, ending in this function</t>
+          <t>COLUMN — Dependent functions</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Read left to right. The function that shows the answer sits at the END, and everything feeding it comes before it. A loop is marked where a chain turns back on itself. Chains are cut at five levels and eight paths, and say so.</t>
+          <t>A dependent function is one whose output is used by another function, in a chain that ends at a screen. These columns list the dependent functions behind this one: those one step below it, how many there are in total, and all of them however many steps away.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Same figure as (S16)</t>
+          <t>COLUMN — The chain, ending in this function</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Where the same figure appears under more than one identifier, the row names the surviving identifier and why. Nothing is deleted: identifiers are never reused, so a folded row stays visible and says what it became.</t>
+          <t>Read left to right. The function that shows the answer sits at the END, and everything feeding it comes before it. A loop is marked where a chain turns back on itself. Chains are cut at five levels and eight paths, and say so.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Questions for you (numbered)</t>
+          <t>COLUMN — Same figure as (S16)</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>My open questions about that engine or figure, each with a number that never changes. A number is never reused or renumbered, so an answer can always be matched to its question.</t>
+          <t>Where the same figure appears under more than one identifier, the row names the surviving identifier and why. Nothing is deleted: identifiers are never reused, so a folded row stays visible and says what it became.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — YOUR ANSWER — use the same number</t>
+          <t>COLUMN — Questions for you (numbered)</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Answer here, starting each answer with the question number. Nothing else in the file needs to line up.</t>
+          <t>My open questions about that engine or figure, each with a number that never changes. A number is never reused or renumbered, so an answer can always be matched to its question.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Errors or findings to address</t>
+          <t>COLUMN — YOUR ANSWER — use the same number</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>What is known to be wrong or unproved about this figure, in plain English. Blank means nothing is on record yet — not that nothing is wrong.</t>
+          <t>Answer here, starting each answer with the question number. Nothing else in the file needs to line up.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Decisions made (S03)</t>
+          <t>COLUMN — Errors or findings to address</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>The rulings and assumptions that govern this figure, each marked with WHOSE decision it was: [Founder] his own ruling, [The person] something the user set, [Built in] an assumption nobody chose on a screen — which is usually why a number looks wrong. The standing display and rounding rule applies to every row and is stated at the top of this tab.</t>
+          <t>What is known to be wrong or unproved about this figure, in plain English. Blank means nothing is on record yet — not that nothing is wrong.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (mathematical)</t>
+          <t>COLUMN — Decisions made (S03)</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
+          <t>The rulings and assumptions that govern this figure, each marked with WHOSE decision it was: [Founder] his own ruling, [The person] something the user set, [Built in] an assumption nobody chose on a screen — which is usually why a number looks wrong. The standing display and rounding rule applies to every row and is stated at the top of this tab.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Formula (in words)</t>
+          <t>COLUMN — Formula (mathematical)</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
+          <t>The rule written as arithmetic, so it can be followed symbol by symbol and checked against the code.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Engine ID</t>
+          <t>COLUMN — Formula (in words)</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
+          <t>The same rule in plain English, followable by hand. Where the engine has a row in the old master this is its wording, carried over; where it does not, it is written here from reading the code.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Your name for it (72-metric file)</t>
+          <t>COLUMN — Engine ID</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
+          <t>The identifier of that engine. Blank where the figure is worked out on the screen itself rather than by an engine — which is itself a finding.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Core screen?</t>
+          <t>COLUMN — Your name for it (72-metric file)</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Whether the screen is part of the 55-70 core, the agreed first scope. Currently NOT DETERMINED on every row: the core list has never been written down, so no row can honestly claim to be in or out of it.</t>
+          <t>The founder's own name for the same figure, from METRICS-DELIVERABLE-ANSWERED-2026-08-20.xlsx. This column is the bridge between his vocabulary and the code's.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>COLUMN — Core screen?</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Whether the screen is part of the 55-70 core, the agreed first scope. Currently NOT DETERMINED on every row: the core list has never been written down, so no row can honestly claim to be in or out of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
           <t>COLUMN — Row status</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>VERIFIED with its date means a person read the screen and confirmed the chain. NOT STARTED means the screen has not been read yet. Nothing in between is claimed.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr"/>
-      <c r="B53" s="3" t="inlineStr"/>
-    </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>COLUMN — Input ID</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>The identifier of a raw input, per the same standard.</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Variable name</t>
+          <t>COLUMN — Input ID</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>What the raw value is called.</t>
+          <t>The identifier of a raw input, per the same standard.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Source</t>
+          <t>COLUMN — Variable name</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
+          <t>What the raw value is called.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>COLUMN — Which metric uses it</t>
+          <t>COLUMN — Source</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Every metric identifier that depends on this input.</t>
+          <t>Where the value comes from: the person typed it, an institution download, a connected provider, or another engine computed it.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>COLUMN — Which metric uses it</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Every metric identifier that depends on this input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
           <t>COLUMN — Which engine uses it</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>Every engine identifier that reads this input.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr"/>
-      <c r="B59" s="3" t="inlineStr"/>
-    </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Complies with — naming</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Complies with — identifiers</t>
+          <t>Complies with — naming</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_file-and-folder-naming_v01.md</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>Complies with — identifiers</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/standards/moneykeel_naming_spec_unique-identifier_v01.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
           <t>Complies with — objectives</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>MoneyKeel/documents/standards/moneykeel_calc_spec_objectives-and-verification_v01.md</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr"/>
-      <c r="B63" s="3" t="inlineStr"/>
-    </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>COVERAGE — screens read so far</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>COVERAGE — screens read so far</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>49 of 49. Every screen in the app has been read: the five parent screens, every secondary screen and every menu screen. Twelve screens carry no calculated figure and say so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
           <t>COVERAGE — what that means</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>Every screen in the app is listed on its tab. Only Home carries figures so far; the rest are marked NOT STARTED. A rising count is not completeness while screens remain unread.</t>
         </is>
@@ -10937,7 +10949,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Why it was put there</t>
+          <t>What it is for</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -11039,7 +11051,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Can this account hold individual ticker securities?</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -11117,7 +11129,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>APPROVED v6 (2026-07-19): a CONNECTED account splits across the asset classes it actually holds — CDs under bonds, money market + sleeve under cash, options under alternatives, stocks under stocks — with the slices summing EXACTLY to the broker's authoritative balance.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -11197,7 +11209,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>The ONE display name for an account row (build-43 finding #1): institution prefixes the label ONLY when the label doesn't already say it (E*TRADE's own name is "E*Trade Individual Brokerage" — prefixing the institution again rendered "E-Trade E*Trade Individual…"), and the broker's mask suffixes when present so two same-named accounts are tellable apart (wireframe: "Brokerage ...4821").</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -11277,7 +11289,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Display names for a whole LIST of accounts.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -11357,7 +11369,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Produces nothing that is displayed — it does something: saves, syncs or records.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -11435,7 +11447,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>The last four digits of an account, or null when we genuinely don't have them.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -11513,7 +11525,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Which currency is the app showing?</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -11591,7 +11603,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>The one lookup the UI uses.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -11669,7 +11681,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>── duplicate-proofing ───────────────────────────────────────────────────────────────────────── SnapTrade activity ids can change when they reprocess history, so identity = the composite of everything that makes the row THAT row.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -11747,7 +11759,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Σ ACTUAL payments (override ≥ minimum) — what actually leaves your account.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -11826,7 +11838,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Actual money flow for a month from LOGGED data — the exact figures behind the Home cash-flow card, so every screen (Home, Goals) shows the SAME surplus.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -11912,7 +11924,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>── Listen for notification taps ───────────────────────────────────</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -11990,7 +12002,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>The account ids a transaction can touch.</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -12068,7 +12080,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>What's LEFT of this month's surplus to put to work = surplus − already-allocated this month (never &lt; 0).</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -12146,7 +12158,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>How is my invested money spread?</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -12224,7 +12236,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -12303,7 +12315,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -12381,7 +12393,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Reaches outside the app for its answer — a feed, a file or a stored record.</t>
+          <t>What is worth saying about this spending?</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -12459,7 +12471,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Annual employee 401(k) limit for the user's age (adds the 50+ catch-up).</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -12537,7 +12549,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>ONE annual cash-flow roll-up, derived entirely from the per-month income grid + spendByMonth — the SAME bases the savings-plan and budget already use.</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -12623,7 +12635,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Annual coupon income = face value × coupon rate (paid as cash).</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -12701,7 +12713,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -12779,7 +12791,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -12857,7 +12869,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Annual NET contribution of a source: jobs use gross; rentals net out operating expenses.</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -12935,7 +12947,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Annual amount of what the user ENTERED (not grossed up) — for display.</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -13013,7 +13025,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Apply one transaction to the accounts (pure).</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -13092,7 +13104,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Approximate yield to maturity (standard approximation), decimal.</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -13171,7 +13183,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>How much money sits in each of the seven classes?</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -13253,7 +13265,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>WHAT the account is (asset class).</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -13331,7 +13343,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>What do we know about this kind of account?</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -13409,7 +13421,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Build asset accounts from onboarding answers (accumulation: retirement savings + holdings).</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -13488,7 +13500,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Per-holding contribution to the portfolio's period return = weight × the holding's return (pts).</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -13566,7 +13578,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Prompt for Face ID / Touch ID / device passcode.</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -13644,7 +13656,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Summarize per-month available-to-save from a 12-month cash-flow grid.</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -13722,7 +13734,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -13802,7 +13814,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -13880,7 +13892,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Benchmark return + its source/period for an asset kind.</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -13958,7 +13970,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Benchmark expected annual return for an asset kind — user override if set, else the ASSET_KINDS default.</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -14036,7 +14048,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>What should this holding be compared against?</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -14114,7 +14126,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Calendar months (1-12) benefits are received — e.g.</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -14192,7 +14204,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Annual benefits = monthly amount × the months it's actually received.</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -14271,7 +14283,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Blended expected return across the EARMARKED nest egg, weighted by each holding's share.</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -14353,7 +14365,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>The volatility of THIS portfolio — each account's own class volatility, weighted the way the money actually is (the same weighting `blendedReturn` uses, so the pair always describes one portfolio).</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -14434,7 +14446,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>What are this holding's bond facts?</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -14512,7 +14524,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>What happens to this bond if interest rates move?</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -14591,7 +14603,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -14670,7 +14682,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -14756,7 +14768,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Month-to-date actual spending vs the planned budget, bucketed.</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -14838,7 +14850,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>How much of everything sits in each account, and what return do they blend to?</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -14916,7 +14928,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>projected_to_save = net monthly income − monthly spending.</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -14994,7 +15006,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>My net worth changed since last time — what actually caused it?</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -15072,7 +15084,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Build the dated 12-month grid.</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -15158,7 +15170,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Today's SnapshotDay, observed from the live account state.</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -15236,7 +15248,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>What is the whole debt picture?</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -15318,7 +15330,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Months to reach each goal at the given monthly savings capacity.</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -15397,7 +15409,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -15480,7 +15492,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Ranked insights (highest priority first).</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -15558,7 +15570,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Build the new accounts to CREATE when committing an itemization.</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -15638,7 +15650,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>What is this household worth?</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -15716,7 +15728,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Build the month-by-month paycheck.</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -15802,7 +15814,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Build the per-holding rows for a period from positions + a price-series lookup.</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -15888,7 +15900,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -15967,7 +15979,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Build a snapshot from EXPLICIT net-worth rows.</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -16053,7 +16065,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Produces nothing that is displayed — it does something: saves, syncs or records.</t>
+          <t>── DEK lifecycle (the cached, unwrapped key the sync layer uses) ───── Cache the unwrapped DEK (memory + keychain).</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -16131,7 +16143,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Is there any record at all on or before this date?</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -16209,7 +16221,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Produces nothing that is displayed — it does something: saves, syncs or records.</t>
+          <t>── Cancel streak reminder (e.g.</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -16287,7 +16299,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>If I sold this today, how much of the gain is long-term and how much short-term?</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -16365,7 +16377,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -16443,7 +16455,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Produces nothing that is displayed — it does something: saves, syncs or records.</t>
+          <t>Report a caught error.</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -16521,7 +16533,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Signed cash effect on the primary account (for display).</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -16599,7 +16611,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Cash &amp; cash equivalents (Term #3) — THE cash number, and the same one the Net Worth CASH group shows.</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -16681,7 +16693,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Build the 12-month cash-flow picture.</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -16767,7 +16779,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Canonical per-category planned $/month — the ONE conversion the buckets AND the Budget screen share, so a category's on-screen line item ALWAYS reconciles with its bucket total (build-34 #3).</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -16845,7 +16857,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>The claim window: the month the person turns 62 → the month they turn 70.</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -16923,7 +16935,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Plain words for an account's slice inside a class row.</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -17001,7 +17013,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Classify one institution word.</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -17079,7 +17091,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>B7 (founder brief 2026-08-20): classification lives in the ONE engine — this road only adapts.</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -17157,7 +17169,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -17235,7 +17247,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Produces nothing that is displayed — it does something: saves, syncs or records.</t>
+          <t>Forget the DEK (on logout / account deletion).</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -17313,7 +17325,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Cost-of-living factor for a free-text location.</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -17391,7 +17403,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Compare paying `extraMonthly` into the mortgage against putting the same money into Treasuries.</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -17469,7 +17481,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Mark an account's wrapper as USER-CONFIRMED — future syncs never override it.</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -17547,7 +17559,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>How old a connected account's last successful sync is.</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -17625,7 +17637,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>The class an account SHOULD carry under the current rule.</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -17704,7 +17716,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>What did I pay for this in total?</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -17782,7 +17794,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Total annual coupon income across the user's INDIVIDUAL bonds (kept for the Bonds screen summary).</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -17862,7 +17874,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>What can we honestly say about a window starting on `from`?</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -17942,7 +17954,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Does the record actually cover this window?</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
@@ -18020,7 +18032,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Whether reports are actually shipping to Sentry (DSN + SDK present).</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -18098,7 +18110,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it, but it only changes how a value LOOKS — it does no arithmetic.</t>
+          <t>Create an invite code pointing at this household's shared data doc.</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -18176,7 +18188,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -18254,7 +18266,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -18332,7 +18344,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -18410,7 +18422,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Age in whole years from birth month/year, as of `asOf` (defaults to now).</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -18488,7 +18500,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>The email of the account currently signed in to Firebase — the authoritative identity that account-level actions (delete, reauth) operate on.</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -18566,7 +18578,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Retirement income (ri_*) counts as CURRENT income only when the user actually receives it now — i.e.</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -18644,7 +18656,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -18722,7 +18734,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Current yield = annual coupon ÷ current price/value.</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -18800,7 +18812,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Every incomplete promise across the given accounts.</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -18878,7 +18890,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>"14 March 2022".</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -18956,7 +18968,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>What do we know about this kind of debt?</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -19034,7 +19046,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -19112,7 +19124,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>What debts should exist from the setup answers?</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -19192,7 +19204,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>What is the text of the file that was picked?</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -19270,7 +19282,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Decrypt a synced value: ciphertext → object; legacy plaintext object → returned as-is; null if it's ciphertext we can't decrypt (no key).</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -19350,7 +19362,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Decrypt an 'enc:'-tagged blob.</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -19428,7 +19440,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>The standard deduction with the age-65 additions (E8).</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -19506,7 +19518,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Which of these activities are new since the last sync?</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -19584,7 +19596,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>B47 finding 11 — a debt's repayment SHAPE.</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -19662,7 +19674,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>Produces nothing that is displayed — it does something: saves, syncs or records.</t>
+          <t>Permanently delete the signed-in user's account (App Store Guideline 5.1.1(v)).</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -19744,7 +19756,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>---- deterministic depletion ---- Age the portfolio runs out (deterministic), or null if it lasts to the horizon.</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -19824,7 +19836,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>The direction an event implies, where the event itself decides it.</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -19902,7 +19914,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>B6 (founder brief 2026-08-20): the odds a person sees, to the nearest 5 — with one honesty guard at each end: 100 means "every simulated future worked" and 0 means "none did", and neither claim may be minted by rounding.</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -19980,7 +19992,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -20061,7 +20073,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Earliest dated lot — the day this holding became YOUR money.</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -20139,7 +20151,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Default % of an account that's earmarked for retirement (rest funds other goals).</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -20218,7 +20230,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>The retirement-earmarked $ for one account (uses the saved % or the smart default).</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -20298,7 +20310,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Distinct investment kinds present in the earmarked nest egg (for the benchmark editor).</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -20378,7 +20390,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -20456,7 +20468,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>NEGATIVE CASH FLOW DRAINS WEALTH — committed contributions don't create money.</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -20542,7 +20554,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -20628,7 +20640,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Blended effective rate (total tax / gross).</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -20706,7 +20718,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>What share of my income actually goes in tax?</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
@@ -20784,7 +20796,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -20862,7 +20874,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>"What if a $X emergency hit right now?" — can your cash absorb it, and how long would you last.</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -20948,7 +20960,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>Produces nothing that is displayed — it does something: saves, syncs or records.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -21026,7 +21038,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -21104,7 +21116,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Employer match resolved to $/month.</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -21182,7 +21194,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>── The sync layer's interface (operates on the cached DEK) ─────────── Encrypt a payload with the cached DEK.</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -21261,7 +21273,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -21339,7 +21351,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -21417,7 +21429,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Level annual equity spread across the months it vests (0 for most students).</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -21498,7 +21510,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Per-calendar-year vesting cash flow across all schedule rows — drives the chart &amp; table.</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -21577,7 +21589,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Value of one vesting-schedule row.</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -21655,7 +21667,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Vest-month weights (Jan→Dec, summing to 1) from the equity grant rows — THE one placement rule.</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -21733,7 +21745,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -21811,7 +21823,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Extra income sources beyond salary/rental/equity (self-employment, investment, benefits, support, scholarship, other), split into taxable vs non-taxable steady monthly amounts + a one-time Jan amount.</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -21892,7 +21904,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Price factor over the trailing window: last close ÷ the close at (now − months).</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -21970,7 +21982,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>Reaches outside the app for its answer — a feed, a file or a stored record.</t>
+          <t>What are inflation and the 10-year Treasury yield?</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -22048,7 +22060,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Fetch many tickers in parallel; returns only the ones that resolved.</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -22126,7 +22138,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Effective tax rate in use: the user's manual rate, else the IRS-schedule estimate on taxable income.</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -22204,7 +22216,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>The first date the record covers — so a change figure can say what it is measured FROM, rather than presenting a figure measured from install day as though it covered the year.</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -22282,7 +22294,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -22360,7 +22372,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>The plain-English comparison sentence for the detail view — fixed, human-reviewed templates.</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -22438,7 +22450,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Full amount, no minor units (matches the app's whole-number money style), locale-grouped.</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -22516,7 +22528,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Same as formatMoney but keeps 2 decimal places — for precise amounts (transactions, holdings, recurring lines).</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -22594,7 +22606,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>The FRA as words a person recognises — "67", or "66 and 4 months".</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -22672,7 +22684,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Full retirement age in YEARS (fractional — 66y4m = 66.333…), from the birth year.</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -22750,7 +22762,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it, but it only changes how a value LOOKS — it does no arithmetic.</t>
+          <t>The banner sentence — plural-correct, and absent (null) when nothing is missing.</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -22828,7 +22840,7 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>── Key generation ─────────────────────────────────────────────────── A fresh random 256-bit data key (hex).</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
@@ -22906,7 +22918,7 @@
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>A human-friendly recovery code, e.g.</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -22984,7 +22996,7 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -23063,7 +23075,7 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>The cached DEK (memory → keychain), or null if it hasn't been unwrapped on this install yet.</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -23141,7 +23153,7 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
@@ -23224,7 +23236,7 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>The public read-model (spec IncomeState): totals, effective rate, monthly grid.</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
@@ -23308,7 +23320,7 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Profile + derived planning values (current age, years to retirement, horizon).</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -23389,7 +23401,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Reaches outside the app for its answer — a feed, a file or a stored record.</t>
+          <t>Read a single-document-per-user collection (e.g.</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -23467,7 +23479,7 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Months remaining: from the target date if set, else the goal's `duration` (months).</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -23545,7 +23557,7 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Funded %, clamped 0–100.</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -23623,7 +23635,7 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
@@ -23702,7 +23714,7 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
@@ -23781,7 +23793,7 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Gross annual baseline = jobs (gross) + rentals (gross − expenses), all annualized.</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -23859,7 +23871,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Invert the schedule: the gross income whose take-home equals `net` (bisection).</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -23937,7 +23949,7 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>A representative full-month GROSS salary (the highest month — undiluted by $0 gap months).</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -24017,7 +24029,7 @@
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>── Deterministic projection (instant — drives the live sliders; no RNG) ────────────── Assumes the average return every year (no market swings).</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
@@ -24095,7 +24107,7 @@
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>The plan's guaranteed-income input as separate streams of OUTSIDE money only. Answers: zer</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -24173,7 +24185,7 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>The dated guaranteed-income rows for the next 12 months (the F2 grid seam).</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -24251,7 +24263,7 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -24329,7 +24341,7 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>True iff every measured account's story begins IN the ledger (openable honestly).</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -24407,7 +24419,7 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Produces nothing that is displayed — it does something: saves, syncs or records.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -24485,7 +24497,7 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Where the money to close the gap actually comes from — the breakdown that stops a person subtracting and concluding the app cannot add up (founder, 2026-08-14).</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -24564,7 +24576,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>What holdings are in this file?</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -24643,7 +24655,7 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -24721,7 +24733,7 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>FOUNDER RULE 2026-08-04 (supersedes the money-market=cash rule and the 12-month CD split): CASH means cash only — a sweep/settlement balance.</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -24799,7 +24811,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -24885,7 +24897,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>A representative 12-month cash-flow grid (Jan→Dec) that honors lumpiness: salary &amp; net rental are steady every month; the annual bonus lands in December; the signing bonus is one-time (January); equity is the level annual vesting spread across the month-of-year its vest dates fall on (so quarterly vesting shows up as quarterly spikes).</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -24971,7 +24983,7 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>B-30: infer the debt type from its name so a "Mortgage" is treated as a mortgage (homeowner DTI guideline), not lumped into OTHER (renter guideline).</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
@@ -25049,7 +25061,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>A broker just sent us data — what changes?</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -25135,7 +25147,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>Produces nothing that is displayed — it does something: saves, syncs or records.</t>
+          <t>Initialise crash reporting once, at app start.</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -25213,7 +25225,7 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Canonical annual INTEREST income across all interest-bearing holdings (Term #6).</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -25294,7 +25306,7 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Legacy fallback for rows recorded before undo_prev: a synthetic opposite transaction.</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
@@ -25372,7 +25384,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Investable assets (Term #4) = all financial assets (cash + investments + retirement balances), EXCLUDING real estate + personal property.</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -25452,7 +25464,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>FOUNDER RULE 2026-08-04: the NW change PERCENT is measured on cash + investments only — property values move only when someone retypes them, so a total-net-worth percent is noise.</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -25530,7 +25542,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Investment income (cash dividends/interest/coupons, not reinvested) over the trailing window — feeds the Income module.</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -25608,7 +25620,7 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Investments / holdings (allocation view, Term #4) = equities + fixed income + alternatives, ACROSS all wrappers (so a 401(k)'s stocks count).</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
@@ -25686,7 +25698,7 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Is this account an "other investment" — an alternative held at a manual value (not a bond, not cash/property)?</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
@@ -25764,7 +25776,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>An AssetAccount is a bond if its ASSET CLASS is bonds (spec §2: "detected by assetClass, NOT maturity date").</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -25842,7 +25854,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Produces nothing that is displayed — it does something: saves, syncs or records.</t>
+          <t>Does this account type sit under the Cash heading on screen?</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -25920,7 +25932,7 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
@@ -25998,7 +26010,7 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>── Low-level AES helpers (also used to wrap the DEK) ─────────────────</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
@@ -26076,7 +26088,7 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>True only when the device has biometric hardware AND the user has enrolled a biometric/passcode.</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
@@ -26154,7 +26166,7 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Money leaves the account: withdrawals, fees, and transfers with no recognized counter-account.</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -26232,7 +26244,7 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Did the personal return produce a number, or a reason it could not?</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
@@ -26310,7 +26322,7 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Is a ticker plausibly valid before we spend a network call?</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
@@ -26388,7 +26400,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>True when the asset is a real/physical asset (real estate or personal property) — excluded from investable assets and the nest egg (Term #4/#7).</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -26467,7 +26479,7 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Produces nothing that is displayed — it does something: saves, syncs or records.</t>
+          <t>Lump balance − Σ holdings.</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -26546,7 +26558,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>The account total AFTER itemizing.</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -26627,7 +26639,7 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Produces nothing that is displayed — it does something: saves, syncs or records.</t>
+          <t>Σ of the itemized holding values.</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -26705,7 +26717,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Is base salary present in calendar month i (0-11)?</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -26785,7 +26797,7 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Produces nothing that is displayed — it does something: saves, syncs or records.</t>
+          <t>Claim membership in {householdId} by writing the member doc the security rules gate access on.</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -26863,7 +26875,7 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>How much more you can still put into your 401(k) this year (incl.</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -26941,7 +26953,7 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>What is the most recent price we hold for this?</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -27019,7 +27031,7 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -27099,7 +27111,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -27177,7 +27189,7 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -27255,7 +27267,7 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -27333,7 +27345,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -27411,7 +27423,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -27489,7 +27501,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -27567,7 +27579,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -27645,7 +27657,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>Reaches outside the app for its answer — a feed, a file or a stored record.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -27725,7 +27737,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Reaches outside the app for its answer — a feed, a file or a stored record.</t>
+          <t>The member's own top-level doc fields (householdId + decrypted appState) in one read.</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -27805,7 +27817,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>UNIT LANDMINE (P0): `aprPct` is a PERCENT (7 = 7%), unlike Debt.interest_rate_apr which is a DECIMAL (0.07).</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -27883,7 +27895,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Reaches outside the app for its answer — a feed, a file or a stored record.</t>
+          <t>Returns the user plus the unlock status: • needsRecovery=true → the password can't open the data (it was reset); prompt for the recovery code.</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -27965,7 +27977,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>Produces nothing that is displayed — it does something: saves, syncs or records.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -28043,7 +28055,7 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>What if I had moved this money?</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -28122,7 +28134,7 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Fixed income by its words.</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -28200,7 +28212,7 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>Reaches outside the app for its answer — a feed, a file or a stored record.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -28278,7 +28290,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>The user's own long-term capital-gains rate, from their income + filing status (federal).</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -28356,7 +28368,7 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Build the stored envelope: the DEK locked by both the password and the recovery code.</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -28434,7 +28446,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>The ONE writer — stamps the version and keeps the arithmetic identity by construction.</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -28512,7 +28524,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>Build a full transaction (id + created_at) from a partial.</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -28590,7 +28602,7 @@
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>What kind of account is this, and how is it taxed?</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -28668,7 +28680,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>A line arrived from the broker. Is this money you paid IN, money you took OUT, or something that happened inside the account?</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -28746,7 +28758,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>What is this option position worth, and what do we call it?</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -28824,7 +28836,7 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>B7 (founder brief 2026-08-20): classification lives in the ONE engine — name first, broker tag as fallback only.</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -28902,7 +28914,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>The marginal bracket rate (decimal) for an income (on taxable income, after deduction).</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -28980,7 +28992,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -29058,7 +29070,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>What is this holding worth right now?</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -29137,7 +29149,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>The existing account a fresh import from `institution` should offer to update (or null).</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -29215,7 +29227,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>FOUNDER RULE 2026-08-04 (supersedes build-34 #8's 12-month split): ANY maturity-dated instrument is a BOND — it pays interest, so it must sit in the measured bucket regardless of how soon it matures.</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -29293,7 +29305,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>The short label that rides beside a change figure, always — whether the window is covered or not.</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -29372,7 +29384,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>FOUNDER RULE 2026-08-04: record how far back the broker's OWN activity feed reaches, so a "past year" income figure can label itself honestly.</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -29450,7 +29462,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>The one decision rule.</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -29528,7 +29540,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>The highest ladder rung at or below `netWorth` (0 when below the first rung).</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -29606,7 +29618,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>'$500k' / '$1M' — the label the celebration line uses.</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -29684,7 +29696,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Term #9 — TWO clearly-named monthly-debt numbers (they're different concepts, not a bug to pick one): Σ MINIMUM required payments — the contractual obligation.</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -29763,7 +29775,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>Produces nothing that is displayed — it does something: saves, syncs or records.</t>
+          <t>Currency/locale-aware (delegates to the active money format; defaults to USD/en-US).</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -29841,7 +29853,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>Produces nothing that is displayed — it does something: saves, syncs or records.</t>
+          <t>Same, but keeps cents — for precise amounts (transactions, holdings).</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -29919,7 +29931,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Compact form for tight spaces (chart labels, donut center).</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -29997,7 +30009,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>XIRR via bisection — deterministic, no derivative games.</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -30076,7 +30088,7 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>"March 2022" — a month a person reads, not a date stamp.</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -30154,7 +30166,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Total monthly contributions across types + employer match (feeds the retirement projection).</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -30233,7 +30245,7 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Monthly money you MUST keep paying — the recurring (non-monthly excluded) Critical + Important bills.</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -30319,7 +30331,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Monthly savings (the FLOW) — Build-47 walk row 7: DERIVED as the 12-month average of surplusByMonth, so the flat figure and the by-month figures can never drift apart (they used to be two parallel formulas that merely CLAIMED to reconcile).</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -30405,7 +30417,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>PRD F2#11 — the ONE per-calendar-month effective tax-rate vector (Jan→Dec).</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -30491,7 +30503,7 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>── B47 finding 11: the installment two-way math — enter the payment OR the end date, the app computes the other.</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -30569,7 +30581,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Months to reach the goal at a given monthly contribution (0 if funded; null if contribution &lt;= 0).</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -30647,7 +30659,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Whole months from `now` to the target month ('YYYY-MM'); &gt;=1, or null if no/!invalid date.</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -30725,7 +30737,7 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Run the plan twice and report both results.</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -30805,7 +30817,7 @@
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>What the NAME (symbol + description together) says, or null when it says nothing.</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -30883,7 +30895,7 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, but no chain from it reaches a screen.</t>
+          <t>── the cash sleeve, deduped ─────────────────────────────────────────────────────────────────── SnapTrade counts money-market (cash_equivalent) positions INSIDE balances.cash too.</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -30961,7 +30973,7 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>What do we call this new thing?</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -31039,7 +31051,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -31120,7 +31132,7 @@
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>Label basis for the non-monthly bucket (e.g.</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -31198,7 +31210,7 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>Its answer feeds another function, and that chain ends at a screen.</t>
+          <t>Normalize ONE stored entry: v1 passes validated; a legacy blob (no `v`) maps best-effort; anything without a real month + net worth is dropped (null), never charted.</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -31276,7 +31288,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -31354,7 +31366,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it, but it only changes how a value LOOKS — it does no arithmetic.</t>
+          <t>NOT DETERMINED — the code carries no note saying what this is for, and it has no row in the old inventory. Needs reading.</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -31433,7 +31445,7 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>How do we state the odds in words?</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -31511,7 +31523,7 @@
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>A screen calls it directly, so its answer is on a screen.</t>
+          <t>NOT DETERMINED